--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -2008,13 +2008,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.37853135417</v>
+        <v>46077.54519802083</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55453159723</v>
+        <v>46092.721198263884</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.44251555555</v>
+        <v>46112.60918222222</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2057,13 +2057,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.378532048606</v>
+        <v>46077.54519871528</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55450226852</v>
+        <v>46092.72116893518</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55453317129</v>
+        <v>46092.721199837964</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2122,13 +2122,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.37853246528</v>
+        <v>46077.54519913194</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55450283564</v>
+        <v>46092.721169502314</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.48084798611</v>
+        <v>46134.64751465278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2187,13 +2187,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.37853282408</v>
+        <v>46077.54519949074</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.554503287036</v>
+        <v>46092.7211699537</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.48088872685</v>
+        <v>46134.647555393516</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2252,13 +2252,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.378533194445</v>
+        <v>46077.54519986111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55450377315</v>
+        <v>46092.721170439814</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.48092777778</v>
+        <v>46134.64759444444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2317,13 +2317,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.37853353009</v>
+        <v>46077.545200196764</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55450440972</v>
+        <v>46092.72117107639</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.48096153935</v>
+        <v>46134.64762820602</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2382,11 +2382,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.37853386574</v>
+        <v>46077.545200532404</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.33967887731</v>
+        <v>46114.50634554398</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2429,13 +2429,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.37853422454</v>
+        <v>46077.5452008912</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.33966869213</v>
+        <v>46114.5063353588</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.33969057871</v>
+        <v>46114.506357245366</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2494,11 +2494,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.37853454861</v>
+        <v>46077.54520121528</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46135.02439115741</v>
+        <v>46135.19105782408</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2557,11 +2557,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46125.653105613426</v>
+        <v>46125.8197722801</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46133.004227997684</v>
+        <v>46133.17089466435</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2610,11 +2610,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46125.653381446755</v>
+        <v>46125.820048113426</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46133.004229976854</v>
+        <v>46133.17089664352</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2663,11 +2663,11 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46125.653666238424</v>
+        <v>46125.82033290509</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46133.004231377316</v>
+        <v>46133.17089804398</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2716,11 +2716,11 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46125.65397035879</v>
+        <v>46125.82063702546</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46133.00423262731</v>
+        <v>46133.17089929398</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2769,13 +2769,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.37853484954</v>
+        <v>46077.5452015162</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.33866949074</v>
+        <v>46114.50533615741</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.33868350694</v>
+        <v>46114.50535017361</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2822,13 +2822,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.37853097222</v>
+        <v>46077.54519763889</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.385715833334</v>
+        <v>46097.5523825</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.385732916664</v>
+        <v>46097.552399583336</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2887,13 +2887,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.3785321412</v>
+        <v>46077.54519880787</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.33833371528</v>
+        <v>46114.50500038195</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.33835142361</v>
+        <v>46114.505018090276</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2952,13 +2952,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.37853248842</v>
+        <v>46077.545199155094</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.385891805556</v>
+        <v>46097.55255847222</v>
       </c>
       <c r="D20" s="5">
-        <v>46125.596121608796</v>
+        <v>46125.76278827546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -3017,13 +3017,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.37853289352</v>
+        <v>46077.54519956018</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.33864616898</v>
+        <v>46114.50531283565</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.338670625</v>
+        <v>46114.50533729167</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3082,13 +3082,13 @@
         <v>85</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.37853325231</v>
+        <v>46077.54519991898</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46080277778</v>
+        <v>46122.627469444444</v>
       </c>
       <c r="D22" s="5">
-        <v>46125.73139984954</v>
+        <v>46125.89806651621</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -3131,13 +3131,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.378533958334</v>
+        <v>46077.545200625</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38576923611</v>
+        <v>46097.55243590278</v>
       </c>
       <c r="D23" s="8">
-        <v>46097.38578491898</v>
+        <v>46097.55245158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -3196,13 +3196,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.37853364584</v>
+        <v>46077.545200312496</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38560695601</v>
+        <v>46097.552273622685</v>
       </c>
       <c r="D24" s="5">
-        <v>46135.597870694444</v>
+        <v>46135.764537361116</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3261,13 +3261,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.37853428241</v>
+        <v>46077.54520094907</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.340227002314</v>
+        <v>46114.50689366898</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.34024363426</v>
+        <v>46114.50691030093</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3326,13 +3326,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.37853461805</v>
+        <v>46077.54520128472</v>
       </c>
       <c r="C26" s="5">
-        <v>46122.46078450231</v>
+        <v>46122.627451168984</v>
       </c>
       <c r="D26" s="5">
-        <v>46122.46080328704</v>
+        <v>46122.6274699537</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3391,13 +3391,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.38662109953</v>
+        <v>46077.553287766204</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.33919636574</v>
+        <v>46114.505863032406</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.33942283565</v>
+        <v>46114.50608950232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3456,11 +3456,11 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.378529884256</v>
+        <v>46077.54519655093</v>
       </c>
       <c r="C28" s="6"/>
       <c r="D28" s="5">
-        <v>46169.678465613426</v>
+        <v>46169.8451322801</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3519,11 +3519,11 @@
         <v>111</v>
       </c>
       <c r="B29" s="8">
-        <v>46125.52567444445</v>
+        <v>46125.69234111111</v>
       </c>
       <c r="C29" s="9"/>
       <c r="D29" s="8">
-        <v>46169.67847935185</v>
+        <v>46169.84514601852</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>112</v>
@@ -3582,11 +3582,11 @@
         <v>114</v>
       </c>
       <c r="B30" s="5">
-        <v>46125.525740717596</v>
+        <v>46125.69240738426</v>
       </c>
       <c r="C30" s="6"/>
       <c r="D30" s="5">
-        <v>46169.67849265046</v>
+        <v>46169.845159317134</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>115</v>
@@ -3645,11 +3645,11 @@
         <v>117</v>
       </c>
       <c r="B31" s="8">
-        <v>46125.52892121528</v>
+        <v>46125.69558788194</v>
       </c>
       <c r="C31" s="9"/>
       <c r="D31" s="8">
-        <v>46169.678522013885</v>
+        <v>46169.845188680556</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>118</v>
@@ -3708,11 +3708,11 @@
         <v>120</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.37853021991</v>
+        <v>46077.545196886575</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.5259155324</v>
+        <v>46182.69258219907</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>121</v>
@@ -3757,13 +3757,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.37853045139</v>
+        <v>46077.54519711806</v>
       </c>
       <c r="C33" s="8">
-        <v>46155.707855706016</v>
+        <v>46155.87452237269</v>
       </c>
       <c r="D33" s="8">
-        <v>46155.7078571412</v>
+        <v>46155.87452380787</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3822,13 +3822,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.37853072917</v>
+        <v>46077.54519739583</v>
       </c>
       <c r="C34" s="5">
-        <v>46114.338860081014</v>
+        <v>46114.505526747686</v>
       </c>
       <c r="D34" s="5">
-        <v>46114.33886135417</v>
+        <v>46114.50552802083</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3887,13 +3887,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.37853099537</v>
+        <v>46077.54519766204</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.69955048611</v>
+        <v>46155.86621715278</v>
       </c>
       <c r="D35" s="8">
-        <v>46155.6995518287</v>
+        <v>46155.86621849537</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3952,13 +3952,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.37853125</v>
+        <v>46077.54519791667</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.338964814815</v>
+        <v>46114.50563148149</v>
       </c>
       <c r="D36" s="5">
-        <v>46125.74698085648</v>
+        <v>46125.91364752315</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -4017,13 +4017,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.378530462964</v>
+        <v>46077.54519712963</v>
       </c>
       <c r="C37" s="8">
-        <v>46158.591688009255</v>
+        <v>46158.75835467593</v>
       </c>
       <c r="D37" s="8">
-        <v>46158.5916903125</v>
+        <v>46158.75835697917</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -4082,13 +4082,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.378530682865</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.385650324075</v>
+        <v>46097.55231699074</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38565210648</v>
+        <v>46097.552318773145</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -4147,13 +4147,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.37853090277</v>
+        <v>46077.545197569445</v>
       </c>
       <c r="C39" s="8">
-        <v>46155.72882087963</v>
+        <v>46155.895487546295</v>
       </c>
       <c r="D39" s="8">
-        <v>46155.728822199075</v>
+        <v>46155.89548886574</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -4212,13 +4212,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.37853112268</v>
+        <v>46077.54519778935</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.52589453704</v>
+        <v>46182.6925612037</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.52590822917</v>
+        <v>46182.69257489583</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -4277,13 +4277,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.37853138889</v>
+        <v>46077.54519805555</v>
       </c>
       <c r="C41" s="8">
-        <v>46182.5148516551</v>
+        <v>46182.681518321755</v>
       </c>
       <c r="D41" s="8">
-        <v>46182.51485332176</v>
+        <v>46182.68151998843</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4342,13 +4342,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.378531608796</v>
+        <v>46077.54519827546</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.52588083333</v>
+        <v>46182.6925475</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.5258822801</v>
+        <v>46182.692548946754</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4407,13 +4407,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.378531828705</v>
+        <v>46077.54519849537</v>
       </c>
       <c r="C43" s="8">
-        <v>46126.663939363425</v>
+        <v>46126.8306060301</v>
       </c>
       <c r="D43" s="8">
-        <v>46126.66395278936</v>
+        <v>46126.830619456014</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4472,13 +4472,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.37853207176</v>
+        <v>46077.54519873843</v>
       </c>
       <c r="C44" s="5">
-        <v>46126.66246944445</v>
+        <v>46126.82913611111</v>
       </c>
       <c r="D44" s="5">
-        <v>46126.66247059028</v>
+        <v>46126.829137256944</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4537,13 +4537,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.378530138885</v>
+        <v>46077.54519680556</v>
       </c>
       <c r="C45" s="8">
-        <v>46126.66392466435</v>
+        <v>46126.83059133102</v>
       </c>
       <c r="D45" s="8">
-        <v>46126.663925960645</v>
+        <v>46126.83059262732</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4602,13 +4602,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.422494513885</v>
+        <v>46077.58916118056</v>
       </c>
       <c r="C46" s="5">
-        <v>46126.66291380787</v>
+        <v>46126.829580474536</v>
       </c>
       <c r="D46" s="5">
-        <v>46126.66292728009</v>
+        <v>46126.829593946764</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4667,13 +4667,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.42261591435</v>
+        <v>46077.589282581015</v>
       </c>
       <c r="C47" s="8">
-        <v>46126.66237184028</v>
+        <v>46126.82903850694</v>
       </c>
       <c r="D47" s="8">
-        <v>46126.66237319444</v>
+        <v>46126.82903986111</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4732,13 +4732,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.42283101851</v>
+        <v>46077.589497685185</v>
       </c>
       <c r="C48" s="5">
-        <v>46126.662899421295</v>
+        <v>46126.82956608797</v>
       </c>
       <c r="D48" s="5">
-        <v>46126.66290059028</v>
+        <v>46126.829567256944</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4797,13 +4797,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.3785315162</v>
+        <v>46077.54519818287</v>
       </c>
       <c r="C49" s="8">
-        <v>46147.721473784724</v>
+        <v>46147.88814045139</v>
       </c>
       <c r="D49" s="8">
-        <v>46147.72147583333</v>
+        <v>46147.8881425</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4862,13 +4862,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.37853177083</v>
+        <v>46077.545198437496</v>
       </c>
       <c r="C50" s="5">
-        <v>46097.386023935185</v>
+        <v>46097.55269060185</v>
       </c>
       <c r="D50" s="5">
-        <v>46125.7320777662</v>
+        <v>46125.89874443287</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4927,13 +4927,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.37853203704</v>
+        <v>46077.54519870371</v>
       </c>
       <c r="C51" s="8">
-        <v>46147.68399586805</v>
+        <v>46147.85066253472</v>
       </c>
       <c r="D51" s="8">
-        <v>46150.616598078705</v>
+        <v>46150.78326474537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -4992,11 +4992,11 @@
         <v>185</v>
       </c>
       <c r="B52" s="5">
-        <v>46125.52922377315</v>
+        <v>46125.69589043982</v>
       </c>
       <c r="C52" s="6"/>
       <c r="D52" s="5">
-        <v>46169.67725637731</v>
+        <v>46169.84392304398</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>186</v>
@@ -5055,11 +5055,11 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46125.53804006944</v>
+        <v>46125.70470673611</v>
       </c>
       <c r="C53" s="9"/>
       <c r="D53" s="8">
-        <v>46169.67730944444</v>
+        <v>46169.84397611111</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>119</v>
@@ -5108,11 +5108,11 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46125.53822739584</v>
+        <v>46125.704894062495</v>
       </c>
       <c r="C54" s="6"/>
       <c r="D54" s="5">
-        <v>46169.67732578704</v>
+        <v>46169.84399245371</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5161,11 +5161,11 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.516661539354</v>
+        <v>46125.68332820602</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46169.67817712963</v>
+        <v>46169.844843796294</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5224,11 +5224,11 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.5385794676</v>
+        <v>46125.70524613426</v>
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46169.67736613426</v>
+        <v>46169.84403280093</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>113</v>
@@ -5277,11 +5277,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.53871626157</v>
+        <v>46125.70538292824</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46169.67825121528</v>
+        <v>46169.84491788194</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5330,11 +5330,11 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.55176141203</v>
+        <v>46125.718428078704</v>
       </c>
       <c r="C58" s="6"/>
       <c r="D58" s="5">
-        <v>46125.554855243055</v>
+        <v>46125.72152190973</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>205</v>
@@ -5383,11 +5383,11 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.551973877315</v>
+        <v>46125.718640543986</v>
       </c>
       <c r="C59" s="9"/>
       <c r="D59" s="8">
-        <v>46125.55501534722</v>
+        <v>46125.721682013886</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5436,11 +5436,11 @@
         <v>208</v>
       </c>
       <c r="B60" s="5">
-        <v>46125.55231115741</v>
+        <v>46125.71897782407</v>
       </c>
       <c r="C60" s="6"/>
       <c r="D60" s="5">
-        <v>46125.55514546296</v>
+        <v>46125.72181212963</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5489,11 +5489,11 @@
         <v>210</v>
       </c>
       <c r="B61" s="8">
-        <v>46125.55246883102</v>
+        <v>46125.71913549768</v>
       </c>
       <c r="C61" s="9"/>
       <c r="D61" s="8">
-        <v>46125.55530224537</v>
+        <v>46125.72196891204</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>211</v>
@@ -5542,11 +5542,11 @@
         <v>212</v>
       </c>
       <c r="B62" s="5">
-        <v>46126.64923972222</v>
+        <v>46126.81590638889</v>
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46126.64971946759</v>
+        <v>46126.81638613426</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5589,11 +5589,11 @@
         <v>214</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.5267843287</v>
+        <v>46125.69345099537</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46169.67747048612</v>
+        <v>46169.84413715277</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>215</v>
@@ -5652,11 +5652,11 @@
         <v>217</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.53893203704</v>
+        <v>46125.7055987037</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46169.67750365741</v>
+        <v>46169.844170324075</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>116</v>
@@ -5705,11 +5705,11 @@
         <v>219</v>
       </c>
       <c r="B65" s="8">
-        <v>46125.539031168984</v>
+        <v>46125.70569783565</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.67752806713</v>
+        <v>46169.8441947338</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>220</v>
@@ -5758,11 +5758,11 @@
         <v>222</v>
       </c>
       <c r="B66" s="5">
-        <v>46077.37853229167</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46127.531820081014</v>
+        <v>46127.698486747686</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>223</v>
@@ -5805,13 +5805,13 @@
         <v>225</v>
       </c>
       <c r="B67" s="8">
-        <v>46077.378532546296</v>
+        <v>46077.54519921297</v>
       </c>
       <c r="C67" s="8">
-        <v>46127.53098657407</v>
+        <v>46127.69765324074</v>
       </c>
       <c r="D67" s="8">
-        <v>46182.662784976856</v>
+        <v>46182.82945164352</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>
@@ -5870,13 +5870,13 @@
         <v>230</v>
       </c>
       <c r="B68" s="5">
-        <v>46125.529720879626</v>
+        <v>46125.6963875463</v>
       </c>
       <c r="C68" s="5">
-        <v>46127.53096575232</v>
+        <v>46127.69763241898</v>
       </c>
       <c r="D68" s="5">
-        <v>46127.53096708334</v>
+        <v>46127.697633749995</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>231</v>
@@ -5925,13 +5925,13 @@
         <v>232</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.52990164352</v>
+        <v>46125.69656831019</v>
       </c>
       <c r="C69" s="8">
-        <v>46127.53097228009</v>
+        <v>46127.69763894676</v>
       </c>
       <c r="D69" s="8">
-        <v>46127.53097391204</v>
+        <v>46127.6976405787</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>233</v>
@@ -5980,13 +5980,13 @@
         <v>234</v>
       </c>
       <c r="B70" s="5">
-        <v>46077.37853006944</v>
+        <v>46077.545196736115</v>
       </c>
       <c r="C70" s="5">
-        <v>46127.53123206018</v>
+        <v>46127.69789872685</v>
       </c>
       <c r="D70" s="5">
-        <v>46127.531246099534</v>
+        <v>46127.697912766205</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>235</v>
@@ -6045,13 +6045,13 @@
         <v>237</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.531222245365</v>
+        <v>46125.69788891204</v>
       </c>
       <c r="C71" s="8">
-        <v>46127.53121677083</v>
+        <v>46127.697883437504</v>
       </c>
       <c r="D71" s="8">
-        <v>46127.531218344906</v>
+        <v>46127.69788501157</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>231</v>
@@ -6100,13 +6100,13 @@
         <v>240</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.53134434028</v>
+        <v>46125.69801100694</v>
       </c>
       <c r="C72" s="5">
-        <v>46127.53120533565</v>
+        <v>46127.69787200232</v>
       </c>
       <c r="D72" s="5">
-        <v>46127.53120662037</v>
+        <v>46127.697873287034</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>233</v>
@@ -6155,13 +6155,13 @@
         <v>243</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.538085196764</v>
+        <v>46090.70475186342</v>
       </c>
       <c r="C73" s="8">
-        <v>46127.531810162036</v>
+        <v>46127.69847682871</v>
       </c>
       <c r="D73" s="8">
-        <v>46127.53182487268</v>
+        <v>46127.698491539355</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>108</v>
@@ -6220,13 +6220,13 @@
         <v>245</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.531473703704</v>
+        <v>46125.69814037037</v>
       </c>
       <c r="C74" s="5">
-        <v>46127.531782986116</v>
+        <v>46127.69844965277</v>
       </c>
       <c r="D74" s="5">
-        <v>46127.53178466435</v>
+        <v>46127.698451331016</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>231</v>
@@ -6275,13 +6275,13 @@
         <v>246</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.53165609954</v>
+        <v>46125.6983227662</v>
       </c>
       <c r="C75" s="8">
-        <v>46127.53179329861</v>
+        <v>46127.69845996528</v>
       </c>
       <c r="D75" s="8">
-        <v>46127.53179476852</v>
+        <v>46127.69846143518</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>233</v>
@@ -6330,11 +6330,11 @@
         <v>247</v>
       </c>
       <c r="B76" s="5">
-        <v>46090.53813152778</v>
+        <v>46090.70479819445</v>
       </c>
       <c r="C76" s="6"/>
       <c r="D76" s="5">
-        <v>46168.006661481486</v>
+        <v>46168.17332814814</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>248</v>
@@ -6393,11 +6393,11 @@
         <v>251</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.532529178236</v>
+        <v>46125.69919584491</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46167.001553009264</v>
+        <v>46167.16821967592</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>231</v>
@@ -6444,11 +6444,11 @@
         <v>253</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.53265070602</v>
+        <v>46125.69931737268</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.00155489583</v>
+        <v>46167.168221562504</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>233</v>
@@ -6495,11 +6495,11 @@
         <v>255</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.37853043982</v>
+        <v>46077.54519710648</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46125.733331446754</v>
+        <v>46125.899998113426</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>256</v>
@@ -6542,11 +6542,11 @@
         <v>258</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.378531180555</v>
+        <v>46077.54519784723</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46147.68400511574</v>
+        <v>46147.850671782406</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>259</v>
@@ -6605,11 +6605,11 @@
         <v>263</v>
       </c>
       <c r="B81" s="8">
-        <v>46125.52948887731</v>
+        <v>46125.69615554398</v>
       </c>
       <c r="C81" s="9"/>
       <c r="D81" s="8">
-        <v>46125.73628340277</v>
+        <v>46125.902950069445</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>264</v>
@@ -6668,11 +6668,11 @@
         <v>266</v>
       </c>
       <c r="B82" s="5">
-        <v>46125.53309398148</v>
+        <v>46125.699760648145</v>
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46125.73628356482</v>
+        <v>46125.90295023148</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>267</v>
@@ -6731,11 +6731,11 @@
         <v>269</v>
       </c>
       <c r="B83" s="8">
-        <v>46077.37853180556</v>
+        <v>46077.545198472224</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46125.74423070602</v>
+        <v>46125.91089737268</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>270</v>
@@ -6794,11 +6794,11 @@
         <v>274</v>
       </c>
       <c r="B84" s="5">
-        <v>46125.60878079861</v>
+        <v>46125.775447465276</v>
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46125.7442296875</v>
+        <v>46125.910896354166</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>275</v>
@@ -6847,11 +6847,11 @@
         <v>277</v>
       </c>
       <c r="B85" s="8">
-        <v>46125.60892753472</v>
+        <v>46125.77559420139</v>
       </c>
       <c r="C85" s="9"/>
       <c r="D85" s="8">
-        <v>46125.7439246875</v>
+        <v>46125.91059135417</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>278</v>
@@ -6900,11 +6900,11 @@
         <v>279</v>
       </c>
       <c r="B86" s="5">
-        <v>46125.609070046296</v>
+        <v>46125.77573671297</v>
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46125.744063425926</v>
+        <v>46125.9107300926</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>268</v>
@@ -6953,11 +6953,11 @@
         <v>280</v>
       </c>
       <c r="B87" s="8">
-        <v>46077.37853238426</v>
+        <v>46077.545199050925</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46129.63708084491</v>
+        <v>46129.80374751157</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>281</v>
@@ -7000,11 +7000,11 @@
         <v>283</v>
       </c>
       <c r="B88" s="5">
-        <v>46077.37853266204</v>
+        <v>46077.5451993287</v>
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46129.63732300926</v>
+        <v>46129.80398967593</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>284</v>
@@ -7063,11 +7063,11 @@
         <v>287</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.37853291667</v>
+        <v>46077.54519958333</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46139.00166430556</v>
+        <v>46139.16833097222</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>288</v>
@@ -7126,11 +7126,11 @@
         <v>290</v>
       </c>
       <c r="B90" s="5">
-        <v>46125.61333424768</v>
+        <v>46125.780000914354</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46139.00442302083</v>
+        <v>46139.1710896875</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>231</v>
@@ -7179,11 +7179,11 @@
         <v>295</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.61305056713</v>
+        <v>46125.779717233796</v>
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46139.00442142361</v>
+        <v>46139.17108809028</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>233</v>
@@ -7232,11 +7232,11 @@
         <v>297</v>
       </c>
       <c r="B92" s="5">
-        <v>46077.37853318287</v>
+        <v>46077.54519984954</v>
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46141.00143453704</v>
+        <v>46141.1681012037</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>298</v>
@@ -7295,11 +7295,11 @@
         <v>299</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.61477962963</v>
+        <v>46125.7814462963</v>
       </c>
       <c r="C93" s="9"/>
       <c r="D93" s="8">
-        <v>46141.00332423611</v>
+        <v>46141.16999090278</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>231</v>
@@ -7348,11 +7348,11 @@
         <v>302</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.614917604165</v>
+        <v>46125.78158427084</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46141.003326157406</v>
+        <v>46141.16999282407</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>233</v>
@@ -7401,11 +7401,11 @@
         <v>305</v>
       </c>
       <c r="B95" s="8">
-        <v>46077.378533449075</v>
+        <v>46077.54520011574</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46125.62362574074</v>
+        <v>46125.79029240741</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>256</v>
@@ -7448,11 +7448,11 @@
         <v>307</v>
       </c>
       <c r="B96" s="5">
-        <v>46077.37853141203</v>
+        <v>46077.545198078704</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.69955877315</v>
+        <v>46155.866225439815</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>308</v>
@@ -7511,11 +7511,11 @@
         <v>310</v>
       </c>
       <c r="B97" s="8">
-        <v>46077.37853112268</v>
+        <v>46077.54519778935</v>
       </c>
       <c r="C97" s="9"/>
       <c r="D97" s="8">
-        <v>46155.728829699074</v>
+        <v>46155.895496365745</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>311</v>
@@ -7574,11 +7574,11 @@
         <v>313</v>
       </c>
       <c r="B98" s="5">
-        <v>46077.37853408565</v>
+        <v>46077.54520075231</v>
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46126.66394534722</v>
+        <v>46126.83061201389</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>314</v>
@@ -7637,11 +7637,11 @@
         <v>315</v>
       </c>
       <c r="B99" s="8">
-        <v>46077.378530682865</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46182.52589795139</v>
+        <v>46182.69256461806</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>58</v>
@@ -7700,11 +7700,11 @@
         <v>317</v>
       </c>
       <c r="B100" s="5">
-        <v>46077.39129883102</v>
+        <v>46077.55796549769</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46128.503233564814</v>
+        <v>46128.669900231485</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>318</v>
@@ -7763,11 +7763,11 @@
         <v>319</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.623623680556</v>
+        <v>46125.79029034722</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46125.737085706016</v>
+        <v>46125.90375237269</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>320</v>
@@ -7820,11 +7820,11 @@
         <v>321</v>
       </c>
       <c r="B102" s="5">
-        <v>46077.37853174769</v>
+        <v>46077.54519841435</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46125.73924667824</v>
+        <v>46125.905913344905</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>322</v>
@@ -7867,11 +7867,11 @@
         <v>324</v>
       </c>
       <c r="B103" s="8">
-        <v>46077.37853209491</v>
+        <v>46077.545198761574</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46150.002224375</v>
+        <v>46150.16889104167</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>325</v>
@@ -7930,11 +7930,11 @@
         <v>326</v>
       </c>
       <c r="B104" s="5">
-        <v>46125.618860069444</v>
+        <v>46125.785526736116</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46148.00291173611</v>
+        <v>46148.169578402776</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>231</v>
@@ -7983,11 +7983,11 @@
         <v>329</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.619656145835</v>
+        <v>46125.7863228125</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46148.00288280092</v>
+        <v>46148.169549467595</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>233</v>
@@ -8036,11 +8036,11 @@
         <v>332</v>
       </c>
       <c r="B106" s="5">
-        <v>46077.39166046296</v>
+        <v>46077.558327129635</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46154.001161458335</v>
+        <v>46154.167828125</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>333</v>
@@ -8099,11 +8099,11 @@
         <v>334</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.62647851852</v>
+        <v>46125.793145185184</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46154.00229175926</v>
+        <v>46154.16895842593</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>231</v>
@@ -8152,11 +8152,11 @@
         <v>337</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.62659856481</v>
+        <v>46125.79326523148</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46154.00229326389</v>
+        <v>46154.168959930554</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>233</v>
@@ -8205,11 +8205,11 @@
         <v>340</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.378532800925</v>
+        <v>46077.5451994676</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46156.00106879629</v>
+        <v>46156.167735462965</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>341</v>
@@ -8268,11 +8268,11 @@
         <v>342</v>
       </c>
       <c r="B110" s="5">
-        <v>46125.62675127314</v>
+        <v>46125.793417939814</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46156.002217754634</v>
+        <v>46156.16888442129</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>231</v>
@@ -8321,11 +8321,11 @@
         <v>345</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.6268628588</v>
+        <v>46125.793529525465</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46156.002219409726</v>
+        <v>46156.16888607639</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>233</v>
@@ -8374,11 +8374,11 @@
         <v>348</v>
       </c>
       <c r="B112" s="5">
-        <v>46077.37853313657</v>
+        <v>46077.54519980324</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.029408449074</v>
+        <v>46161.196075115746</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>349</v>
@@ -8437,11 +8437,11 @@
         <v>350</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.62697039352</v>
+        <v>46125.79363706018</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46160.00261324074</v>
+        <v>46160.16927990741</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>231</v>
@@ -8490,11 +8490,11 @@
         <v>353</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.62709875</v>
+        <v>46125.79376541667</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46160.00261517361</v>
+        <v>46160.16928184028</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>233</v>
@@ -8543,11 +8543,11 @@
         <v>356</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.37853243056</v>
+        <v>46077.54519909722</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46163.00383574074</v>
+        <v>46163.1705024074</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>357</v>
@@ -8606,11 +8606,11 @@
         <v>358</v>
       </c>
       <c r="B116" s="5">
-        <v>46125.62742210648</v>
+        <v>46125.79408877315</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.00236327546</v>
+        <v>46162.16902994213</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>231</v>
@@ -8659,11 +8659,11 @@
         <v>361</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.62755608796</v>
+        <v>46125.79422275463</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46162.00236474537</v>
+        <v>46162.169031412035</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>233</v>
@@ -8712,11 +8712,11 @@
         <v>364</v>
       </c>
       <c r="B118" s="5">
-        <v>46077.37853346065</v>
+        <v>46077.545200127315</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46165.030673483794</v>
+        <v>46165.197340150466</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>365</v>
@@ -8775,11 +8775,11 @@
         <v>366</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.62767509259</v>
+        <v>46125.79434175926</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46164.00248200231</v>
+        <v>46164.16914866898</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>231</v>
@@ -8826,11 +8826,11 @@
         <v>368</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.62779353009</v>
+        <v>46125.79446019676</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.00248363426</v>
+        <v>46164.16915030092</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>233</v>
@@ -8877,11 +8877,11 @@
         <v>370</v>
       </c>
       <c r="B121" s="8">
-        <v>46077.37853377315</v>
+        <v>46077.54520043981</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46169.02913077547</v>
+        <v>46169.19579744213</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>371</v>
@@ -8940,11 +8940,11 @@
         <v>372</v>
       </c>
       <c r="B122" s="5">
-        <v>46125.62793141203</v>
+        <v>46125.794598078704</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46168.002096655095</v>
+        <v>46168.16876332176</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>231</v>
@@ -8991,11 +8991,11 @@
         <v>374</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.62805658564</v>
+        <v>46125.794723252315</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.00209804398</v>
+        <v>46168.168764710645</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>233</v>
@@ -9042,11 +9042,11 @@
         <v>376</v>
       </c>
       <c r="B124" s="5">
-        <v>46077.37853105324</v>
+        <v>46077.54519771991</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46125.74054834491</v>
+        <v>46125.907215011575</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>377</v>
@@ -9089,11 +9089,11 @@
         <v>379</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.378531504626</v>
+        <v>46077.5451981713</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46170.032856238424</v>
+        <v>46170.199522905095</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>380</v>
@@ -9152,11 +9152,11 @@
         <v>384</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.64569723379</v>
+        <v>46125.81236390046</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46169.0018784375</v>
+        <v>46169.16854510417</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>231</v>
@@ -9203,11 +9203,11 @@
         <v>386</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.64585586806</v>
+        <v>46125.81252253472</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46169.0018800463</v>
+        <v>46169.168546712965</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>233</v>
@@ -9254,11 +9254,11 @@
         <v>388</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.6460805324</v>
+        <v>46125.812747199074</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46169.00188140046</v>
+        <v>46169.16854806713</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>389</v>
@@ -9305,11 +9305,11 @@
         <v>391</v>
       </c>
       <c r="B129" s="8">
-        <v>46125.646602141205</v>
+        <v>46125.81326880787</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.001882743054</v>
+        <v>46169.16854940972</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>61</v>
@@ -9356,11 +9356,11 @@
         <v>393</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.647173634265</v>
+        <v>46125.81384030092</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.00188401621</v>
+        <v>46169.168550682865</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>64</v>
@@ -9407,11 +9407,11 @@
         <v>395</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.647435543986</v>
+        <v>46125.81410221064</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46169.001885624995</v>
+        <v>46169.16855229167</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>67</v>
@@ -9458,11 +9458,11 @@
         <v>397</v>
       </c>
       <c r="B132" s="5">
-        <v>46077.37853181713</v>
+        <v>46077.5451984838</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46175.03565800926</v>
+        <v>46175.20232467593</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>398</v>
@@ -9521,11 +9521,11 @@
         <v>400</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.64815408565</v>
+        <v>46125.81482075232</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46174.00276666667</v>
+        <v>46174.16943333333</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>231</v>
@@ -9574,11 +9574,11 @@
         <v>402</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.64828011574</v>
+        <v>46125.81494678241</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46174.00276837963</v>
+        <v>46174.16943504629</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>233</v>
@@ -9627,11 +9627,11 @@
         <v>404</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.64849368056</v>
+        <v>46125.81516034722</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46174.002769733794</v>
+        <v>46174.169436400465</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>389</v>
@@ -9680,11 +9680,11 @@
         <v>406</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.64864410879</v>
+        <v>46125.81531077546</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46174.00277118056</v>
+        <v>46174.169437847224</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>61</v>
@@ -9733,11 +9733,11 @@
         <v>408</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.6487852662</v>
+        <v>46125.81545193287</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46174.002772604166</v>
+        <v>46174.16943927083</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>64</v>
@@ -9786,11 +9786,11 @@
         <v>410</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.64890609954</v>
+        <v>46125.81557276621</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46174.002773796296</v>
+        <v>46174.16944046297</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>411</v>
@@ -9839,11 +9839,11 @@
         <v>413</v>
       </c>
       <c r="B139" s="8">
-        <v>46077.37853229167</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46176.029254189816</v>
+        <v>46176.19592085648</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>414</v>
@@ -9902,11 +9902,11 @@
         <v>417</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.64911434028</v>
+        <v>46125.815781006946</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46175.001645798606</v>
+        <v>46175.16831246528</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>231</v>
@@ -9953,11 +9953,11 @@
         <v>419</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.64925351852</v>
+        <v>46125.81592018518</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46175.00164739584</v>
+        <v>46175.168314062495</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>233</v>
@@ -10004,11 +10004,11 @@
         <v>421</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.64939738426</v>
+        <v>46125.81606405093</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46175.00164880787</v>
+        <v>46175.16831547454</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>57</v>
@@ -10055,11 +10055,11 @@
         <v>423</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.64952605324</v>
+        <v>46125.81619271991</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46175.00165010417</v>
+        <v>46175.16831677083</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>61</v>
@@ -10106,11 +10106,11 @@
         <v>425</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.64965439815</v>
+        <v>46125.81632106482</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46175.00165146991</v>
+        <v>46175.16831813657</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>64</v>
@@ -10157,11 +10157,11 @@
         <v>427</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.649802002314</v>
+        <v>46125.816468668985</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46175.00165288194</v>
+        <v>46175.16831954861</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>411</v>
@@ -10208,11 +10208,11 @@
         <v>429</v>
       </c>
       <c r="B146" s="5">
-        <v>46077.37853260417</v>
+        <v>46077.54519927083</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46177.02263348379</v>
+        <v>46177.189300150465</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>430</v>
@@ -10271,11 +10271,11 @@
         <v>433</v>
       </c>
       <c r="B147" s="8">
-        <v>46125.649941006945</v>
+        <v>46125.81660767361</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46176.00170306713</v>
+        <v>46176.1683697338</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>231</v>
@@ -10322,11 +10322,11 @@
         <v>434</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.650069166666</v>
+        <v>46125.81673583333</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46176.00170451389</v>
+        <v>46176.16837118055</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>233</v>
@@ -10373,11 +10373,11 @@
         <v>435</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.650201331024</v>
+        <v>46125.81686799768</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46176.0017056713</v>
+        <v>46176.16837233797</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>389</v>
@@ -10424,11 +10424,11 @@
         <v>436</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.65031788194</v>
+        <v>46125.81698454861</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46176.00170678241</v>
+        <v>46176.16837344907</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>61</v>
@@ -10475,11 +10475,11 @@
         <v>437</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.650468148146</v>
+        <v>46125.81713481482</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46176.00170797454</v>
+        <v>46176.1683746412</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>64</v>
@@ -10526,11 +10526,11 @@
         <v>438</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.650595520834</v>
+        <v>46125.8172621875</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46176.001709178236</v>
+        <v>46176.16837584491</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>411</v>
@@ -10577,11 +10577,11 @@
         <v>439</v>
       </c>
       <c r="B153" s="8">
-        <v>46077.37853299768</v>
+        <v>46077.54519966435</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.740548368056</v>
+        <v>46125.90721503472</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>440</v>
@@ -10624,11 +10624,11 @@
         <v>442</v>
       </c>
       <c r="B154" s="5">
-        <v>46077.378533298615</v>
+        <v>46077.54519996527</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46185.001184768524</v>
+        <v>46185.16785143518</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>443</v>
@@ -10687,11 +10687,11 @@
         <v>446</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.37853361111</v>
+        <v>46077.545200277775</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46185.00118724537</v>
+        <v>46185.16785391203</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>447</v>
@@ -10750,11 +10750,11 @@
         <v>449</v>
       </c>
       <c r="B156" s="5">
-        <v>46090.54328194444</v>
+        <v>46090.70994861111</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46125.74112125</v>
+        <v>46125.907787916665</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>450</v>
@@ -10803,11 +10803,11 @@
         <v>452</v>
       </c>
       <c r="B157" s="8">
-        <v>46090.54338682871</v>
+        <v>46090.71005349537</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46185.03103875</v>
+        <v>46185.197705416664</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>453</v>
@@ -10866,11 +10866,11 @@
         <v>455</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.54293944444</v>
+        <v>46090.70960611111</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46125.74146892361</v>
+        <v>46125.908135590274</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>456</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -701,7 +701,7 @@
     <t>hgutierrez@zitron.com</t>
   </si>
   <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB</t>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ</t>
   </si>
   <si>
     <t>1214046914974309</t>
@@ -5811,7 +5811,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D67" s="8">
-        <v>46182.82945164352</v>
+        <v>46188.669512673616</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>226</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -810,7 +810,7 @@
     <t xml:space="preserve">Recepcion Corte Plasma </t>
   </si>
   <si>
-    <t xml:space="preserve">Control de calidad corte plasma,Generación OC </t>
+    <t>Control de calidad corte plasma,Preparacion material</t>
   </si>
   <si>
     <t>1214046914974318</t>
@@ -843,7 +843,7 @@
     <t>Control de calidad corte laser</t>
   </si>
   <si>
-    <t xml:space="preserve">Control de calidad corte laser, plasma y mecanizado,Generación OC </t>
+    <t>Control de calidad corte laser, plasma y mecanizado,Preparacion material</t>
   </si>
   <si>
     <t>1214046914974448</t>
@@ -858,22 +858,28 @@
     <t>1213390413187418</t>
   </si>
   <si>
-    <t>Fabricación externa :</t>
-  </si>
-  <si>
-    <t>Armado Fabricación externo ,Generación OC ,Control de calidad Armado</t>
+    <t>Caldereria</t>
+  </si>
+  <si>
+    <t>Armado Fabricación externo ,Preparacion material,Control de calidad Armado</t>
   </si>
   <si>
     <t>1213390413187419</t>
   </si>
   <si>
-    <t xml:space="preserve">Generación OC </t>
+    <t>Preparacion material</t>
+  </si>
+  <si>
+    <t>Nicolás Mol</t>
+  </si>
+  <si>
+    <t>nicolas.mol@zitron.com</t>
   </si>
   <si>
     <t>Recepcion Corte Plasma ,Control de calidad Mecanizado,Control de calidad corte laser</t>
   </si>
   <si>
-    <t>Fabricación externa :,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6</t>
+    <t>Caldereria,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6</t>
   </si>
   <si>
     <t>1213390413187420</t>
@@ -888,13 +894,7 @@
     <t>1214046914974462</t>
   </si>
   <si>
-    <t>Nicolás Mol</t>
-  </si>
-  <si>
-    <t>nicolas.mol@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC ,Check Planos</t>
+    <t>Preparacion material,Check Planos</t>
   </si>
   <si>
     <t>Armado Fabricación externo ,OT 4202 ZVN 1-22-400/6</t>
@@ -6964,7 +6964,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46129.80374751157</v>
+        <v>46191.72825035879</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>281</v>
@@ -7011,7 +7011,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46129.80398967593</v>
+        <v>46191.72813158565</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>284</v>
@@ -7020,10 +7020,10 @@
         <v>26</v>
       </c>
       <c r="G88" s="6" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="H88" s="6" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="I88" s="5">
         <v>46100</v>
@@ -7044,10 +7044,10 @@
         <v>281</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P88" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q88" s="5">
         <v>46108</v>
@@ -7067,26 +7067,26 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B89" s="8">
         <v>46077.54519958333</v>
       </c>
       <c r="C89" s="9"/>
       <c r="D89" s="8">
-        <v>46139.16833097222</v>
+        <v>46191.7283396412</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>195</v>
+        <v>285</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>196</v>
+        <v>286</v>
       </c>
       <c r="I89" s="8">
         <v>46111</v>
@@ -7125,19 +7125,19 @@
         <v>0</v>
       </c>
       <c r="U89" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B90" s="5">
         <v>46125.780000914354</v>
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46139.1710896875</v>
+        <v>46191.72843072917</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>231</v>
@@ -7146,10 +7146,10 @@
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I90" s="5">
         <v>46111</v>
@@ -7167,7 +7167,7 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>293</v>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="C91" s="9"/>
       <c r="D91" s="8">
-        <v>46139.17108809028</v>
+        <v>46191.72847037037</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>233</v>
@@ -7199,10 +7199,10 @@
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I91" s="8">
         <v>46111</v>
@@ -7220,7 +7220,7 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="O91" s="9" t="s">
         <v>293</v>
@@ -7294,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="U92" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
@@ -7573,7 +7573,7 @@
         <v>0</v>
       </c>
       <c r="U97" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
@@ -7929,7 +7929,7 @@
         <v>0</v>
       </c>
       <c r="U103" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
@@ -8098,7 +8098,7 @@
         <v>0</v>
       </c>
       <c r="U106" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
@@ -9859,10 +9859,10 @@
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I139" s="8">
         <v>46175</v>
@@ -9922,10 +9922,10 @@
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I140" s="6"/>
       <c r="J140" s="5">
@@ -9973,10 +9973,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -10024,10 +10024,10 @@
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10075,10 +10075,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10126,10 +10126,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10177,10 +10177,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -10228,10 +10228,10 @@
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I146" s="5">
         <v>46176</v>
@@ -10291,10 +10291,10 @@
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I147" s="9"/>
       <c r="J147" s="8">
@@ -10342,10 +10342,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10393,10 +10393,10 @@
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10444,10 +10444,10 @@
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10495,10 +10495,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10546,10 +10546,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>292</v>
+        <v>286</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10928,7 +10928,7 @@
         <v>0</v>
       </c>
       <c r="U158" s="12" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1865" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="462">
   <si>
     <t>50001499- EQ. CHAPARRAL</t>
   </si>
@@ -343,43 +343,43 @@
     <t>Propuesta compras:,Generación OC corte laser</t>
   </si>
   <si>
+    <t>1214046914974302</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4202 -4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc fabricación externa  OT 4202 -4203 </t>
+  </si>
+  <si>
+    <t>1214046914974303</t>
+  </si>
+  <si>
+    <t>Propuesta mecanizado OT 4202 -4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación oc mecanizado OT 4202 -4203 </t>
+  </si>
+  <si>
+    <t>1214046914974306</t>
+  </si>
+  <si>
+    <t>Propuesta Corte Plasma  OT 4202 -4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación oc corte plasma OT 4202 -4203  </t>
+  </si>
+  <si>
+    <t>1213390413187363</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor,Alabe,Tablero OT 4217 - 4218 - 4226 -4227,rodete,Sensores,Corte Laser</t>
+  </si>
+  <si>
     <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1214046914974302</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4202 -4203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc fabricación externa  OT 4202 -4203 </t>
-  </si>
-  <si>
-    <t>1214046914974303</t>
-  </si>
-  <si>
-    <t>Propuesta mecanizado OT 4202 -4203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación oc mecanizado OT 4202 -4203 </t>
-  </si>
-  <si>
-    <t>1214046914974306</t>
-  </si>
-  <si>
-    <t>Propuesta Corte Plasma  OT 4202 -4203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación oc corte plasma OT 4202 -4203  </t>
-  </si>
-  <si>
-    <t>1213390413187363</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor,Alabe,Tablero OT 4217 - 4218 - 4226 -4227,rodete,Sensores,Corte Laser</t>
   </si>
   <si>
     <t>1213390413187373</t>
@@ -657,6 +657,18 @@
  </t>
   </si>
   <si>
+    <t xml:space="preserve">Liberacion control de calidad Carcaza </t>
+  </si>
+  <si>
+    <t>1215844283879129</t>
+  </si>
+  <si>
+    <t>Nicolás López</t>
+  </si>
+  <si>
+    <t>nicolas.lopez@zitron.com</t>
+  </si>
+  <si>
     <t>1214046914974304</t>
   </si>
   <si>
@@ -747,7 +759,7 @@
     <t>1213575386156378</t>
   </si>
   <si>
-    <t>Ingenieria y diseño:,Propuesta Fabricación externa  OT 4202 -4203,Propuesta mecanizado OT 4202 -4203,Propuesta Corte Plasma  OT 4202 -4203,Propuesta corte laser OT 4202 -4203,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6</t>
+    <t>Ingenieria y diseño:,Propuesta Fabricación externa  OT 4202 -4203,Propuesta mecanizado OT 4202 -4203,Propuesta Corte Plasma  OT 4202 -4203,Propuesta corte laser OT 4202 -4203,OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper),OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper),OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper),OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper)</t>
   </si>
   <si>
     <t>1214046914974313</t>
@@ -828,12 +840,6 @@
     <t>Control de calidad corte laser, plasma y mecanizado</t>
   </si>
   <si>
-    <t>Nicolás López</t>
-  </si>
-  <si>
-    <t>nicolas.lopez@zitron.com</t>
-  </si>
-  <si>
     <t>Control de calidad corte plasma,Control de calidad Mecanizado,Control de calidad corte laser</t>
   </si>
   <si>
@@ -861,7 +867,7 @@
     <t>Caldereria</t>
   </si>
   <si>
-    <t>Armado Fabricación externo ,Preparacion material,Control de calidad Armado</t>
+    <t xml:space="preserve">Armado Fabricación  ,Preparacion material,Control de calidad </t>
   </si>
   <si>
     <t>1213390413187419</t>
@@ -879,13 +885,16 @@
     <t>Recepcion Corte Plasma ,Control de calidad Mecanizado,Control de calidad corte laser</t>
   </si>
   <si>
-    <t>Caldereria,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6</t>
+    <t>Caldereria,OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper),OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper)</t>
   </si>
   <si>
     <t>1213390413187420</t>
   </si>
   <si>
-    <t xml:space="preserve">Armado Fabricación externo </t>
+    <t xml:space="preserve">Armado Fabricación  </t>
+  </si>
+  <si>
+    <t>OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper),OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper)</t>
   </si>
   <si>
     <t>Media</t>
@@ -894,40 +903,46 @@
     <t>1214046914974462</t>
   </si>
   <si>
+    <t>OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper)</t>
+  </si>
+  <si>
     <t>Preparacion material,Check Planos</t>
   </si>
   <si>
-    <t>Armado Fabricación externo ,OT 4202 ZVN 1-22-400/6</t>
+    <t>Armado Fabricación  ,OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper)</t>
   </si>
   <si>
     <t>1214046914974461</t>
   </si>
   <si>
-    <t>Armado Fabricación externo ,OT 4203 ZVN 1-22-575/6</t>
+    <t>OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper)</t>
+  </si>
+  <si>
+    <t>Armado Fabricación  ,OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper)</t>
   </si>
   <si>
     <t>1213390413187421</t>
   </si>
   <si>
-    <t>Control de calidad Armado</t>
+    <t xml:space="preserve">Control de calidad </t>
   </si>
   <si>
     <t>1214046914974469</t>
   </si>
   <si>
-    <t>OT 4202 ZVN 1-22-400/6,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4202 ZVN 1-22-400/6,Control de calidad Armado</t>
+    <t>OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper),Check Planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4202 ZVN 1-22-400/6,Control de calidad </t>
   </si>
   <si>
     <t>1214046914974470</t>
   </si>
   <si>
-    <t>OT 4203 ZVN 1-22-575/6,Check Planos</t>
-  </si>
-  <si>
-    <t>OT 4203 ZVN 1-22-575/6,Control de calidad Armado</t>
+    <t>OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper),Check Planos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4203 ZVN 1-22-575/6,Control de calidad </t>
   </si>
   <si>
     <t>1213390413187422</t>
@@ -996,7 +1011,7 @@
     <t>1214046914974477</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4202 ZVN 1-22-400/6,Recepcion Fabricación externa </t>
+    <t xml:space="preserve">OT 4202 ZVN 1-22-400/6 (Tobera, piza conexion, damper),Recepcion Fabricación externa </t>
   </si>
   <si>
     <t>Revestimiento,OT 4202 ZVN 1-22-400/6</t>
@@ -1005,7 +1020,7 @@
     <t>1214046914974478</t>
   </si>
   <si>
-    <t xml:space="preserve">OT 4203 ZVN 1-22-575/6,Recepcion Fabricación externa </t>
+    <t xml:space="preserve">OT 4203 ZVN 1-22-575/6 (Tobera, piza conexion, damper),Recepcion Fabricación externa </t>
   </si>
   <si>
     <t>Revestimiento,OT 4203 ZVN 1-22-575/6</t>
@@ -1907,7 +1922,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U158"/>
+  <dimension ref="A1:U159"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -3089,7 +3104,7 @@
         <v>46122.627469444444</v>
       </c>
       <c r="D22" s="5">
-        <v>46125.89806651621</v>
+        <v>46191.76425234954</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -3459,9 +3474,11 @@
       <c r="B28" s="5">
         <v>46077.54519655093</v>
       </c>
-      <c r="C28" s="6"/>
+      <c r="C28" s="5">
+        <v>46191.76405297454</v>
+      </c>
       <c r="D28" s="5">
-        <v>46169.8451322801</v>
+        <v>46191.76406943287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3505,8 +3522,8 @@
       <c r="R28" s="5">
         <v>46013</v>
       </c>
-      <c r="S28" s="12" t="s">
-        <v>110</v>
+      <c r="S28" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T28" s="6">
         <v>1</v>
@@ -3517,17 +3534,19 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B29" s="8">
         <v>46125.69234111111</v>
       </c>
-      <c r="C29" s="9"/>
+      <c r="C29" s="8">
+        <v>46191.76408129629</v>
+      </c>
       <c r="D29" s="8">
-        <v>46169.84514601852</v>
+        <v>46191.764096643514</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
@@ -3560,7 +3579,7 @@
         <v>108</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="Q29" s="8">
         <v>46136</v>
@@ -3568,11 +3587,11 @@
       <c r="R29" s="8">
         <v>46135</v>
       </c>
-      <c r="S29" s="12" t="s">
-        <v>110</v>
+      <c r="S29" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T29" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" s="11" t="s">
         <v>32</v>
@@ -3580,17 +3599,19 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B30" s="5">
         <v>46125.69240738426</v>
       </c>
-      <c r="C30" s="6"/>
+      <c r="C30" s="5">
+        <v>46191.764104965274</v>
+      </c>
       <c r="D30" s="5">
-        <v>46169.845159317134</v>
+        <v>46191.764121307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
@@ -3623,7 +3644,7 @@
         <v>108</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="Q30" s="5">
         <v>46136</v>
@@ -3631,11 +3652,11 @@
       <c r="R30" s="5">
         <v>46135</v>
       </c>
-      <c r="S30" s="12" t="s">
-        <v>110</v>
+      <c r="S30" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T30" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="11" t="s">
         <v>32</v>
@@ -3643,17 +3664,19 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B31" s="8">
         <v>46125.69558788194</v>
       </c>
-      <c r="C31" s="9"/>
+      <c r="C31" s="8">
+        <v>46191.76414623843</v>
+      </c>
       <c r="D31" s="8">
-        <v>46169.845188680556</v>
+        <v>46191.76416752315</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
@@ -3686,7 +3709,7 @@
         <v>108</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q31" s="8">
         <v>46136</v>
@@ -3694,11 +3717,11 @@
       <c r="R31" s="8">
         <v>46135</v>
       </c>
-      <c r="S31" s="12" t="s">
-        <v>110</v>
+      <c r="S31" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T31" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U31" s="11" t="s">
         <v>32</v>
@@ -3706,7 +3729,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B32" s="5">
         <v>46077.545196886575</v>
@@ -3716,7 +3739,7 @@
         <v>46182.69258219907</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3740,7 +3763,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3748,7 +3771,7 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="12" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
@@ -3794,13 +3817,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
         <v>127</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q33" s="8">
         <v>46153</v>
@@ -4054,13 +4077,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O37" s="9" t="s">
         <v>140</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q37" s="8">
         <v>46136</v>
@@ -4249,13 +4272,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O40" s="6" t="s">
         <v>149</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q40" s="5">
         <v>46122</v>
@@ -4444,13 +4467,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O43" s="9" t="s">
         <v>158</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q43" s="8">
         <v>46070</v>
@@ -4639,13 +4662,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O46" s="6" t="s">
         <v>169</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q46" s="5">
         <v>46121</v>
@@ -4834,13 +4857,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O49" s="9" t="s">
         <v>178</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="Q49" s="8">
         <v>46069</v>
@@ -4869,7 +4892,7 @@
         <v>46097.55269060185</v>
       </c>
       <c r="D50" s="5">
-        <v>46125.89874443287</v>
+        <v>46191.764061747686</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4995,9 +5018,11 @@
       <c r="B52" s="5">
         <v>46125.69589043982</v>
       </c>
-      <c r="C52" s="6"/>
+      <c r="C52" s="5">
+        <v>46191.76882001157</v>
+      </c>
       <c r="D52" s="5">
-        <v>46169.84392304398</v>
+        <v>46191.76988886574</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>186</v>
@@ -5027,7 +5052,7 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O52" s="6" t="s">
         <v>187</v>
@@ -5041,11 +5066,11 @@
       <c r="R52" s="5">
         <v>46078</v>
       </c>
-      <c r="S52" s="11" t="s">
-        <v>55</v>
+      <c r="S52" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="T52" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U52" s="11" t="s">
         <v>32</v>
@@ -5058,12 +5083,14 @@
       <c r="B53" s="8">
         <v>46125.70470673611</v>
       </c>
-      <c r="C53" s="9"/>
+      <c r="C53" s="8">
+        <v>46191.769818437504</v>
+      </c>
       <c r="D53" s="8">
-        <v>46169.84397611111</v>
+        <v>46191.76981975694</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
@@ -5093,7 +5120,7 @@
         <v>186</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="P53" s="9" t="s">
         <v>189</v>
@@ -5111,9 +5138,11 @@
       <c r="B54" s="5">
         <v>46125.704894062495</v>
       </c>
-      <c r="C54" s="6"/>
+      <c r="C54" s="5">
+        <v>46191.76987311343</v>
+      </c>
       <c r="D54" s="5">
-        <v>46169.84399245371</v>
+        <v>46191.76987484954</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5146,7 +5175,7 @@
         <v>186</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P54" s="6" t="s">
         <v>192</v>
@@ -5196,7 +5225,7 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="O55" s="9" t="s">
         <v>197</v>
@@ -5229,10 +5258,10 @@
       </c>
       <c r="C56" s="6"/>
       <c r="D56" s="5">
-        <v>46191.68418592593</v>
+        <v>46191.7640874537</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
@@ -5262,7 +5291,7 @@
         <v>194</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P56" s="6" t="s">
         <v>199</v>
@@ -5282,7 +5311,7 @@
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46169.84491788194</v>
+        <v>46191.768077870365</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5368,7 +5397,7 @@
         <v>201</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P58" s="6" t="s">
         <v>201</v>
@@ -5421,7 +5450,7 @@
         <v>201</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P59" s="9" t="s">
         <v>201</v>
@@ -5474,7 +5503,7 @@
         <v>201</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P60" s="6" t="s">
         <v>201</v>
@@ -5527,7 +5556,7 @@
         <v>201</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P61" s="9" t="s">
         <v>201</v>
@@ -5547,7 +5576,7 @@
       </c>
       <c r="C62" s="6"/>
       <c r="D62" s="5">
-        <v>46191.68418570602</v>
+        <v>46191.76844943287</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5580,10 +5609,10 @@
         <v>201</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>26</v>
+        <v>214</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5593,32 +5622,30 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46125.69345099537</v>
+        <v>46191.76807549769</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46169.84413715277</v>
+        <v>46191.768449236115</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="I63" s="8">
-        <v>46078</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="I63" s="9"/>
       <c r="J63" s="8">
-        <v>46093</v>
+        <v>46114</v>
       </c>
       <c r="K63" s="9" t="s">
         <v>26</v>
@@ -5630,43 +5657,33 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>121</v>
+        <v>201</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="Q63" s="8">
-        <v>46093</v>
-      </c>
-      <c r="R63" s="8">
-        <v>46078</v>
-      </c>
-      <c r="S63" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T63" s="9">
-        <v>0</v>
-      </c>
-      <c r="U63" s="11" t="s">
-        <v>32</v>
-      </c>
+      <c r="Q63" s="9"/>
+      <c r="R63" s="9"/>
+      <c r="S63" s="9"/>
+      <c r="T63" s="9"/>
+      <c r="U63" s="9"/>
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.7055987037</v>
+        <v>46125.69345099537</v>
       </c>
       <c r="C64" s="6"/>
       <c r="D64" s="5">
-        <v>46169.844170324075</v>
+        <v>46191.787197858794</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>116</v>
+        <v>219</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
@@ -5681,7 +5698,7 @@
         <v>46078</v>
       </c>
       <c r="J64" s="5">
-        <v>46084</v>
+        <v>46093</v>
       </c>
       <c r="K64" s="6" t="s">
         <v>26</v>
@@ -5693,33 +5710,43 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>215</v>
+        <v>120</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>115</v>
+        <v>220</v>
       </c>
       <c r="P64" s="6" t="s">
-        <v>218</v>
-      </c>
-      <c r="Q64" s="6"/>
-      <c r="R64" s="6"/>
-      <c r="S64" s="6"/>
-      <c r="T64" s="6"/>
-      <c r="U64" s="6"/>
+        <v>26</v>
+      </c>
+      <c r="Q64" s="5">
+        <v>46093</v>
+      </c>
+      <c r="R64" s="5">
+        <v>46078</v>
+      </c>
+      <c r="S64" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T64" s="6">
+        <v>0</v>
+      </c>
+      <c r="U64" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="B65" s="8">
-        <v>46125.70569783565</v>
+        <v>46125.7055987037</v>
       </c>
       <c r="C65" s="9"/>
       <c r="D65" s="8">
-        <v>46169.8441947338</v>
+        <v>46191.764111006945</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>220</v>
+        <v>115</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
@@ -5731,10 +5758,10 @@
         <v>168</v>
       </c>
       <c r="I65" s="8">
-        <v>46085</v>
+        <v>46078</v>
       </c>
       <c r="J65" s="8">
-        <v>46093</v>
+        <v>46084</v>
       </c>
       <c r="K65" s="9" t="s">
         <v>26</v>
@@ -5746,13 +5773,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5762,27 +5789,33 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46077.54519895834</v>
+        <v>46125.70569783565</v>
       </c>
       <c r="C66" s="6"/>
       <c r="D66" s="5">
-        <v>46127.698486747686</v>
+        <v>46169.8441947338</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H66" s="6"/>
-      <c r="I66" s="6"/>
-      <c r="J66" s="6"/>
+        <v>167</v>
+      </c>
+      <c r="H66" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="I66" s="5">
+        <v>46085</v>
+      </c>
+      <c r="J66" s="5">
+        <v>46093</v>
+      </c>
       <c r="K66" s="6" t="s">
         <v>26</v>
       </c>
@@ -5790,16 +5823,16 @@
         <v>26</v>
       </c>
       <c r="M66" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>26</v>
+        <v>219</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>224</v>
+        <v>115</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>26</v>
+        <v>225</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5809,93 +5842,75 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B67" s="8">
-        <v>46077.54519921297</v>
-      </c>
-      <c r="C67" s="8">
-        <v>46127.69765324074</v>
-      </c>
+        <v>46077.54519895834</v>
+      </c>
+      <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46188.669512673616</v>
+        <v>46127.698486747686</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F67" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G67" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="H67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="H67" s="9"/>
+      <c r="I67" s="9"/>
+      <c r="J67" s="9"/>
+      <c r="K67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M67" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="N67" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="O67" s="9" t="s">
         <v>228</v>
       </c>
-      <c r="I67" s="8">
-        <v>46013</v>
-      </c>
-      <c r="J67" s="8">
-        <v>46017</v>
-      </c>
-      <c r="K67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M67" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N67" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="O67" s="9" t="s">
-        <v>229</v>
-      </c>
       <c r="P67" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q67" s="8">
-        <v>46016</v>
-      </c>
-      <c r="R67" s="8">
-        <v>46013</v>
-      </c>
-      <c r="S67" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T67" s="9">
-        <v>1</v>
-      </c>
-      <c r="U67" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q67" s="9"/>
+      <c r="R67" s="9"/>
+      <c r="S67" s="9"/>
+      <c r="T67" s="9"/>
+      <c r="U67" s="9"/>
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="B68" s="5">
+        <v>46077.54519921297</v>
+      </c>
+      <c r="C68" s="5">
+        <v>46127.69765324074</v>
+      </c>
+      <c r="D68" s="5">
+        <v>46188.669512673616</v>
+      </c>
+      <c r="E68" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="B68" s="5">
-        <v>46125.6963875463</v>
-      </c>
-      <c r="C68" s="5">
-        <v>46127.69763241898</v>
-      </c>
-      <c r="D68" s="5">
-        <v>46127.697633749995</v>
-      </c>
-      <c r="E68" s="6" t="s">
+      <c r="F68" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G68" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F68" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G68" s="6" t="s">
-        <v>227</v>
-      </c>
       <c r="H68" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I68" s="5">
         <v>46013</v>
@@ -5913,44 +5928,54 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>79</v>
+        <v>233</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q68" s="6"/>
-      <c r="R68" s="6"/>
-      <c r="S68" s="6"/>
-      <c r="T68" s="6"/>
-      <c r="U68" s="6"/>
+        <v>227</v>
+      </c>
+      <c r="Q68" s="5">
+        <v>46016</v>
+      </c>
+      <c r="R68" s="5">
+        <v>46013</v>
+      </c>
+      <c r="S68" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T68" s="6">
+        <v>1</v>
+      </c>
+      <c r="U68" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
+        <v>234</v>
+      </c>
+      <c r="B69" s="8">
+        <v>46125.6963875463</v>
+      </c>
+      <c r="C69" s="8">
+        <v>46127.69763241898</v>
+      </c>
+      <c r="D69" s="8">
+        <v>46127.697633749995</v>
+      </c>
+      <c r="E69" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F69" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G69" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="H69" s="9" t="s">
         <v>232</v>
-      </c>
-      <c r="B69" s="8">
-        <v>46125.69656831019</v>
-      </c>
-      <c r="C69" s="8">
-        <v>46127.69763894676</v>
-      </c>
-      <c r="D69" s="8">
-        <v>46127.6976405787</v>
-      </c>
-      <c r="E69" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="F69" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G69" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="H69" s="9" t="s">
-        <v>228</v>
       </c>
       <c r="I69" s="8">
         <v>46013</v>
@@ -5968,13 +5993,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="O69" s="9" t="s">
         <v>79</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -5984,34 +6009,34 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46077.545196736115</v>
+        <v>46125.69656831019</v>
       </c>
       <c r="C70" s="5">
-        <v>46127.69789872685</v>
+        <v>46127.69763894676</v>
       </c>
       <c r="D70" s="5">
-        <v>46127.697912766205</v>
+        <v>46127.6976405787</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F70" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G70" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H70" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I70" s="5">
-        <v>46066</v>
+        <v>46013</v>
       </c>
       <c r="J70" s="5">
-        <v>46072</v>
+        <v>46017</v>
       </c>
       <c r="K70" s="6" t="s">
         <v>26</v>
@@ -6023,54 +6048,44 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>236</v>
+        <v>79</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q70" s="5">
-        <v>46072</v>
-      </c>
-      <c r="R70" s="5">
-        <v>46006</v>
-      </c>
-      <c r="S70" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T70" s="6">
-        <v>1</v>
-      </c>
-      <c r="U70" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="Q70" s="6"/>
+      <c r="R70" s="6"/>
+      <c r="S70" s="6"/>
+      <c r="T70" s="6"/>
+      <c r="U70" s="6"/>
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B71" s="8">
-        <v>46125.69788891204</v>
+        <v>46077.545196736115</v>
       </c>
       <c r="C71" s="8">
-        <v>46127.697883437504</v>
+        <v>46127.69789872685</v>
       </c>
       <c r="D71" s="8">
-        <v>46127.69788501157</v>
+        <v>46127.697912766205</v>
       </c>
       <c r="E71" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F71" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G71" s="9" t="s">
         <v>231</v>
       </c>
-      <c r="F71" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G71" s="9" t="s">
-        <v>227</v>
-      </c>
       <c r="H71" s="9" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I71" s="8">
         <v>46066</v>
@@ -6088,44 +6103,54 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q71" s="9"/>
-      <c r="R71" s="9"/>
-      <c r="S71" s="9"/>
-      <c r="T71" s="9"/>
-      <c r="U71" s="9"/>
+        <v>227</v>
+      </c>
+      <c r="Q71" s="8">
+        <v>46072</v>
+      </c>
+      <c r="R71" s="8">
+        <v>46006</v>
+      </c>
+      <c r="S71" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T71" s="9">
+        <v>1</v>
+      </c>
+      <c r="U71" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.69801100694</v>
+        <v>46125.69788891204</v>
       </c>
       <c r="C72" s="5">
-        <v>46127.69787200232</v>
+        <v>46127.697883437504</v>
       </c>
       <c r="D72" s="5">
-        <v>46127.697873287034</v>
+        <v>46127.69788501157</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I72" s="5">
         <v>46066</v>
@@ -6143,13 +6168,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6159,34 +6184,34 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46090.70475186342</v>
+        <v>46125.69801100694</v>
       </c>
       <c r="C73" s="8">
-        <v>46127.69847682871</v>
+        <v>46127.69787200232</v>
       </c>
       <c r="D73" s="8">
-        <v>46127.698491539355</v>
+        <v>46127.697873287034</v>
       </c>
       <c r="E73" s="9" t="s">
-        <v>108</v>
+        <v>237</v>
       </c>
       <c r="F73" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G73" s="9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H73" s="9" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I73" s="8">
-        <v>46073</v>
+        <v>46066</v>
       </c>
       <c r="J73" s="8">
-        <v>46073</v>
+        <v>46072</v>
       </c>
       <c r="K73" s="9" t="s">
         <v>26</v>
@@ -6198,54 +6223,44 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>244</v>
-      </c>
-      <c r="Q73" s="8">
-        <v>46073</v>
-      </c>
-      <c r="R73" s="8">
-        <v>46073</v>
-      </c>
-      <c r="S73" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="T73" s="9">
-        <v>1</v>
-      </c>
-      <c r="U73" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="Q73" s="9"/>
+      <c r="R73" s="9"/>
+      <c r="S73" s="9"/>
+      <c r="T73" s="9"/>
+      <c r="U73" s="9"/>
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B74" s="5">
-        <v>46125.69814037037</v>
+        <v>46090.70475186342</v>
       </c>
       <c r="C74" s="5">
-        <v>46127.69844965277</v>
+        <v>46127.69847682871</v>
       </c>
       <c r="D74" s="5">
-        <v>46127.698451331016</v>
+        <v>46127.698491539355</v>
       </c>
       <c r="E74" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F74" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G74" s="6" t="s">
         <v>231</v>
       </c>
-      <c r="F74" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G74" s="6" t="s">
-        <v>227</v>
-      </c>
       <c r="H74" s="6" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I74" s="5">
         <v>46073</v>
@@ -6263,44 +6278,54 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>108</v>
+        <v>227</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="Q74" s="6"/>
-      <c r="R74" s="6"/>
-      <c r="S74" s="6"/>
-      <c r="T74" s="6"/>
-      <c r="U74" s="6"/>
+        <v>248</v>
+      </c>
+      <c r="Q74" s="5">
+        <v>46073</v>
+      </c>
+      <c r="R74" s="5">
+        <v>46073</v>
+      </c>
+      <c r="S74" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T74" s="6">
+        <v>1</v>
+      </c>
+      <c r="U74" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.6983227662</v>
+        <v>46125.69814037037</v>
       </c>
       <c r="C75" s="8">
-        <v>46127.69845996528</v>
+        <v>46127.69844965277</v>
       </c>
       <c r="D75" s="8">
-        <v>46127.69846143518</v>
+        <v>46127.698451331016</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="I75" s="8">
         <v>46073</v>
@@ -6321,7 +6346,7 @@
         <v>108</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>108</v>
@@ -6334,32 +6359,34 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B76" s="5">
-        <v>46090.70479819445</v>
-      </c>
-      <c r="C76" s="6"/>
+        <v>46125.6983227662</v>
+      </c>
+      <c r="C76" s="5">
+        <v>46127.69845996528</v>
+      </c>
       <c r="D76" s="5">
-        <v>46168.17332814814</v>
+        <v>46127.69846143518</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="F76" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G76" s="6" t="s">
-        <v>249</v>
+        <v>231</v>
       </c>
       <c r="H76" s="6" t="s">
-        <v>250</v>
+        <v>232</v>
       </c>
       <c r="I76" s="5">
-        <v>46167</v>
+        <v>46073</v>
       </c>
       <c r="J76" s="5">
-        <v>46167</v>
+        <v>46073</v>
       </c>
       <c r="K76" s="6" t="s">
         <v>26</v>
@@ -6371,54 +6398,46 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>223</v>
+        <v>108</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>223</v>
-      </c>
-      <c r="Q76" s="5">
-        <v>46167</v>
-      </c>
-      <c r="R76" s="5">
-        <v>46167</v>
-      </c>
-      <c r="S76" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T76" s="6">
-        <v>0</v>
-      </c>
-      <c r="U76" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="Q76" s="6"/>
+      <c r="R76" s="6"/>
+      <c r="S76" s="6"/>
+      <c r="T76" s="6"/>
+      <c r="U76" s="6"/>
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
         <v>251</v>
       </c>
       <c r="B77" s="8">
-        <v>46125.69919584491</v>
+        <v>46090.70479819445</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46167.16821967592</v>
+        <v>46168.17332814814</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>231</v>
+        <v>252</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>250</v>
-      </c>
-      <c r="I77" s="9"/>
+        <v>254</v>
+      </c>
+      <c r="I77" s="8">
+        <v>46167</v>
+      </c>
       <c r="J77" s="8">
         <v>46167</v>
       </c>
@@ -6432,42 +6451,52 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>248</v>
+        <v>227</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="Q77" s="9"/>
-      <c r="R77" s="9"/>
-      <c r="S77" s="9"/>
-      <c r="T77" s="9"/>
-      <c r="U77" s="9"/>
+        <v>227</v>
+      </c>
+      <c r="Q77" s="8">
+        <v>46167</v>
+      </c>
+      <c r="R77" s="8">
+        <v>46167</v>
+      </c>
+      <c r="S77" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T77" s="9">
+        <v>0</v>
+      </c>
+      <c r="U77" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.69931737268</v>
+        <v>46125.69919584491</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.168221562504</v>
+        <v>46167.16821967592</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6483,13 +6512,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6499,27 +6528,31 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B79" s="8">
-        <v>46077.54519710648</v>
+        <v>46125.69931737268</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46125.899998113426</v>
+        <v>46167.168221562504</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>256</v>
+        <v>237</v>
       </c>
       <c r="F79" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H79" s="9"/>
+        <v>253</v>
+      </c>
+      <c r="H79" s="9" t="s">
+        <v>254</v>
+      </c>
       <c r="I79" s="9"/>
-      <c r="J79" s="9"/>
+      <c r="J79" s="8">
+        <v>46167</v>
+      </c>
       <c r="K79" s="9" t="s">
         <v>26</v>
       </c>
@@ -6527,16 +6560,16 @@
         <v>26</v>
       </c>
       <c r="M79" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>26</v>
+        <v>252</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>26</v>
+        <v>258</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6546,89 +6579,77 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.54519784723</v>
+        <v>46077.54519710648</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46147.850671782406</v>
+        <v>46191.76957280093</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G80" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="H80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6"/>
+      <c r="K80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M80" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N80" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O80" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="I80" s="5">
-        <v>46094</v>
-      </c>
-      <c r="J80" s="5">
-        <v>46097</v>
-      </c>
-      <c r="K80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M80" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N80" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="O80" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="P80" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="Q80" s="5">
-        <v>46097</v>
-      </c>
-      <c r="R80" s="5">
-        <v>46094</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q80" s="6"/>
+      <c r="R80" s="6"/>
       <c r="S80" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="T80" s="6">
-        <v>0</v>
-      </c>
-      <c r="U80" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>122</v>
+      </c>
+      <c r="T80" s="6"/>
+      <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
+        <v>262</v>
+      </c>
+      <c r="B81" s="8">
+        <v>46077.54519784723</v>
+      </c>
+      <c r="C81" s="8">
+        <v>46191.76955590278</v>
+      </c>
+      <c r="D81" s="8">
+        <v>46191.7695737037</v>
+      </c>
+      <c r="E81" s="9" t="s">
         <v>263</v>
       </c>
-      <c r="B81" s="8">
-        <v>46125.69615554398</v>
-      </c>
-      <c r="C81" s="9"/>
-      <c r="D81" s="8">
-        <v>46125.902950069445</v>
-      </c>
-      <c r="E81" s="9" t="s">
+      <c r="F81" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G81" s="9" t="s">
         <v>264</v>
       </c>
-      <c r="F81" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G81" s="9" t="s">
-        <v>260</v>
-      </c>
       <c r="H81" s="9" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I81" s="8">
         <v>46094</v>
@@ -6646,13 +6667,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="Q81" s="8">
         <v>46097</v>
@@ -6660,11 +6681,11 @@
       <c r="R81" s="8">
         <v>46094</v>
       </c>
-      <c r="S81" s="11" t="s">
-        <v>55</v>
+      <c r="S81" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T81" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U81" s="11" t="s">
         <v>32</v>
@@ -6672,26 +6693,28 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B82" s="5">
-        <v>46125.699760648145</v>
-      </c>
-      <c r="C82" s="6"/>
+        <v>46125.69615554398</v>
+      </c>
+      <c r="C82" s="5">
+        <v>46191.77013172454</v>
+      </c>
       <c r="D82" s="5">
-        <v>46125.90295023148</v>
+        <v>46191.77014716435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="I82" s="5">
         <v>46094</v>
@@ -6709,13 +6732,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q82" s="5">
         <v>46097</v>
@@ -6723,11 +6746,11 @@
       <c r="R82" s="5">
         <v>46094</v>
       </c>
-      <c r="S82" s="11" t="s">
-        <v>55</v>
+      <c r="S82" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T82" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U82" s="11" t="s">
         <v>32</v>
@@ -6735,56 +6758,56 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B83" s="8">
-        <v>46077.545198472224</v>
+        <v>46125.699760648145</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46125.91089737268</v>
+        <v>46125.90295023148</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="H83" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I83" s="8">
+        <v>46094</v>
+      </c>
+      <c r="J83" s="8">
+        <v>46097</v>
+      </c>
+      <c r="K83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M83" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N83" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="O83" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="P83" s="9" t="s">
         <v>272</v>
       </c>
-      <c r="I83" s="8">
-        <v>46098</v>
-      </c>
-      <c r="J83" s="8">
-        <v>46099</v>
-      </c>
-      <c r="K83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M83" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N83" s="9" t="s">
-        <v>256</v>
-      </c>
-      <c r="O83" s="9" t="s">
-        <v>273</v>
-      </c>
-      <c r="P83" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="Q83" s="8">
-        <v>46099</v>
+        <v>46097</v>
       </c>
       <c r="R83" s="8">
-        <v>46098</v>
+        <v>46094</v>
       </c>
       <c r="S83" s="11" t="s">
         <v>55</v>
@@ -6798,26 +6821,28 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="B84" s="5">
+        <v>46077.545198472224</v>
+      </c>
+      <c r="C84" s="5">
+        <v>46191.769443275465</v>
+      </c>
+      <c r="D84" s="5">
+        <v>46191.770536875</v>
+      </c>
+      <c r="E84" s="6" t="s">
         <v>274</v>
       </c>
-      <c r="B84" s="5">
-        <v>46125.775447465276</v>
-      </c>
-      <c r="C84" s="6"/>
-      <c r="D84" s="5">
-        <v>46125.910896354166</v>
-      </c>
-      <c r="E84" s="6" t="s">
-        <v>275</v>
-      </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="I84" s="5">
         <v>46098</v>
@@ -6835,42 +6860,54 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>276</v>
-      </c>
-      <c r="Q84" s="6"/>
-      <c r="R84" s="6"/>
-      <c r="S84" s="6"/>
-      <c r="T84" s="6"/>
-      <c r="U84" s="6"/>
+        <v>260</v>
+      </c>
+      <c r="Q84" s="5">
+        <v>46099</v>
+      </c>
+      <c r="R84" s="5">
+        <v>46098</v>
+      </c>
+      <c r="S84" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T84" s="6">
+        <v>1</v>
+      </c>
+      <c r="U84" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="B85" s="8">
+        <v>46125.775447465276</v>
+      </c>
+      <c r="C85" s="8">
+        <v>46191.769735925925</v>
+      </c>
+      <c r="D85" s="8">
+        <v>46191.76973724537</v>
+      </c>
+      <c r="E85" s="9" t="s">
         <v>277</v>
       </c>
-      <c r="B85" s="8">
-        <v>46125.77559420139</v>
-      </c>
-      <c r="C85" s="9"/>
-      <c r="D85" s="8">
-        <v>46125.91059135417</v>
-      </c>
-      <c r="E85" s="9" t="s">
-        <v>278</v>
-      </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="I85" s="8">
         <v>46098</v>
@@ -6888,13 +6925,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6907,23 +6944,25 @@
         <v>279</v>
       </c>
       <c r="B86" s="5">
-        <v>46125.77573671297</v>
-      </c>
-      <c r="C86" s="6"/>
+        <v>46125.77559420139</v>
+      </c>
+      <c r="C86" s="5">
+        <v>46191.7705319213</v>
+      </c>
       <c r="D86" s="5">
-        <v>46125.9107300926</v>
+        <v>46191.77053325232</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>268</v>
+        <v>280</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="I86" s="5">
         <v>46098</v>
@@ -6941,13 +6980,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -6957,27 +6996,33 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B87" s="8">
-        <v>46077.545199050925</v>
+        <v>46125.77573671297</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46191.72825035879</v>
+        <v>46125.9107300926</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F87" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H87" s="9"/>
-      <c r="I87" s="9"/>
-      <c r="J87" s="9"/>
+        <v>216</v>
+      </c>
+      <c r="H87" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I87" s="8">
+        <v>46098</v>
+      </c>
+      <c r="J87" s="8">
+        <v>46099</v>
+      </c>
       <c r="K87" s="9" t="s">
         <v>26</v>
       </c>
@@ -6985,16 +7030,16 @@
         <v>26</v>
       </c>
       <c r="M87" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>26</v>
+        <v>274</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>26</v>
+        <v>278</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7004,152 +7049,146 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="B88" s="5">
+        <v>46077.545199050925</v>
+      </c>
+      <c r="C88" s="5">
+        <v>46191.770449421296</v>
+      </c>
+      <c r="D88" s="5">
+        <v>46191.77046482639</v>
+      </c>
+      <c r="E88" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="B88" s="5">
-        <v>46077.5451993287</v>
-      </c>
-      <c r="C88" s="6"/>
-      <c r="D88" s="5">
-        <v>46191.72813158565</v>
-      </c>
-      <c r="E88" s="6" t="s">
+      <c r="F88" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="H88" s="6"/>
+      <c r="I88" s="6"/>
+      <c r="J88" s="6"/>
+      <c r="K88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M88" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="N88" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="O88" s="6" t="s">
         <v>284</v>
       </c>
-      <c r="F88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G88" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="H88" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="I88" s="5">
-        <v>46100</v>
-      </c>
-      <c r="J88" s="5">
-        <v>46108</v>
-      </c>
-      <c r="K88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M88" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N88" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="O88" s="6" t="s">
-        <v>287</v>
-      </c>
       <c r="P88" s="6" t="s">
-        <v>288</v>
-      </c>
-      <c r="Q88" s="5">
-        <v>46108</v>
-      </c>
-      <c r="R88" s="5">
-        <v>46100</v>
-      </c>
-      <c r="S88" s="11" t="s">
-        <v>55</v>
+        <v>26</v>
+      </c>
+      <c r="Q88" s="6"/>
+      <c r="R88" s="6"/>
+      <c r="S88" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T88" s="6">
-        <v>0</v>
-      </c>
-      <c r="U88" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="U88" s="6"/>
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="B89" s="8">
+        <v>46077.5451993287</v>
+      </c>
+      <c r="C89" s="8">
+        <v>46191.76127780092</v>
+      </c>
+      <c r="D89" s="8">
+        <v>46191.77013883102</v>
+      </c>
+      <c r="E89" s="9" t="s">
+        <v>286</v>
+      </c>
+      <c r="F89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G89" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="H89" s="9" t="s">
+        <v>288</v>
+      </c>
+      <c r="I89" s="8">
+        <v>46100</v>
+      </c>
+      <c r="J89" s="8">
+        <v>46108</v>
+      </c>
+      <c r="K89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M89" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N89" s="9" t="s">
+        <v>283</v>
+      </c>
+      <c r="O89" s="9" t="s">
         <v>289</v>
       </c>
-      <c r="B89" s="8">
-        <v>46077.54519958333</v>
-      </c>
-      <c r="C89" s="9"/>
-      <c r="D89" s="8">
-        <v>46191.7283396412</v>
-      </c>
-      <c r="E89" s="9" t="s">
+      <c r="P89" s="9" t="s">
         <v>290</v>
       </c>
-      <c r="F89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G89" s="9" t="s">
-        <v>285</v>
-      </c>
-      <c r="H89" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="I89" s="8">
-        <v>46111</v>
-      </c>
-      <c r="J89" s="8">
-        <v>46139</v>
-      </c>
-      <c r="K89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M89" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N89" s="9" t="s">
-        <v>281</v>
-      </c>
-      <c r="O89" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="P89" s="9" t="s">
-        <v>281</v>
-      </c>
       <c r="Q89" s="8">
-        <v>46139</v>
+        <v>46108</v>
       </c>
       <c r="R89" s="8">
-        <v>46111</v>
-      </c>
-      <c r="S89" s="11" t="s">
-        <v>55</v>
+        <v>46100</v>
+      </c>
+      <c r="S89" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T89" s="9">
-        <v>0</v>
-      </c>
-      <c r="U89" s="12" t="s">
-        <v>291</v>
+        <v>1</v>
+      </c>
+      <c r="U89" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
+        <v>291</v>
+      </c>
+      <c r="B90" s="5">
+        <v>46077.54519958333</v>
+      </c>
+      <c r="C90" s="5">
+        <v>46191.76363961806</v>
+      </c>
+      <c r="D90" s="5">
+        <v>46191.76662447916</v>
+      </c>
+      <c r="E90" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="B90" s="5">
-        <v>46125.780000914354</v>
-      </c>
-      <c r="C90" s="6"/>
-      <c r="D90" s="5">
-        <v>46191.72843072917</v>
-      </c>
-      <c r="E90" s="6" t="s">
-        <v>231</v>
-      </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I90" s="5">
         <v>46111</v>
@@ -7167,42 +7206,54 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="O90" s="6" t="s">
         <v>293</v>
       </c>
       <c r="P90" s="6" t="s">
+        <v>283</v>
+      </c>
+      <c r="Q90" s="5">
+        <v>46139</v>
+      </c>
+      <c r="R90" s="5">
+        <v>46111</v>
+      </c>
+      <c r="S90" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T90" s="6">
+        <v>1</v>
+      </c>
+      <c r="U90" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="6"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
         <v>295</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.779717233796</v>
-      </c>
-      <c r="C91" s="9"/>
+        <v>46125.780000914354</v>
+      </c>
+      <c r="C91" s="8">
+        <v>46191.76360844907</v>
+      </c>
       <c r="D91" s="8">
-        <v>46191.72847037037</v>
+        <v>46191.76361026621</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I91" s="8">
         <v>46111</v>
@@ -7220,13 +7271,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7236,89 +7287,83 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="B92" s="5">
+        <v>46125.779717233796</v>
+      </c>
+      <c r="C92" s="5">
+        <v>46191.76362376157</v>
+      </c>
+      <c r="D92" s="5">
+        <v>46191.76362532408</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H92" s="6" t="s">
+        <v>288</v>
+      </c>
+      <c r="I92" s="5">
+        <v>46111</v>
+      </c>
+      <c r="J92" s="5">
+        <v>46139</v>
+      </c>
+      <c r="K92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M92" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N92" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="O92" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="B92" s="5">
-        <v>46077.54519984954</v>
-      </c>
-      <c r="C92" s="6"/>
-      <c r="D92" s="5">
-        <v>46141.1681012037</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G92" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="H92" s="6" t="s">
-        <v>272</v>
-      </c>
-      <c r="I92" s="5">
-        <v>46140</v>
-      </c>
-      <c r="J92" s="5">
-        <v>46141</v>
-      </c>
-      <c r="K92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M92" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N92" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="O92" s="6" t="s">
-        <v>236</v>
-      </c>
       <c r="P92" s="6" t="s">
-        <v>281</v>
-      </c>
-      <c r="Q92" s="5">
-        <v>46141</v>
-      </c>
-      <c r="R92" s="5">
-        <v>46140</v>
-      </c>
-      <c r="S92" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="T92" s="6">
-        <v>0</v>
-      </c>
-      <c r="U92" s="12" t="s">
-        <v>291</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="Q92" s="6"/>
+      <c r="R92" s="6"/>
+      <c r="S92" s="6"/>
+      <c r="T92" s="6"/>
+      <c r="U92" s="6"/>
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B93" s="8">
-        <v>46125.7814462963</v>
-      </c>
-      <c r="C93" s="9"/>
+        <v>46077.54519984954</v>
+      </c>
+      <c r="C93" s="8">
+        <v>46191.77043608796</v>
+      </c>
       <c r="D93" s="8">
-        <v>46141.16999090278</v>
+        <v>46191.77044953704</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>231</v>
+        <v>303</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="I93" s="8">
         <v>46140</v>
@@ -7336,42 +7381,52 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>301</v>
-      </c>
-      <c r="Q93" s="9"/>
-      <c r="R93" s="9"/>
-      <c r="S93" s="9"/>
-      <c r="T93" s="9"/>
-      <c r="U93" s="9"/>
+        <v>283</v>
+      </c>
+      <c r="Q93" s="8">
+        <v>46141</v>
+      </c>
+      <c r="R93" s="8">
+        <v>46140</v>
+      </c>
+      <c r="S93" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T93" s="9">
+        <v>1</v>
+      </c>
+      <c r="U93" s="12" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.78158427084</v>
+        <v>46125.7814462963</v>
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46141.16999282407</v>
+        <v>46191.768744236106</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>233</v>
+        <v>296</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>271</v>
+        <v>216</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>272</v>
+        <v>217</v>
       </c>
       <c r="I94" s="5">
         <v>46140</v>
@@ -7389,13 +7444,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7405,27 +7460,33 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B95" s="8">
-        <v>46077.54520011574</v>
+        <v>46125.78158427084</v>
       </c>
       <c r="C95" s="9"/>
       <c r="D95" s="8">
-        <v>46125.79029240741</v>
+        <v>46191.768768229165</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="F95" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H95" s="9"/>
-      <c r="I95" s="9"/>
-      <c r="J95" s="9"/>
+        <v>216</v>
+      </c>
+      <c r="H95" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="I95" s="8">
+        <v>46140</v>
+      </c>
+      <c r="J95" s="8">
+        <v>46141</v>
+      </c>
       <c r="K95" s="9" t="s">
         <v>26</v>
       </c>
@@ -7433,16 +7494,16 @@
         <v>26</v>
       </c>
       <c r="M95" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>26</v>
+        <v>303</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>26</v>
+        <v>309</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7452,33 +7513,27 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B96" s="5">
-        <v>46077.545198078704</v>
+        <v>46077.54520011574</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46155.866225439815</v>
+        <v>46191.786592488425</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>308</v>
+        <v>260</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G96" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="H96" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I96" s="5">
-        <v>46154</v>
-      </c>
-      <c r="J96" s="5">
-        <v>46155</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H96" s="6"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6"/>
       <c r="K96" s="6" t="s">
         <v>26</v>
       </c>
@@ -7486,214 +7541,208 @@
         <v>26</v>
       </c>
       <c r="M96" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N96" s="6" t="s">
-        <v>256</v>
+        <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>133</v>
+        <v>311</v>
       </c>
       <c r="P96" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q96" s="5">
-        <v>46155</v>
-      </c>
-      <c r="R96" s="5">
-        <v>46154</v>
-      </c>
-      <c r="S96" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T96" s="6">
-        <v>0</v>
-      </c>
-      <c r="U96" s="10" t="s">
-        <v>128</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q96" s="6"/>
+      <c r="R96" s="6"/>
+      <c r="S96" s="6"/>
+      <c r="T96" s="6"/>
+      <c r="U96" s="6"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B97" s="8">
-        <v>46077.54519778935</v>
-      </c>
-      <c r="C97" s="9"/>
+        <v>46077.545198078704</v>
+      </c>
+      <c r="C97" s="8">
+        <v>46191.78640506945</v>
+      </c>
       <c r="D97" s="8">
-        <v>46155.895496365745</v>
+        <v>46191.78642105324</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H97" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I97" s="8">
+        <v>46154</v>
+      </c>
+      <c r="J97" s="8">
+        <v>46155</v>
+      </c>
+      <c r="K97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M97" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N97" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="H97" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="I97" s="8">
-        <v>46139</v>
-      </c>
-      <c r="J97" s="8">
-        <v>46140</v>
-      </c>
-      <c r="K97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M97" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N97" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="O97" s="9" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Q97" s="8">
-        <v>46140</v>
+        <v>46155</v>
       </c>
       <c r="R97" s="8">
-        <v>46139</v>
-      </c>
-      <c r="S97" s="11" t="s">
-        <v>55</v>
+        <v>46154</v>
+      </c>
+      <c r="S97" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T97" s="9">
-        <v>0</v>
-      </c>
-      <c r="U97" s="12" t="s">
-        <v>291</v>
+        <v>1</v>
+      </c>
+      <c r="U97" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B98" s="5">
-        <v>46077.54520075231</v>
-      </c>
-      <c r="C98" s="6"/>
+        <v>46077.54519778935</v>
+      </c>
+      <c r="C98" s="5">
+        <v>46191.78658587963</v>
+      </c>
       <c r="D98" s="5">
-        <v>46126.83061201389</v>
+        <v>46191.78660222222</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H98" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I98" s="5">
+        <v>46139</v>
+      </c>
+      <c r="J98" s="5">
+        <v>46140</v>
+      </c>
+      <c r="K98" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L98" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M98" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N98" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H98" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I98" s="5">
-        <v>46071</v>
-      </c>
-      <c r="J98" s="5">
-        <v>46072</v>
-      </c>
-      <c r="K98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M98" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N98" s="6" t="s">
-        <v>256</v>
-      </c>
       <c r="O98" s="6" t="s">
-        <v>163</v>
+        <v>145</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="Q98" s="5">
-        <v>46072</v>
+        <v>46140</v>
       </c>
       <c r="R98" s="5">
-        <v>46071</v>
-      </c>
-      <c r="S98" s="12" t="s">
-        <v>110</v>
+        <v>46139</v>
+      </c>
+      <c r="S98" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T98" s="6">
-        <v>0</v>
-      </c>
-      <c r="U98" s="11" t="s">
-        <v>32</v>
+        <v>1</v>
+      </c>
+      <c r="U98" s="12" t="s">
+        <v>294</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="B99" s="8">
-        <v>46077.54519734954</v>
+        <v>46077.54520075231</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46182.69256461806</v>
+        <v>46126.83061201389</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>58</v>
+        <v>319</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H99" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I99" s="8">
+        <v>46071</v>
+      </c>
+      <c r="J99" s="8">
+        <v>46072</v>
+      </c>
+      <c r="K99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M99" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N99" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="H99" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="I99" s="8">
-        <v>46125</v>
-      </c>
-      <c r="J99" s="8">
-        <v>46126</v>
-      </c>
-      <c r="K99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M99" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N99" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="O99" s="9" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="Q99" s="8">
-        <v>46126</v>
+        <v>46072</v>
       </c>
       <c r="R99" s="8">
-        <v>46125</v>
+        <v>46071</v>
       </c>
       <c r="S99" s="12" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="T99" s="9">
         <v>0</v>
@@ -7704,59 +7753,59 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="B100" s="5">
-        <v>46077.55796549769</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46128.669900231485</v>
+        <v>46182.69256461806</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>318</v>
+        <v>58</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
+        <v>264</v>
+      </c>
+      <c r="H100" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I100" s="5">
+        <v>46125</v>
+      </c>
+      <c r="J100" s="5">
+        <v>46126</v>
+      </c>
+      <c r="K100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="L100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="M100" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="N100" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="H100" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="I100" s="5">
-        <v>46122</v>
-      </c>
-      <c r="J100" s="5">
+      <c r="O100" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="P100" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="Q100" s="5">
+        <v>46126</v>
+      </c>
+      <c r="R100" s="5">
         <v>46125</v>
       </c>
-      <c r="K100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M100" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N100" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="O100" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="P100" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="Q100" s="5">
-        <v>46125</v>
-      </c>
-      <c r="R100" s="5">
-        <v>46122</v>
-      </c>
       <c r="S100" s="12" t="s">
-        <v>110</v>
+        <v>122</v>
       </c>
       <c r="T100" s="6">
         <v>0</v>
@@ -7767,84 +7816,96 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B101" s="8">
-        <v>46125.79029034722</v>
+        <v>46077.55796549769</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46125.90375237269</v>
+        <v>46191.787866087965</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="H101" s="9" t="s">
+        <v>265</v>
+      </c>
+      <c r="I101" s="8">
+        <v>46122</v>
+      </c>
+      <c r="J101" s="8">
+        <v>46125</v>
+      </c>
+      <c r="K101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M101" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N101" s="9" t="s">
         <v>260</v>
       </c>
-      <c r="H101" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="I101" s="8">
-        <v>46114</v>
-      </c>
-      <c r="J101" s="8">
-        <v>46115</v>
-      </c>
-      <c r="K101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M101" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N101" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="O101" s="9" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>236</v>
+        <v>314</v>
       </c>
       <c r="Q101" s="8">
-        <v>46115</v>
+        <v>46125</v>
       </c>
       <c r="R101" s="8">
-        <v>46114</v>
-      </c>
-      <c r="S101" s="9"/>
-      <c r="T101" s="9"/>
-      <c r="U101" s="9"/>
+        <v>46122</v>
+      </c>
+      <c r="S101" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="T101" s="9">
+        <v>0</v>
+      </c>
+      <c r="U101" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B102" s="5">
-        <v>46077.54519841435</v>
+        <v>46125.79029034722</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46125.905913344905</v>
+        <v>46125.90375237269</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="6"/>
+        <v>264</v>
+      </c>
+      <c r="H102" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="I102" s="5">
+        <v>46114</v>
+      </c>
+      <c r="J102" s="5">
+        <v>46115</v>
+      </c>
       <c r="K102" s="6" t="s">
         <v>26</v>
       </c>
@@ -7852,52 +7913,50 @@
         <v>26</v>
       </c>
       <c r="M102" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>26</v>
+        <v>260</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>323</v>
+        <v>201</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="6"/>
+        <v>240</v>
+      </c>
+      <c r="Q102" s="5">
+        <v>46115</v>
+      </c>
+      <c r="R102" s="5">
+        <v>46114</v>
+      </c>
       <c r="S102" s="6"/>
       <c r="T102" s="6"/>
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B103" s="8">
-        <v>46077.545198761574</v>
+        <v>46077.54519841435</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46150.16889104167</v>
+        <v>46125.905913344905</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F103" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G103" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H103" s="9" t="s">
-        <v>99</v>
-      </c>
-      <c r="I103" s="8">
-        <v>46142</v>
-      </c>
-      <c r="J103" s="8">
-        <v>46150</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H103" s="9"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="9"/>
       <c r="K103" s="9" t="s">
         <v>26</v>
       </c>
@@ -7905,46 +7964,36 @@
         <v>26</v>
       </c>
       <c r="M103" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N103" s="9" t="s">
-        <v>322</v>
+        <v>26</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>236</v>
+        <v>328</v>
       </c>
       <c r="P103" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q103" s="8">
-        <v>46150</v>
-      </c>
-      <c r="R103" s="8">
-        <v>46142</v>
-      </c>
-      <c r="S103" s="12" t="s">
-        <v>110</v>
-      </c>
-      <c r="T103" s="9">
-        <v>0</v>
-      </c>
-      <c r="U103" s="12" t="s">
-        <v>291</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q103" s="9"/>
+      <c r="R103" s="9"/>
+      <c r="S103" s="9"/>
+      <c r="T103" s="9"/>
+      <c r="U103" s="9"/>
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B104" s="5">
-        <v>46125.785526736116</v>
+        <v>46077.545198761574</v>
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46148.169578402776</v>
+        <v>46150.16889104167</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>231</v>
+        <v>330</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -7956,10 +8005,10 @@
         <v>99</v>
       </c>
       <c r="I104" s="5">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="J104" s="5">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="K104" s="6" t="s">
         <v>26</v>
@@ -7971,33 +8020,43 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="O104" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="P104" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="P104" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="Q104" s="6"/>
-      <c r="R104" s="6"/>
-      <c r="S104" s="6"/>
-      <c r="T104" s="6"/>
-      <c r="U104" s="6"/>
+      <c r="Q104" s="5">
+        <v>46150</v>
+      </c>
+      <c r="R104" s="5">
+        <v>46142</v>
+      </c>
+      <c r="S104" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="T104" s="6">
+        <v>0</v>
+      </c>
+      <c r="U104" s="12" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.7863228125</v>
+        <v>46125.785526736116</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46148.169549467595</v>
+        <v>46148.169578402776</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
@@ -8024,13 +8083,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8040,17 +8099,17 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B106" s="5">
-        <v>46077.558327129635</v>
+        <v>46125.7863228125</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46154.167828125</v>
+        <v>46148.169549467595</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>333</v>
+        <v>237</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8062,10 +8121,10 @@
         <v>99</v>
       </c>
       <c r="I106" s="5">
-        <v>46153</v>
+        <v>46140</v>
       </c>
       <c r="J106" s="5">
-        <v>46154</v>
+        <v>46148</v>
       </c>
       <c r="K106" s="6" t="s">
         <v>26</v>
@@ -8077,43 +8136,33 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>236</v>
+        <v>335</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q106" s="5">
-        <v>46154</v>
-      </c>
-      <c r="R106" s="5">
-        <v>46153</v>
-      </c>
-      <c r="S106" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T106" s="6">
-        <v>0</v>
-      </c>
-      <c r="U106" s="12" t="s">
-        <v>291</v>
-      </c>
+        <v>336</v>
+      </c>
+      <c r="Q106" s="6"/>
+      <c r="R106" s="6"/>
+      <c r="S106" s="6"/>
+      <c r="T106" s="6"/>
+      <c r="U106" s="6"/>
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46125.793145185184</v>
+        <v>46077.558327129635</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46154.16895842593</v>
+        <v>46154.167828125</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>231</v>
+        <v>338</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8140,33 +8189,43 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>335</v>
+        <v>240</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>336</v>
-      </c>
-      <c r="Q107" s="9"/>
-      <c r="R107" s="9"/>
-      <c r="S107" s="9"/>
-      <c r="T107" s="9"/>
-      <c r="U107" s="9"/>
+        <v>327</v>
+      </c>
+      <c r="Q107" s="8">
+        <v>46154</v>
+      </c>
+      <c r="R107" s="8">
+        <v>46153</v>
+      </c>
+      <c r="S107" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T107" s="9">
+        <v>0</v>
+      </c>
+      <c r="U107" s="12" t="s">
+        <v>294</v>
+      </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.79326523148</v>
+        <v>46125.793145185184</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46154.168959930554</v>
+        <v>46154.16895842593</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
@@ -8193,13 +8252,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8209,17 +8268,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46077.5451994676</v>
+        <v>46125.79326523148</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46156.167735462965</v>
+        <v>46154.168959930554</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>341</v>
+        <v>237</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8231,10 +8290,10 @@
         <v>99</v>
       </c>
       <c r="I109" s="8">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="J109" s="8">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="K109" s="9" t="s">
         <v>26</v>
@@ -8246,43 +8305,33 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>236</v>
+        <v>343</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q109" s="8">
-        <v>46126</v>
-      </c>
-      <c r="R109" s="8">
-        <v>46155</v>
-      </c>
-      <c r="S109" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T109" s="9">
-        <v>0</v>
-      </c>
-      <c r="U109" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="Q109" s="9"/>
+      <c r="R109" s="9"/>
+      <c r="S109" s="9"/>
+      <c r="T109" s="9"/>
+      <c r="U109" s="9"/>
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46125.793417939814</v>
+        <v>46077.5451994676</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46156.16888442129</v>
+        <v>46156.167735462965</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>231</v>
+        <v>346</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8309,33 +8358,43 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>341</v>
+        <v>327</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>343</v>
+        <v>240</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>344</v>
-      </c>
-      <c r="Q110" s="6"/>
-      <c r="R110" s="6"/>
-      <c r="S110" s="6"/>
-      <c r="T110" s="6"/>
-      <c r="U110" s="6"/>
+        <v>327</v>
+      </c>
+      <c r="Q110" s="5">
+        <v>46126</v>
+      </c>
+      <c r="R110" s="5">
+        <v>46155</v>
+      </c>
+      <c r="S110" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T110" s="6">
+        <v>0</v>
+      </c>
+      <c r="U110" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.793529525465</v>
+        <v>46125.793417939814</v>
       </c>
       <c r="C111" s="9"/>
       <c r="D111" s="8">
-        <v>46156.16888607639</v>
+        <v>46191.786593055556</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
@@ -8362,13 +8421,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8378,17 +8437,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B112" s="5">
-        <v>46077.54519980324</v>
+        <v>46125.793529525465</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46161.196075115746</v>
+        <v>46191.78659372685</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>349</v>
+        <v>237</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8400,10 +8459,10 @@
         <v>99</v>
       </c>
       <c r="I112" s="5">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="J112" s="5">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="K112" s="6" t="s">
         <v>26</v>
@@ -8415,43 +8474,33 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>322</v>
+        <v>346</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>236</v>
+        <v>351</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q112" s="5">
-        <v>46160</v>
-      </c>
-      <c r="R112" s="5">
-        <v>46157</v>
-      </c>
-      <c r="S112" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T112" s="6">
-        <v>0</v>
-      </c>
-      <c r="U112" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>352</v>
+      </c>
+      <c r="Q112" s="6"/>
+      <c r="R112" s="6"/>
+      <c r="S112" s="6"/>
+      <c r="T112" s="6"/>
+      <c r="U112" s="6"/>
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B113" s="8">
-        <v>46125.79363706018</v>
+        <v>46077.54519980324</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46160.16927990741</v>
+        <v>46191.78814039352</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>231</v>
+        <v>354</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8478,33 +8527,45 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>351</v>
+        <v>240</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="Q113" s="9"/>
-      <c r="R113" s="9"/>
-      <c r="S113" s="9"/>
-      <c r="T113" s="9"/>
-      <c r="U113" s="9"/>
+        <v>327</v>
+      </c>
+      <c r="Q113" s="8">
+        <v>46160</v>
+      </c>
+      <c r="R113" s="8">
+        <v>46157</v>
+      </c>
+      <c r="S113" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T113" s="9">
+        <v>0</v>
+      </c>
+      <c r="U113" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.79376541667</v>
-      </c>
-      <c r="C114" s="6"/>
+        <v>46125.79363706018</v>
+      </c>
+      <c r="C114" s="5">
+        <v>46191.78813390047</v>
+      </c>
       <c r="D114" s="5">
-        <v>46160.16928184028</v>
+        <v>46191.78813570602</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
@@ -8531,13 +8592,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8547,17 +8608,17 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B115" s="8">
-        <v>46077.54519909722</v>
+        <v>46125.79376541667</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46163.1705024074</v>
+        <v>46191.78890746528</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>357</v>
+        <v>237</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8569,10 +8630,10 @@
         <v>99</v>
       </c>
       <c r="I115" s="8">
-        <v>46161</v>
+        <v>46157</v>
       </c>
       <c r="J115" s="8">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="K115" s="9" t="s">
         <v>26</v>
@@ -8584,43 +8645,33 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>322</v>
+        <v>354</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>236</v>
+        <v>359</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q115" s="8">
-        <v>46162</v>
-      </c>
-      <c r="R115" s="8">
-        <v>46161</v>
-      </c>
-      <c r="S115" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T115" s="9">
-        <v>0</v>
-      </c>
-      <c r="U115" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>360</v>
+      </c>
+      <c r="Q115" s="9"/>
+      <c r="R115" s="9"/>
+      <c r="S115" s="9"/>
+      <c r="T115" s="9"/>
+      <c r="U115" s="9"/>
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="B116" s="5">
-        <v>46125.79408877315</v>
+        <v>46077.54519909722</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46162.16902994213</v>
+        <v>46163.1705024074</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>231</v>
+        <v>362</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8647,33 +8698,43 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>359</v>
+        <v>240</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>360</v>
-      </c>
-      <c r="Q116" s="6"/>
-      <c r="R116" s="6"/>
-      <c r="S116" s="6"/>
-      <c r="T116" s="6"/>
-      <c r="U116" s="6"/>
+        <v>327</v>
+      </c>
+      <c r="Q116" s="5">
+        <v>46162</v>
+      </c>
+      <c r="R116" s="5">
+        <v>46161</v>
+      </c>
+      <c r="S116" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T116" s="6">
+        <v>0</v>
+      </c>
+      <c r="U116" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.79422275463</v>
+        <v>46125.79408877315</v>
       </c>
       <c r="C117" s="9"/>
       <c r="D117" s="8">
-        <v>46162.169031412035</v>
+        <v>46191.78814143519</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
@@ -8700,13 +8761,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8716,17 +8777,17 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B118" s="5">
-        <v>46077.545200127315</v>
+        <v>46125.79422275463</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46165.197340150466</v>
+        <v>46191.786412430556</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>365</v>
+        <v>237</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8738,10 +8799,10 @@
         <v>99</v>
       </c>
       <c r="I118" s="5">
-        <v>46164</v>
+        <v>46161</v>
       </c>
       <c r="J118" s="5">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="K118" s="6" t="s">
         <v>26</v>
@@ -8753,43 +8814,33 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>322</v>
+        <v>362</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>236</v>
+        <v>367</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q118" s="5">
-        <v>46164</v>
-      </c>
-      <c r="R118" s="5">
-        <v>46164</v>
-      </c>
-      <c r="S118" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T118" s="6">
-        <v>0</v>
-      </c>
-      <c r="U118" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="Q118" s="6"/>
+      <c r="R118" s="6"/>
+      <c r="S118" s="6"/>
+      <c r="T118" s="6"/>
+      <c r="U118" s="6"/>
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B119" s="8">
-        <v>46125.79434175926</v>
+        <v>46077.545200127315</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46164.16914866898</v>
+        <v>46165.197340150466</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>231</v>
+        <v>370</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8800,7 +8851,9 @@
       <c r="H119" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="I119" s="9"/>
+      <c r="I119" s="8">
+        <v>46164</v>
+      </c>
       <c r="J119" s="8">
         <v>46164</v>
       </c>
@@ -8814,33 +8867,43 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>365</v>
+        <v>327</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>367</v>
-      </c>
-      <c r="Q119" s="9"/>
-      <c r="R119" s="9"/>
-      <c r="S119" s="9"/>
-      <c r="T119" s="9"/>
-      <c r="U119" s="9"/>
+        <v>327</v>
+      </c>
+      <c r="Q119" s="8">
+        <v>46164</v>
+      </c>
+      <c r="R119" s="8">
+        <v>46164</v>
+      </c>
+      <c r="S119" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T119" s="9">
+        <v>0</v>
+      </c>
+      <c r="U119" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.79446019676</v>
+        <v>46125.79434175926</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.16915030092</v>
+        <v>46164.16914866898</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
@@ -8865,13 +8928,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8881,17 +8944,17 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B121" s="8">
-        <v>46077.54520043981</v>
+        <v>46125.79446019676</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46169.19579744213</v>
+        <v>46164.16915030092</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>371</v>
+        <v>237</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -8902,11 +8965,9 @@
       <c r="H121" s="9" t="s">
         <v>99</v>
       </c>
-      <c r="I121" s="8">
-        <v>46168</v>
-      </c>
+      <c r="I121" s="9"/>
       <c r="J121" s="8">
-        <v>46168</v>
+        <v>46164</v>
       </c>
       <c r="K121" s="9" t="s">
         <v>26</v>
@@ -8918,43 +8979,33 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>322</v>
+        <v>370</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>322</v>
-      </c>
-      <c r="Q121" s="8">
-        <v>46168</v>
-      </c>
-      <c r="R121" s="8">
-        <v>46168</v>
-      </c>
-      <c r="S121" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T121" s="9">
-        <v>0</v>
-      </c>
-      <c r="U121" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>374</v>
+      </c>
+      <c r="Q121" s="9"/>
+      <c r="R121" s="9"/>
+      <c r="S121" s="9"/>
+      <c r="T121" s="9"/>
+      <c r="U121" s="9"/>
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B122" s="5">
-        <v>46125.794598078704</v>
+        <v>46077.54520043981</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46168.16876332176</v>
+        <v>46169.19579744213</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>231</v>
+        <v>376</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -8965,7 +9016,9 @@
       <c r="H122" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="I122" s="6"/>
+      <c r="I122" s="5">
+        <v>46168</v>
+      </c>
       <c r="J122" s="5">
         <v>46168</v>
       </c>
@@ -8979,33 +9032,43 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>371</v>
+        <v>327</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="Q122" s="6"/>
-      <c r="R122" s="6"/>
-      <c r="S122" s="6"/>
-      <c r="T122" s="6"/>
-      <c r="U122" s="6"/>
+        <v>327</v>
+      </c>
+      <c r="Q122" s="5">
+        <v>46168</v>
+      </c>
+      <c r="R122" s="5">
+        <v>46168</v>
+      </c>
+      <c r="S122" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T122" s="6">
+        <v>0</v>
+      </c>
+      <c r="U122" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.794723252315</v>
+        <v>46125.794598078704</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.168764710645</v>
+        <v>46168.16876332176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
@@ -9030,13 +9093,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9046,27 +9109,31 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B124" s="5">
-        <v>46077.54519771991</v>
+        <v>46125.794723252315</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46125.907215011575</v>
+        <v>46168.168764710645</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>377</v>
+        <v>237</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H124" s="6"/>
+        <v>99</v>
+      </c>
+      <c r="H124" s="6" t="s">
+        <v>99</v>
+      </c>
       <c r="I124" s="6"/>
-      <c r="J124" s="6"/>
+      <c r="J124" s="5">
+        <v>46168</v>
+      </c>
       <c r="K124" s="6" t="s">
         <v>26</v>
       </c>
@@ -9074,16 +9141,16 @@
         <v>26</v>
       </c>
       <c r="M124" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>26</v>
+        <v>376</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>26</v>
+        <v>380</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9093,33 +9160,27 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.5451981713</v>
+        <v>46077.54519771991</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46170.199522905095</v>
+        <v>46125.907215011575</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F125" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="H125" s="9" t="s">
-        <v>382</v>
-      </c>
-      <c r="I125" s="8">
-        <v>46169</v>
-      </c>
-      <c r="J125" s="8">
-        <v>46169</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H125" s="9"/>
+      <c r="I125" s="9"/>
+      <c r="J125" s="9"/>
       <c r="K125" s="9" t="s">
         <v>26</v>
       </c>
@@ -9127,57 +9188,49 @@
         <v>26</v>
       </c>
       <c r="M125" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N125" s="9" t="s">
-        <v>377</v>
+        <v>26</v>
       </c>
       <c r="O125" s="9" t="s">
         <v>383</v>
       </c>
       <c r="P125" s="9" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q125" s="8">
-        <v>46169</v>
-      </c>
-      <c r="R125" s="8">
-        <v>46169</v>
-      </c>
-      <c r="S125" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T125" s="9">
-        <v>0</v>
-      </c>
-      <c r="U125" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q125" s="9"/>
+      <c r="R125" s="9"/>
+      <c r="S125" s="9"/>
+      <c r="T125" s="9"/>
+      <c r="U125" s="9"/>
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
         <v>384</v>
       </c>
       <c r="B126" s="5">
-        <v>46125.81236390046</v>
+        <v>46077.5451981713</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46169.16854510417</v>
+        <v>46170.199522905095</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>231</v>
+        <v>385</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="I126" s="6"/>
+        <v>387</v>
+      </c>
+      <c r="I126" s="5">
+        <v>46169</v>
+      </c>
       <c r="J126" s="5">
         <v>46169</v>
       </c>
@@ -9191,42 +9244,52 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>231</v>
+        <v>388</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>385</v>
-      </c>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="6"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
+        <v>382</v>
+      </c>
+      <c r="Q126" s="5">
+        <v>46169</v>
+      </c>
+      <c r="R126" s="5">
+        <v>46169</v>
+      </c>
+      <c r="S126" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0</v>
+      </c>
+      <c r="U126" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.81252253472</v>
+        <v>46125.81236390046</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46169.168546712965</v>
+        <v>46169.16854510417</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -9242,13 +9305,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9258,26 +9321,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.812747199074</v>
+        <v>46125.81252253472</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46169.16854806713</v>
+        <v>46169.168546712965</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -9293,13 +9356,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9309,26 +9372,26 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B129" s="8">
-        <v>46125.81326880787</v>
+        <v>46125.812747199074</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.16854940972</v>
+        <v>46169.16854806713</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>61</v>
+        <v>394</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9344,13 +9407,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9360,26 +9423,26 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.81384030092</v>
+        <v>46125.81326880787</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.168550682865</v>
+        <v>46169.16854940972</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9395,13 +9458,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9411,26 +9474,26 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.81410221064</v>
+        <v>46125.81384030092</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46169.16855229167</v>
+        <v>46169.168550682865</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9446,13 +9509,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9462,32 +9525,30 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="B132" s="5">
-        <v>46077.5451984838</v>
+        <v>46125.81410221064</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46175.20232467593</v>
+        <v>46169.16855229167</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>398</v>
+        <v>67</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>99</v>
+        <v>386</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>99</v>
-      </c>
-      <c r="I132" s="5">
-        <v>46170</v>
-      </c>
+        <v>387</v>
+      </c>
+      <c r="I132" s="6"/>
       <c r="J132" s="5">
-        <v>46174</v>
+        <v>46169</v>
       </c>
       <c r="K132" s="6" t="s">
         <v>26</v>
@@ -9499,43 +9560,33 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>399</v>
+        <v>67</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="Q132" s="5">
-        <v>46174</v>
-      </c>
-      <c r="R132" s="5">
-        <v>46170</v>
-      </c>
-      <c r="S132" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T132" s="6">
-        <v>0</v>
-      </c>
-      <c r="U132" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>401</v>
+      </c>
+      <c r="Q132" s="6"/>
+      <c r="R132" s="6"/>
+      <c r="S132" s="6"/>
+      <c r="T132" s="6"/>
+      <c r="U132" s="6"/>
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B133" s="8">
-        <v>46125.81482075232</v>
+        <v>46077.5451984838</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46174.16943333333</v>
+        <v>46175.20232467593</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>231</v>
+        <v>403</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9562,33 +9613,43 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>398</v>
+        <v>382</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>231</v>
+        <v>404</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="Q133" s="9"/>
-      <c r="R133" s="9"/>
-      <c r="S133" s="9"/>
-      <c r="T133" s="9"/>
-      <c r="U133" s="9"/>
+        <v>382</v>
+      </c>
+      <c r="Q133" s="8">
+        <v>46174</v>
+      </c>
+      <c r="R133" s="8">
+        <v>46170</v>
+      </c>
+      <c r="S133" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T133" s="9">
+        <v>0</v>
+      </c>
+      <c r="U133" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.81494678241</v>
+        <v>46125.81482075232</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46174.16943504629</v>
+        <v>46174.16943333333</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
@@ -9615,13 +9676,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9631,17 +9692,17 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.81516034722</v>
+        <v>46125.81494678241</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46174.169436400465</v>
+        <v>46174.16943504629</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9668,13 +9729,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9684,17 +9745,17 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.81531077546</v>
+        <v>46125.81516034722</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46174.169437847224</v>
+        <v>46174.169436400465</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>61</v>
+        <v>394</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9721,13 +9782,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>61</v>
+        <v>394</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9737,17 +9798,17 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.81545193287</v>
+        <v>46125.81531077546</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46174.16943927083</v>
+        <v>46174.169437847224</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
@@ -9774,13 +9835,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9790,17 +9851,17 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.81557276621</v>
+        <v>46125.81545193287</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46174.16944046297</v>
+        <v>46174.16943927083</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>411</v>
+        <v>64</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
@@ -9827,13 +9888,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9843,32 +9904,32 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B139" s="8">
-        <v>46077.54519895834</v>
+        <v>46125.81557276621</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46176.19592085648</v>
+        <v>46174.16944046297</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>285</v>
+        <v>99</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>286</v>
+        <v>99</v>
       </c>
       <c r="I139" s="8">
-        <v>46175</v>
+        <v>46170</v>
       </c>
       <c r="J139" s="8">
-        <v>46175</v>
+        <v>46174</v>
       </c>
       <c r="K139" s="9" t="s">
         <v>26</v>
@@ -9880,54 +9941,46 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>415</v>
+        <v>67</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>416</v>
-      </c>
-      <c r="Q139" s="8">
-        <v>46175</v>
-      </c>
-      <c r="R139" s="8">
-        <v>46175</v>
-      </c>
-      <c r="S139" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T139" s="9">
-        <v>0</v>
-      </c>
-      <c r="U139" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>417</v>
+      </c>
+      <c r="Q139" s="9"/>
+      <c r="R139" s="9"/>
+      <c r="S139" s="9"/>
+      <c r="T139" s="9"/>
+      <c r="U139" s="9"/>
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B140" s="5">
-        <v>46125.815781006946</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46175.16831246528</v>
+        <v>46176.19592085648</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>231</v>
+        <v>419</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="I140" s="6"/>
+        <v>288</v>
+      </c>
+      <c r="I140" s="5">
+        <v>46175</v>
+      </c>
       <c r="J140" s="5">
         <v>46175</v>
       </c>
@@ -9941,42 +9994,52 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>414</v>
+        <v>382</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>231</v>
+        <v>420</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>418</v>
-      </c>
-      <c r="Q140" s="6"/>
-      <c r="R140" s="6"/>
-      <c r="S140" s="6"/>
-      <c r="T140" s="6"/>
-      <c r="U140" s="6"/>
+        <v>421</v>
+      </c>
+      <c r="Q140" s="5">
+        <v>46175</v>
+      </c>
+      <c r="R140" s="5">
+        <v>46175</v>
+      </c>
+      <c r="S140" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T140" s="6">
+        <v>0</v>
+      </c>
+      <c r="U140" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.81592018518</v>
+        <v>46125.815781006946</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46175.168314062495</v>
+        <v>46175.16831246528</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -9992,13 +10055,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10008,26 +10071,26 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.81606405093</v>
+        <v>46125.81592018518</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46175.16831547454</v>
+        <v>46175.168314062495</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10043,13 +10106,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10059,26 +10122,26 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.81619271991</v>
+        <v>46125.81606405093</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46175.16831677083</v>
+        <v>46175.16831547454</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10094,13 +10157,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>61</v>
+        <v>394</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10110,26 +10173,26 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.81632106482</v>
+        <v>46125.81619271991</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46175.16831813657</v>
+        <v>46175.16831677083</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10145,13 +10208,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10161,26 +10224,26 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.816468668985</v>
+        <v>46125.81632106482</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46175.16831954861</v>
+        <v>46175.16831813657</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>411</v>
+        <v>64</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -10196,13 +10259,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>411</v>
+        <v>64</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10212,32 +10275,30 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="B146" s="5">
-        <v>46077.54519927083</v>
+        <v>46125.816468668985</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46177.189300150465</v>
+        <v>46175.16831954861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="I146" s="5">
-        <v>46176</v>
-      </c>
+        <v>288</v>
+      </c>
+      <c r="I146" s="6"/>
       <c r="J146" s="5">
-        <v>46176</v>
+        <v>46175</v>
       </c>
       <c r="K146" s="6" t="s">
         <v>26</v>
@@ -10249,54 +10310,46 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>377</v>
+        <v>419</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>431</v>
+        <v>416</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>432</v>
-      </c>
-      <c r="Q146" s="5">
-        <v>46176</v>
-      </c>
-      <c r="R146" s="5">
-        <v>46176</v>
-      </c>
-      <c r="S146" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T146" s="6">
-        <v>0</v>
-      </c>
-      <c r="U146" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>433</v>
+      </c>
+      <c r="Q146" s="6"/>
+      <c r="R146" s="6"/>
+      <c r="S146" s="6"/>
+      <c r="T146" s="6"/>
+      <c r="U146" s="6"/>
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B147" s="8">
-        <v>46125.81660767361</v>
+        <v>46077.54519927083</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46176.1683697338</v>
+        <v>46177.189300150465</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>231</v>
+        <v>435</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>286</v>
-      </c>
-      <c r="I147" s="9"/>
+        <v>288</v>
+      </c>
+      <c r="I147" s="8">
+        <v>46176</v>
+      </c>
       <c r="J147" s="8">
         <v>46176</v>
       </c>
@@ -10310,42 +10363,52 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>430</v>
+        <v>382</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>231</v>
+        <v>436</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>430</v>
-      </c>
-      <c r="Q147" s="9"/>
-      <c r="R147" s="9"/>
-      <c r="S147" s="9"/>
-      <c r="T147" s="9"/>
-      <c r="U147" s="9"/>
+        <v>437</v>
+      </c>
+      <c r="Q147" s="8">
+        <v>46176</v>
+      </c>
+      <c r="R147" s="8">
+        <v>46176</v>
+      </c>
+      <c r="S147" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T147" s="9">
+        <v>0</v>
+      </c>
+      <c r="U147" s="11" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.81673583333</v>
+        <v>46125.81660767361</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46176.16837118055</v>
+        <v>46176.1683697338</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10361,13 +10424,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10377,26 +10440,26 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.81686799768</v>
+        <v>46125.81673583333</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46176.16837233797</v>
+        <v>46176.16837118055</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>389</v>
+        <v>237</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10412,13 +10475,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>57</v>
+        <v>237</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10428,26 +10491,26 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.81698454861</v>
+        <v>46125.81686799768</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46176.16837344907</v>
+        <v>46176.16837233797</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>61</v>
+        <v>394</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10463,13 +10526,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10479,26 +10542,26 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.81713481482</v>
+        <v>46125.81698454861</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46176.1683746412</v>
+        <v>46176.16837344907</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10514,13 +10577,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10530,26 +10593,26 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.8172621875</v>
+        <v>46125.81713481482</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46176.16837584491</v>
+        <v>46176.1683746412</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>411</v>
+        <v>64</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10565,13 +10628,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>411</v>
+        <v>64</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10581,27 +10644,31 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="B153" s="8">
-        <v>46077.54519966435</v>
+        <v>46125.8172621875</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46125.90721503472</v>
+        <v>46176.16837584491</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>440</v>
+        <v>416</v>
       </c>
       <c r="F153" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H153" s="9"/>
+        <v>287</v>
+      </c>
+      <c r="H153" s="9" t="s">
+        <v>288</v>
+      </c>
       <c r="I153" s="9"/>
-      <c r="J153" s="9"/>
+      <c r="J153" s="8">
+        <v>46176</v>
+      </c>
       <c r="K153" s="9" t="s">
         <v>26</v>
       </c>
@@ -10609,16 +10676,16 @@
         <v>26</v>
       </c>
       <c r="M153" s="9" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>26</v>
+        <v>435</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>441</v>
+        <v>416</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>26</v>
+        <v>435</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10628,33 +10695,27 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B154" s="5">
-        <v>46077.54519996527</v>
+        <v>46077.54519966435</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46186.20134465278</v>
+        <v>46125.90721503472</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G154" s="6" t="s">
-        <v>444</v>
-      </c>
-      <c r="H154" s="6" t="s">
-        <v>445</v>
-      </c>
-      <c r="I154" s="5">
-        <v>46177</v>
-      </c>
-      <c r="J154" s="5">
-        <v>46185</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H154" s="6"/>
+      <c r="I154" s="6"/>
+      <c r="J154" s="6"/>
       <c r="K154" s="6" t="s">
         <v>26</v>
       </c>
@@ -10662,55 +10723,45 @@
         <v>26</v>
       </c>
       <c r="M154" s="6" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N154" s="6" t="s">
-        <v>440</v>
+        <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>430</v>
+        <v>446</v>
       </c>
       <c r="P154" s="6" t="s">
-        <v>440</v>
-      </c>
-      <c r="Q154" s="5">
-        <v>46185</v>
-      </c>
-      <c r="R154" s="5">
-        <v>46177</v>
-      </c>
-      <c r="S154" s="11" t="s">
-        <v>55</v>
-      </c>
-      <c r="T154" s="6">
-        <v>0</v>
-      </c>
-      <c r="U154" s="11" t="s">
-        <v>32</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q154" s="6"/>
+      <c r="R154" s="6"/>
+      <c r="S154" s="6"/>
+      <c r="T154" s="6"/>
+      <c r="U154" s="6"/>
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.545200277775</v>
+        <v>46077.54519996527</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46186.201344699075</v>
+        <v>46186.20134465278</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="I155" s="8">
         <v>46177</v>
@@ -10728,13 +10779,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="Q155" s="8">
         <v>46185</v>
@@ -10754,27 +10805,33 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B156" s="5">
-        <v>46090.70994861111</v>
+        <v>46077.545200277775</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46125.907787916665</v>
+        <v>46186.201344699075</v>
       </c>
       <c r="E156" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>449</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="F156" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H156" s="6"/>
-      <c r="I156" s="6"/>
-      <c r="J156" s="6"/>
+      <c r="I156" s="5">
+        <v>46177</v>
+      </c>
+      <c r="J156" s="5">
+        <v>46185</v>
+      </c>
       <c r="K156" s="6" t="s">
         <v>26</v>
       </c>
@@ -10782,58 +10839,56 @@
         <v>26</v>
       </c>
       <c r="M156" s="6" t="s">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>26</v>
+        <v>445</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q156" s="6"/>
-      <c r="R156" s="6"/>
+        <v>445</v>
+      </c>
+      <c r="Q156" s="5">
+        <v>46185</v>
+      </c>
+      <c r="R156" s="5">
+        <v>46177</v>
+      </c>
       <c r="S156" s="11" t="s">
         <v>55</v>
       </c>
       <c r="T156" s="6">
         <v>0</v>
       </c>
-      <c r="U156" s="10" t="s">
-        <v>128</v>
+      <c r="U156" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="B157" s="8">
-        <v>46090.71005349537</v>
+        <v>46090.70994861111</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46185.197705416664</v>
+        <v>46125.907787916665</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="F157" s="9" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G157" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="H157" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="I157" s="8">
-        <v>46176</v>
-      </c>
-      <c r="J157" s="8">
-        <v>46184</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="H157" s="9"/>
+      <c r="I157" s="9"/>
+      <c r="J157" s="9"/>
       <c r="K157" s="9" t="s">
         <v>26</v>
       </c>
@@ -10841,46 +10896,42 @@
         <v>26</v>
       </c>
       <c r="M157" s="9" t="s">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="N157" s="9" t="s">
-        <v>450</v>
+        <v>26</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>430</v>
+        <v>456</v>
       </c>
       <c r="P157" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="Q157" s="8">
-        <v>46184</v>
-      </c>
-      <c r="R157" s="8">
-        <v>46176</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="Q157" s="9"/>
+      <c r="R157" s="9"/>
       <c r="S157" s="11" t="s">
         <v>55</v>
       </c>
       <c r="T157" s="9">
         <v>0</v>
       </c>
-      <c r="U157" s="11" t="s">
-        <v>32</v>
+      <c r="U157" s="10" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.70960611111</v>
+        <v>46090.71005349537</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46188.18224864583</v>
+        <v>46185.197705416664</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10892,10 +10943,10 @@
         <v>50</v>
       </c>
       <c r="I158" s="5">
-        <v>46185</v>
+        <v>46176</v>
       </c>
       <c r="J158" s="5">
-        <v>46195</v>
+        <v>46184</v>
       </c>
       <c r="K158" s="6" t="s">
         <v>26</v>
@@ -10907,19 +10958,19 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>453</v>
+        <v>435</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="Q158" s="5">
-        <v>46195</v>
+        <v>46184</v>
       </c>
       <c r="R158" s="5">
-        <v>46185</v>
+        <v>46176</v>
       </c>
       <c r="S158" s="11" t="s">
         <v>55</v>
@@ -10927,8 +10978,71 @@
       <c r="T158" s="6">
         <v>0</v>
       </c>
-      <c r="U158" s="12" t="s">
-        <v>291</v>
+      <c r="U158" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A159" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="B159" s="8">
+        <v>46090.70960611111</v>
+      </c>
+      <c r="C159" s="9"/>
+      <c r="D159" s="8">
+        <v>46188.18224864583</v>
+      </c>
+      <c r="E159" s="9" t="s">
+        <v>461</v>
+      </c>
+      <c r="F159" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G159" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="H159" s="9" t="s">
+        <v>50</v>
+      </c>
+      <c r="I159" s="8">
+        <v>46185</v>
+      </c>
+      <c r="J159" s="8">
+        <v>46195</v>
+      </c>
+      <c r="K159" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="L159" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="M159" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="N159" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="O159" s="9" t="s">
+        <v>458</v>
+      </c>
+      <c r="P159" s="9" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q159" s="8">
+        <v>46195</v>
+      </c>
+      <c r="R159" s="8">
+        <v>46185</v>
+      </c>
+      <c r="S159" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="T159" s="9">
+        <v>0</v>
+      </c>
+      <c r="U159" s="12" t="s">
+        <v>294</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -7823,7 +7823,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46191.787866087965</v>
+        <v>46192.79300131944</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>323</v>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46191.78890746528</v>
+        <v>46192.79081532407</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>237</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -7351,7 +7351,7 @@
         <v>46191.77043608796</v>
       </c>
       <c r="D93" s="8">
-        <v>46191.77044953704</v>
+        <v>46193.954018240736</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>303</v>
@@ -7395,8 +7395,8 @@
       <c r="R93" s="8">
         <v>46140</v>
       </c>
-      <c r="S93" s="10" t="s">
-        <v>31</v>
+      <c r="S93" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="T93" s="9">
         <v>1</v>
@@ -7412,9 +7412,11 @@
       <c r="B94" s="5">
         <v>46125.7814462963</v>
       </c>
-      <c r="C94" s="6"/>
+      <c r="C94" s="5">
+        <v>46193.953992442126</v>
+      </c>
       <c r="D94" s="5">
-        <v>46191.768744236106</v>
+        <v>46193.953995034724</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>296</v>
@@ -7465,9 +7467,11 @@
       <c r="B95" s="8">
         <v>46125.78158427084</v>
       </c>
-      <c r="C95" s="9"/>
+      <c r="C95" s="8">
+        <v>46193.95400423611</v>
+      </c>
       <c r="D95" s="8">
-        <v>46191.768768229165</v>
+        <v>46193.9540056713</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>300</v>
@@ -8053,7 +8057,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46148.169578402776</v>
+        <v>46193.95399858797</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>235</v>
@@ -8106,7 +8110,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46148.169549467595</v>
+        <v>46193.954008518514</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>237</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -714,7 +714,7 @@
     <t>hgutierrez@zitron.com</t>
   </si>
   <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4</t>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214046914974309</t>
@@ -5898,7 +5898,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46195.535889039355</v>
+        <v>46195.580413449075</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -7965,7 +7965,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46125.905913344905</v>
+        <v>46195.86928554398</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>327</v>
@@ -8010,9 +8010,11 @@
       <c r="B104" s="5">
         <v>46077.545198761574</v>
       </c>
-      <c r="C104" s="6"/>
+      <c r="C104" s="5">
+        <v>46195.86927984953</v>
+      </c>
       <c r="D104" s="5">
-        <v>46150.16889104167</v>
+        <v>46195.86929523148</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>330</v>
@@ -8056,11 +8058,11 @@
       <c r="R104" s="5">
         <v>46142</v>
       </c>
-      <c r="S104" s="12" t="s">
-        <v>122</v>
+      <c r="S104" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T104" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U104" s="12" t="s">
         <v>294</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5195,7 +5195,7 @@
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.689754340274</v>
+        <v>46195.914978217595</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -11015,7 +11015,7 @@
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46195.16796179398</v>
+        <v>46196.17368006945</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>461</v>
@@ -11065,8 +11065,8 @@
       <c r="T159" s="9">
         <v>0</v>
       </c>
-      <c r="U159" s="12" t="s">
-        <v>294</v>
+      <c r="U159" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5916,7 +5916,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46195.580413449075</v>
+        <v>46196.769709699074</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -8352,7 +8352,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46156.167735462965</v>
+        <v>46197.504649062495</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>346</v>
@@ -8413,9 +8413,11 @@
       <c r="B111" s="8">
         <v>46125.793417939814</v>
       </c>
-      <c r="C111" s="9"/>
+      <c r="C111" s="8">
+        <v>46197.50464319444</v>
+      </c>
       <c r="D111" s="8">
-        <v>46191.786593055556</v>
+        <v>46197.504645196765</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>235</v>
@@ -8586,7 +8588,7 @@
         <v>46191.78813390047</v>
       </c>
       <c r="D114" s="5">
-        <v>46191.78813570602</v>
+        <v>46197.50464966435</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>235</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -8694,7 +8694,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46163.1705024074</v>
+        <v>46197.59958541667</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>362</v>
@@ -8755,9 +8755,11 @@
       <c r="B117" s="8">
         <v>46125.79408877315</v>
       </c>
-      <c r="C117" s="9"/>
+      <c r="C117" s="8">
+        <v>46197.599578124995</v>
+      </c>
       <c r="D117" s="8">
-        <v>46191.78814143519</v>
+        <v>46197.59958061343</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>235</v>
@@ -8926,7 +8928,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46164.16914866898</v>
+        <v>46197.59958675926</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>235</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -2024,13 +2024,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.54519802083</v>
+        <v>46077.37853135417</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.721198263884</v>
+        <v>46092.55453159723</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.60918222222</v>
+        <v>46112.44251555555</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2073,13 +2073,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.54519871528</v>
+        <v>46077.378532048606</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72116893518</v>
+        <v>46092.55450226852</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.721199837964</v>
+        <v>46092.55453317129</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2138,13 +2138,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.54519913194</v>
+        <v>46077.37853246528</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.721169502314</v>
+        <v>46092.55450283564</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64751465278</v>
+        <v>46134.48084798611</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2203,13 +2203,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.54519949074</v>
+        <v>46077.37853282408</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.7211699537</v>
+        <v>46092.554503287036</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.647555393516</v>
+        <v>46134.48088872685</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2268,13 +2268,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.54519986111</v>
+        <v>46077.378533194445</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.721170439814</v>
+        <v>46092.55450377315</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64759444444</v>
+        <v>46134.48092777778</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2333,13 +2333,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.545200196764</v>
+        <v>46077.37853353009</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72117107639</v>
+        <v>46092.55450440972</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64762820602</v>
+        <v>46134.48096153935</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2398,11 +2398,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.545200532404</v>
+        <v>46077.37853386574</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.50634554398</v>
+        <v>46114.33967887731</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2445,13 +2445,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.5452008912</v>
+        <v>46077.37853422454</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.5063353588</v>
+        <v>46114.33966869213</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.506357245366</v>
+        <v>46114.33969057871</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2510,11 +2510,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.54520121528</v>
+        <v>46077.37853454861</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46135.19105782408</v>
+        <v>46135.02439115741</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2573,11 +2573,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46125.8197722801</v>
+        <v>46125.653105613426</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46133.17089466435</v>
+        <v>46133.004227997684</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2626,11 +2626,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46125.820048113426</v>
+        <v>46125.653381446755</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46133.17089664352</v>
+        <v>46133.004229976854</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2679,11 +2679,11 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46125.82033290509</v>
+        <v>46125.653666238424</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46133.17089804398</v>
+        <v>46133.004231377316</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2732,11 +2732,11 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46125.82063702546</v>
+        <v>46125.65397035879</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46133.17089929398</v>
+        <v>46133.00423262731</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2785,13 +2785,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.5452015162</v>
+        <v>46077.37853484954</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.50533615741</v>
+        <v>46114.33866949074</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.50535017361</v>
+        <v>46114.33868350694</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2838,13 +2838,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.54519763889</v>
+        <v>46077.37853097222</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.5523825</v>
+        <v>46097.385715833334</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.552399583336</v>
+        <v>46097.385732916664</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2903,13 +2903,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.54519880787</v>
+        <v>46077.3785321412</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.50500038195</v>
+        <v>46114.33833371528</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.505018090276</v>
+        <v>46114.33835142361</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2968,13 +2968,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.545199155094</v>
+        <v>46077.37853248842</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.55255847222</v>
+        <v>46097.385891805556</v>
       </c>
       <c r="D20" s="5">
-        <v>46125.76278827546</v>
+        <v>46125.596121608796</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -3033,13 +3033,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.54519956018</v>
+        <v>46077.37853289352</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.50531283565</v>
+        <v>46114.33864616898</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.50533729167</v>
+        <v>46114.338670625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3098,13 +3098,13 @@
         <v>85</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.54519991898</v>
+        <v>46077.37853325231</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.627469444444</v>
+        <v>46122.46080277778</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.76425234954</v>
+        <v>46191.59758568287</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -3147,13 +3147,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.545200625</v>
+        <v>46077.378533958334</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.55243590278</v>
+        <v>46097.38576923611</v>
       </c>
       <c r="D23" s="8">
-        <v>46097.55245158565</v>
+        <v>46097.38578491898</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -3212,13 +3212,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.545200312496</v>
+        <v>46077.37853364584</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.552273622685</v>
+        <v>46097.38560695601</v>
       </c>
       <c r="D24" s="5">
-        <v>46135.764537361116</v>
+        <v>46135.597870694444</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3277,13 +3277,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.54520094907</v>
+        <v>46077.37853428241</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.50689366898</v>
+        <v>46114.340227002314</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.50691030093</v>
+        <v>46114.34024363426</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3342,13 +3342,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.54520128472</v>
+        <v>46077.37853461805</v>
       </c>
       <c r="C26" s="5">
-        <v>46122.627451168984</v>
+        <v>46122.46078450231</v>
       </c>
       <c r="D26" s="5">
-        <v>46122.6274699537</v>
+        <v>46122.46080328704</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3407,13 +3407,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.553287766204</v>
+        <v>46077.38662109953</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.505863032406</v>
+        <v>46114.33919636574</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.50608950232</v>
+        <v>46114.33942283565</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3472,13 +3472,13 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.54519655093</v>
+        <v>46077.378529884256</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.76405297454</v>
+        <v>46191.59738630787</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.76406943287</v>
+        <v>46191.5974027662</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3537,13 +3537,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46125.69234111111</v>
+        <v>46125.52567444445</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.76408129629</v>
+        <v>46191.59741462963</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.764096643514</v>
+        <v>46191.59742997686</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3602,13 +3602,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46125.69240738426</v>
+        <v>46125.525740717596</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.764104965274</v>
+        <v>46191.59743829861</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.764121307875</v>
+        <v>46191.5974546412</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3667,13 +3667,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46125.69558788194</v>
+        <v>46125.52892121528</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.76414623843</v>
+        <v>46191.59747957176</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.76416752315</v>
+        <v>46191.597500856486</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3732,11 +3732,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.545196886575</v>
+        <v>46077.37853021991</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.69258219907</v>
+        <v>46182.5259155324</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3781,13 +3781,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.54519711806</v>
+        <v>46077.37853045139</v>
       </c>
       <c r="C33" s="8">
-        <v>46155.87452237269</v>
+        <v>46155.707855706016</v>
       </c>
       <c r="D33" s="8">
-        <v>46155.87452380787</v>
+        <v>46155.7078571412</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3846,13 +3846,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.54519739583</v>
+        <v>46077.37853072917</v>
       </c>
       <c r="C34" s="5">
-        <v>46114.505526747686</v>
+        <v>46114.338860081014</v>
       </c>
       <c r="D34" s="5">
-        <v>46114.50552802083</v>
+        <v>46114.33886135417</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3911,13 +3911,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.54519766204</v>
+        <v>46077.37853099537</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.86621715278</v>
+        <v>46155.69955048611</v>
       </c>
       <c r="D35" s="8">
-        <v>46155.86621849537</v>
+        <v>46155.6995518287</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3976,13 +3976,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.54519791667</v>
+        <v>46077.37853125</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.50563148149</v>
+        <v>46114.338964814815</v>
       </c>
       <c r="D36" s="5">
-        <v>46125.91364752315</v>
+        <v>46125.74698085648</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -4041,13 +4041,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.54519712963</v>
+        <v>46077.378530462964</v>
       </c>
       <c r="C37" s="8">
-        <v>46158.75835467593</v>
+        <v>46158.591688009255</v>
       </c>
       <c r="D37" s="8">
-        <v>46158.75835697917</v>
+        <v>46158.5916903125</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -4106,13 +4106,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.54519734954</v>
+        <v>46077.378530682865</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.55231699074</v>
+        <v>46097.385650324075</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.552318773145</v>
+        <v>46097.38565210648</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -4171,13 +4171,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.545197569445</v>
+        <v>46077.37853090277</v>
       </c>
       <c r="C39" s="8">
-        <v>46155.895487546295</v>
+        <v>46155.72882087963</v>
       </c>
       <c r="D39" s="8">
-        <v>46155.89548886574</v>
+        <v>46155.728822199075</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -4236,13 +4236,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.54519778935</v>
+        <v>46077.37853112268</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.6925612037</v>
+        <v>46182.52589453704</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.69257489583</v>
+        <v>46182.52590822917</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -4301,13 +4301,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.54519805555</v>
+        <v>46077.37853138889</v>
       </c>
       <c r="C41" s="8">
-        <v>46182.681518321755</v>
+        <v>46182.5148516551</v>
       </c>
       <c r="D41" s="8">
-        <v>46182.68151998843</v>
+        <v>46182.51485332176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4366,13 +4366,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.54519827546</v>
+        <v>46077.378531608796</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.6925475</v>
+        <v>46182.52588083333</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.692548946754</v>
+        <v>46182.5258822801</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4431,13 +4431,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.54519849537</v>
+        <v>46077.378531828705</v>
       </c>
       <c r="C43" s="8">
-        <v>46126.8306060301</v>
+        <v>46126.663939363425</v>
       </c>
       <c r="D43" s="8">
-        <v>46126.830619456014</v>
+        <v>46126.66395278936</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4496,13 +4496,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.54519873843</v>
+        <v>46077.37853207176</v>
       </c>
       <c r="C44" s="5">
-        <v>46126.82913611111</v>
+        <v>46126.66246944445</v>
       </c>
       <c r="D44" s="5">
-        <v>46126.829137256944</v>
+        <v>46126.66247059028</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4561,13 +4561,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.54519680556</v>
+        <v>46077.378530138885</v>
       </c>
       <c r="C45" s="8">
-        <v>46126.83059133102</v>
+        <v>46126.66392466435</v>
       </c>
       <c r="D45" s="8">
-        <v>46126.83059262732</v>
+        <v>46126.663925960645</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4626,13 +4626,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.58916118056</v>
+        <v>46077.422494513885</v>
       </c>
       <c r="C46" s="5">
-        <v>46126.829580474536</v>
+        <v>46126.66291380787</v>
       </c>
       <c r="D46" s="5">
-        <v>46126.829593946764</v>
+        <v>46126.66292728009</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4691,13 +4691,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.589282581015</v>
+        <v>46077.42261591435</v>
       </c>
       <c r="C47" s="8">
-        <v>46126.82903850694</v>
+        <v>46126.66237184028</v>
       </c>
       <c r="D47" s="8">
-        <v>46126.82903986111</v>
+        <v>46126.66237319444</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4756,13 +4756,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.589497685185</v>
+        <v>46077.42283101851</v>
       </c>
       <c r="C48" s="5">
-        <v>46126.82956608797</v>
+        <v>46126.662899421295</v>
       </c>
       <c r="D48" s="5">
-        <v>46126.829567256944</v>
+        <v>46126.66290059028</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4821,13 +4821,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.54519818287</v>
+        <v>46077.3785315162</v>
       </c>
       <c r="C49" s="8">
-        <v>46147.88814045139</v>
+        <v>46147.721473784724</v>
       </c>
       <c r="D49" s="8">
-        <v>46147.8881425</v>
+        <v>46147.72147583333</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4886,13 +4886,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.545198437496</v>
+        <v>46077.37853177083</v>
       </c>
       <c r="C50" s="5">
-        <v>46097.55269060185</v>
+        <v>46097.386023935185</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.764061747686</v>
+        <v>46191.597395081015</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4951,13 +4951,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.54519870371</v>
+        <v>46077.37853203704</v>
       </c>
       <c r="C51" s="8">
-        <v>46147.85066253472</v>
+        <v>46147.68399586805</v>
       </c>
       <c r="D51" s="8">
-        <v>46150.78326474537</v>
+        <v>46150.616598078705</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -5016,13 +5016,13 @@
         <v>185</v>
       </c>
       <c r="B52" s="5">
-        <v>46125.69589043982</v>
+        <v>46125.52922377315</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.76882001157</v>
+        <v>46191.60215334491</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.76988886574</v>
+        <v>46191.603222199075</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>186</v>
@@ -5081,13 +5081,13 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46125.70470673611</v>
+        <v>46125.53804006944</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.769818437504</v>
+        <v>46191.60315177083</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.76981975694</v>
+        <v>46191.60315309028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>118</v>
@@ -5136,13 +5136,13 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46125.704894062495</v>
+        <v>46125.53822739584</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.76987311343</v>
+        <v>46191.60320644676</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.76987484954</v>
+        <v>46191.603208182874</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5191,11 +5191,11 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.68332820602</v>
+        <v>46125.516661539354</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.914978217595</v>
+        <v>46195.748311550924</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5254,13 +5254,13 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.70524613426</v>
+        <v>46125.5385794676</v>
       </c>
       <c r="C56" s="5">
-        <v>46195.689746724536</v>
+        <v>46195.52308005787</v>
       </c>
       <c r="D56" s="5">
-        <v>46195.68974824074</v>
+        <v>46195.52308157407</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>112</v>
@@ -5309,11 +5309,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.70538292824</v>
+        <v>46125.53871626157</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.69646179398</v>
+        <v>46195.52979512731</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5362,13 +5362,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.718428078704</v>
+        <v>46125.55176141203</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.694698113424</v>
+        <v>46195.52803144676</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.69469942129</v>
+        <v>46195.52803275463</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>205</v>
@@ -5417,13 +5417,13 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.718640543986</v>
+        <v>46125.551973877315</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.694708229166</v>
+        <v>46195.5280415625</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.69470958333</v>
+        <v>46195.52804291667</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5472,13 +5472,13 @@
         <v>208</v>
       </c>
       <c r="B60" s="5">
-        <v>46125.71897782407</v>
+        <v>46125.55231115741</v>
       </c>
       <c r="C60" s="5">
-        <v>46195.69645509259</v>
+        <v>46195.52978842593</v>
       </c>
       <c r="D60" s="5">
-        <v>46195.69645640046</v>
+        <v>46195.529789733795</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5527,13 +5527,13 @@
         <v>210</v>
       </c>
       <c r="B61" s="8">
-        <v>46125.71913549768</v>
+        <v>46125.55246883102</v>
       </c>
       <c r="C61" s="8">
-        <v>46195.69541388889</v>
+        <v>46195.528747222226</v>
       </c>
       <c r="D61" s="8">
-        <v>46195.69541526621</v>
+        <v>46195.528748599536</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>211</v>
@@ -5582,13 +5582,13 @@
         <v>212</v>
       </c>
       <c r="B62" s="5">
-        <v>46126.81590638889</v>
+        <v>46126.64923972222</v>
       </c>
       <c r="C62" s="5">
-        <v>46195.69561555555</v>
+        <v>46195.52894888889</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.69561689815</v>
+        <v>46195.528950231484</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5637,11 +5637,11 @@
         <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46191.76807549769</v>
+        <v>46191.60140883102</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.695621990744</v>
+        <v>46195.52895532407</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>214</v>
@@ -5688,13 +5688,13 @@
         <v>218</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.69345099537</v>
+        <v>46125.5267843287</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.659945023144</v>
+        <v>46195.49327835648</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.6599575</v>
+        <v>46195.49329083333</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>219</v>
@@ -5753,13 +5753,13 @@
         <v>221</v>
       </c>
       <c r="B65" s="8">
-        <v>46125.7055987037</v>
+        <v>46125.53893203704</v>
       </c>
       <c r="C65" s="8">
-        <v>46195.6598427662</v>
+        <v>46195.49317609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.65984503472</v>
+        <v>46195.49317836805</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>115</v>
@@ -5808,13 +5808,13 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46125.70569783565</v>
+        <v>46125.539031168984</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.65992416667</v>
+        <v>46195.4932575</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.65992711806</v>
+        <v>46195.49326045139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5863,11 +5863,11 @@
         <v>226</v>
       </c>
       <c r="B67" s="8">
-        <v>46077.54519895834</v>
+        <v>46077.37853229167</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.698486747686</v>
+        <v>46127.531820081014</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>227</v>
@@ -5910,13 +5910,13 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46077.54519921297</v>
+        <v>46077.378532546296</v>
       </c>
       <c r="C68" s="5">
-        <v>46127.69765324074</v>
+        <v>46127.53098657407</v>
       </c>
       <c r="D68" s="5">
-        <v>46196.769709699074</v>
+        <v>46196.6030430324</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>
@@ -5975,13 +5975,13 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.6963875463</v>
+        <v>46125.529720879626</v>
       </c>
       <c r="C69" s="8">
-        <v>46127.69763241898</v>
+        <v>46127.53096575232</v>
       </c>
       <c r="D69" s="8">
-        <v>46127.697633749995</v>
+        <v>46127.53096708334</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -6030,13 +6030,13 @@
         <v>236</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.69656831019</v>
+        <v>46125.52990164352</v>
       </c>
       <c r="C70" s="5">
-        <v>46127.69763894676</v>
+        <v>46127.53097228009</v>
       </c>
       <c r="D70" s="5">
-        <v>46127.6976405787</v>
+        <v>46127.53097391204</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>237</v>
@@ -6085,13 +6085,13 @@
         <v>238</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.545196736115</v>
+        <v>46077.37853006944</v>
       </c>
       <c r="C71" s="8">
-        <v>46127.69789872685</v>
+        <v>46127.53123206018</v>
       </c>
       <c r="D71" s="8">
-        <v>46127.697912766205</v>
+        <v>46127.531246099534</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>239</v>
@@ -6150,13 +6150,13 @@
         <v>241</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.69788891204</v>
+        <v>46125.531222245365</v>
       </c>
       <c r="C72" s="5">
-        <v>46127.697883437504</v>
+        <v>46127.53121677083</v>
       </c>
       <c r="D72" s="5">
-        <v>46127.69788501157</v>
+        <v>46127.531218344906</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>235</v>
@@ -6205,13 +6205,13 @@
         <v>244</v>
       </c>
       <c r="B73" s="8">
-        <v>46125.69801100694</v>
+        <v>46125.53134434028</v>
       </c>
       <c r="C73" s="8">
-        <v>46127.69787200232</v>
+        <v>46127.53120533565</v>
       </c>
       <c r="D73" s="8">
-        <v>46127.697873287034</v>
+        <v>46127.53120662037</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>237</v>
@@ -6260,13 +6260,13 @@
         <v>247</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.70475186342</v>
+        <v>46090.538085196764</v>
       </c>
       <c r="C74" s="5">
-        <v>46127.69847682871</v>
+        <v>46127.531810162036</v>
       </c>
       <c r="D74" s="5">
-        <v>46127.698491539355</v>
+        <v>46127.53182487268</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>108</v>
@@ -6325,13 +6325,13 @@
         <v>249</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.69814037037</v>
+        <v>46125.531473703704</v>
       </c>
       <c r="C75" s="8">
-        <v>46127.69844965277</v>
+        <v>46127.531782986116</v>
       </c>
       <c r="D75" s="8">
-        <v>46127.698451331016</v>
+        <v>46127.53178466435</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>235</v>
@@ -6380,13 +6380,13 @@
         <v>250</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.6983227662</v>
+        <v>46125.53165609954</v>
       </c>
       <c r="C76" s="5">
-        <v>46127.69845996528</v>
+        <v>46127.53179329861</v>
       </c>
       <c r="D76" s="5">
-        <v>46127.69846143518</v>
+        <v>46127.53179476852</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>237</v>
@@ -6435,11 +6435,11 @@
         <v>251</v>
       </c>
       <c r="B77" s="8">
-        <v>46090.70479819445</v>
+        <v>46090.53813152778</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46168.17332814814</v>
+        <v>46168.006661481486</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>252</v>
@@ -6498,11 +6498,11 @@
         <v>255</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.69919584491</v>
+        <v>46125.532529178236</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.16821967592</v>
+        <v>46167.001553009264</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>235</v>
@@ -6549,11 +6549,11 @@
         <v>257</v>
       </c>
       <c r="B79" s="8">
-        <v>46125.69931737268</v>
+        <v>46125.53265070602</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46167.168221562504</v>
+        <v>46167.00155489583</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>237</v>
@@ -6600,11 +6600,11 @@
         <v>259</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.54519710648</v>
+        <v>46077.37853043982</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.76957280093</v>
+        <v>46191.602906134256</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>260</v>
@@ -6649,13 +6649,13 @@
         <v>262</v>
       </c>
       <c r="B81" s="8">
-        <v>46077.54519784723</v>
+        <v>46077.378531180555</v>
       </c>
       <c r="C81" s="8">
-        <v>46191.76955590278</v>
+        <v>46191.60288923611</v>
       </c>
       <c r="D81" s="8">
-        <v>46191.7695737037</v>
+        <v>46191.60290703704</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>263</v>
@@ -6714,13 +6714,13 @@
         <v>267</v>
       </c>
       <c r="B82" s="5">
-        <v>46125.69615554398</v>
+        <v>46125.52948887731</v>
       </c>
       <c r="C82" s="5">
-        <v>46191.77013172454</v>
+        <v>46191.603465057866</v>
       </c>
       <c r="D82" s="5">
-        <v>46191.77014716435</v>
+        <v>46191.60348049768</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>268</v>
@@ -6779,11 +6779,11 @@
         <v>270</v>
       </c>
       <c r="B83" s="8">
-        <v>46125.699760648145</v>
+        <v>46125.53309398148</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.65994334491</v>
+        <v>46195.493276678244</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>271</v>
@@ -6842,13 +6842,13 @@
         <v>273</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.545198472224</v>
+        <v>46077.37853180556</v>
       </c>
       <c r="C84" s="5">
-        <v>46191.769443275465</v>
+        <v>46191.602776608794</v>
       </c>
       <c r="D84" s="5">
-        <v>46191.770536875</v>
+        <v>46191.60387020833</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>274</v>
@@ -6907,13 +6907,13 @@
         <v>276</v>
       </c>
       <c r="B85" s="8">
-        <v>46125.775447465276</v>
+        <v>46125.60878079861</v>
       </c>
       <c r="C85" s="8">
-        <v>46191.769735925925</v>
+        <v>46191.60306925926</v>
       </c>
       <c r="D85" s="8">
-        <v>46191.76973724537</v>
+        <v>46191.603070578705</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>277</v>
@@ -6962,13 +6962,13 @@
         <v>279</v>
       </c>
       <c r="B86" s="5">
-        <v>46125.77559420139</v>
+        <v>46125.60892753472</v>
       </c>
       <c r="C86" s="5">
-        <v>46191.7705319213</v>
+        <v>46191.60386525463</v>
       </c>
       <c r="D86" s="5">
-        <v>46191.77053325232</v>
+        <v>46191.60386658565</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>280</v>
@@ -7017,11 +7017,11 @@
         <v>281</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.77573671297</v>
+        <v>46125.609070046296</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46125.9107300926</v>
+        <v>46125.744063425926</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>272</v>
@@ -7070,13 +7070,13 @@
         <v>282</v>
       </c>
       <c r="B88" s="5">
-        <v>46077.545199050925</v>
+        <v>46077.37853238426</v>
       </c>
       <c r="C88" s="5">
-        <v>46191.770449421296</v>
+        <v>46191.603782754624</v>
       </c>
       <c r="D88" s="5">
-        <v>46191.77046482639</v>
+        <v>46191.60379815972</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>283</v>
@@ -7123,13 +7123,13 @@
         <v>285</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.5451993287</v>
+        <v>46077.37853266204</v>
       </c>
       <c r="C89" s="8">
-        <v>46191.76127780092</v>
+        <v>46191.594611134264</v>
       </c>
       <c r="D89" s="8">
-        <v>46191.77013883102</v>
+        <v>46191.60347216435</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>286</v>
@@ -7188,13 +7188,13 @@
         <v>291</v>
       </c>
       <c r="B90" s="5">
-        <v>46077.54519958333</v>
+        <v>46077.37853291667</v>
       </c>
       <c r="C90" s="5">
-        <v>46191.76363961806</v>
+        <v>46191.59697295139</v>
       </c>
       <c r="D90" s="5">
-        <v>46191.76662447916</v>
+        <v>46191.599957812505</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>292</v>
@@ -7253,13 +7253,13 @@
         <v>295</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.780000914354</v>
+        <v>46125.61333424768</v>
       </c>
       <c r="C91" s="8">
-        <v>46191.76360844907</v>
+        <v>46191.59694178241</v>
       </c>
       <c r="D91" s="8">
-        <v>46191.76361026621</v>
+        <v>46191.596943599536</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>296</v>
@@ -7308,13 +7308,13 @@
         <v>299</v>
       </c>
       <c r="B92" s="5">
-        <v>46125.779717233796</v>
+        <v>46125.61305056713</v>
       </c>
       <c r="C92" s="5">
-        <v>46191.76362376157</v>
+        <v>46191.59695709491</v>
       </c>
       <c r="D92" s="5">
-        <v>46191.76362532408</v>
+        <v>46191.59695865741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>300</v>
@@ -7363,13 +7363,13 @@
         <v>302</v>
       </c>
       <c r="B93" s="8">
-        <v>46077.54519984954</v>
+        <v>46077.37853318287</v>
       </c>
       <c r="C93" s="8">
-        <v>46191.77043608796</v>
+        <v>46191.6037694213</v>
       </c>
       <c r="D93" s="8">
-        <v>46193.954018240736</v>
+        <v>46193.78735157408</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>303</v>
@@ -7428,13 +7428,13 @@
         <v>304</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.7814462963</v>
+        <v>46125.61477962963</v>
       </c>
       <c r="C94" s="5">
-        <v>46193.953992442126</v>
+        <v>46193.78732577546</v>
       </c>
       <c r="D94" s="5">
-        <v>46193.953995034724</v>
+        <v>46193.78732836805</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>296</v>
@@ -7483,13 +7483,13 @@
         <v>307</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.78158427084</v>
+        <v>46125.614917604165</v>
       </c>
       <c r="C95" s="8">
-        <v>46193.95400423611</v>
+        <v>46193.78733756945</v>
       </c>
       <c r="D95" s="8">
-        <v>46193.9540056713</v>
+        <v>46193.78733900463</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>300</v>
@@ -7538,11 +7538,11 @@
         <v>310</v>
       </c>
       <c r="B96" s="5">
-        <v>46077.54520011574</v>
+        <v>46077.378533449075</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46191.786592488425</v>
+        <v>46191.61992582176</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>260</v>
@@ -7585,13 +7585,13 @@
         <v>312</v>
       </c>
       <c r="B97" s="8">
-        <v>46077.545198078704</v>
+        <v>46077.37853141203</v>
       </c>
       <c r="C97" s="8">
-        <v>46191.78640506945</v>
+        <v>46191.61973840278</v>
       </c>
       <c r="D97" s="8">
-        <v>46191.78642105324</v>
+        <v>46191.61975438657</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>313</v>
@@ -7650,13 +7650,13 @@
         <v>315</v>
       </c>
       <c r="B98" s="5">
-        <v>46077.54519778935</v>
+        <v>46077.37853112268</v>
       </c>
       <c r="C98" s="5">
-        <v>46191.78658587963</v>
+        <v>46191.619919212964</v>
       </c>
       <c r="D98" s="5">
-        <v>46191.78660222222</v>
+        <v>46191.61993555556</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>316</v>
@@ -7715,11 +7715,11 @@
         <v>318</v>
       </c>
       <c r="B99" s="8">
-        <v>46077.54520075231</v>
+        <v>46077.37853408565</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46126.83061201389</v>
+        <v>46126.66394534722</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>319</v>
@@ -7778,11 +7778,11 @@
         <v>320</v>
       </c>
       <c r="B100" s="5">
-        <v>46077.54519734954</v>
+        <v>46077.378530682865</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.69256461806</v>
+        <v>46182.52589795139</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>58</v>
@@ -7841,11 +7841,11 @@
         <v>322</v>
       </c>
       <c r="B101" s="8">
-        <v>46077.55796549769</v>
+        <v>46077.39129883102</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46192.79300131944</v>
+        <v>46192.62633465278</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>323</v>
@@ -7904,11 +7904,11 @@
         <v>324</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.79029034722</v>
+        <v>46125.623623680556</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46125.90375237269</v>
+        <v>46125.737085706016</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>325</v>
@@ -7961,11 +7961,11 @@
         <v>326</v>
       </c>
       <c r="B103" s="8">
-        <v>46077.54519841435</v>
+        <v>46077.37853174769</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.86928554398</v>
+        <v>46195.702618877316</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>327</v>
@@ -8008,13 +8008,13 @@
         <v>329</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.545198761574</v>
+        <v>46077.37853209491</v>
       </c>
       <c r="C104" s="5">
-        <v>46195.86927984953</v>
+        <v>46195.702613182875</v>
       </c>
       <c r="D104" s="5">
-        <v>46195.86929523148</v>
+        <v>46195.70262856482</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>330</v>
@@ -8073,11 +8073,11 @@
         <v>331</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.785526736116</v>
+        <v>46125.618860069444</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46193.95399858797</v>
+        <v>46193.787331921296</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>235</v>
@@ -8126,11 +8126,11 @@
         <v>334</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.7863228125</v>
+        <v>46125.619656145835</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46193.954008518514</v>
+        <v>46193.78734185185</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>237</v>
@@ -8179,11 +8179,11 @@
         <v>337</v>
       </c>
       <c r="B107" s="8">
-        <v>46077.558327129635</v>
+        <v>46077.39166046296</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46154.167828125</v>
+        <v>46154.001161458335</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>338</v>
@@ -8242,11 +8242,11 @@
         <v>339</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.793145185184</v>
+        <v>46125.62647851852</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46154.16895842593</v>
+        <v>46154.00229175926</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>235</v>
@@ -8295,11 +8295,11 @@
         <v>342</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.79326523148</v>
+        <v>46125.62659856481</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46154.168959930554</v>
+        <v>46154.00229326389</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>237</v>
@@ -8348,11 +8348,11 @@
         <v>345</v>
       </c>
       <c r="B110" s="5">
-        <v>46077.5451994676</v>
+        <v>46077.378532800925</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46197.504649062495</v>
+        <v>46197.33798239584</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>346</v>
@@ -8411,13 +8411,13 @@
         <v>347</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.793417939814</v>
+        <v>46125.62675127314</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.50464319444</v>
+        <v>46197.33797652778</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.504645196765</v>
+        <v>46197.33797853009</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>235</v>
@@ -8466,11 +8466,11 @@
         <v>350</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.793529525465</v>
+        <v>46125.6268628588</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46191.78659372685</v>
+        <v>46191.61992706019</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>237</v>
@@ -8519,11 +8519,11 @@
         <v>353</v>
       </c>
       <c r="B113" s="8">
-        <v>46077.54519980324</v>
+        <v>46077.37853313657</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.60860170139</v>
+        <v>46197.44193503472</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>354</v>
@@ -8582,11 +8582,11 @@
         <v>355</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.79363706018</v>
+        <v>46125.62697039352</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.60859815972</v>
+        <v>46197.44193149306</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>235</v>
@@ -8635,11 +8635,11 @@
         <v>358</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.79376541667</v>
+        <v>46125.62709875</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46192.79081532407</v>
+        <v>46192.62414865741</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>237</v>
@@ -8688,11 +8688,11 @@
         <v>361</v>
       </c>
       <c r="B116" s="5">
-        <v>46077.54519909722</v>
+        <v>46077.37853243056</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.60844440972</v>
+        <v>46197.44177774306</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>362</v>
@@ -8751,13 +8751,13 @@
         <v>363</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.79408877315</v>
+        <v>46125.62742210648</v>
       </c>
       <c r="C117" s="8">
-        <v>46197.599578124995</v>
+        <v>46197.43291145834</v>
       </c>
       <c r="D117" s="8">
-        <v>46197.6086021875</v>
+        <v>46197.44193552084</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>235</v>
@@ -8806,11 +8806,11 @@
         <v>366</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.79422275463</v>
+        <v>46125.62755608796</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46191.786412430556</v>
+        <v>46191.61974576389</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>237</v>
@@ -8859,11 +8859,11 @@
         <v>369</v>
       </c>
       <c r="B119" s="8">
-        <v>46077.545200127315</v>
+        <v>46077.37853346065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46165.197340150466</v>
+        <v>46165.030673483794</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>370</v>
@@ -8922,11 +8922,11 @@
         <v>371</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.79434175926</v>
+        <v>46125.62767509259</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46197.59958675926</v>
+        <v>46197.43292009259</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>235</v>
@@ -8973,11 +8973,11 @@
         <v>373</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.79446019676</v>
+        <v>46125.62779353009</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46164.16915030092</v>
+        <v>46164.00248363426</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>237</v>
@@ -9024,11 +9024,11 @@
         <v>375</v>
       </c>
       <c r="B122" s="5">
-        <v>46077.54520043981</v>
+        <v>46077.37853377315</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46169.19579744213</v>
+        <v>46169.02913077547</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>376</v>
@@ -9087,11 +9087,11 @@
         <v>377</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.794598078704</v>
+        <v>46125.62793141203</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.16876332176</v>
+        <v>46168.002096655095</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>235</v>
@@ -9138,11 +9138,11 @@
         <v>379</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.794723252315</v>
+        <v>46125.62805658564</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46168.168764710645</v>
+        <v>46168.00209804398</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>237</v>
@@ -9189,11 +9189,11 @@
         <v>381</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.54519771991</v>
+        <v>46077.37853105324</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46125.907215011575</v>
+        <v>46125.74054834491</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>382</v>
@@ -9236,11 +9236,11 @@
         <v>384</v>
       </c>
       <c r="B126" s="5">
-        <v>46077.5451981713</v>
+        <v>46077.378531504626</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46170.199522905095</v>
+        <v>46170.032856238424</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>385</v>
@@ -9299,11 +9299,11 @@
         <v>389</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.81236390046</v>
+        <v>46125.64569723379</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46169.16854510417</v>
+        <v>46169.0018784375</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>235</v>
@@ -9350,11 +9350,11 @@
         <v>391</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.81252253472</v>
+        <v>46125.64585586806</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46169.168546712965</v>
+        <v>46169.0018800463</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>237</v>
@@ -9401,11 +9401,11 @@
         <v>393</v>
       </c>
       <c r="B129" s="8">
-        <v>46125.812747199074</v>
+        <v>46125.6460805324</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.16854806713</v>
+        <v>46169.00188140046</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>394</v>
@@ -9452,11 +9452,11 @@
         <v>396</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.81326880787</v>
+        <v>46125.646602141205</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.16854940972</v>
+        <v>46169.001882743054</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>61</v>
@@ -9503,11 +9503,11 @@
         <v>398</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.81384030092</v>
+        <v>46125.647173634265</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46169.168550682865</v>
+        <v>46169.00188401621</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>64</v>
@@ -9554,11 +9554,11 @@
         <v>400</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.81410221064</v>
+        <v>46125.647435543986</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46169.16855229167</v>
+        <v>46169.001885624995</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>67</v>
@@ -9605,11 +9605,11 @@
         <v>402</v>
       </c>
       <c r="B133" s="8">
-        <v>46077.5451984838</v>
+        <v>46077.37853181713</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46175.20232467593</v>
+        <v>46175.03565800926</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>403</v>
@@ -9668,11 +9668,11 @@
         <v>405</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.81482075232</v>
+        <v>46125.64815408565</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46174.16943333333</v>
+        <v>46174.00276666667</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>235</v>
@@ -9721,11 +9721,11 @@
         <v>407</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.81494678241</v>
+        <v>46125.64828011574</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46174.16943504629</v>
+        <v>46174.00276837963</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>237</v>
@@ -9774,11 +9774,11 @@
         <v>409</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.81516034722</v>
+        <v>46125.64849368056</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46174.169436400465</v>
+        <v>46174.002769733794</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>394</v>
@@ -9827,11 +9827,11 @@
         <v>411</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.81531077546</v>
+        <v>46125.64864410879</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46174.169437847224</v>
+        <v>46174.00277118056</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>61</v>
@@ -9880,11 +9880,11 @@
         <v>413</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.81545193287</v>
+        <v>46125.6487852662</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46174.16943927083</v>
+        <v>46174.002772604166</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>64</v>
@@ -9933,11 +9933,11 @@
         <v>415</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.81557276621</v>
+        <v>46125.64890609954</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46174.16944046297</v>
+        <v>46174.002773796296</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>416</v>
@@ -9986,11 +9986,11 @@
         <v>418</v>
       </c>
       <c r="B140" s="5">
-        <v>46077.54519895834</v>
+        <v>46077.37853229167</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46176.19592085648</v>
+        <v>46176.029254189816</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>419</v>
@@ -10049,11 +10049,11 @@
         <v>422</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.815781006946</v>
+        <v>46125.64911434028</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46175.16831246528</v>
+        <v>46175.001645798606</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>235</v>
@@ -10100,11 +10100,11 @@
         <v>424</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.81592018518</v>
+        <v>46125.64925351852</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46175.168314062495</v>
+        <v>46175.00164739584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>237</v>
@@ -10151,11 +10151,11 @@
         <v>426</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.81606405093</v>
+        <v>46125.64939738426</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46175.16831547454</v>
+        <v>46175.00164880787</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>57</v>
@@ -10202,11 +10202,11 @@
         <v>428</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.81619271991</v>
+        <v>46125.64952605324</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46175.16831677083</v>
+        <v>46175.00165010417</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>61</v>
@@ -10253,11 +10253,11 @@
         <v>430</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.81632106482</v>
+        <v>46125.64965439815</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46175.16831813657</v>
+        <v>46175.00165146991</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>64</v>
@@ -10304,11 +10304,11 @@
         <v>432</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.816468668985</v>
+        <v>46125.649802002314</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46175.16831954861</v>
+        <v>46175.00165288194</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>416</v>
@@ -10355,11 +10355,11 @@
         <v>434</v>
       </c>
       <c r="B147" s="8">
-        <v>46077.54519927083</v>
+        <v>46077.37853260417</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46177.189300150465</v>
+        <v>46177.02263348379</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>435</v>
@@ -10418,11 +10418,11 @@
         <v>438</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.81660767361</v>
+        <v>46125.649941006945</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46176.1683697338</v>
+        <v>46176.00170306713</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>235</v>
@@ -10469,11 +10469,11 @@
         <v>439</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.81673583333</v>
+        <v>46125.650069166666</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46176.16837118055</v>
+        <v>46176.00170451389</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>237</v>
@@ -10520,11 +10520,11 @@
         <v>440</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.81686799768</v>
+        <v>46125.650201331024</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46176.16837233797</v>
+        <v>46176.0017056713</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>394</v>
@@ -10571,11 +10571,11 @@
         <v>441</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.81698454861</v>
+        <v>46125.65031788194</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46176.16837344907</v>
+        <v>46176.00170678241</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>61</v>
@@ -10622,11 +10622,11 @@
         <v>442</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.81713481482</v>
+        <v>46125.650468148146</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46176.1683746412</v>
+        <v>46176.00170797454</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>64</v>
@@ -10673,11 +10673,11 @@
         <v>443</v>
       </c>
       <c r="B153" s="8">
-        <v>46125.8172621875</v>
+        <v>46125.650595520834</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46176.16837584491</v>
+        <v>46176.001709178236</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>416</v>
@@ -10724,11 +10724,11 @@
         <v>444</v>
       </c>
       <c r="B154" s="5">
-        <v>46077.54519966435</v>
+        <v>46077.37853299768</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46125.90721503472</v>
+        <v>46125.740548368056</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>445</v>
@@ -10771,11 +10771,11 @@
         <v>447</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.54519996527</v>
+        <v>46077.378533298615</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46186.20134465278</v>
+        <v>46186.034677986114</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>448</v>
@@ -10834,11 +10834,11 @@
         <v>451</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.545200277775</v>
+        <v>46077.37853361111</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46186.201344699075</v>
+        <v>46186.0346780324</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>452</v>
@@ -10897,11 +10897,11 @@
         <v>454</v>
       </c>
       <c r="B157" s="8">
-        <v>46090.70994861111</v>
+        <v>46090.54328194444</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46125.907787916665</v>
+        <v>46125.74112125</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>455</v>
@@ -10950,11 +10950,11 @@
         <v>457</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.71005349537</v>
+        <v>46090.54338682871</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46185.197705416664</v>
+        <v>46185.03103875</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>458</v>
@@ -11013,11 +11013,11 @@
         <v>460</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.70960611111</v>
+        <v>46090.54293944444</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46196.17368006945</v>
+        <v>46196.00701340278</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>461</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="464">
   <si>
     <t>50001499- EQ. CHAPARRAL</t>
   </si>
@@ -708,19 +708,25 @@
     <t>Planos Preliminar</t>
   </si>
   <si>
+    <t>Gonzalo Javier Dávila Bade</t>
+  </si>
+  <si>
+    <t>gonzalo.davila@zitron.com</t>
+  </si>
+  <si>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+  </si>
+  <si>
+    <t>1214046914974309</t>
+  </si>
+  <si>
+    <t>OT 4202 ZVN 1-22-400/6</t>
+  </si>
+  <si>
     <t>Hernan Roberto Gutierrez Barrientos</t>
   </si>
   <si>
     <t>hgutierrez@zitron.com</t>
-  </si>
-  <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
-  </si>
-  <si>
-    <t>1214046914974309</t>
-  </si>
-  <si>
-    <t>OT 4202 ZVN 1-22-400/6</t>
   </si>
   <si>
     <t>1214046914974310</t>
@@ -2024,13 +2030,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.37853135417</v>
+        <v>46077.54519802083</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55453159723</v>
+        <v>46092.721198263884</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.44251555555</v>
+        <v>46112.60918222222</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2073,13 +2079,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.378532048606</v>
+        <v>46077.54519871528</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55450226852</v>
+        <v>46092.72116893518</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55453317129</v>
+        <v>46092.721199837964</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2138,13 +2144,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.37853246528</v>
+        <v>46077.54519913194</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55450283564</v>
+        <v>46092.721169502314</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.48084798611</v>
+        <v>46134.64751465278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2203,13 +2209,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.37853282408</v>
+        <v>46077.54519949074</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.554503287036</v>
+        <v>46092.7211699537</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.48088872685</v>
+        <v>46134.647555393516</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2268,13 +2274,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.378533194445</v>
+        <v>46077.54519986111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55450377315</v>
+        <v>46092.721170439814</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.48092777778</v>
+        <v>46134.64759444444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2333,13 +2339,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.37853353009</v>
+        <v>46077.545200196764</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55450440972</v>
+        <v>46092.72117107639</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.48096153935</v>
+        <v>46134.64762820602</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2398,11 +2404,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.37853386574</v>
+        <v>46077.545200532404</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.33967887731</v>
+        <v>46114.50634554398</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2445,13 +2451,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.37853422454</v>
+        <v>46077.5452008912</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.33966869213</v>
+        <v>46114.5063353588</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.33969057871</v>
+        <v>46114.506357245366</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2510,11 +2516,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.37853454861</v>
+        <v>46077.54520121528</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46135.02439115741</v>
+        <v>46135.19105782408</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2573,11 +2579,11 @@
         <v>56</v>
       </c>
       <c r="B13" s="8">
-        <v>46125.653105613426</v>
+        <v>46125.8197722801</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46133.004227997684</v>
+        <v>46133.17089466435</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2626,11 +2632,11 @@
         <v>60</v>
       </c>
       <c r="B14" s="5">
-        <v>46125.653381446755</v>
+        <v>46125.820048113426</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46133.004229976854</v>
+        <v>46133.17089664352</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2679,11 +2685,11 @@
         <v>63</v>
       </c>
       <c r="B15" s="8">
-        <v>46125.653666238424</v>
+        <v>46125.82033290509</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46133.004231377316</v>
+        <v>46133.17089804398</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2732,11 +2738,11 @@
         <v>66</v>
       </c>
       <c r="B16" s="5">
-        <v>46125.65397035879</v>
+        <v>46125.82063702546</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46133.00423262731</v>
+        <v>46133.17089929398</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -2785,13 +2791,13 @@
         <v>69</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.37853484954</v>
+        <v>46077.5452015162</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.33866949074</v>
+        <v>46114.50533615741</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.33868350694</v>
+        <v>46114.50535017361</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>70</v>
@@ -2838,13 +2844,13 @@
         <v>72</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.37853097222</v>
+        <v>46077.54519763889</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.385715833334</v>
+        <v>46097.5523825</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.385732916664</v>
+        <v>46097.552399583336</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>73</v>
@@ -2903,13 +2909,13 @@
         <v>75</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.3785321412</v>
+        <v>46077.54519880787</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.33833371528</v>
+        <v>46114.50500038195</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.33835142361</v>
+        <v>46114.505018090276</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>76</v>
@@ -2968,13 +2974,13 @@
         <v>78</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.37853248842</v>
+        <v>46077.545199155094</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.385891805556</v>
+        <v>46097.55255847222</v>
       </c>
       <c r="D20" s="5">
-        <v>46125.596121608796</v>
+        <v>46125.76278827546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>79</v>
@@ -3033,13 +3039,13 @@
         <v>81</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.37853289352</v>
+        <v>46077.54519956018</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.33864616898</v>
+        <v>46114.50531283565</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.338670625</v>
+        <v>46114.50533729167</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>82</v>
@@ -3098,13 +3104,13 @@
         <v>85</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.37853325231</v>
+        <v>46077.54519991898</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46080277778</v>
+        <v>46122.627469444444</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.59758568287</v>
+        <v>46191.76425234954</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>86</v>
@@ -3147,13 +3153,13 @@
         <v>88</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.378533958334</v>
+        <v>46077.545200625</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38576923611</v>
+        <v>46097.55243590278</v>
       </c>
       <c r="D23" s="8">
-        <v>46097.38578491898</v>
+        <v>46097.55245158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>89</v>
@@ -3212,13 +3218,13 @@
         <v>91</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.37853364584</v>
+        <v>46077.545200312496</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38560695601</v>
+        <v>46097.552273622685</v>
       </c>
       <c r="D24" s="5">
-        <v>46135.597870694444</v>
+        <v>46135.764537361116</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>92</v>
@@ -3277,13 +3283,13 @@
         <v>94</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.37853428241</v>
+        <v>46077.54520094907</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.340227002314</v>
+        <v>46114.50689366898</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.34024363426</v>
+        <v>46114.50691030093</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>95</v>
@@ -3342,13 +3348,13 @@
         <v>97</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.37853461805</v>
+        <v>46077.54520128472</v>
       </c>
       <c r="C26" s="5">
-        <v>46122.46078450231</v>
+        <v>46122.627451168984</v>
       </c>
       <c r="D26" s="5">
-        <v>46122.46080328704</v>
+        <v>46122.6274699537</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>98</v>
@@ -3407,13 +3413,13 @@
         <v>101</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.38662109953</v>
+        <v>46077.553287766204</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.33919636574</v>
+        <v>46114.505863032406</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.33942283565</v>
+        <v>46114.50608950232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>102</v>
@@ -3472,13 +3478,13 @@
         <v>104</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.378529884256</v>
+        <v>46077.54519655093</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.59738630787</v>
+        <v>46191.76405297454</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.5974027662</v>
+        <v>46191.76406943287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>105</v>
@@ -3537,13 +3543,13 @@
         <v>110</v>
       </c>
       <c r="B29" s="8">
-        <v>46125.52567444445</v>
+        <v>46125.69234111111</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.59741462963</v>
+        <v>46191.76408129629</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.59742997686</v>
+        <v>46191.764096643514</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>111</v>
@@ -3602,13 +3608,13 @@
         <v>113</v>
       </c>
       <c r="B30" s="5">
-        <v>46125.525740717596</v>
+        <v>46125.69240738426</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.59743829861</v>
+        <v>46191.764104965274</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.5974546412</v>
+        <v>46191.764121307875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>114</v>
@@ -3667,13 +3673,13 @@
         <v>116</v>
       </c>
       <c r="B31" s="8">
-        <v>46125.52892121528</v>
+        <v>46125.69558788194</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.59747957176</v>
+        <v>46191.76414623843</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.597500856486</v>
+        <v>46191.76416752315</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>117</v>
@@ -3732,11 +3738,11 @@
         <v>119</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.37853021991</v>
+        <v>46077.545196886575</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.5259155324</v>
+        <v>46182.69258219907</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>120</v>
@@ -3781,13 +3787,13 @@
         <v>123</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.37853045139</v>
+        <v>46077.54519711806</v>
       </c>
       <c r="C33" s="8">
-        <v>46155.707855706016</v>
+        <v>46155.87452237269</v>
       </c>
       <c r="D33" s="8">
-        <v>46155.7078571412</v>
+        <v>46155.87452380787</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>124</v>
@@ -3846,13 +3852,13 @@
         <v>129</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.37853072917</v>
+        <v>46077.54519739583</v>
       </c>
       <c r="C34" s="5">
-        <v>46114.338860081014</v>
+        <v>46114.505526747686</v>
       </c>
       <c r="D34" s="5">
-        <v>46114.33886135417</v>
+        <v>46114.50552802083</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>130</v>
@@ -3911,13 +3917,13 @@
         <v>132</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.37853099537</v>
+        <v>46077.54519766204</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.69955048611</v>
+        <v>46155.86621715278</v>
       </c>
       <c r="D35" s="8">
-        <v>46155.6995518287</v>
+        <v>46155.86621849537</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>133</v>
@@ -3976,13 +3982,13 @@
         <v>135</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.37853125</v>
+        <v>46077.54519791667</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.338964814815</v>
+        <v>46114.50563148149</v>
       </c>
       <c r="D36" s="5">
-        <v>46125.74698085648</v>
+        <v>46125.91364752315</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>136</v>
@@ -4041,13 +4047,13 @@
         <v>138</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.378530462964</v>
+        <v>46077.54519712963</v>
       </c>
       <c r="C37" s="8">
-        <v>46158.591688009255</v>
+        <v>46158.75835467593</v>
       </c>
       <c r="D37" s="8">
-        <v>46158.5916903125</v>
+        <v>46158.75835697917</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>139</v>
@@ -4106,13 +4112,13 @@
         <v>141</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.378530682865</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.385650324075</v>
+        <v>46097.55231699074</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38565210648</v>
+        <v>46097.552318773145</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>142</v>
@@ -4171,13 +4177,13 @@
         <v>144</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.37853090277</v>
+        <v>46077.545197569445</v>
       </c>
       <c r="C39" s="8">
-        <v>46155.72882087963</v>
+        <v>46155.895487546295</v>
       </c>
       <c r="D39" s="8">
-        <v>46155.728822199075</v>
+        <v>46155.89548886574</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>145</v>
@@ -4236,13 +4242,13 @@
         <v>147</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.37853112268</v>
+        <v>46077.54519778935</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.52589453704</v>
+        <v>46182.6925612037</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.52590822917</v>
+        <v>46182.69257489583</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>148</v>
@@ -4301,13 +4307,13 @@
         <v>150</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.37853138889</v>
+        <v>46077.54519805555</v>
       </c>
       <c r="C41" s="8">
-        <v>46182.5148516551</v>
+        <v>46182.681518321755</v>
       </c>
       <c r="D41" s="8">
-        <v>46182.51485332176</v>
+        <v>46182.68151998843</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>151</v>
@@ -4366,13 +4372,13 @@
         <v>153</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.378531608796</v>
+        <v>46077.54519827546</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.52588083333</v>
+        <v>46182.6925475</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.5258822801</v>
+        <v>46182.692548946754</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>154</v>
@@ -4431,13 +4437,13 @@
         <v>156</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.378531828705</v>
+        <v>46077.54519849537</v>
       </c>
       <c r="C43" s="8">
-        <v>46126.663939363425</v>
+        <v>46126.8306060301</v>
       </c>
       <c r="D43" s="8">
-        <v>46126.66395278936</v>
+        <v>46126.830619456014</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>157</v>
@@ -4496,13 +4502,13 @@
         <v>159</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.37853207176</v>
+        <v>46077.54519873843</v>
       </c>
       <c r="C44" s="5">
-        <v>46126.66246944445</v>
+        <v>46126.82913611111</v>
       </c>
       <c r="D44" s="5">
-        <v>46126.66247059028</v>
+        <v>46126.829137256944</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>160</v>
@@ -4561,13 +4567,13 @@
         <v>162</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.378530138885</v>
+        <v>46077.54519680556</v>
       </c>
       <c r="C45" s="8">
-        <v>46126.66392466435</v>
+        <v>46126.83059133102</v>
       </c>
       <c r="D45" s="8">
-        <v>46126.663925960645</v>
+        <v>46126.83059262732</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>163</v>
@@ -4626,13 +4632,13 @@
         <v>165</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.422494513885</v>
+        <v>46077.58916118056</v>
       </c>
       <c r="C46" s="5">
-        <v>46126.66291380787</v>
+        <v>46126.829580474536</v>
       </c>
       <c r="D46" s="5">
-        <v>46126.66292728009</v>
+        <v>46126.829593946764</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>166</v>
@@ -4691,13 +4697,13 @@
         <v>170</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.42261591435</v>
+        <v>46077.589282581015</v>
       </c>
       <c r="C47" s="8">
-        <v>46126.66237184028</v>
+        <v>46126.82903850694</v>
       </c>
       <c r="D47" s="8">
-        <v>46126.66237319444</v>
+        <v>46126.82903986111</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>171</v>
@@ -4756,13 +4762,13 @@
         <v>173</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.42283101851</v>
+        <v>46077.589497685185</v>
       </c>
       <c r="C48" s="5">
-        <v>46126.662899421295</v>
+        <v>46126.82956608797</v>
       </c>
       <c r="D48" s="5">
-        <v>46126.66290059028</v>
+        <v>46126.829567256944</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>174</v>
@@ -4821,13 +4827,13 @@
         <v>176</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.3785315162</v>
+        <v>46077.54519818287</v>
       </c>
       <c r="C49" s="8">
-        <v>46147.721473784724</v>
+        <v>46147.88814045139</v>
       </c>
       <c r="D49" s="8">
-        <v>46147.72147583333</v>
+        <v>46147.8881425</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>177</v>
@@ -4886,13 +4892,13 @@
         <v>179</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.37853177083</v>
+        <v>46077.545198437496</v>
       </c>
       <c r="C50" s="5">
-        <v>46097.386023935185</v>
+        <v>46097.55269060185</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.597395081015</v>
+        <v>46191.764061747686</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>180</v>
@@ -4951,13 +4957,13 @@
         <v>182</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.37853203704</v>
+        <v>46077.54519870371</v>
       </c>
       <c r="C51" s="8">
-        <v>46147.68399586805</v>
+        <v>46147.85066253472</v>
       </c>
       <c r="D51" s="8">
-        <v>46150.616598078705</v>
+        <v>46150.78326474537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>183</v>
@@ -5016,13 +5022,13 @@
         <v>185</v>
       </c>
       <c r="B52" s="5">
-        <v>46125.52922377315</v>
+        <v>46125.69589043982</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.60215334491</v>
+        <v>46191.76882001157</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.603222199075</v>
+        <v>46191.76988886574</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>186</v>
@@ -5081,13 +5087,13 @@
         <v>188</v>
       </c>
       <c r="B53" s="8">
-        <v>46125.53804006944</v>
+        <v>46125.70470673611</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.60315177083</v>
+        <v>46191.769818437504</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.60315309028</v>
+        <v>46191.76981975694</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>118</v>
@@ -5136,13 +5142,13 @@
         <v>190</v>
       </c>
       <c r="B54" s="5">
-        <v>46125.53822739584</v>
+        <v>46125.704894062495</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.60320644676</v>
+        <v>46191.76987311343</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.603208182874</v>
+        <v>46191.76987484954</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>191</v>
@@ -5191,11 +5197,11 @@
         <v>193</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.516661539354</v>
+        <v>46125.68332820602</v>
       </c>
       <c r="C55" s="9"/>
       <c r="D55" s="8">
-        <v>46195.748311550924</v>
+        <v>46195.914978217595</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>194</v>
@@ -5254,13 +5260,13 @@
         <v>198</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.5385794676</v>
+        <v>46125.70524613426</v>
       </c>
       <c r="C56" s="5">
-        <v>46195.52308005787</v>
+        <v>46195.689746724536</v>
       </c>
       <c r="D56" s="5">
-        <v>46195.52308157407</v>
+        <v>46195.68974824074</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>112</v>
@@ -5309,11 +5315,11 @@
         <v>200</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.53871626157</v>
+        <v>46125.70538292824</v>
       </c>
       <c r="C57" s="9"/>
       <c r="D57" s="8">
-        <v>46195.52979512731</v>
+        <v>46195.69646179398</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>201</v>
@@ -5362,13 +5368,13 @@
         <v>204</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.55176141203</v>
+        <v>46125.718428078704</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.52803144676</v>
+        <v>46195.694698113424</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.52803275463</v>
+        <v>46195.69469942129</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>205</v>
@@ -5417,13 +5423,13 @@
         <v>206</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.551973877315</v>
+        <v>46125.718640543986</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.5280415625</v>
+        <v>46195.694708229166</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.52804291667</v>
+        <v>46195.69470958333</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>207</v>
@@ -5472,13 +5478,13 @@
         <v>208</v>
       </c>
       <c r="B60" s="5">
-        <v>46125.55231115741</v>
+        <v>46125.71897782407</v>
       </c>
       <c r="C60" s="5">
-        <v>46195.52978842593</v>
+        <v>46195.69645509259</v>
       </c>
       <c r="D60" s="5">
-        <v>46195.529789733795</v>
+        <v>46195.69645640046</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>209</v>
@@ -5527,13 +5533,13 @@
         <v>210</v>
       </c>
       <c r="B61" s="8">
-        <v>46125.55246883102</v>
+        <v>46125.71913549768</v>
       </c>
       <c r="C61" s="8">
-        <v>46195.528747222226</v>
+        <v>46195.69541388889</v>
       </c>
       <c r="D61" s="8">
-        <v>46195.528748599536</v>
+        <v>46195.69541526621</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>211</v>
@@ -5582,13 +5588,13 @@
         <v>212</v>
       </c>
       <c r="B62" s="5">
-        <v>46126.64923972222</v>
+        <v>46126.81590638889</v>
       </c>
       <c r="C62" s="5">
-        <v>46195.52894888889</v>
+        <v>46195.69561555555</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.528950231484</v>
+        <v>46195.69561689815</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>213</v>
@@ -5637,11 +5643,11 @@
         <v>215</v>
       </c>
       <c r="B63" s="8">
-        <v>46191.60140883102</v>
+        <v>46191.76807549769</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.52895532407</v>
+        <v>46195.695621990744</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>214</v>
@@ -5688,13 +5694,13 @@
         <v>218</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.5267843287</v>
+        <v>46125.69345099537</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.49327835648</v>
+        <v>46195.659945023144</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.49329083333</v>
+        <v>46195.6599575</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>219</v>
@@ -5753,13 +5759,13 @@
         <v>221</v>
       </c>
       <c r="B65" s="8">
-        <v>46125.53893203704</v>
+        <v>46125.7055987037</v>
       </c>
       <c r="C65" s="8">
-        <v>46195.49317609954</v>
+        <v>46195.6598427662</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.49317836805</v>
+        <v>46195.65984503472</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>115</v>
@@ -5808,13 +5814,13 @@
         <v>223</v>
       </c>
       <c r="B66" s="5">
-        <v>46125.539031168984</v>
+        <v>46125.70569783565</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.4932575</v>
+        <v>46195.65992416667</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.49326045139</v>
+        <v>46195.65992711806</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>224</v>
@@ -5863,11 +5869,11 @@
         <v>226</v>
       </c>
       <c r="B67" s="8">
-        <v>46077.37853229167</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.531820081014</v>
+        <v>46127.698486747686</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>227</v>
@@ -5910,13 +5916,13 @@
         <v>229</v>
       </c>
       <c r="B68" s="5">
-        <v>46077.378532546296</v>
+        <v>46077.54519921297</v>
       </c>
       <c r="C68" s="5">
-        <v>46127.53098657407</v>
+        <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46196.6030430324</v>
+        <v>46197.708269930554</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>
@@ -5975,13 +5981,13 @@
         <v>234</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.529720879626</v>
+        <v>46125.6963875463</v>
       </c>
       <c r="C69" s="8">
-        <v>46127.53096575232</v>
+        <v>46127.69763241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46127.53096708334</v>
+        <v>46127.697633749995</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>235</v>
@@ -5990,10 +5996,10 @@
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I69" s="8">
         <v>46013</v>
@@ -6027,28 +6033,28 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B70" s="5">
+        <v>46125.69656831019</v>
+      </c>
+      <c r="C70" s="5">
+        <v>46127.69763894676</v>
+      </c>
+      <c r="D70" s="5">
+        <v>46127.6976405787</v>
+      </c>
+      <c r="E70" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="B70" s="5">
-        <v>46125.52990164352</v>
-      </c>
-      <c r="C70" s="5">
-        <v>46127.53097228009</v>
-      </c>
-      <c r="D70" s="5">
-        <v>46127.53097391204</v>
-      </c>
-      <c r="E70" s="6" t="s">
+      <c r="H70" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I70" s="5">
         <v>46013</v>
@@ -6072,7 +6078,7 @@
         <v>79</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6082,19 +6088,19 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.37853006944</v>
+        <v>46077.545196736115</v>
       </c>
       <c r="C71" s="8">
-        <v>46127.53123206018</v>
+        <v>46127.69789872685</v>
       </c>
       <c r="D71" s="8">
-        <v>46127.531246099534</v>
+        <v>46197.708300150465</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
@@ -6124,7 +6130,7 @@
         <v>227</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P71" s="9" t="s">
         <v>227</v>
@@ -6147,16 +6153,16 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.531222245365</v>
+        <v>46125.69788891204</v>
       </c>
       <c r="C72" s="5">
-        <v>46127.53121677083</v>
+        <v>46127.697883437504</v>
       </c>
       <c r="D72" s="5">
-        <v>46127.531218344906</v>
+        <v>46127.69788501157</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>235</v>
@@ -6165,10 +6171,10 @@
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I72" s="5">
         <v>46066</v>
@@ -6186,13 +6192,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6202,28 +6208,28 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B73" s="8">
-        <v>46125.53134434028</v>
+        <v>46125.69801100694</v>
       </c>
       <c r="C73" s="8">
-        <v>46127.53120533565</v>
+        <v>46127.69787200232</v>
       </c>
       <c r="D73" s="8">
-        <v>46127.53120662037</v>
+        <v>46127.697873287034</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>237</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>232</v>
       </c>
       <c r="I73" s="8">
         <v>46066</v>
@@ -6241,13 +6247,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6257,16 +6263,16 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.538085196764</v>
+        <v>46090.70475186342</v>
       </c>
       <c r="C74" s="5">
-        <v>46127.531810162036</v>
+        <v>46127.69847682871</v>
       </c>
       <c r="D74" s="5">
-        <v>46127.53182487268</v>
+        <v>46127.698491539355</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>108</v>
@@ -6275,10 +6281,10 @@
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I74" s="5">
         <v>46073</v>
@@ -6299,10 +6305,10 @@
         <v>227</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q74" s="5">
         <v>46073</v>
@@ -6322,16 +6328,16 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.531473703704</v>
+        <v>46125.69814037037</v>
       </c>
       <c r="C75" s="8">
-        <v>46127.531782986116</v>
+        <v>46127.69844965277</v>
       </c>
       <c r="D75" s="8">
-        <v>46127.53178466435</v>
+        <v>46127.698451331016</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>235</v>
@@ -6340,10 +6346,10 @@
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="I75" s="8">
         <v>46073</v>
@@ -6377,28 +6383,28 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.53165609954</v>
+        <v>46125.6983227662</v>
       </c>
       <c r="C76" s="5">
-        <v>46127.53179329861</v>
+        <v>46127.69845996528</v>
       </c>
       <c r="D76" s="5">
-        <v>46127.53179476852</v>
+        <v>46127.69846143518</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>237</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>231</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>232</v>
       </c>
       <c r="I76" s="5">
         <v>46073</v>
@@ -6419,7 +6425,7 @@
         <v>108</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P76" s="6" t="s">
         <v>108</v>
@@ -6432,26 +6438,26 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B77" s="8">
-        <v>46090.53813152778</v>
+        <v>46090.70479819445</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46168.006661481486</v>
+        <v>46168.17332814814</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I77" s="8">
         <v>46167</v>
@@ -6472,7 +6478,7 @@
         <v>227</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P77" s="9" t="s">
         <v>227</v>
@@ -6495,14 +6501,14 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.532529178236</v>
+        <v>46125.69919584491</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.001553009264</v>
+        <v>46167.16821967592</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>235</v>
@@ -6511,10 +6517,10 @@
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6530,13 +6536,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O78" s="6" t="s">
         <v>235</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6546,26 +6552,26 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B79" s="8">
-        <v>46125.53265070602</v>
+        <v>46125.69931737268</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46167.00155489583</v>
+        <v>46167.168221562504</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -6581,13 +6587,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6597,17 +6603,17 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.37853043982</v>
+        <v>46077.54519710648</v>
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46191.602906134256</v>
+        <v>46191.76957280093</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6631,7 +6637,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6646,28 +6652,28 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B81" s="8">
-        <v>46077.378531180555</v>
+        <v>46077.54519784723</v>
       </c>
       <c r="C81" s="8">
-        <v>46191.60288923611</v>
+        <v>46191.76955590278</v>
       </c>
       <c r="D81" s="8">
-        <v>46191.60290703704</v>
+        <v>46191.7695737037</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I81" s="8">
         <v>46094</v>
@@ -6685,13 +6691,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O81" s="9" t="s">
         <v>183</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="Q81" s="8">
         <v>46097</v>
@@ -6711,28 +6717,28 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="B82" s="5">
+        <v>46125.69615554398</v>
+      </c>
+      <c r="C82" s="5">
+        <v>46191.77013172454</v>
+      </c>
+      <c r="D82" s="5">
+        <v>46191.77014716435</v>
+      </c>
+      <c r="E82" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F82" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G82" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="H82" s="6" t="s">
         <v>267</v>
-      </c>
-      <c r="B82" s="5">
-        <v>46125.52948887731</v>
-      </c>
-      <c r="C82" s="5">
-        <v>46191.603465057866</v>
-      </c>
-      <c r="D82" s="5">
-        <v>46191.60348049768</v>
-      </c>
-      <c r="E82" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="F82" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G82" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="H82" s="6" t="s">
-        <v>265</v>
       </c>
       <c r="I82" s="5">
         <v>46094</v>
@@ -6750,13 +6756,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O82" s="6" t="s">
         <v>191</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="Q82" s="5">
         <v>46097</v>
@@ -6776,26 +6782,26 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B83" s="8">
-        <v>46125.53309398148</v>
+        <v>46125.699760648145</v>
       </c>
       <c r="C83" s="9"/>
       <c r="D83" s="8">
-        <v>46195.493276678244</v>
+        <v>46195.65994334491</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I83" s="8">
         <v>46094</v>
@@ -6813,13 +6819,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O83" s="9" t="s">
         <v>224</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="Q83" s="8">
         <v>46097</v>
@@ -6839,19 +6845,19 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.37853180556</v>
+        <v>46077.545198472224</v>
       </c>
       <c r="C84" s="5">
-        <v>46191.602776608794</v>
+        <v>46191.769443275465</v>
       </c>
       <c r="D84" s="5">
-        <v>46191.60387020833</v>
+        <v>46191.770536875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
@@ -6878,13 +6884,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q84" s="5">
         <v>46099</v>
@@ -6904,19 +6910,19 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B85" s="8">
-        <v>46125.60878079861</v>
+        <v>46125.775447465276</v>
       </c>
       <c r="C85" s="8">
-        <v>46191.60306925926</v>
+        <v>46191.769735925925</v>
       </c>
       <c r="D85" s="8">
-        <v>46191.603070578705</v>
+        <v>46191.76973724537</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
@@ -6943,13 +6949,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6959,19 +6965,19 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B86" s="5">
-        <v>46125.60892753472</v>
+        <v>46125.77559420139</v>
       </c>
       <c r="C86" s="5">
-        <v>46191.60386525463</v>
+        <v>46191.7705319213</v>
       </c>
       <c r="D86" s="5">
-        <v>46191.60386658565</v>
+        <v>46191.77053325232</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
@@ -6998,13 +7004,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7014,17 +7020,17 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.609070046296</v>
+        <v>46125.77573671297</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46125.744063425926</v>
+        <v>46125.9107300926</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
@@ -7051,13 +7057,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7067,19 +7073,19 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B88" s="5">
-        <v>46077.37853238426</v>
+        <v>46077.545199050925</v>
       </c>
       <c r="C88" s="5">
-        <v>46191.603782754624</v>
+        <v>46191.770449421296</v>
       </c>
       <c r="D88" s="5">
-        <v>46191.60379815972</v>
+        <v>46191.77046482639</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -7103,7 +7109,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -7120,28 +7126,28 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.37853266204</v>
+        <v>46077.5451993287</v>
       </c>
       <c r="C89" s="8">
-        <v>46191.594611134264</v>
+        <v>46191.76127780092</v>
       </c>
       <c r="D89" s="8">
-        <v>46191.60347216435</v>
+        <v>46191.77013883102</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I89" s="8">
         <v>46100</v>
@@ -7159,13 +7165,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="Q89" s="8">
         <v>46108</v>
@@ -7185,28 +7191,28 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B90" s="5">
-        <v>46077.37853291667</v>
+        <v>46077.54519958333</v>
       </c>
       <c r="C90" s="5">
-        <v>46191.59697295139</v>
+        <v>46191.76363961806</v>
       </c>
       <c r="D90" s="5">
-        <v>46191.599957812505</v>
+        <v>46191.76662447916</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I90" s="5">
         <v>46111</v>
@@ -7224,13 +7230,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q90" s="5">
         <v>46139</v>
@@ -7245,33 +7251,33 @@
         <v>1</v>
       </c>
       <c r="U90" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.61333424768</v>
+        <v>46125.780000914354</v>
       </c>
       <c r="C91" s="8">
-        <v>46191.59694178241</v>
+        <v>46191.76360844907</v>
       </c>
       <c r="D91" s="8">
-        <v>46191.596943599536</v>
+        <v>46191.76361026621</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I91" s="8">
         <v>46111</v>
@@ -7289,13 +7295,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7305,28 +7311,28 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B92" s="5">
-        <v>46125.61305056713</v>
+        <v>46125.779717233796</v>
       </c>
       <c r="C92" s="5">
-        <v>46191.59695709491</v>
+        <v>46191.76362376157</v>
       </c>
       <c r="D92" s="5">
-        <v>46191.59695865741</v>
+        <v>46191.76362532408</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I92" s="5">
         <v>46111</v>
@@ -7344,13 +7350,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7360,19 +7366,19 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B93" s="8">
-        <v>46077.37853318287</v>
+        <v>46077.54519984954</v>
       </c>
       <c r="C93" s="8">
-        <v>46191.6037694213</v>
+        <v>46191.77043608796</v>
       </c>
       <c r="D93" s="8">
-        <v>46193.78735157408</v>
+        <v>46193.954018240736</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
@@ -7399,13 +7405,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="Q93" s="8">
         <v>46141</v>
@@ -7420,24 +7426,24 @@
         <v>1</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.61477962963</v>
+        <v>46125.7814462963</v>
       </c>
       <c r="C94" s="5">
-        <v>46193.78732577546</v>
+        <v>46193.953992442126</v>
       </c>
       <c r="D94" s="5">
-        <v>46193.78732836805</v>
+        <v>46193.953995034724</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
@@ -7464,13 +7470,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7480,19 +7486,19 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.614917604165</v>
+        <v>46125.78158427084</v>
       </c>
       <c r="C95" s="8">
-        <v>46193.78733756945</v>
+        <v>46193.95400423611</v>
       </c>
       <c r="D95" s="8">
-        <v>46193.78733900463</v>
+        <v>46193.9540056713</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
@@ -7519,13 +7525,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7535,17 +7541,17 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B96" s="5">
-        <v>46077.378533449075</v>
+        <v>46077.54520011574</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46191.61992582176</v>
+        <v>46191.786592488425</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7569,7 +7575,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7582,28 +7588,28 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B97" s="8">
-        <v>46077.37853141203</v>
+        <v>46077.545198078704</v>
       </c>
       <c r="C97" s="8">
-        <v>46191.61973840278</v>
+        <v>46191.78640506945</v>
       </c>
       <c r="D97" s="8">
-        <v>46191.61975438657</v>
+        <v>46191.78642105324</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I97" s="8">
         <v>46154</v>
@@ -7621,13 +7627,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O97" s="9" t="s">
         <v>133</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q97" s="8">
         <v>46155</v>
@@ -7647,28 +7653,28 @@
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B98" s="5">
-        <v>46077.37853112268</v>
+        <v>46077.54519778935</v>
       </c>
       <c r="C98" s="5">
-        <v>46191.619919212964</v>
+        <v>46191.78658587963</v>
       </c>
       <c r="D98" s="5">
-        <v>46191.61993555556</v>
+        <v>46191.78660222222</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I98" s="5">
         <v>46139</v>
@@ -7686,13 +7692,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O98" s="6" t="s">
         <v>145</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q98" s="5">
         <v>46140</v>
@@ -7707,31 +7713,31 @@
         <v>1</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B99" s="8">
-        <v>46077.37853408565</v>
+        <v>46077.54520075231</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46126.66394534722</v>
+        <v>46126.83061201389</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I99" s="8">
         <v>46071</v>
@@ -7749,13 +7755,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O99" s="9" t="s">
         <v>163</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="Q99" s="8">
         <v>46072</v>
@@ -7775,14 +7781,14 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B100" s="5">
-        <v>46077.378530682865</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46182.52589795139</v>
+        <v>46182.69256461806</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>58</v>
@@ -7791,10 +7797,10 @@
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I100" s="5">
         <v>46125</v>
@@ -7812,13 +7818,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O100" s="6" t="s">
         <v>154</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="Q100" s="5">
         <v>46126</v>
@@ -7838,26 +7844,26 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B101" s="8">
-        <v>46077.39129883102</v>
+        <v>46077.55796549769</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46192.62633465278</v>
+        <v>46192.79300131944</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I101" s="8">
         <v>46122</v>
@@ -7875,13 +7881,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O101" s="9" t="s">
         <v>174</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="Q101" s="8">
         <v>46125</v>
@@ -7901,26 +7907,26 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.623623680556</v>
+        <v>46125.79029034722</v>
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46125.737085706016</v>
+        <v>46125.90375237269</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="I102" s="5">
         <v>46114</v>
@@ -7938,13 +7944,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="O102" s="6" t="s">
         <v>201</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q102" s="5">
         <v>46115</v>
@@ -7958,17 +7964,17 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B103" s="8">
-        <v>46077.37853174769</v>
+        <v>46077.54519841435</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.702618877316</v>
+        <v>46195.86928554398</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>25</v>
@@ -7992,7 +7998,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>26</v>
@@ -8005,19 +8011,19 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.37853209491</v>
+        <v>46077.545198761574</v>
       </c>
       <c r="C104" s="5">
-        <v>46195.702613182875</v>
+        <v>46195.86927984953</v>
       </c>
       <c r="D104" s="5">
-        <v>46195.70262856482</v>
+        <v>46195.86929523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
@@ -8044,13 +8050,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q104" s="5">
         <v>46150</v>
@@ -8065,19 +8071,19 @@
         <v>1</v>
       </c>
       <c r="U104" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.618860069444</v>
+        <v>46125.785526736116</v>
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46193.787331921296</v>
+        <v>46193.95399858797</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>235</v>
@@ -8107,13 +8113,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8123,17 +8129,17 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.619656145835</v>
+        <v>46125.7863228125</v>
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46193.78734185185</v>
+        <v>46193.954008518514</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
@@ -8160,13 +8166,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8176,17 +8182,17 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B107" s="8">
-        <v>46077.39166046296</v>
+        <v>46077.558327129635</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46154.001161458335</v>
+        <v>46154.167828125</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
@@ -8213,13 +8219,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q107" s="8">
         <v>46154</v>
@@ -8234,19 +8240,19 @@
         <v>0</v>
       </c>
       <c r="U107" s="12" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.62647851852</v>
+        <v>46125.793145185184</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46154.00229175926</v>
+        <v>46154.16895842593</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>235</v>
@@ -8276,13 +8282,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8292,17 +8298,17 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.62659856481</v>
+        <v>46125.79326523148</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46154.00229326389</v>
+        <v>46154.168959930554</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
@@ -8329,13 +8335,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8345,17 +8351,17 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B110" s="5">
-        <v>46077.378532800925</v>
+        <v>46077.5451994676</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46197.33798239584</v>
+        <v>46197.504649062495</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
@@ -8382,13 +8388,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q110" s="5">
         <v>46126</v>
@@ -8408,16 +8414,16 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.62675127314</v>
+        <v>46125.793417939814</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.33797652778</v>
+        <v>46197.50464319444</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.33797853009</v>
+        <v>46197.504645196765</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>235</v>
@@ -8447,13 +8453,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8463,17 +8469,17 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.6268628588</v>
+        <v>46125.793529525465</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46191.61992706019</v>
+        <v>46191.78659372685</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
@@ -8500,13 +8506,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8516,17 +8522,17 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B113" s="8">
-        <v>46077.37853313657</v>
+        <v>46077.54519980324</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.44193503472</v>
+        <v>46197.60860170139</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
@@ -8553,13 +8559,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q113" s="8">
         <v>46160</v>
@@ -8579,14 +8585,14 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.62697039352</v>
+        <v>46125.79363706018</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.44193149306</v>
+        <v>46197.60859815972</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>235</v>
@@ -8616,13 +8622,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8632,17 +8638,17 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.62709875</v>
+        <v>46125.79376541667</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46192.62414865741</v>
+        <v>46192.79081532407</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
@@ -8669,13 +8675,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8685,17 +8691,17 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B116" s="5">
-        <v>46077.37853243056</v>
+        <v>46077.54519909722</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.44177774306</v>
+        <v>46197.60844440972</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
@@ -8722,13 +8728,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q116" s="5">
         <v>46162</v>
@@ -8748,16 +8754,16 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.62742210648</v>
+        <v>46125.79408877315</v>
       </c>
       <c r="C117" s="8">
-        <v>46197.43291145834</v>
+        <v>46197.599578124995</v>
       </c>
       <c r="D117" s="8">
-        <v>46197.44193552084</v>
+        <v>46197.6086021875</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>235</v>
@@ -8787,13 +8793,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8803,17 +8809,17 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.62755608796</v>
+        <v>46125.79422275463</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46191.61974576389</v>
+        <v>46191.786412430556</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
@@ -8840,13 +8846,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8856,17 +8862,17 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B119" s="8">
-        <v>46077.37853346065</v>
+        <v>46077.545200127315</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46165.030673483794</v>
+        <v>46165.197340150466</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
@@ -8893,13 +8899,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q119" s="8">
         <v>46164</v>
@@ -8919,14 +8925,14 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.62767509259</v>
+        <v>46125.79434175926</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46197.43292009259</v>
+        <v>46197.59958675926</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>235</v>
@@ -8954,13 +8960,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O120" s="6" t="s">
         <v>235</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8970,17 +8976,17 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.62779353009</v>
+        <v>46125.79446019676</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46164.00248363426</v>
+        <v>46164.16915030092</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
@@ -9005,13 +9011,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9021,17 +9027,17 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B122" s="5">
-        <v>46077.37853377315</v>
+        <v>46077.54520043981</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46169.02913077547</v>
+        <v>46169.19579744213</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
@@ -9058,13 +9064,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="Q122" s="5">
         <v>46168</v>
@@ -9084,14 +9090,14 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.62793141203</v>
+        <v>46125.794598078704</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.002096655095</v>
+        <v>46168.16876332176</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>235</v>
@@ -9119,13 +9125,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O123" s="9" t="s">
         <v>235</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9135,17 +9141,17 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.62805658564</v>
+        <v>46125.794723252315</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46168.00209804398</v>
+        <v>46168.168764710645</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
@@ -9170,13 +9176,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9186,17 +9192,17 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.37853105324</v>
+        <v>46077.54519771991</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46125.74054834491</v>
+        <v>46125.907215011575</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>25</v>
@@ -9220,7 +9226,7 @@
         <v>26</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>26</v>
@@ -9233,26 +9239,26 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B126" s="5">
-        <v>46077.378531504626</v>
+        <v>46077.5451981713</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46170.032856238424</v>
+        <v>46170.199522905095</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I126" s="5">
         <v>46169</v>
@@ -9270,13 +9276,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q126" s="5">
         <v>46169</v>
@@ -9296,14 +9302,14 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.64569723379</v>
+        <v>46125.81236390046</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46169.0018784375</v>
+        <v>46169.16854510417</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>235</v>
@@ -9312,10 +9318,10 @@
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -9331,13 +9337,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O127" s="9" t="s">
         <v>235</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9347,26 +9353,26 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.64585586806</v>
+        <v>46125.81252253472</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46169.0018800463</v>
+        <v>46169.168546712965</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -9382,13 +9388,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9398,26 +9404,26 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B129" s="8">
-        <v>46125.6460805324</v>
+        <v>46125.812747199074</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.00188140046</v>
+        <v>46169.16854806713</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9433,13 +9439,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O129" s="9" t="s">
         <v>57</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9449,14 +9455,14 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.646602141205</v>
+        <v>46125.81326880787</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.001882743054</v>
+        <v>46169.16854940972</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>61</v>
@@ -9465,10 +9471,10 @@
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9484,13 +9490,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O130" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9500,14 +9506,14 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.647173634265</v>
+        <v>46125.81384030092</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46169.00188401621</v>
+        <v>46169.168550682865</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>64</v>
@@ -9516,10 +9522,10 @@
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9535,13 +9541,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O131" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9551,14 +9557,14 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.647435543986</v>
+        <v>46125.81410221064</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46169.001885624995</v>
+        <v>46169.16855229167</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>67</v>
@@ -9567,10 +9573,10 @@
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9586,13 +9592,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="O132" s="6" t="s">
         <v>67</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9602,17 +9608,17 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B133" s="8">
-        <v>46077.37853181713</v>
+        <v>46077.5451984838</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46175.03565800926</v>
+        <v>46175.20232467593</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
@@ -9639,13 +9645,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q133" s="8">
         <v>46174</v>
@@ -9665,14 +9671,14 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.64815408565</v>
+        <v>46125.81482075232</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46174.00276666667</v>
+        <v>46174.16943333333</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>235</v>
@@ -9702,13 +9708,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O134" s="6" t="s">
         <v>235</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9718,17 +9724,17 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.64828011574</v>
+        <v>46125.81494678241</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46174.00276837963</v>
+        <v>46174.16943504629</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
@@ -9755,13 +9761,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9771,17 +9777,17 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.64849368056</v>
+        <v>46125.81516034722</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46174.002769733794</v>
+        <v>46174.169436400465</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
@@ -9808,13 +9814,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9824,14 +9830,14 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.64864410879</v>
+        <v>46125.81531077546</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46174.00277118056</v>
+        <v>46174.169437847224</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>61</v>
@@ -9861,13 +9867,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O137" s="9" t="s">
         <v>61</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9877,14 +9883,14 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.6487852662</v>
+        <v>46125.81545193287</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46174.002772604166</v>
+        <v>46174.16943927083</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>64</v>
@@ -9914,13 +9920,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O138" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9930,17 +9936,17 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.64890609954</v>
+        <v>46125.81557276621</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46174.002773796296</v>
+        <v>46174.16944046297</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
@@ -9967,13 +9973,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="O139" s="9" t="s">
         <v>67</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -9983,26 +9989,26 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B140" s="5">
-        <v>46077.37853229167</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46176.029254189816</v>
+        <v>46176.19592085648</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I140" s="5">
         <v>46175</v>
@@ -10020,13 +10026,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="Q140" s="5">
         <v>46175</v>
@@ -10046,14 +10052,14 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.64911434028</v>
+        <v>46125.815781006946</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46175.001645798606</v>
+        <v>46175.16831246528</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>235</v>
@@ -10062,10 +10068,10 @@
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -10081,13 +10087,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O141" s="9" t="s">
         <v>235</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10097,26 +10103,26 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.64925351852</v>
+        <v>46125.81592018518</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46175.00164739584</v>
+        <v>46175.168314062495</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10132,13 +10138,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10148,14 +10154,14 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.64939738426</v>
+        <v>46125.81606405093</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46175.00164880787</v>
+        <v>46175.16831547454</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>57</v>
@@ -10164,10 +10170,10 @@
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10183,13 +10189,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10199,14 +10205,14 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.64952605324</v>
+        <v>46125.81619271991</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46175.00165010417</v>
+        <v>46175.16831677083</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>61</v>
@@ -10215,10 +10221,10 @@
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10234,13 +10240,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O144" s="6" t="s">
         <v>61</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10250,14 +10256,14 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.64965439815</v>
+        <v>46125.81632106482</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46175.00165146991</v>
+        <v>46175.16831813657</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>64</v>
@@ -10266,10 +10272,10 @@
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -10285,13 +10291,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O145" s="9" t="s">
         <v>64</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10301,26 +10307,26 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.649802002314</v>
+        <v>46125.816468668985</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46175.00165288194</v>
+        <v>46175.16831954861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10336,13 +10342,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10352,26 +10358,26 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B147" s="8">
-        <v>46077.37853260417</v>
+        <v>46077.54519927083</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46177.02263348379</v>
+        <v>46177.189300150465</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I147" s="8">
         <v>46176</v>
@@ -10389,13 +10395,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q147" s="8">
         <v>46176</v>
@@ -10415,14 +10421,14 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.649941006945</v>
+        <v>46125.81660767361</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46176.00170306713</v>
+        <v>46176.1683697338</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>235</v>
@@ -10431,10 +10437,10 @@
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10450,13 +10456,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O148" s="6" t="s">
         <v>235</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10466,26 +10472,26 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.650069166666</v>
+        <v>46125.81673583333</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46176.00170451389</v>
+        <v>46176.16837118055</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10501,13 +10507,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10517,26 +10523,26 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.650201331024</v>
+        <v>46125.81686799768</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46176.0017056713</v>
+        <v>46176.16837233797</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10552,13 +10558,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O150" s="6" t="s">
         <v>57</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10568,14 +10574,14 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.65031788194</v>
+        <v>46125.81698454861</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46176.00170678241</v>
+        <v>46176.16837344907</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>61</v>
@@ -10584,10 +10590,10 @@
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10603,13 +10609,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O151" s="9" t="s">
         <v>61</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10619,14 +10625,14 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.650468148146</v>
+        <v>46125.81713481482</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46176.00170797454</v>
+        <v>46176.1683746412</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>64</v>
@@ -10635,10 +10641,10 @@
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10654,13 +10660,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O152" s="6" t="s">
         <v>64</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10670,26 +10676,26 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B153" s="8">
-        <v>46125.650595520834</v>
+        <v>46125.8172621875</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46176.001709178236</v>
+        <v>46176.16837584491</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10705,13 +10711,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10721,17 +10727,17 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B154" s="5">
-        <v>46077.37853299768</v>
+        <v>46077.54519966435</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46125.740548368056</v>
+        <v>46125.90721503472</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>25</v>
@@ -10755,7 +10761,7 @@
         <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10768,26 +10774,26 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.378533298615</v>
+        <v>46077.54519996527</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46186.034677986114</v>
+        <v>46186.20134465278</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="I155" s="8">
         <v>46177</v>
@@ -10805,13 +10811,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q155" s="8">
         <v>46185</v>
@@ -10831,26 +10837,26 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.37853361111</v>
+        <v>46077.545200277775</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46186.0346780324</v>
+        <v>46186.201344699075</v>
       </c>
       <c r="E156" s="6" t="s">
+        <v>454</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>452</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>449</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>450</v>
       </c>
       <c r="I156" s="5">
         <v>46177</v>
@@ -10868,13 +10874,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="Q156" s="5">
         <v>46185</v>
@@ -10894,17 +10900,17 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="B157" s="8">
-        <v>46090.54328194444</v>
+        <v>46090.70994861111</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46125.74112125</v>
+        <v>46125.907787916665</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>25</v>
@@ -10928,7 +10934,7 @@
         <v>26</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>26</v>
@@ -10947,17 +10953,17 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.54338682871</v>
+        <v>46090.71005349537</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46185.03103875</v>
+        <v>46185.197705416664</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -10984,13 +10990,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Q158" s="5">
         <v>46184</v>
@@ -11010,17 +11016,17 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.54293944444</v>
+        <v>46090.70960611111</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46196.00701340278</v>
+        <v>46196.17368006945</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -11047,13 +11053,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="Q159" s="8">
         <v>46195</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5922,7 +5922,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.708269930554</v>
+        <v>46197.85981012732</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -8698,7 +8698,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46197.60844440972</v>
+        <v>46198.61729309028</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>364</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5700,7 +5700,7 @@
         <v>46195.659945023144</v>
       </c>
       <c r="D64" s="5">
-        <v>46195.6599575</v>
+        <v>46198.83151038195</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>219</v>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46168.17332814814</v>
+        <v>46198.7984696875</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>254</v>
@@ -6608,9 +6608,11 @@
       <c r="B80" s="5">
         <v>46077.54519710648</v>
       </c>
-      <c r="C80" s="6"/>
+      <c r="C80" s="5">
+        <v>46198.83128773148</v>
+      </c>
       <c r="D80" s="5">
-        <v>46191.76957280093</v>
+        <v>46198.831302199076</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>262</v>
@@ -6644,10 +6646,12 @@
       </c>
       <c r="Q80" s="6"/>
       <c r="R80" s="6"/>
-      <c r="S80" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="T80" s="6"/>
+      <c r="S80" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T80" s="6">
+        <v>1</v>
+      </c>
       <c r="U80" s="6"/>
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
@@ -6787,9 +6791,11 @@
       <c r="B83" s="8">
         <v>46125.699760648145</v>
       </c>
-      <c r="C83" s="9"/>
+      <c r="C83" s="8">
+        <v>46198.83126899306</v>
+      </c>
       <c r="D83" s="8">
-        <v>46195.65994334491</v>
+        <v>46198.83128892361</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>273</v>
@@ -6833,11 +6839,11 @@
       <c r="R83" s="8">
         <v>46094</v>
       </c>
-      <c r="S83" s="12" t="s">
-        <v>122</v>
+      <c r="S83" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T83" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U83" s="11" t="s">
         <v>32</v>
@@ -7027,7 +7033,7 @@
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46125.9107300926</v>
+        <v>46198.831276655095</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>274</v>
@@ -7725,7 +7731,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46126.83061201389</v>
+        <v>46198.83795861111</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>321</v>
@@ -7851,7 +7857,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46192.79300131944</v>
+        <v>46198.839731319444</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>325</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -2583,7 +2583,7 @@
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46133.17089466435</v>
+        <v>46198.87202709491</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>57</v>
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46133.17089664352</v>
+        <v>46198.872028495374</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>61</v>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46133.17089804398</v>
+        <v>46198.872029826394</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>64</v>
@@ -2742,7 +2742,7 @@
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46133.17089929398</v>
+        <v>46198.87203136574</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>67</v>
@@ -7554,7 +7554,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46191.786592488425</v>
+        <v>46198.87202574074</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>262</v>
@@ -7792,9 +7792,11 @@
       <c r="B100" s="5">
         <v>46077.54519734954</v>
       </c>
-      <c r="C100" s="6"/>
+      <c r="C100" s="5">
+        <v>46198.872020173614</v>
+      </c>
       <c r="D100" s="5">
-        <v>46182.69256461806</v>
+        <v>46198.87203554398</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>58</v>
@@ -7838,11 +7840,11 @@
       <c r="R100" s="5">
         <v>46125</v>
       </c>
-      <c r="S100" s="12" t="s">
-        <v>122</v>
+      <c r="S100" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T100" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U100" s="11" t="s">
         <v>32</v>
@@ -7857,7 +7859,7 @@
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46198.839731319444</v>
+        <v>46198.87327074074</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>325</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -7731,7 +7731,7 @@
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46198.83795861111</v>
+        <v>46199.847719363424</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>321</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -7924,9 +7924,11 @@
       <c r="B102" s="5">
         <v>46125.79029034722</v>
       </c>
-      <c r="C102" s="6"/>
+      <c r="C102" s="5">
+        <v>46204.68543188657</v>
+      </c>
       <c r="D102" s="5">
-        <v>46204.659611875</v>
+        <v>46204.68545116898</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>327</v>
@@ -7970,10 +7972,12 @@
       <c r="R102" s="5">
         <v>46114</v>
       </c>
-      <c r="S102" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="T102" s="6"/>
+      <c r="S102" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="T102" s="6">
+        <v>1</v>
+      </c>
       <c r="U102" s="6"/>
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
@@ -8097,7 +8101,7 @@
       </c>
       <c r="C105" s="9"/>
       <c r="D105" s="8">
-        <v>46193.95399858797</v>
+        <v>46204.68543935185</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>235</v>
@@ -8150,7 +8154,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46193.954008518514</v>
+        <v>46204.685440601854</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>239</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1879" uniqueCount="466">
   <si>
     <t>50001499- EQ. CHAPARRAL</t>
   </si>
@@ -173,6 +173,12 @@
   </si>
   <si>
     <t>Revisión tableros pruebas</t>
+  </si>
+  <si>
+    <t>sergio saavedra fernandez</t>
+  </si>
+  <si>
+    <t>sergio.saavedra@zitron.com</t>
   </si>
   <si>
     <t xml:space="preserve">OT 4217 TABLERO VDF 400 KW,OT 4218 TABLERO PLC,OT 4226 TABLERO VDF 575 KW,OT 4227 TABLERO PLC - MT </t>
@@ -2520,7 +2526,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46135.19105782408</v>
+        <v>46204.87323738426</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2529,10 +2535,10 @@
         <v>26</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I12" s="5">
         <v>46127</v>
@@ -2553,7 +2559,7 @@
         <v>45</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="P12" s="6" t="s">
         <v>45</v>
@@ -2565,7 +2571,7 @@
         <v>46127</v>
       </c>
       <c r="S12" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T12" s="6">
         <v>0</v>
@@ -2576,26 +2582,26 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B13" s="8">
         <v>46125.8197722801</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46198.87202709491</v>
+        <v>46204.87334092593</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F13" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G13" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I13" s="8">
         <v>46127</v>
@@ -2616,10 +2622,10 @@
         <v>53</v>
       </c>
       <c r="O13" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P13" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="Q13" s="9"/>
       <c r="R13" s="9"/>
@@ -2629,26 +2635,26 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B14" s="5">
         <v>46125.820048113426</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46198.872028495374</v>
+        <v>46204.8733403125</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I14" s="5">
         <v>46127</v>
@@ -2669,10 +2675,10 @@
         <v>53</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
@@ -2682,26 +2688,26 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="B15" s="8">
         <v>46125.82033290509</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46198.872029826394</v>
+        <v>46204.8733396875</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I15" s="8">
         <v>46127</v>
@@ -2722,10 +2728,10 @@
         <v>53</v>
       </c>
       <c r="O15" s="9" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P15" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="Q15" s="9"/>
       <c r="R15" s="9"/>
@@ -2735,26 +2741,26 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B16" s="5">
         <v>46125.82063702546</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46198.87203136574</v>
+        <v>46204.87333894676</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G16" s="6" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="I16" s="5">
         <v>46127</v>
@@ -2775,10 +2781,10 @@
         <v>53</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="Q16" s="6"/>
       <c r="R16" s="6"/>
@@ -2788,7 +2794,7 @@
     </row>
     <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B17" s="8">
         <v>46077.5452015162</v>
@@ -2800,7 +2806,7 @@
         <v>46114.50535017361</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="F17" s="9" t="s">
         <v>25</v>
@@ -2824,7 +2830,7 @@
         <v>26</v>
       </c>
       <c r="O17" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="P17" s="9" t="s">
         <v>26</v>
@@ -2841,7 +2847,7 @@
     </row>
     <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B18" s="5">
         <v>46077.54519763889</v>
@@ -2853,7 +2859,7 @@
         <v>46097.552399583336</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>26</v>
@@ -2880,13 +2886,13 @@
         <v>26</v>
       </c>
       <c r="N18" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O18" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P18" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="Q18" s="5">
         <v>46003</v>
@@ -2906,7 +2912,7 @@
     </row>
     <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="7" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B19" s="8">
         <v>46077.54519880787</v>
@@ -2918,7 +2924,7 @@
         <v>46114.505018090276</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>26</v>
@@ -2945,13 +2951,13 @@
         <v>26</v>
       </c>
       <c r="N19" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>40</v>
       </c>
       <c r="P19" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="Q19" s="8">
         <v>46010</v>
@@ -2971,7 +2977,7 @@
     </row>
     <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="B20" s="5">
         <v>46077.545199155094</v>
@@ -2983,7 +2989,7 @@
         <v>46125.76278827546</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F20" s="6" t="s">
         <v>26</v>
@@ -3010,13 +3016,13 @@
         <v>26</v>
       </c>
       <c r="N20" s="6" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O20" s="6" t="s">
         <v>40</v>
       </c>
       <c r="P20" s="6" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="Q20" s="5">
         <v>46010</v>
@@ -3036,7 +3042,7 @@
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B21" s="8">
         <v>46077.54519956018</v>
@@ -3048,7 +3054,7 @@
         <v>46114.50533729167</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F21" s="9" t="s">
         <v>26</v>
@@ -3075,13 +3081,13 @@
         <v>26</v>
       </c>
       <c r="N21" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="O21" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="P21" s="9" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="Q21" s="8">
         <v>46010</v>
@@ -3101,7 +3107,7 @@
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B22" s="5">
         <v>46077.54519991898</v>
@@ -3113,7 +3119,7 @@
         <v>46191.76425234954</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>25</v>
@@ -3137,7 +3143,7 @@
         <v>26</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="P22" s="6" t="s">
         <v>26</v>
@@ -3150,7 +3156,7 @@
     </row>
     <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="B23" s="8">
         <v>46077.545200625</v>
@@ -3162,7 +3168,7 @@
         <v>46097.55245158565</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F23" s="9" t="s">
         <v>26</v>
@@ -3189,13 +3195,13 @@
         <v>26</v>
       </c>
       <c r="N23" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O23" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="P23" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="Q23" s="8">
         <v>46007</v>
@@ -3215,7 +3221,7 @@
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="B24" s="5">
         <v>46077.545200312496</v>
@@ -3227,7 +3233,7 @@
         <v>46135.764537361116</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>26</v>
@@ -3254,13 +3260,13 @@
         <v>26</v>
       </c>
       <c r="N24" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P24" s="6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="Q24" s="5">
         <v>46014</v>
@@ -3280,7 +3286,7 @@
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B25" s="8">
         <v>46077.54520094907</v>
@@ -3292,7 +3298,7 @@
         <v>46114.50691030093</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F25" s="9" t="s">
         <v>26</v>
@@ -3319,13 +3325,13 @@
         <v>26</v>
       </c>
       <c r="N25" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O25" s="9" t="s">
         <v>48</v>
       </c>
       <c r="P25" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="Q25" s="8">
         <v>46008</v>
@@ -3345,7 +3351,7 @@
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B26" s="5">
         <v>46077.54520128472</v>
@@ -3357,16 +3363,16 @@
         <v>46122.6274699537</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I26" s="5">
         <v>46013</v>
@@ -3384,13 +3390,13 @@
         <v>26</v>
       </c>
       <c r="N26" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P26" s="6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Q26" s="5">
         <v>46014</v>
@@ -3410,7 +3416,7 @@
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B27" s="8">
         <v>46077.553287766204</v>
@@ -3422,7 +3428,7 @@
         <v>46114.50608950232</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>26</v>
@@ -3449,13 +3455,13 @@
         <v>26</v>
       </c>
       <c r="N27" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O27" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P27" s="9" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="Q27" s="8">
         <v>46014</v>
@@ -3475,7 +3481,7 @@
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B28" s="5">
         <v>46077.54519655093</v>
@@ -3487,16 +3493,16 @@
         <v>46191.76406943287</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F28" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G28" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I28" s="5">
         <v>46076</v>
@@ -3514,13 +3520,13 @@
         <v>26</v>
       </c>
       <c r="N28" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P28" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="Q28" s="5">
         <v>46015</v>
@@ -3540,7 +3546,7 @@
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B29" s="8">
         <v>46125.69234111111</v>
@@ -3552,16 +3558,16 @@
         <v>46191.764096643514</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F29" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G29" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I29" s="8">
         <v>46076</v>
@@ -3579,13 +3585,13 @@
         <v>26</v>
       </c>
       <c r="N29" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O29" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P29" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="Q29" s="8">
         <v>46136</v>
@@ -3605,7 +3611,7 @@
     </row>
     <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>46125.69240738426</v>
@@ -3617,16 +3623,16 @@
         <v>46191.764121307875</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F30" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G30" s="6" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I30" s="5">
         <v>46076</v>
@@ -3644,13 +3650,13 @@
         <v>26</v>
       </c>
       <c r="N30" s="6" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P30" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="Q30" s="5">
         <v>46136</v>
@@ -3670,7 +3676,7 @@
     </row>
     <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B31" s="8">
         <v>46125.69558788194</v>
@@ -3682,16 +3688,16 @@
         <v>46191.76416752315</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F31" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G31" s="9" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H31" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I31" s="8">
         <v>46076</v>
@@ -3709,13 +3715,13 @@
         <v>26</v>
       </c>
       <c r="N31" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="O31" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P31" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="Q31" s="8">
         <v>46136</v>
@@ -3735,7 +3741,7 @@
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B32" s="5">
         <v>46077.545196886575</v>
@@ -3745,7 +3751,7 @@
         <v>46182.69258219907</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F32" s="6" t="s">
         <v>25</v>
@@ -3769,7 +3775,7 @@
         <v>26</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P32" s="6" t="s">
         <v>26</v>
@@ -3777,14 +3783,14 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B33" s="8">
         <v>46077.54519711806</v>
@@ -3796,16 +3802,16 @@
         <v>46155.87452380787</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F33" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G33" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H33" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I33" s="8">
         <v>46008</v>
@@ -3823,13 +3829,13 @@
         <v>26</v>
       </c>
       <c r="N33" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="P33" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q33" s="8">
         <v>46153</v>
@@ -3838,18 +3844,18 @@
         <v>46008</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
       </c>
       <c r="U33" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="B34" s="5">
         <v>46077.54519739583</v>
@@ -3861,16 +3867,16 @@
         <v>46114.50552802083</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F34" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I34" s="5">
         <v>46008</v>
@@ -3888,13 +3894,13 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="P34" s="6" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="Q34" s="5">
         <v>46030</v>
@@ -3903,18 +3909,18 @@
         <v>46007</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
       </c>
       <c r="U34" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="7" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B35" s="8">
         <v>46077.54519766204</v>
@@ -3926,16 +3932,16 @@
         <v>46155.86621849537</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H35" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I35" s="8">
         <v>46028</v>
@@ -3953,13 +3959,13 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O35" s="9" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P35" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="Q35" s="8">
         <v>46162</v>
@@ -3968,18 +3974,18 @@
         <v>46034</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
       </c>
       <c r="U35" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="B36" s="5">
         <v>46077.54519791667</v>
@@ -3991,16 +3997,16 @@
         <v>46125.91364752315</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F36" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I36" s="5">
         <v>46028</v>
@@ -4018,13 +4024,13 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="P36" s="6" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="Q36" s="5">
         <v>46071</v>
@@ -4033,18 +4039,18 @@
         <v>46031</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
       </c>
       <c r="U36" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="7" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B37" s="8">
         <v>46077.54519712963</v>
@@ -4056,16 +4062,16 @@
         <v>46158.75835697917</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F37" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H37" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I37" s="8">
         <v>46015</v>
@@ -4083,13 +4089,13 @@
         <v>26</v>
       </c>
       <c r="N37" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O37" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="P37" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q37" s="8">
         <v>46136</v>
@@ -4098,7 +4104,7 @@
         <v>46015</v>
       </c>
       <c r="S37" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -4109,7 +4115,7 @@
     </row>
     <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="4" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B38" s="5">
         <v>46077.54519734954</v>
@@ -4121,16 +4127,16 @@
         <v>46097.552318773145</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F38" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I38" s="5">
         <v>46015</v>
@@ -4148,13 +4154,13 @@
         <v>26</v>
       </c>
       <c r="N38" s="6" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="P38" s="6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="Q38" s="5">
         <v>46016</v>
@@ -4163,18 +4169,18 @@
         <v>46014</v>
       </c>
       <c r="S38" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
       </c>
       <c r="U38" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="7" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B39" s="8">
         <v>46077.545197569445</v>
@@ -4186,16 +4192,16 @@
         <v>46155.89548886574</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F39" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H39" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I39" s="8">
         <v>46020</v>
@@ -4213,13 +4219,13 @@
         <v>26</v>
       </c>
       <c r="N39" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O39" s="9" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="P39" s="9" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q39" s="8">
         <v>46135</v>
@@ -4228,18 +4234,18 @@
         <v>46017</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
       </c>
       <c r="U39" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B40" s="5">
         <v>46077.54519778935</v>
@@ -4251,16 +4257,16 @@
         <v>46182.69257489583</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H40" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I40" s="5">
         <v>46009</v>
@@ -4278,13 +4284,13 @@
         <v>26</v>
       </c>
       <c r="N40" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="P40" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q40" s="5">
         <v>46122</v>
@@ -4304,7 +4310,7 @@
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B41" s="8">
         <v>46077.54519805555</v>
@@ -4316,16 +4322,16 @@
         <v>46182.68151998843</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F41" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H41" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I41" s="8">
         <v>46009</v>
@@ -4343,13 +4349,13 @@
         <v>26</v>
       </c>
       <c r="N41" s="9" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O41" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P41" s="9" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="Q41" s="8">
         <v>46021</v>
@@ -4358,18 +4364,18 @@
         <v>46014</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
       </c>
       <c r="U41" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B42" s="5">
         <v>46077.54519827546</v>
@@ -4381,16 +4387,16 @@
         <v>46182.692548946754</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F42" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I42" s="5">
         <v>46021</v>
@@ -4408,13 +4414,13 @@
         <v>26</v>
       </c>
       <c r="N42" s="6" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="P42" s="6" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q42" s="5">
         <v>46122</v>
@@ -4423,18 +4429,18 @@
         <v>46022</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
       </c>
       <c r="U42" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="7" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B43" s="8">
         <v>46077.54519849537</v>
@@ -4446,16 +4452,16 @@
         <v>46126.830619456014</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F43" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I43" s="8">
         <v>46015</v>
@@ -4473,13 +4479,13 @@
         <v>26</v>
       </c>
       <c r="N43" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O43" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="P43" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q43" s="8">
         <v>46070</v>
@@ -4499,7 +4505,7 @@
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="B44" s="5">
         <v>46077.54519873843</v>
@@ -4511,16 +4517,16 @@
         <v>46126.829137256944</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F44" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I44" s="5">
         <v>46015</v>
@@ -4538,13 +4544,13 @@
         <v>26</v>
       </c>
       <c r="N44" s="6" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="P44" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="Q44" s="5">
         <v>46016</v>
@@ -4553,18 +4559,18 @@
         <v>46014</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
       </c>
       <c r="U44" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="7" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B45" s="8">
         <v>46077.54519680556</v>
@@ -4576,16 +4582,16 @@
         <v>46126.83059262732</v>
       </c>
       <c r="E45" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F45" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H45" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="I45" s="8">
         <v>46020</v>
@@ -4603,13 +4609,13 @@
         <v>26</v>
       </c>
       <c r="N45" s="9" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O45" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="P45" s="9" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="Q45" s="8">
         <v>46070</v>
@@ -4618,18 +4624,18 @@
         <v>46017</v>
       </c>
       <c r="S45" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T45" s="9">
         <v>0</v>
       </c>
       <c r="U45" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B46" s="5">
         <v>46077.58916118056</v>
@@ -4641,16 +4647,16 @@
         <v>46126.829593946764</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="F46" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G46" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I46" s="5">
         <v>46015</v>
@@ -4668,13 +4674,13 @@
         <v>26</v>
       </c>
       <c r="N46" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O46" s="6" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P46" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q46" s="5">
         <v>46121</v>
@@ -4694,7 +4700,7 @@
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="7" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B47" s="8">
         <v>46077.589282581015</v>
@@ -4706,16 +4712,16 @@
         <v>46126.82903986111</v>
       </c>
       <c r="E47" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F47" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G47" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H47" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I47" s="8">
         <v>46015</v>
@@ -4733,13 +4739,13 @@
         <v>26</v>
       </c>
       <c r="N47" s="9" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O47" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="P47" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="Q47" s="8">
         <v>46052</v>
@@ -4748,18 +4754,18 @@
         <v>46014</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
       </c>
       <c r="U47" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B48" s="5">
         <v>46077.589497685185</v>
@@ -4771,16 +4777,16 @@
         <v>46126.829567256944</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F48" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G48" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I48" s="5">
         <v>46044</v>
@@ -4798,13 +4804,13 @@
         <v>26</v>
       </c>
       <c r="N48" s="6" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="O48" s="6" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P48" s="6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="Q48" s="5">
         <v>46134</v>
@@ -4813,18 +4819,18 @@
         <v>46055</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
       </c>
       <c r="U48" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A49" s="7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="B49" s="8">
         <v>46077.54519818287</v>
@@ -4836,16 +4842,16 @@
         <v>46147.8881425</v>
       </c>
       <c r="E49" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F49" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G49" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I49" s="8">
         <v>46078</v>
@@ -4863,13 +4869,13 @@
         <v>26</v>
       </c>
       <c r="N49" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O49" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="P49" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="Q49" s="8">
         <v>46069</v>
@@ -4889,7 +4895,7 @@
     </row>
     <row r="50" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="B50" s="5">
         <v>46077.545198437496</v>
@@ -4901,16 +4907,16 @@
         <v>46191.764061747686</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F50" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G50" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I50" s="5">
         <v>46078</v>
@@ -4928,13 +4934,13 @@
         <v>26</v>
       </c>
       <c r="N50" s="6" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O50" s="6" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="P50" s="6" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="Q50" s="5">
         <v>46037</v>
@@ -4943,18 +4949,18 @@
         <v>46014</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
       </c>
       <c r="U50" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A51" s="7" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B51" s="8">
         <v>46077.54519870371</v>
@@ -4966,16 +4972,16 @@
         <v>46150.78326474537</v>
       </c>
       <c r="E51" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F51" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G51" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H51" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I51" s="8">
         <v>46085</v>
@@ -4993,13 +4999,13 @@
         <v>26</v>
       </c>
       <c r="N51" s="9" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O51" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P51" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="Q51" s="8">
         <v>46069</v>
@@ -5008,18 +5014,18 @@
         <v>46038</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
       </c>
       <c r="U51" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="B52" s="5">
         <v>46125.69589043982</v>
@@ -5031,16 +5037,16 @@
         <v>46191.76988886574</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F52" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G52" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H52" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I52" s="5">
         <v>46078</v>
@@ -5058,10 +5064,10 @@
         <v>26</v>
       </c>
       <c r="N52" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O52" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="P52" s="6" t="s">
         <v>26</v>
@@ -5073,7 +5079,7 @@
         <v>46078</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -5084,7 +5090,7 @@
     </row>
     <row r="53" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A53" s="7" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B53" s="8">
         <v>46125.70470673611</v>
@@ -5096,16 +5102,16 @@
         <v>46191.76981975694</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F53" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I53" s="8">
         <v>46078</v>
@@ -5123,13 +5129,13 @@
         <v>26</v>
       </c>
       <c r="N53" s="9" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O53" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="P53" s="9" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q53" s="9"/>
       <c r="R53" s="9"/>
@@ -5139,7 +5145,7 @@
     </row>
     <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" s="4" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="B54" s="5">
         <v>46125.704894062495</v>
@@ -5151,16 +5157,16 @@
         <v>46191.76987484954</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F54" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G54" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H54" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I54" s="5">
         <v>46085</v>
@@ -5178,13 +5184,13 @@
         <v>26</v>
       </c>
       <c r="N54" s="6" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O54" s="6" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="P54" s="6" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Q54" s="6"/>
       <c r="R54" s="6"/>
@@ -5194,7 +5200,7 @@
     </row>
     <row r="55" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A55" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B55" s="8">
         <v>46125.68332820602</v>
@@ -5206,16 +5212,16 @@
         <v>46204.65962090278</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F55" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I55" s="8">
         <v>46078</v>
@@ -5233,10 +5239,10 @@
         <v>26</v>
       </c>
       <c r="N55" s="9" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O55" s="9" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P55" s="9" t="s">
         <v>26</v>
@@ -5259,7 +5265,7 @@
     </row>
     <row r="56" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B56" s="5">
         <v>46125.70524613426</v>
@@ -5271,16 +5277,16 @@
         <v>46195.68974824074</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F56" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G56" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H56" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I56" s="5">
         <v>46078</v>
@@ -5298,13 +5304,13 @@
         <v>26</v>
       </c>
       <c r="N56" s="6" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O56" s="6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="P56" s="6" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="Q56" s="6"/>
       <c r="R56" s="6"/>
@@ -5314,7 +5320,7 @@
     </row>
     <row r="57" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A57" s="7" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="B57" s="8">
         <v>46125.70538292824</v>
@@ -5326,16 +5332,16 @@
         <v>46204.6595946875</v>
       </c>
       <c r="E57" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F57" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G57" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H57" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I57" s="8">
         <v>46085</v>
@@ -5353,13 +5359,13 @@
         <v>26</v>
       </c>
       <c r="N57" s="9" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O57" s="9" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="P57" s="9" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="Q57" s="9"/>
       <c r="R57" s="9"/>
@@ -5369,7 +5375,7 @@
     </row>
     <row r="58" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="B58" s="5">
         <v>46125.718428078704</v>
@@ -5381,16 +5387,16 @@
         <v>46195.69469942129</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="F58" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G58" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H58" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I58" s="5">
         <v>46085</v>
@@ -5408,13 +5414,13 @@
         <v>26</v>
       </c>
       <c r="N58" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O58" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P58" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q58" s="6"/>
       <c r="R58" s="6"/>
@@ -5424,7 +5430,7 @@
     </row>
     <row r="59" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A59" s="7" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B59" s="8">
         <v>46125.718640543986</v>
@@ -5436,16 +5442,16 @@
         <v>46195.69470958333</v>
       </c>
       <c r="E59" s="9" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F59" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G59" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H59" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I59" s="8">
         <v>46085</v>
@@ -5463,13 +5469,13 @@
         <v>26</v>
       </c>
       <c r="N59" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O59" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q59" s="9"/>
       <c r="R59" s="9"/>
@@ -5479,7 +5485,7 @@
     </row>
     <row r="60" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B60" s="5">
         <v>46125.71897782407</v>
@@ -5491,16 +5497,16 @@
         <v>46195.69645640046</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="F60" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G60" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H60" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I60" s="5">
         <v>46085</v>
@@ -5518,13 +5524,13 @@
         <v>26</v>
       </c>
       <c r="N60" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O60" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P60" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q60" s="6"/>
       <c r="R60" s="6"/>
@@ -5534,7 +5540,7 @@
     </row>
     <row r="61" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A61" s="7" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="B61" s="8">
         <v>46125.71913549768</v>
@@ -5546,16 +5552,16 @@
         <v>46195.69541526621</v>
       </c>
       <c r="E61" s="9" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F61" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G61" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H61" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I61" s="8">
         <v>46085</v>
@@ -5573,13 +5579,13 @@
         <v>26</v>
       </c>
       <c r="N61" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O61" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="Q61" s="9"/>
       <c r="R61" s="9"/>
@@ -5589,7 +5595,7 @@
     </row>
     <row r="62" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B62" s="5">
         <v>46126.81590638889</v>
@@ -5601,16 +5607,16 @@
         <v>46195.69561689815</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="F62" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G62" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="H62" s="6" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="I62" s="5">
         <v>46085</v>
@@ -5628,13 +5634,13 @@
         <v>26</v>
       </c>
       <c r="N62" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O62" s="6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="P62" s="6" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="Q62" s="6"/>
       <c r="R62" s="6"/>
@@ -5644,7 +5650,7 @@
     </row>
     <row r="63" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A63" s="7" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B63" s="8">
         <v>46191.76807549769</v>
@@ -5654,16 +5660,16 @@
         <v>46195.695621990744</v>
       </c>
       <c r="E63" s="9" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="F63" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G63" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H63" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I63" s="9"/>
       <c r="J63" s="8">
@@ -5679,10 +5685,10 @@
         <v>26</v>
       </c>
       <c r="N63" s="9" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="O63" s="9" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="P63" s="9" t="s">
         <v>26</v>
@@ -5695,7 +5701,7 @@
     </row>
     <row r="64" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B64" s="5">
         <v>46125.69345099537</v>
@@ -5707,16 +5713,16 @@
         <v>46198.83151038195</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F64" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G64" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H64" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I64" s="5">
         <v>46078</v>
@@ -5734,10 +5740,10 @@
         <v>26</v>
       </c>
       <c r="N64" s="6" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O64" s="6" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="P64" s="6" t="s">
         <v>26</v>
@@ -5760,7 +5766,7 @@
     </row>
     <row r="65" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A65" s="7" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="B65" s="8">
         <v>46125.7055987037</v>
@@ -5772,16 +5778,16 @@
         <v>46195.65984503472</v>
       </c>
       <c r="E65" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F65" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G65" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H65" s="9" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I65" s="8">
         <v>46078</v>
@@ -5799,13 +5805,13 @@
         <v>26</v>
       </c>
       <c r="N65" s="9" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O65" s="9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="Q65" s="9"/>
       <c r="R65" s="9"/>
@@ -5815,7 +5821,7 @@
     </row>
     <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="B66" s="5">
         <v>46125.70569783565</v>
@@ -5827,16 +5833,16 @@
         <v>46195.65992711806</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="F66" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G66" s="6" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H66" s="6" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="I66" s="5">
         <v>46085</v>
@@ -5854,13 +5860,13 @@
         <v>26</v>
       </c>
       <c r="N66" s="6" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="O66" s="6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="P66" s="6" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="Q66" s="6"/>
       <c r="R66" s="6"/>
@@ -5870,7 +5876,7 @@
     </row>
     <row r="67" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A67" s="7" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B67" s="8">
         <v>46077.54519895834</v>
@@ -5880,7 +5886,7 @@
         <v>46127.698486747686</v>
       </c>
       <c r="E67" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="F67" s="9" t="s">
         <v>25</v>
@@ -5904,7 +5910,7 @@
         <v>26</v>
       </c>
       <c r="O67" s="9" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="P67" s="9" t="s">
         <v>26</v>
@@ -5917,7 +5923,7 @@
     </row>
     <row r="68" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A68" s="4" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B68" s="5">
         <v>46077.54519921297</v>
@@ -5929,16 +5935,16 @@
         <v>46197.85981012732</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="F68" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G68" s="6" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H68" s="6" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I68" s="5">
         <v>46013</v>
@@ -5956,13 +5962,13 @@
         <v>26</v>
       </c>
       <c r="N68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O68" s="6" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="P68" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q68" s="5">
         <v>46016</v>
@@ -5982,7 +5988,7 @@
     </row>
     <row r="69" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A69" s="7" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B69" s="8">
         <v>46125.6963875463</v>
@@ -5994,16 +6000,16 @@
         <v>46127.697633749995</v>
       </c>
       <c r="E69" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F69" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G69" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H69" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I69" s="8">
         <v>46013</v>
@@ -6021,13 +6027,13 @@
         <v>26</v>
       </c>
       <c r="N69" s="9" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O69" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P69" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="Q69" s="9"/>
       <c r="R69" s="9"/>
@@ -6037,7 +6043,7 @@
     </row>
     <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B70" s="5">
         <v>46125.69656831019</v>
@@ -6049,16 +6055,16 @@
         <v>46127.6976405787</v>
       </c>
       <c r="E70" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F70" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G70" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H70" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="F70" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G70" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H70" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I70" s="5">
         <v>46013</v>
@@ -6076,13 +6082,13 @@
         <v>26</v>
       </c>
       <c r="N70" s="6" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="O70" s="6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="P70" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="Q70" s="6"/>
       <c r="R70" s="6"/>
@@ -6092,7 +6098,7 @@
     </row>
     <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="7" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B71" s="8">
         <v>46077.545196736115</v>
@@ -6104,16 +6110,16 @@
         <v>46197.708300150465</v>
       </c>
       <c r="E71" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="F71" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G71" s="9" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="H71" s="9" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="I71" s="8">
         <v>46066</v>
@@ -6131,13 +6137,13 @@
         <v>26</v>
       </c>
       <c r="N71" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O71" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P71" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q71" s="8">
         <v>46072</v>
@@ -6157,7 +6163,7 @@
     </row>
     <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="4" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B72" s="5">
         <v>46125.69788891204</v>
@@ -6169,16 +6175,16 @@
         <v>46127.69788501157</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F72" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G72" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H72" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I72" s="5">
         <v>46066</v>
@@ -6196,13 +6202,13 @@
         <v>26</v>
       </c>
       <c r="N72" s="6" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O72" s="6" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P72" s="6" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="Q72" s="6"/>
       <c r="R72" s="6"/>
@@ -6212,7 +6218,7 @@
     </row>
     <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="7" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B73" s="8">
         <v>46125.69801100694</v>
@@ -6224,16 +6230,16 @@
         <v>46127.697873287034</v>
       </c>
       <c r="E73" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="F73" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G73" s="9" t="s">
+        <v>238</v>
+      </c>
+      <c r="H73" s="9" t="s">
         <v>239</v>
-      </c>
-      <c r="F73" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G73" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="H73" s="9" t="s">
-        <v>237</v>
       </c>
       <c r="I73" s="8">
         <v>46066</v>
@@ -6251,13 +6257,13 @@
         <v>26</v>
       </c>
       <c r="N73" s="9" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="O73" s="9" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="P73" s="9" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="Q73" s="9"/>
       <c r="R73" s="9"/>
@@ -6267,7 +6273,7 @@
     </row>
     <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="4" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B74" s="5">
         <v>46090.70475186342</v>
@@ -6279,16 +6285,16 @@
         <v>46127.698491539355</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F74" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G74" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H74" s="6" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I74" s="5">
         <v>46073</v>
@@ -6306,13 +6312,13 @@
         <v>26</v>
       </c>
       <c r="N74" s="6" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O74" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P74" s="6" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="Q74" s="5">
         <v>46073</v>
@@ -6332,7 +6338,7 @@
     </row>
     <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="7" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B75" s="8">
         <v>46125.69814037037</v>
@@ -6344,16 +6350,16 @@
         <v>46127.698451331016</v>
       </c>
       <c r="E75" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F75" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G75" s="9" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="H75" s="9" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="I75" s="8">
         <v>46073</v>
@@ -6371,13 +6377,13 @@
         <v>26</v>
       </c>
       <c r="N75" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O75" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P75" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q75" s="9"/>
       <c r="R75" s="9"/>
@@ -6387,7 +6393,7 @@
     </row>
     <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="4" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B76" s="5">
         <v>46125.6983227662</v>
@@ -6399,16 +6405,16 @@
         <v>46127.69846143518</v>
       </c>
       <c r="E76" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="F76" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G76" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="H76" s="6" t="s">
         <v>239</v>
-      </c>
-      <c r="F76" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G76" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="H76" s="6" t="s">
-        <v>237</v>
       </c>
       <c r="I76" s="5">
         <v>46073</v>
@@ -6426,13 +6432,13 @@
         <v>26</v>
       </c>
       <c r="N76" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="O76" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P76" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="Q76" s="6"/>
       <c r="R76" s="6"/>
@@ -6442,7 +6448,7 @@
     </row>
     <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="7" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B77" s="8">
         <v>46090.70479819445</v>
@@ -6452,16 +6458,16 @@
         <v>46198.7984696875</v>
       </c>
       <c r="E77" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F77" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G77" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H77" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I77" s="8">
         <v>46167</v>
@@ -6479,13 +6485,13 @@
         <v>26</v>
       </c>
       <c r="N77" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="O77" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="Q77" s="8">
         <v>46167</v>
@@ -6494,7 +6500,7 @@
         <v>46167</v>
       </c>
       <c r="S77" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T77" s="9">
         <v>0</v>
@@ -6505,7 +6511,7 @@
     </row>
     <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="4" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B78" s="5">
         <v>46125.69919584491</v>
@@ -6515,16 +6521,16 @@
         <v>46167.16821967592</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F78" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G78" s="6" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H78" s="6" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I78" s="6"/>
       <c r="J78" s="5">
@@ -6540,13 +6546,13 @@
         <v>26</v>
       </c>
       <c r="N78" s="6" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O78" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P78" s="6" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="Q78" s="6"/>
       <c r="R78" s="6"/>
@@ -6556,7 +6562,7 @@
     </row>
     <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="7" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B79" s="8">
         <v>46125.69931737268</v>
@@ -6566,16 +6572,16 @@
         <v>46167.168221562504</v>
       </c>
       <c r="E79" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F79" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G79" s="9" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="H79" s="9" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="I79" s="9"/>
       <c r="J79" s="8">
@@ -6591,13 +6597,13 @@
         <v>26</v>
       </c>
       <c r="N79" s="9" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="O79" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="Q79" s="9"/>
       <c r="R79" s="9"/>
@@ -6607,7 +6613,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="4" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B80" s="5">
         <v>46077.54519710648</v>
@@ -6619,7 +6625,7 @@
         <v>46198.831302199076</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F80" s="6" t="s">
         <v>25</v>
@@ -6643,7 +6649,7 @@
         <v>26</v>
       </c>
       <c r="O80" s="6" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P80" s="6" t="s">
         <v>26</v>
@@ -6660,7 +6666,7 @@
     </row>
     <row r="81" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A81" s="7" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B81" s="8">
         <v>46077.54519784723</v>
@@ -6672,16 +6678,16 @@
         <v>46191.7695737037</v>
       </c>
       <c r="E81" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F81" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G81" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H81" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I81" s="8">
         <v>46094</v>
@@ -6699,13 +6705,13 @@
         <v>26</v>
       </c>
       <c r="N81" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O81" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="Q81" s="8">
         <v>46097</v>
@@ -6725,7 +6731,7 @@
     </row>
     <row r="82" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A82" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B82" s="5">
         <v>46125.69615554398</v>
@@ -6737,16 +6743,16 @@
         <v>46191.77014716435</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="F82" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G82" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H82" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I82" s="5">
         <v>46094</v>
@@ -6764,13 +6770,13 @@
         <v>26</v>
       </c>
       <c r="N82" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O82" s="6" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P82" s="6" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="Q82" s="5">
         <v>46097</v>
@@ -6790,7 +6796,7 @@
     </row>
     <row r="83" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A83" s="7" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="B83" s="8">
         <v>46125.699760648145</v>
@@ -6802,16 +6808,16 @@
         <v>46198.83128892361</v>
       </c>
       <c r="E83" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="F83" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G83" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H83" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I83" s="8">
         <v>46094</v>
@@ -6829,13 +6835,13 @@
         <v>26</v>
       </c>
       <c r="N83" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O83" s="9" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q83" s="8">
         <v>46097</v>
@@ -6855,7 +6861,7 @@
     </row>
     <row r="84" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A84" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B84" s="5">
         <v>46077.545198472224</v>
@@ -6867,16 +6873,16 @@
         <v>46191.770536875</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="F84" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G84" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H84" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I84" s="5">
         <v>46098</v>
@@ -6894,13 +6900,13 @@
         <v>26</v>
       </c>
       <c r="N84" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O84" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P84" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Q84" s="5">
         <v>46099</v>
@@ -6920,7 +6926,7 @@
     </row>
     <row r="85" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A85" s="7" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="B85" s="8">
         <v>46125.775447465276</v>
@@ -6932,16 +6938,16 @@
         <v>46191.76973724537</v>
       </c>
       <c r="E85" s="9" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F85" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G85" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H85" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I85" s="8">
         <v>46098</v>
@@ -6959,13 +6965,13 @@
         <v>26</v>
       </c>
       <c r="N85" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O85" s="9" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="P85" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q85" s="9"/>
       <c r="R85" s="9"/>
@@ -6975,7 +6981,7 @@
     </row>
     <row r="86" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A86" s="4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B86" s="5">
         <v>46125.77559420139</v>
@@ -6987,16 +6993,16 @@
         <v>46191.77053325232</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F86" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G86" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H86" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I86" s="5">
         <v>46098</v>
@@ -7014,13 +7020,13 @@
         <v>26</v>
       </c>
       <c r="N86" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O86" s="6" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="P86" s="6" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="Q86" s="6"/>
       <c r="R86" s="6"/>
@@ -7030,7 +7036,7 @@
     </row>
     <row r="87" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A87" s="7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B87" s="8">
         <v>46125.77573671297</v>
@@ -7040,16 +7046,16 @@
         <v>46198.831276655095</v>
       </c>
       <c r="E87" s="9" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F87" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G87" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H87" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I87" s="8">
         <v>46098</v>
@@ -7067,13 +7073,13 @@
         <v>26</v>
       </c>
       <c r="N87" s="9" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O87" s="9" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P87" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="Q87" s="9"/>
       <c r="R87" s="9"/>
@@ -7083,7 +7089,7 @@
     </row>
     <row r="88" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A88" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B88" s="5">
         <v>46077.545199050925</v>
@@ -7095,7 +7101,7 @@
         <v>46191.77046482639</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="F88" s="6" t="s">
         <v>25</v>
@@ -7119,7 +7125,7 @@
         <v>26</v>
       </c>
       <c r="O88" s="6" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P88" s="6" t="s">
         <v>26</v>
@@ -7136,7 +7142,7 @@
     </row>
     <row r="89" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A89" s="7" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B89" s="8">
         <v>46077.5451993287</v>
@@ -7148,16 +7154,16 @@
         <v>46191.77013883102</v>
       </c>
       <c r="E89" s="9" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="F89" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G89" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H89" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I89" s="8">
         <v>46100</v>
@@ -7175,13 +7181,13 @@
         <v>26</v>
       </c>
       <c r="N89" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O89" s="9" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P89" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Q89" s="8">
         <v>46108</v>
@@ -7201,7 +7207,7 @@
     </row>
     <row r="90" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A90" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B90" s="5">
         <v>46077.54519958333</v>
@@ -7213,16 +7219,16 @@
         <v>46191.76662447916</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F90" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G90" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H90" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I90" s="5">
         <v>46111</v>
@@ -7240,13 +7246,13 @@
         <v>26</v>
       </c>
       <c r="N90" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O90" s="6" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P90" s="6" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q90" s="5">
         <v>46139</v>
@@ -7261,12 +7267,12 @@
         <v>1</v>
       </c>
       <c r="U90" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="91" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A91" s="7" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B91" s="8">
         <v>46125.780000914354</v>
@@ -7278,16 +7284,16 @@
         <v>46191.76361026621</v>
       </c>
       <c r="E91" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F91" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G91" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H91" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I91" s="8">
         <v>46111</v>
@@ -7305,13 +7311,13 @@
         <v>26</v>
       </c>
       <c r="N91" s="9" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O91" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P91" s="9" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="Q91" s="9"/>
       <c r="R91" s="9"/>
@@ -7321,7 +7327,7 @@
     </row>
     <row r="92" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A92" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B92" s="5">
         <v>46125.779717233796</v>
@@ -7333,16 +7339,16 @@
         <v>46191.76362532408</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F92" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H92" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I92" s="5">
         <v>46111</v>
@@ -7360,13 +7366,13 @@
         <v>26</v>
       </c>
       <c r="N92" s="6" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="O92" s="6" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P92" s="6" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Q92" s="6"/>
       <c r="R92" s="6"/>
@@ -7376,7 +7382,7 @@
     </row>
     <row r="93" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A93" s="7" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B93" s="8">
         <v>46077.54519984954</v>
@@ -7388,16 +7394,16 @@
         <v>46193.954018240736</v>
       </c>
       <c r="E93" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F93" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G93" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H93" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I93" s="8">
         <v>46140</v>
@@ -7415,13 +7421,13 @@
         <v>26</v>
       </c>
       <c r="N93" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O93" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="P93" s="9" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="Q93" s="8">
         <v>46141</v>
@@ -7430,18 +7436,18 @@
         <v>46140</v>
       </c>
       <c r="S93" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T93" s="9">
         <v>1</v>
       </c>
       <c r="U93" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="94" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A94" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B94" s="5">
         <v>46125.7814462963</v>
@@ -7453,16 +7459,16 @@
         <v>46193.953995034724</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="F94" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H94" s="6" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I94" s="5">
         <v>46140</v>
@@ -7480,13 +7486,13 @@
         <v>26</v>
       </c>
       <c r="N94" s="6" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O94" s="6" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="P94" s="6" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="Q94" s="6"/>
       <c r="R94" s="6"/>
@@ -7496,7 +7502,7 @@
     </row>
     <row r="95" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A95" s="7" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B95" s="8">
         <v>46125.78158427084</v>
@@ -7508,16 +7514,16 @@
         <v>46193.9540056713</v>
       </c>
       <c r="E95" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F95" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G95" s="9" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="H95" s="9" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="I95" s="8">
         <v>46140</v>
@@ -7535,13 +7541,13 @@
         <v>26</v>
       </c>
       <c r="N95" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="O95" s="9" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P95" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Q95" s="9"/>
       <c r="R95" s="9"/>
@@ -7551,7 +7557,7 @@
     </row>
     <row r="96" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A96" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B96" s="5">
         <v>46077.54520011574</v>
@@ -7561,7 +7567,7 @@
         <v>46198.87202574074</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F96" s="6" t="s">
         <v>25</v>
@@ -7585,7 +7591,7 @@
         <v>26</v>
       </c>
       <c r="O96" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="P96" s="6" t="s">
         <v>26</v>
@@ -7598,7 +7604,7 @@
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A97" s="7" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B97" s="8">
         <v>46077.545198078704</v>
@@ -7610,16 +7616,16 @@
         <v>46191.78642105324</v>
       </c>
       <c r="E97" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F97" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G97" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H97" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I97" s="8">
         <v>46154</v>
@@ -7637,13 +7643,13 @@
         <v>26</v>
       </c>
       <c r="N97" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O97" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="P97" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q97" s="8">
         <v>46155</v>
@@ -7658,12 +7664,12 @@
         <v>1</v>
       </c>
       <c r="U97" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="98" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A98" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B98" s="5">
         <v>46077.54519778935</v>
@@ -7675,16 +7681,16 @@
         <v>46191.78660222222</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F98" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G98" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H98" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I98" s="5">
         <v>46139</v>
@@ -7702,13 +7708,13 @@
         <v>26</v>
       </c>
       <c r="N98" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O98" s="6" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P98" s="6" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q98" s="5">
         <v>46140</v>
@@ -7723,12 +7729,12 @@
         <v>1</v>
       </c>
       <c r="U98" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="99" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A99" s="7" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B99" s="8">
         <v>46077.54520075231</v>
@@ -7738,16 +7744,16 @@
         <v>46199.847719363424</v>
       </c>
       <c r="E99" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="F99" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G99" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H99" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I99" s="8">
         <v>46071</v>
@@ -7765,13 +7771,13 @@
         <v>26</v>
       </c>
       <c r="N99" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O99" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P99" s="9" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="Q99" s="8">
         <v>46072</v>
@@ -7780,7 +7786,7 @@
         <v>46071</v>
       </c>
       <c r="S99" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T99" s="9">
         <v>0</v>
@@ -7791,7 +7797,7 @@
     </row>
     <row r="100" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A100" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B100" s="5">
         <v>46077.54519734954</v>
@@ -7803,16 +7809,16 @@
         <v>46198.87203554398</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F100" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G100" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H100" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I100" s="5">
         <v>46125</v>
@@ -7830,13 +7836,13 @@
         <v>26</v>
       </c>
       <c r="N100" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O100" s="6" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P100" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Q100" s="5">
         <v>46126</v>
@@ -7856,7 +7862,7 @@
     </row>
     <row r="101" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A101" s="7" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B101" s="8">
         <v>46077.55796549769</v>
@@ -7866,16 +7872,16 @@
         <v>46198.87327074074</v>
       </c>
       <c r="E101" s="9" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F101" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G101" s="9" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H101" s="9" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I101" s="8">
         <v>46122</v>
@@ -7893,13 +7899,13 @@
         <v>26</v>
       </c>
       <c r="N101" s="9" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O101" s="9" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="P101" s="9" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="Q101" s="8">
         <v>46125</v>
@@ -7908,7 +7914,7 @@
         <v>46122</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
@@ -7919,7 +7925,7 @@
     </row>
     <row r="102" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A102" s="4" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B102" s="5">
         <v>46125.79029034722</v>
@@ -7931,16 +7937,16 @@
         <v>46204.68545116898</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F102" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G102" s="6" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="H102" s="6" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="I102" s="5">
         <v>46114</v>
@@ -7958,13 +7964,13 @@
         <v>26</v>
       </c>
       <c r="N102" s="6" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O102" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="P102" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="Q102" s="5">
         <v>46115</v>
@@ -7982,7 +7988,7 @@
     </row>
     <row r="103" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A103" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B103" s="8">
         <v>46077.54519841435</v>
@@ -7992,7 +7998,7 @@
         <v>46195.86928554398</v>
       </c>
       <c r="E103" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F103" s="9" t="s">
         <v>25</v>
@@ -8016,7 +8022,7 @@
         <v>26</v>
       </c>
       <c r="O103" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="P103" s="9" t="s">
         <v>26</v>
@@ -8029,7 +8035,7 @@
     </row>
     <row r="104" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A104" s="4" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="B104" s="5">
         <v>46077.545198761574</v>
@@ -8041,16 +8047,16 @@
         <v>46195.86929523148</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F104" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G104" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H104" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I104" s="5">
         <v>46142</v>
@@ -8068,13 +8074,13 @@
         <v>26</v>
       </c>
       <c r="N104" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O104" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P104" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q104" s="5">
         <v>46150</v>
@@ -8089,12 +8095,12 @@
         <v>1</v>
       </c>
       <c r="U104" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="105" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A105" s="7" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="B105" s="8">
         <v>46125.785526736116</v>
@@ -8104,16 +8110,16 @@
         <v>46204.68543935185</v>
       </c>
       <c r="E105" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F105" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G105" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H105" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I105" s="8">
         <v>46140</v>
@@ -8131,13 +8137,13 @@
         <v>26</v>
       </c>
       <c r="N105" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O105" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P105" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="Q105" s="9"/>
       <c r="R105" s="9"/>
@@ -8147,7 +8153,7 @@
     </row>
     <row r="106" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A106" s="4" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B106" s="5">
         <v>46125.7863228125</v>
@@ -8157,16 +8163,16 @@
         <v>46204.685440601854</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F106" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G106" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H106" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I106" s="5">
         <v>46140</v>
@@ -8184,13 +8190,13 @@
         <v>26</v>
       </c>
       <c r="N106" s="6" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="O106" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="P106" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="Q106" s="6"/>
       <c r="R106" s="6"/>
@@ -8200,7 +8206,7 @@
     </row>
     <row r="107" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A107" s="7" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B107" s="8">
         <v>46077.558327129635</v>
@@ -8210,16 +8216,16 @@
         <v>46154.167828125</v>
       </c>
       <c r="E107" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="F107" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G107" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H107" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I107" s="8">
         <v>46153</v>
@@ -8237,13 +8243,13 @@
         <v>26</v>
       </c>
       <c r="N107" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O107" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P107" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q107" s="8">
         <v>46154</v>
@@ -8252,18 +8258,18 @@
         <v>46153</v>
       </c>
       <c r="S107" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T107" s="9">
         <v>0</v>
       </c>
       <c r="U107" s="12" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="108" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A108" s="4" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B108" s="5">
         <v>46125.793145185184</v>
@@ -8273,16 +8279,16 @@
         <v>46154.16895842593</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F108" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G108" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H108" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I108" s="5">
         <v>46153</v>
@@ -8300,13 +8306,13 @@
         <v>26</v>
       </c>
       <c r="N108" s="6" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O108" s="6" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="P108" s="6" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="Q108" s="6"/>
       <c r="R108" s="6"/>
@@ -8316,7 +8322,7 @@
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A109" s="7" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B109" s="8">
         <v>46125.79326523148</v>
@@ -8326,16 +8332,16 @@
         <v>46154.168959930554</v>
       </c>
       <c r="E109" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F109" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G109" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H109" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I109" s="8">
         <v>46153</v>
@@ -8353,13 +8359,13 @@
         <v>26</v>
       </c>
       <c r="N109" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="O109" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P109" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="Q109" s="9"/>
       <c r="R109" s="9"/>
@@ -8369,7 +8375,7 @@
     </row>
     <row r="110" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A110" s="4" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B110" s="5">
         <v>46077.5451994676</v>
@@ -8379,16 +8385,16 @@
         <v>46197.504649062495</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F110" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G110" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H110" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I110" s="5">
         <v>46155</v>
@@ -8406,13 +8412,13 @@
         <v>26</v>
       </c>
       <c r="N110" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O110" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P110" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q110" s="5">
         <v>46126</v>
@@ -8421,7 +8427,7 @@
         <v>46155</v>
       </c>
       <c r="S110" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T110" s="6">
         <v>0</v>
@@ -8432,7 +8438,7 @@
     </row>
     <row r="111" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A111" s="7" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B111" s="8">
         <v>46125.793417939814</v>
@@ -8444,16 +8450,16 @@
         <v>46197.504645196765</v>
       </c>
       <c r="E111" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F111" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G111" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H111" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I111" s="8">
         <v>46155</v>
@@ -8471,13 +8477,13 @@
         <v>26</v>
       </c>
       <c r="N111" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O111" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="P111" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="Q111" s="9"/>
       <c r="R111" s="9"/>
@@ -8487,7 +8493,7 @@
     </row>
     <row r="112" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A112" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B112" s="5">
         <v>46125.793529525465</v>
@@ -8497,16 +8503,16 @@
         <v>46191.78659372685</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F112" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G112" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H112" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I112" s="5">
         <v>46155</v>
@@ -8524,13 +8530,13 @@
         <v>26</v>
       </c>
       <c r="N112" s="6" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O112" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="P112" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="Q112" s="6"/>
       <c r="R112" s="6"/>
@@ -8540,7 +8546,7 @@
     </row>
     <row r="113" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A113" s="7" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B113" s="8">
         <v>46077.54519980324</v>
@@ -8550,16 +8556,16 @@
         <v>46197.60860170139</v>
       </c>
       <c r="E113" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F113" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H113" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I113" s="8">
         <v>46157</v>
@@ -8577,13 +8583,13 @@
         <v>26</v>
       </c>
       <c r="N113" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O113" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P113" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q113" s="8">
         <v>46160</v>
@@ -8592,7 +8598,7 @@
         <v>46157</v>
       </c>
       <c r="S113" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T113" s="9">
         <v>0</v>
@@ -8603,7 +8609,7 @@
     </row>
     <row r="114" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A114" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B114" s="5">
         <v>46125.79363706018</v>
@@ -8613,16 +8619,16 @@
         <v>46197.60859815972</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F114" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H114" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I114" s="5">
         <v>46157</v>
@@ -8640,13 +8646,13 @@
         <v>26</v>
       </c>
       <c r="N114" s="6" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O114" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="P114" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Q114" s="6"/>
       <c r="R114" s="6"/>
@@ -8656,7 +8662,7 @@
     </row>
     <row r="115" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A115" s="7" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B115" s="8">
         <v>46125.79376541667</v>
@@ -8666,16 +8672,16 @@
         <v>46192.79081532407</v>
       </c>
       <c r="E115" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F115" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H115" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I115" s="8">
         <v>46157</v>
@@ -8693,13 +8699,13 @@
         <v>26</v>
       </c>
       <c r="N115" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O115" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="P115" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="Q115" s="9"/>
       <c r="R115" s="9"/>
@@ -8709,7 +8715,7 @@
     </row>
     <row r="116" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A116" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B116" s="5">
         <v>46077.54519909722</v>
@@ -8719,16 +8725,16 @@
         <v>46198.61729309028</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="F116" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H116" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I116" s="5">
         <v>46161</v>
@@ -8746,13 +8752,13 @@
         <v>26</v>
       </c>
       <c r="N116" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O116" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P116" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q116" s="5">
         <v>46162</v>
@@ -8761,7 +8767,7 @@
         <v>46161</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
@@ -8772,7 +8778,7 @@
     </row>
     <row r="117" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A117" s="7" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B117" s="8">
         <v>46125.79408877315</v>
@@ -8784,16 +8790,16 @@
         <v>46197.6086021875</v>
       </c>
       <c r="E117" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F117" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H117" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I117" s="8">
         <v>46161</v>
@@ -8811,13 +8817,13 @@
         <v>26</v>
       </c>
       <c r="N117" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O117" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="P117" s="9" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Q117" s="9"/>
       <c r="R117" s="9"/>
@@ -8827,7 +8833,7 @@
     </row>
     <row r="118" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A118" s="4" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B118" s="5">
         <v>46125.79422275463</v>
@@ -8837,16 +8843,16 @@
         <v>46191.786412430556</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F118" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H118" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I118" s="5">
         <v>46161</v>
@@ -8864,13 +8870,13 @@
         <v>26</v>
       </c>
       <c r="N118" s="6" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="O118" s="6" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="P118" s="6" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="Q118" s="6"/>
       <c r="R118" s="6"/>
@@ -8880,7 +8886,7 @@
     </row>
     <row r="119" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A119" s="7" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B119" s="8">
         <v>46077.545200127315</v>
@@ -8890,16 +8896,16 @@
         <v>46165.197340150466</v>
       </c>
       <c r="E119" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F119" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H119" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I119" s="8">
         <v>46164</v>
@@ -8917,13 +8923,13 @@
         <v>26</v>
       </c>
       <c r="N119" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O119" s="9" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P119" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q119" s="8">
         <v>46164</v>
@@ -8932,7 +8938,7 @@
         <v>46164</v>
       </c>
       <c r="S119" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T119" s="9">
         <v>0</v>
@@ -8943,7 +8949,7 @@
     </row>
     <row r="120" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A120" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B120" s="5">
         <v>46125.79434175926</v>
@@ -8953,16 +8959,16 @@
         <v>46197.59958675926</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F120" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H120" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I120" s="6"/>
       <c r="J120" s="5">
@@ -8978,13 +8984,13 @@
         <v>26</v>
       </c>
       <c r="N120" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O120" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P120" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="Q120" s="6"/>
       <c r="R120" s="6"/>
@@ -8994,7 +9000,7 @@
     </row>
     <row r="121" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A121" s="7" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B121" s="8">
         <v>46125.79446019676</v>
@@ -9004,16 +9010,16 @@
         <v>46164.16915030092</v>
       </c>
       <c r="E121" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F121" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H121" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I121" s="9"/>
       <c r="J121" s="8">
@@ -9029,13 +9035,13 @@
         <v>26</v>
       </c>
       <c r="N121" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="O121" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P121" s="9" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="Q121" s="9"/>
       <c r="R121" s="9"/>
@@ -9045,7 +9051,7 @@
     </row>
     <row r="122" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A122" s="4" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B122" s="5">
         <v>46077.54520043981</v>
@@ -9055,16 +9061,16 @@
         <v>46169.19579744213</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G122" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H122" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I122" s="5">
         <v>46168</v>
@@ -9082,13 +9088,13 @@
         <v>26</v>
       </c>
       <c r="N122" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="O122" s="6" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="P122" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="Q122" s="5">
         <v>46168</v>
@@ -9097,7 +9103,7 @@
         <v>46168</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T122" s="6">
         <v>0</v>
@@ -9108,7 +9114,7 @@
     </row>
     <row r="123" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A123" s="7" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B123" s="8">
         <v>46125.794598078704</v>
@@ -9118,16 +9124,16 @@
         <v>46168.16876332176</v>
       </c>
       <c r="E123" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F123" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G123" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H123" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I123" s="9"/>
       <c r="J123" s="8">
@@ -9143,13 +9149,13 @@
         <v>26</v>
       </c>
       <c r="N123" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O123" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P123" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="Q123" s="9"/>
       <c r="R123" s="9"/>
@@ -9159,7 +9165,7 @@
     </row>
     <row r="124" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A124" s="4" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B124" s="5">
         <v>46125.794723252315</v>
@@ -9169,16 +9175,16 @@
         <v>46168.168764710645</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G124" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H124" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I124" s="6"/>
       <c r="J124" s="5">
@@ -9194,13 +9200,13 @@
         <v>26</v>
       </c>
       <c r="N124" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="O124" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P124" s="6" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Q124" s="6"/>
       <c r="R124" s="6"/>
@@ -9210,7 +9216,7 @@
     </row>
     <row r="125" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A125" s="7" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B125" s="8">
         <v>46077.54519771991</v>
@@ -9220,7 +9226,7 @@
         <v>46125.907215011575</v>
       </c>
       <c r="E125" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="F125" s="9" t="s">
         <v>25</v>
@@ -9244,7 +9250,7 @@
         <v>26</v>
       </c>
       <c r="O125" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="P125" s="9" t="s">
         <v>26</v>
@@ -9257,7 +9263,7 @@
     </row>
     <row r="126" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A126" s="4" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B126" s="5">
         <v>46077.5451981713</v>
@@ -9267,16 +9273,16 @@
         <v>46170.199522905095</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F126" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G126" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H126" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I126" s="5">
         <v>46169</v>
@@ -9294,13 +9300,13 @@
         <v>26</v>
       </c>
       <c r="N126" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O126" s="6" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P126" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q126" s="5">
         <v>46169</v>
@@ -9309,7 +9315,7 @@
         <v>46169</v>
       </c>
       <c r="S126" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T126" s="6">
         <v>0</v>
@@ -9320,7 +9326,7 @@
     </row>
     <row r="127" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A127" s="7" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B127" s="8">
         <v>46125.81236390046</v>
@@ -9330,16 +9336,16 @@
         <v>46169.16854510417</v>
       </c>
       <c r="E127" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F127" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G127" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H127" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I127" s="9"/>
       <c r="J127" s="8">
@@ -9355,13 +9361,13 @@
         <v>26</v>
       </c>
       <c r="N127" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O127" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P127" s="9" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="Q127" s="9"/>
       <c r="R127" s="9"/>
@@ -9371,7 +9377,7 @@
     </row>
     <row r="128" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A128" s="4" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B128" s="5">
         <v>46125.81252253472</v>
@@ -9381,16 +9387,16 @@
         <v>46169.168546712965</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F128" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G128" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H128" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I128" s="6"/>
       <c r="J128" s="5">
@@ -9406,13 +9412,13 @@
         <v>26</v>
       </c>
       <c r="N128" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O128" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P128" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="Q128" s="6"/>
       <c r="R128" s="6"/>
@@ -9422,7 +9428,7 @@
     </row>
     <row r="129" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A129" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B129" s="8">
         <v>46125.812747199074</v>
@@ -9432,16 +9438,16 @@
         <v>46169.16854806713</v>
       </c>
       <c r="E129" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F129" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G129" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H129" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I129" s="9"/>
       <c r="J129" s="8">
@@ -9457,13 +9463,13 @@
         <v>26</v>
       </c>
       <c r="N129" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O129" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P129" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="Q129" s="9"/>
       <c r="R129" s="9"/>
@@ -9473,7 +9479,7 @@
     </row>
     <row r="130" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A130" s="4" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B130" s="5">
         <v>46125.81326880787</v>
@@ -9483,16 +9489,16 @@
         <v>46169.16854940972</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F130" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G130" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H130" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I130" s="6"/>
       <c r="J130" s="5">
@@ -9508,13 +9514,13 @@
         <v>26</v>
       </c>
       <c r="N130" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O130" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P130" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Q130" s="6"/>
       <c r="R130" s="6"/>
@@ -9524,7 +9530,7 @@
     </row>
     <row r="131" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A131" s="7" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B131" s="8">
         <v>46125.81384030092</v>
@@ -9534,16 +9540,16 @@
         <v>46169.168550682865</v>
       </c>
       <c r="E131" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F131" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G131" s="9" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H131" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I131" s="9"/>
       <c r="J131" s="8">
@@ -9559,13 +9565,13 @@
         <v>26</v>
       </c>
       <c r="N131" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O131" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P131" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="Q131" s="9"/>
       <c r="R131" s="9"/>
@@ -9575,7 +9581,7 @@
     </row>
     <row r="132" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A132" s="4" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B132" s="5">
         <v>46125.81410221064</v>
@@ -9585,16 +9591,16 @@
         <v>46169.16855229167</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F132" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G132" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="H132" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="I132" s="6"/>
       <c r="J132" s="5">
@@ -9610,13 +9616,13 @@
         <v>26</v>
       </c>
       <c r="N132" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="O132" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P132" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q132" s="6"/>
       <c r="R132" s="6"/>
@@ -9626,7 +9632,7 @@
     </row>
     <row r="133" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A133" s="7" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B133" s="8">
         <v>46077.5451984838</v>
@@ -9636,16 +9642,16 @@
         <v>46175.20232467593</v>
       </c>
       <c r="E133" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F133" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G133" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H133" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I133" s="8">
         <v>46170</v>
@@ -9663,13 +9669,13 @@
         <v>26</v>
       </c>
       <c r="N133" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O133" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="P133" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="Q133" s="8">
         <v>46174</v>
@@ -9678,7 +9684,7 @@
         <v>46170</v>
       </c>
       <c r="S133" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T133" s="9">
         <v>0</v>
@@ -9689,7 +9695,7 @@
     </row>
     <row r="134" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A134" s="4" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B134" s="5">
         <v>46125.81482075232</v>
@@ -9699,16 +9705,16 @@
         <v>46174.16943333333</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F134" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G134" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H134" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I134" s="5">
         <v>46170</v>
@@ -9726,13 +9732,13 @@
         <v>26</v>
       </c>
       <c r="N134" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O134" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P134" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="Q134" s="6"/>
       <c r="R134" s="6"/>
@@ -9742,7 +9748,7 @@
     </row>
     <row r="135" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A135" s="7" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B135" s="8">
         <v>46125.81494678241</v>
@@ -9752,16 +9758,16 @@
         <v>46174.16943504629</v>
       </c>
       <c r="E135" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F135" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G135" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H135" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I135" s="8">
         <v>46170</v>
@@ -9779,13 +9785,13 @@
         <v>26</v>
       </c>
       <c r="N135" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O135" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P135" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="Q135" s="9"/>
       <c r="R135" s="9"/>
@@ -9795,7 +9801,7 @@
     </row>
     <row r="136" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A136" s="4" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B136" s="5">
         <v>46125.81516034722</v>
@@ -9805,16 +9811,16 @@
         <v>46174.169436400465</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G136" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H136" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I136" s="5">
         <v>46170</v>
@@ -9832,13 +9838,13 @@
         <v>26</v>
       </c>
       <c r="N136" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O136" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P136" s="6" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="Q136" s="6"/>
       <c r="R136" s="6"/>
@@ -9848,7 +9854,7 @@
     </row>
     <row r="137" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A137" s="7" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B137" s="8">
         <v>46125.81531077546</v>
@@ -9858,16 +9864,16 @@
         <v>46174.169437847224</v>
       </c>
       <c r="E137" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F137" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G137" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H137" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I137" s="8">
         <v>46170</v>
@@ -9885,13 +9891,13 @@
         <v>26</v>
       </c>
       <c r="N137" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O137" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P137" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="Q137" s="9"/>
       <c r="R137" s="9"/>
@@ -9901,7 +9907,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B138" s="5">
         <v>46125.81545193287</v>
@@ -9911,16 +9917,16 @@
         <v>46174.16943927083</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F138" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G138" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H138" s="6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I138" s="5">
         <v>46170</v>
@@ -9938,13 +9944,13 @@
         <v>26</v>
       </c>
       <c r="N138" s="6" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O138" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -9954,7 +9960,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="7" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B139" s="8">
         <v>46125.81557276621</v>
@@ -9964,16 +9970,16 @@
         <v>46174.16944046297</v>
       </c>
       <c r="E139" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F139" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G139" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H139" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="I139" s="8">
         <v>46170</v>
@@ -9991,13 +9997,13 @@
         <v>26</v>
       </c>
       <c r="N139" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="O139" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="P139" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="Q139" s="9"/>
       <c r="R139" s="9"/>
@@ -10007,7 +10013,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B140" s="5">
         <v>46077.54519895834</v>
@@ -10017,16 +10023,16 @@
         <v>46176.19592085648</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="F140" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G140" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H140" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I140" s="5">
         <v>46175</v>
@@ -10044,13 +10050,13 @@
         <v>26</v>
       </c>
       <c r="N140" s="6" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O140" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="Q140" s="5">
         <v>46175</v>
@@ -10059,7 +10065,7 @@
         <v>46175</v>
       </c>
       <c r="S140" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T140" s="6">
         <v>0</v>
@@ -10070,7 +10076,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="7" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B141" s="8">
         <v>46125.815781006946</v>
@@ -10080,16 +10086,16 @@
         <v>46175.16831246528</v>
       </c>
       <c r="E141" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F141" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G141" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H141" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I141" s="9"/>
       <c r="J141" s="8">
@@ -10105,13 +10111,13 @@
         <v>26</v>
       </c>
       <c r="N141" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O141" s="9" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P141" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="Q141" s="9"/>
       <c r="R141" s="9"/>
@@ -10121,7 +10127,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B142" s="5">
         <v>46125.81592018518</v>
@@ -10131,16 +10137,16 @@
         <v>46175.168314062495</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F142" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G142" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H142" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I142" s="6"/>
       <c r="J142" s="5">
@@ -10156,13 +10162,13 @@
         <v>26</v>
       </c>
       <c r="N142" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O142" s="6" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P142" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Q142" s="6"/>
       <c r="R142" s="6"/>
@@ -10172,7 +10178,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="7" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="B143" s="8">
         <v>46125.81606405093</v>
@@ -10182,16 +10188,16 @@
         <v>46175.16831547454</v>
       </c>
       <c r="E143" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F143" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G143" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H143" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I143" s="9"/>
       <c r="J143" s="8">
@@ -10207,13 +10213,13 @@
         <v>26</v>
       </c>
       <c r="N143" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O143" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="P143" s="9" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Q143" s="9"/>
       <c r="R143" s="9"/>
@@ -10223,7 +10229,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B144" s="5">
         <v>46125.81619271991</v>
@@ -10233,16 +10239,16 @@
         <v>46175.16831677083</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F144" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G144" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H144" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I144" s="6"/>
       <c r="J144" s="5">
@@ -10258,13 +10264,13 @@
         <v>26</v>
       </c>
       <c r="N144" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O144" s="6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P144" s="6" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="Q144" s="6"/>
       <c r="R144" s="6"/>
@@ -10274,7 +10280,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="7" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="B145" s="8">
         <v>46125.81632106482</v>
@@ -10284,16 +10290,16 @@
         <v>46175.16831813657</v>
       </c>
       <c r="E145" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F145" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G145" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H145" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I145" s="9"/>
       <c r="J145" s="8">
@@ -10309,13 +10315,13 @@
         <v>26</v>
       </c>
       <c r="N145" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O145" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P145" s="9" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="Q145" s="9"/>
       <c r="R145" s="9"/>
@@ -10325,7 +10331,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B146" s="5">
         <v>46125.816468668985</v>
@@ -10335,16 +10341,16 @@
         <v>46175.16831954861</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F146" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G146" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H146" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I146" s="6"/>
       <c r="J146" s="5">
@@ -10360,13 +10366,13 @@
         <v>26</v>
       </c>
       <c r="N146" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O146" s="6" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P146" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="Q146" s="6"/>
       <c r="R146" s="6"/>
@@ -10376,7 +10382,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="7" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B147" s="8">
         <v>46077.54519927083</v>
@@ -10386,16 +10392,16 @@
         <v>46177.189300150465</v>
       </c>
       <c r="E147" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F147" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G147" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H147" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I147" s="8">
         <v>46176</v>
@@ -10413,13 +10419,13 @@
         <v>26</v>
       </c>
       <c r="N147" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="O147" s="9" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="P147" s="9" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="Q147" s="8">
         <v>46176</v>
@@ -10428,7 +10434,7 @@
         <v>46176</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T147" s="9">
         <v>0</v>
@@ -10439,7 +10445,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B148" s="5">
         <v>46125.81660767361</v>
@@ -10449,16 +10455,16 @@
         <v>46176.1683697338</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F148" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G148" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H148" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I148" s="6"/>
       <c r="J148" s="5">
@@ -10474,13 +10480,13 @@
         <v>26</v>
       </c>
       <c r="N148" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O148" s="6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="P148" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q148" s="6"/>
       <c r="R148" s="6"/>
@@ -10490,7 +10496,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="7" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B149" s="8">
         <v>46125.81673583333</v>
@@ -10500,16 +10506,16 @@
         <v>46176.16837118055</v>
       </c>
       <c r="E149" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="F149" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G149" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H149" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I149" s="9"/>
       <c r="J149" s="8">
@@ -10525,13 +10531,13 @@
         <v>26</v>
       </c>
       <c r="N149" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O149" s="9" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P149" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q149" s="9"/>
       <c r="R149" s="9"/>
@@ -10541,7 +10547,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B150" s="5">
         <v>46125.81686799768</v>
@@ -10551,16 +10557,16 @@
         <v>46176.16837233797</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F150" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G150" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H150" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I150" s="6"/>
       <c r="J150" s="5">
@@ -10576,13 +10582,13 @@
         <v>26</v>
       </c>
       <c r="N150" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O150" s="6" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P150" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q150" s="6"/>
       <c r="R150" s="6"/>
@@ -10592,7 +10598,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="7" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B151" s="8">
         <v>46125.81698454861</v>
@@ -10602,16 +10608,16 @@
         <v>46176.16837344907</v>
       </c>
       <c r="E151" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F151" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G151" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H151" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I151" s="9"/>
       <c r="J151" s="8">
@@ -10627,13 +10633,13 @@
         <v>26</v>
       </c>
       <c r="N151" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O151" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="P151" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q151" s="9"/>
       <c r="R151" s="9"/>
@@ -10643,7 +10649,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B152" s="5">
         <v>46125.81713481482</v>
@@ -10653,16 +10659,16 @@
         <v>46176.1683746412</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F152" s="6" t="s">
         <v>26</v>
       </c>
       <c r="G152" s="6" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H152" s="6" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I152" s="6"/>
       <c r="J152" s="5">
@@ -10678,13 +10684,13 @@
         <v>26</v>
       </c>
       <c r="N152" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O152" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P152" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q152" s="6"/>
       <c r="R152" s="6"/>
@@ -10694,7 +10700,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="7" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="B153" s="8">
         <v>46125.8172621875</v>
@@ -10704,16 +10710,16 @@
         <v>46176.16837584491</v>
       </c>
       <c r="E153" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F153" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G153" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="H153" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="I153" s="9"/>
       <c r="J153" s="8">
@@ -10729,13 +10735,13 @@
         <v>26</v>
       </c>
       <c r="N153" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O153" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="P153" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="Q153" s="9"/>
       <c r="R153" s="9"/>
@@ -10745,7 +10751,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="B154" s="5">
         <v>46077.54519966435</v>
@@ -10755,7 +10761,7 @@
         <v>46125.90721503472</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="F154" s="6" t="s">
         <v>25</v>
@@ -10779,7 +10785,7 @@
         <v>26</v>
       </c>
       <c r="O154" s="6" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="P154" s="6" t="s">
         <v>26</v>
@@ -10792,7 +10798,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="7" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B155" s="8">
         <v>46077.54519996527</v>
@@ -10802,16 +10808,16 @@
         <v>46186.20134465278</v>
       </c>
       <c r="E155" s="9" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="F155" s="9" t="s">
         <v>26</v>
       </c>
       <c r="G155" s="9" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="H155" s="9" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I155" s="8">
         <v>46177</v>
@@ -10829,13 +10835,13 @@
         <v>26</v>
       </c>
       <c r="N155" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O155" s="9" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P155" s="9" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q155" s="8">
         <v>46185</v>
@@ -10844,7 +10850,7 @@
         <v>46177</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
@@ -10855,7 +10861,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B156" s="5">
         <v>46077.545200277775</v>
@@ -10865,16 +10871,16 @@
         <v>46186.201344699075</v>
       </c>
       <c r="E156" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="F156" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="G156" s="6" t="s">
+        <v>453</v>
+      </c>
+      <c r="H156" s="6" t="s">
         <v>454</v>
-      </c>
-      <c r="F156" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G156" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="H156" s="6" t="s">
-        <v>452</v>
       </c>
       <c r="I156" s="5">
         <v>46177</v>
@@ -10892,13 +10898,13 @@
         <v>26</v>
       </c>
       <c r="N156" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="O156" s="6" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="P156" s="6" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="Q156" s="5">
         <v>46185</v>
@@ -10907,7 +10913,7 @@
         <v>46177</v>
       </c>
       <c r="S156" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T156" s="6">
         <v>0</v>
@@ -10918,7 +10924,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="7" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B157" s="8">
         <v>46090.70994861111</v>
@@ -10928,7 +10934,7 @@
         <v>46125.907787916665</v>
       </c>
       <c r="E157" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F157" s="9" t="s">
         <v>25</v>
@@ -10952,7 +10958,7 @@
         <v>26</v>
       </c>
       <c r="O157" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P157" s="9" t="s">
         <v>26</v>
@@ -10960,18 +10966,18 @@
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
       <c r="S157" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T157" s="9">
         <v>0</v>
       </c>
       <c r="U157" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B158" s="5">
         <v>46090.71005349537</v>
@@ -10981,7 +10987,7 @@
         <v>46185.197705416664</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F158" s="6" t="s">
         <v>26</v>
@@ -11008,13 +11014,13 @@
         <v>26</v>
       </c>
       <c r="N158" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O158" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="P158" s="6" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="Q158" s="5">
         <v>46184</v>
@@ -11023,7 +11029,7 @@
         <v>46176</v>
       </c>
       <c r="S158" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T158" s="6">
         <v>0</v>
@@ -11034,7 +11040,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="7" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B159" s="8">
         <v>46090.70960611111</v>
@@ -11044,7 +11050,7 @@
         <v>46196.17368006945</v>
       </c>
       <c r="E159" s="9" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="F159" s="9" t="s">
         <v>26</v>
@@ -11071,13 +11077,13 @@
         <v>26</v>
       </c>
       <c r="N159" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="O159" s="9" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="P159" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="Q159" s="8">
         <v>46195</v>
@@ -11086,7 +11092,7 @@
         <v>46185</v>
       </c>
       <c r="S159" s="11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="T159" s="9">
         <v>0</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -2036,13 +2036,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.54519802083</v>
+        <v>46077.37853135417</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.721198263884</v>
+        <v>46092.55453159723</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.60918222222</v>
+        <v>46112.44251555555</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2085,13 +2085,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.54519871528</v>
+        <v>46077.378532048606</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.72116893518</v>
+        <v>46092.55450226852</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.721199837964</v>
+        <v>46092.55453317129</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2150,13 +2150,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.54519913194</v>
+        <v>46077.37853246528</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.721169502314</v>
+        <v>46092.55450283564</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.64751465278</v>
+        <v>46134.48084798611</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2215,13 +2215,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.54519949074</v>
+        <v>46077.37853282408</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.7211699537</v>
+        <v>46092.554503287036</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.647555393516</v>
+        <v>46134.48088872685</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2280,13 +2280,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.54519986111</v>
+        <v>46077.378533194445</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.721170439814</v>
+        <v>46092.55450377315</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.64759444444</v>
+        <v>46134.48092777778</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2345,13 +2345,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.545200196764</v>
+        <v>46077.37853353009</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.72117107639</v>
+        <v>46092.55450440972</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.64762820602</v>
+        <v>46134.48096153935</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2410,11 +2410,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.545200532404</v>
+        <v>46077.37853386574</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.50634554398</v>
+        <v>46114.33967887731</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2457,13 +2457,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.5452008912</v>
+        <v>46077.37853422454</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.5063353588</v>
+        <v>46114.33966869213</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.506357245366</v>
+        <v>46114.33969057871</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2522,11 +2522,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.54520121528</v>
+        <v>46077.37853454861</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46204.87323738426</v>
+        <v>46204.70657071759</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2585,11 +2585,11 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46125.8197722801</v>
+        <v>46125.653105613426</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46204.87334092593</v>
+        <v>46204.70667425926</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2638,11 +2638,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46125.820048113426</v>
+        <v>46125.653381446755</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46204.8733403125</v>
+        <v>46204.70667364584</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2691,11 +2691,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46125.82033290509</v>
+        <v>46125.653666238424</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46204.8733396875</v>
+        <v>46204.70667302083</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2744,11 +2744,11 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46125.82063702546</v>
+        <v>46125.65397035879</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46204.87333894676</v>
+        <v>46204.706672280096</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2797,13 +2797,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.5452015162</v>
+        <v>46077.37853484954</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.50533615741</v>
+        <v>46114.33866949074</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.50535017361</v>
+        <v>46114.33868350694</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2850,13 +2850,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.54519763889</v>
+        <v>46077.37853097222</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.5523825</v>
+        <v>46097.385715833334</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.552399583336</v>
+        <v>46097.385732916664</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2915,13 +2915,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.54519880787</v>
+        <v>46077.3785321412</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.50500038195</v>
+        <v>46114.33833371528</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.505018090276</v>
+        <v>46114.33835142361</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2980,13 +2980,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.545199155094</v>
+        <v>46077.37853248842</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.55255847222</v>
+        <v>46097.385891805556</v>
       </c>
       <c r="D20" s="5">
-        <v>46125.76278827546</v>
+        <v>46125.596121608796</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -3045,13 +3045,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.54519956018</v>
+        <v>46077.37853289352</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.50531283565</v>
+        <v>46114.33864616898</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.50533729167</v>
+        <v>46114.338670625</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -3110,13 +3110,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.54519991898</v>
+        <v>46077.37853325231</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.627469444444</v>
+        <v>46122.46080277778</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.76425234954</v>
+        <v>46191.59758568287</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -3159,13 +3159,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.545200625</v>
+        <v>46077.378533958334</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.55243590278</v>
+        <v>46097.38576923611</v>
       </c>
       <c r="D23" s="8">
-        <v>46097.55245158565</v>
+        <v>46097.38578491898</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -3224,13 +3224,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.545200312496</v>
+        <v>46077.37853364584</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.552273622685</v>
+        <v>46097.38560695601</v>
       </c>
       <c r="D24" s="5">
-        <v>46135.764537361116</v>
+        <v>46135.597870694444</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -3289,13 +3289,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.54520094907</v>
+        <v>46077.37853428241</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.50689366898</v>
+        <v>46114.340227002314</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.50691030093</v>
+        <v>46114.34024363426</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -3354,13 +3354,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.54520128472</v>
+        <v>46077.37853461805</v>
       </c>
       <c r="C26" s="5">
-        <v>46122.627451168984</v>
+        <v>46122.46078450231</v>
       </c>
       <c r="D26" s="5">
-        <v>46122.6274699537</v>
+        <v>46122.46080328704</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -3419,13 +3419,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.553287766204</v>
+        <v>46077.38662109953</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.505863032406</v>
+        <v>46114.33919636574</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.50608950232</v>
+        <v>46114.33942283565</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -3484,13 +3484,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.54519655093</v>
+        <v>46077.378529884256</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.76405297454</v>
+        <v>46191.59738630787</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.76406943287</v>
+        <v>46191.5974027662</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -3549,13 +3549,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46125.69234111111</v>
+        <v>46125.52567444445</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.76408129629</v>
+        <v>46191.59741462963</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.764096643514</v>
+        <v>46191.59742997686</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3614,13 +3614,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46125.69240738426</v>
+        <v>46125.525740717596</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.764104965274</v>
+        <v>46191.59743829861</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.764121307875</v>
+        <v>46191.5974546412</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3679,13 +3679,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46125.69558788194</v>
+        <v>46125.52892121528</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.76414623843</v>
+        <v>46191.59747957176</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.76416752315</v>
+        <v>46191.597500856486</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3744,11 +3744,11 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.545196886575</v>
+        <v>46077.37853021991</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.69258219907</v>
+        <v>46182.5259155324</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3793,13 +3793,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.54519711806</v>
+        <v>46077.37853045139</v>
       </c>
       <c r="C33" s="8">
-        <v>46155.87452237269</v>
+        <v>46155.707855706016</v>
       </c>
       <c r="D33" s="8">
-        <v>46155.87452380787</v>
+        <v>46155.7078571412</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3858,13 +3858,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.54519739583</v>
+        <v>46077.37853072917</v>
       </c>
       <c r="C34" s="5">
-        <v>46114.505526747686</v>
+        <v>46114.338860081014</v>
       </c>
       <c r="D34" s="5">
-        <v>46114.50552802083</v>
+        <v>46114.33886135417</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3923,13 +3923,13 @@
         <v>134</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.54519766204</v>
+        <v>46077.37853099537</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.86621715278</v>
+        <v>46155.69955048611</v>
       </c>
       <c r="D35" s="8">
-        <v>46155.86621849537</v>
+        <v>46155.6995518287</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>135</v>
@@ -3988,13 +3988,13 @@
         <v>137</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.54519791667</v>
+        <v>46077.37853125</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.50563148149</v>
+        <v>46114.338964814815</v>
       </c>
       <c r="D36" s="5">
-        <v>46125.91364752315</v>
+        <v>46125.74698085648</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>138</v>
@@ -4053,13 +4053,13 @@
         <v>140</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.54519712963</v>
+        <v>46077.378530462964</v>
       </c>
       <c r="C37" s="8">
-        <v>46158.75835467593</v>
+        <v>46158.591688009255</v>
       </c>
       <c r="D37" s="8">
-        <v>46158.75835697917</v>
+        <v>46158.5916903125</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>141</v>
@@ -4118,13 +4118,13 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.54519734954</v>
+        <v>46077.378530682865</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.55231699074</v>
+        <v>46097.385650324075</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.552318773145</v>
+        <v>46097.38565210648</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4183,13 +4183,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.545197569445</v>
+        <v>46077.37853090277</v>
       </c>
       <c r="C39" s="8">
-        <v>46155.895487546295</v>
+        <v>46155.72882087963</v>
       </c>
       <c r="D39" s="8">
-        <v>46155.89548886574</v>
+        <v>46155.728822199075</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>147</v>
@@ -4248,13 +4248,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.54519778935</v>
+        <v>46077.37853112268</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.6925612037</v>
+        <v>46182.52589453704</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.69257489583</v>
+        <v>46182.52590822917</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -4313,13 +4313,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.54519805555</v>
+        <v>46077.37853138889</v>
       </c>
       <c r="C41" s="8">
-        <v>46182.681518321755</v>
+        <v>46182.5148516551</v>
       </c>
       <c r="D41" s="8">
-        <v>46182.68151998843</v>
+        <v>46182.51485332176</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -4378,13 +4378,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.54519827546</v>
+        <v>46077.378531608796</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.6925475</v>
+        <v>46182.52588083333</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.692548946754</v>
+        <v>46182.5258822801</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -4443,13 +4443,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.54519849537</v>
+        <v>46077.378531828705</v>
       </c>
       <c r="C43" s="8">
-        <v>46126.8306060301</v>
+        <v>46126.663939363425</v>
       </c>
       <c r="D43" s="8">
-        <v>46126.830619456014</v>
+        <v>46126.66395278936</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4508,13 +4508,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.54519873843</v>
+        <v>46077.37853207176</v>
       </c>
       <c r="C44" s="5">
-        <v>46126.82913611111</v>
+        <v>46126.66246944445</v>
       </c>
       <c r="D44" s="5">
-        <v>46126.829137256944</v>
+        <v>46126.66247059028</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4573,13 +4573,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.54519680556</v>
+        <v>46077.378530138885</v>
       </c>
       <c r="C45" s="8">
-        <v>46126.83059133102</v>
+        <v>46126.66392466435</v>
       </c>
       <c r="D45" s="8">
-        <v>46126.83059262732</v>
+        <v>46126.663925960645</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4638,13 +4638,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.58916118056</v>
+        <v>46077.422494513885</v>
       </c>
       <c r="C46" s="5">
-        <v>46126.829580474536</v>
+        <v>46126.66291380787</v>
       </c>
       <c r="D46" s="5">
-        <v>46126.829593946764</v>
+        <v>46126.66292728009</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4703,13 +4703,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.589282581015</v>
+        <v>46077.42261591435</v>
       </c>
       <c r="C47" s="8">
-        <v>46126.82903850694</v>
+        <v>46126.66237184028</v>
       </c>
       <c r="D47" s="8">
-        <v>46126.82903986111</v>
+        <v>46126.66237319444</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4768,13 +4768,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.589497685185</v>
+        <v>46077.42283101851</v>
       </c>
       <c r="C48" s="5">
-        <v>46126.82956608797</v>
+        <v>46126.662899421295</v>
       </c>
       <c r="D48" s="5">
-        <v>46126.829567256944</v>
+        <v>46126.66290059028</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4833,13 +4833,13 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.54519818287</v>
+        <v>46077.3785315162</v>
       </c>
       <c r="C49" s="8">
-        <v>46147.88814045139</v>
+        <v>46147.721473784724</v>
       </c>
       <c r="D49" s="8">
-        <v>46147.8881425</v>
+        <v>46147.72147583333</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4898,13 +4898,13 @@
         <v>181</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.545198437496</v>
+        <v>46077.37853177083</v>
       </c>
       <c r="C50" s="5">
-        <v>46097.55269060185</v>
+        <v>46097.386023935185</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.764061747686</v>
+        <v>46191.597395081015</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4963,13 +4963,13 @@
         <v>184</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.54519870371</v>
+        <v>46077.37853203704</v>
       </c>
       <c r="C51" s="8">
-        <v>46147.85066253472</v>
+        <v>46147.68399586805</v>
       </c>
       <c r="D51" s="8">
-        <v>46150.78326474537</v>
+        <v>46150.616598078705</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -5028,13 +5028,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46125.69589043982</v>
+        <v>46125.52922377315</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.76882001157</v>
+        <v>46191.60215334491</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.76988886574</v>
+        <v>46191.603222199075</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -5093,13 +5093,13 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46125.70470673611</v>
+        <v>46125.53804006944</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.769818437504</v>
+        <v>46191.60315177083</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.76981975694</v>
+        <v>46191.60315309028</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>120</v>
@@ -5148,13 +5148,13 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46125.704894062495</v>
+        <v>46125.53822739584</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.76987311343</v>
+        <v>46191.60320644676</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.76987484954</v>
+        <v>46191.603208182874</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -5203,13 +5203,13 @@
         <v>195</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.68332820602</v>
+        <v>46125.516661539354</v>
       </c>
       <c r="C55" s="8">
-        <v>46204.65960825232</v>
+        <v>46204.492941585646</v>
       </c>
       <c r="D55" s="8">
-        <v>46204.65962090278</v>
+        <v>46204.492954236106</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>196</v>
@@ -5268,13 +5268,13 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.70524613426</v>
+        <v>46125.5385794676</v>
       </c>
       <c r="C56" s="5">
-        <v>46195.689746724536</v>
+        <v>46195.52308005787</v>
       </c>
       <c r="D56" s="5">
-        <v>46195.68974824074</v>
+        <v>46195.52308157407</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>114</v>
@@ -5323,13 +5323,13 @@
         <v>202</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.70538292824</v>
+        <v>46125.53871626157</v>
       </c>
       <c r="C57" s="8">
-        <v>46204.6595924537</v>
+        <v>46204.49292578704</v>
       </c>
       <c r="D57" s="8">
-        <v>46204.6595946875</v>
+        <v>46204.49292802083</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>203</v>
@@ -5378,13 +5378,13 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.718428078704</v>
+        <v>46125.55176141203</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.694698113424</v>
+        <v>46195.52803144676</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.69469942129</v>
+        <v>46195.52803275463</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -5433,13 +5433,13 @@
         <v>208</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.718640543986</v>
+        <v>46125.551973877315</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.694708229166</v>
+        <v>46195.5280415625</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.69470958333</v>
+        <v>46195.52804291667</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -5488,13 +5488,13 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46125.71897782407</v>
+        <v>46125.55231115741</v>
       </c>
       <c r="C60" s="5">
-        <v>46195.69645509259</v>
+        <v>46195.52978842593</v>
       </c>
       <c r="D60" s="5">
-        <v>46195.69645640046</v>
+        <v>46195.529789733795</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5543,13 +5543,13 @@
         <v>212</v>
       </c>
       <c r="B61" s="8">
-        <v>46125.71913549768</v>
+        <v>46125.55246883102</v>
       </c>
       <c r="C61" s="8">
-        <v>46195.69541388889</v>
+        <v>46195.528747222226</v>
       </c>
       <c r="D61" s="8">
-        <v>46195.69541526621</v>
+        <v>46195.528748599536</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>213</v>
@@ -5598,13 +5598,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46126.81590638889</v>
+        <v>46126.64923972222</v>
       </c>
       <c r="C62" s="5">
-        <v>46195.69561555555</v>
+        <v>46195.52894888889</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.69561689815</v>
+        <v>46195.528950231484</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5653,11 +5653,11 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46191.76807549769</v>
+        <v>46191.60140883102</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.695621990744</v>
+        <v>46195.52895532407</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>
@@ -5704,13 +5704,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.69345099537</v>
+        <v>46125.5267843287</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.659945023144</v>
+        <v>46195.49327835648</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.83151038195</v>
+        <v>46198.664843715276</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5769,13 +5769,13 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46125.7055987037</v>
+        <v>46125.53893203704</v>
       </c>
       <c r="C65" s="8">
-        <v>46195.6598427662</v>
+        <v>46195.49317609954</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.65984503472</v>
+        <v>46195.49317836805</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>117</v>
@@ -5824,13 +5824,13 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46125.70569783565</v>
+        <v>46125.539031168984</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.65992416667</v>
+        <v>46195.4932575</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.65992711806</v>
+        <v>46195.49326045139</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5879,11 +5879,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46077.54519895834</v>
+        <v>46077.37853229167</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.698486747686</v>
+        <v>46127.531820081014</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5926,13 +5926,13 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46077.54519921297</v>
+        <v>46077.378532546296</v>
       </c>
       <c r="C68" s="5">
-        <v>46127.69765324074</v>
+        <v>46127.53098657407</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.85981012732</v>
+        <v>46197.69314346065</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5991,13 +5991,13 @@
         <v>236</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.6963875463</v>
+        <v>46125.529720879626</v>
       </c>
       <c r="C69" s="8">
-        <v>46127.69763241898</v>
+        <v>46127.53096575232</v>
       </c>
       <c r="D69" s="8">
-        <v>46127.697633749995</v>
+        <v>46127.53096708334</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>237</v>
@@ -6046,13 +6046,13 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.69656831019</v>
+        <v>46125.52990164352</v>
       </c>
       <c r="C70" s="5">
-        <v>46127.69763894676</v>
+        <v>46127.53097228009</v>
       </c>
       <c r="D70" s="5">
-        <v>46127.6976405787</v>
+        <v>46127.53097391204</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>241</v>
@@ -6101,13 +6101,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.545196736115</v>
+        <v>46077.37853006944</v>
       </c>
       <c r="C71" s="8">
-        <v>46127.69789872685</v>
+        <v>46127.53123206018</v>
       </c>
       <c r="D71" s="8">
-        <v>46197.708300150465</v>
+        <v>46197.541633483794</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>243</v>
@@ -6166,13 +6166,13 @@
         <v>245</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.69788891204</v>
+        <v>46125.531222245365</v>
       </c>
       <c r="C72" s="5">
-        <v>46127.697883437504</v>
+        <v>46127.53121677083</v>
       </c>
       <c r="D72" s="5">
-        <v>46127.69788501157</v>
+        <v>46127.531218344906</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>237</v>
@@ -6221,13 +6221,13 @@
         <v>248</v>
       </c>
       <c r="B73" s="8">
-        <v>46125.69801100694</v>
+        <v>46125.53134434028</v>
       </c>
       <c r="C73" s="8">
-        <v>46127.69787200232</v>
+        <v>46127.53120533565</v>
       </c>
       <c r="D73" s="8">
-        <v>46127.697873287034</v>
+        <v>46127.53120662037</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>241</v>
@@ -6276,13 +6276,13 @@
         <v>251</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.70475186342</v>
+        <v>46090.538085196764</v>
       </c>
       <c r="C74" s="5">
-        <v>46127.69847682871</v>
+        <v>46127.531810162036</v>
       </c>
       <c r="D74" s="5">
-        <v>46127.698491539355</v>
+        <v>46127.53182487268</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
@@ -6341,13 +6341,13 @@
         <v>253</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.69814037037</v>
+        <v>46125.531473703704</v>
       </c>
       <c r="C75" s="8">
-        <v>46127.69844965277</v>
+        <v>46127.531782986116</v>
       </c>
       <c r="D75" s="8">
-        <v>46127.698451331016</v>
+        <v>46127.53178466435</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>237</v>
@@ -6396,13 +6396,13 @@
         <v>254</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.6983227662</v>
+        <v>46125.53165609954</v>
       </c>
       <c r="C76" s="5">
-        <v>46127.69845996528</v>
+        <v>46127.53179329861</v>
       </c>
       <c r="D76" s="5">
-        <v>46127.69846143518</v>
+        <v>46127.53179476852</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>241</v>
@@ -6451,11 +6451,11 @@
         <v>255</v>
       </c>
       <c r="B77" s="8">
-        <v>46090.70479819445</v>
+        <v>46090.53813152778</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.7984696875</v>
+        <v>46198.631803020835</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>256</v>
@@ -6514,11 +6514,11 @@
         <v>259</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.69919584491</v>
+        <v>46125.532529178236</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.16821967592</v>
+        <v>46167.001553009264</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>237</v>
@@ -6565,11 +6565,11 @@
         <v>261</v>
       </c>
       <c r="B79" s="8">
-        <v>46125.69931737268</v>
+        <v>46125.53265070602</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46167.168221562504</v>
+        <v>46167.00155489583</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>241</v>
@@ -6616,13 +6616,13 @@
         <v>263</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.54519710648</v>
+        <v>46077.37853043982</v>
       </c>
       <c r="C80" s="5">
-        <v>46198.83128773148</v>
+        <v>46198.66462106482</v>
       </c>
       <c r="D80" s="5">
-        <v>46198.831302199076</v>
+        <v>46198.664635532405</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>264</v>
@@ -6669,13 +6669,13 @@
         <v>266</v>
       </c>
       <c r="B81" s="8">
-        <v>46077.54519784723</v>
+        <v>46077.378531180555</v>
       </c>
       <c r="C81" s="8">
-        <v>46191.76955590278</v>
+        <v>46191.60288923611</v>
       </c>
       <c r="D81" s="8">
-        <v>46191.7695737037</v>
+        <v>46191.60290703704</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>267</v>
@@ -6734,13 +6734,13 @@
         <v>271</v>
       </c>
       <c r="B82" s="5">
-        <v>46125.69615554398</v>
+        <v>46125.52948887731</v>
       </c>
       <c r="C82" s="5">
-        <v>46191.77013172454</v>
+        <v>46191.603465057866</v>
       </c>
       <c r="D82" s="5">
-        <v>46191.77014716435</v>
+        <v>46191.60348049768</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>272</v>
@@ -6799,13 +6799,13 @@
         <v>274</v>
       </c>
       <c r="B83" s="8">
-        <v>46125.699760648145</v>
+        <v>46125.53309398148</v>
       </c>
       <c r="C83" s="8">
-        <v>46198.83126899306</v>
+        <v>46198.66460232639</v>
       </c>
       <c r="D83" s="8">
-        <v>46198.83128892361</v>
+        <v>46198.66462225694</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>275</v>
@@ -6864,13 +6864,13 @@
         <v>277</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.545198472224</v>
+        <v>46077.37853180556</v>
       </c>
       <c r="C84" s="5">
-        <v>46191.769443275465</v>
+        <v>46191.602776608794</v>
       </c>
       <c r="D84" s="5">
-        <v>46191.770536875</v>
+        <v>46191.60387020833</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>278</v>
@@ -6929,13 +6929,13 @@
         <v>280</v>
       </c>
       <c r="B85" s="8">
-        <v>46125.775447465276</v>
+        <v>46125.60878079861</v>
       </c>
       <c r="C85" s="8">
-        <v>46191.769735925925</v>
+        <v>46191.60306925926</v>
       </c>
       <c r="D85" s="8">
-        <v>46191.76973724537</v>
+        <v>46191.603070578705</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>281</v>
@@ -6984,13 +6984,13 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46125.77559420139</v>
+        <v>46125.60892753472</v>
       </c>
       <c r="C86" s="5">
-        <v>46191.7705319213</v>
+        <v>46191.60386525463</v>
       </c>
       <c r="D86" s="5">
-        <v>46191.77053325232</v>
+        <v>46191.60386658565</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>284</v>
@@ -7039,11 +7039,11 @@
         <v>285</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.77573671297</v>
+        <v>46125.609070046296</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46198.831276655095</v>
+        <v>46198.664609988424</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>276</v>
@@ -7092,13 +7092,13 @@
         <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46077.545199050925</v>
+        <v>46077.37853238426</v>
       </c>
       <c r="C88" s="5">
-        <v>46191.770449421296</v>
+        <v>46191.603782754624</v>
       </c>
       <c r="D88" s="5">
-        <v>46191.77046482639</v>
+        <v>46191.60379815972</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>287</v>
@@ -7145,13 +7145,13 @@
         <v>289</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.5451993287</v>
+        <v>46077.37853266204</v>
       </c>
       <c r="C89" s="8">
-        <v>46191.76127780092</v>
+        <v>46191.594611134264</v>
       </c>
       <c r="D89" s="8">
-        <v>46191.77013883102</v>
+        <v>46191.60347216435</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>290</v>
@@ -7210,13 +7210,13 @@
         <v>295</v>
       </c>
       <c r="B90" s="5">
-        <v>46077.54519958333</v>
+        <v>46077.37853291667</v>
       </c>
       <c r="C90" s="5">
-        <v>46191.76363961806</v>
+        <v>46191.59697295139</v>
       </c>
       <c r="D90" s="5">
-        <v>46191.76662447916</v>
+        <v>46191.599957812505</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>296</v>
@@ -7275,13 +7275,13 @@
         <v>299</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.780000914354</v>
+        <v>46125.61333424768</v>
       </c>
       <c r="C91" s="8">
-        <v>46191.76360844907</v>
+        <v>46191.59694178241</v>
       </c>
       <c r="D91" s="8">
-        <v>46191.76361026621</v>
+        <v>46191.596943599536</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>300</v>
@@ -7330,13 +7330,13 @@
         <v>303</v>
       </c>
       <c r="B92" s="5">
-        <v>46125.779717233796</v>
+        <v>46125.61305056713</v>
       </c>
       <c r="C92" s="5">
-        <v>46191.76362376157</v>
+        <v>46191.59695709491</v>
       </c>
       <c r="D92" s="5">
-        <v>46191.76362532408</v>
+        <v>46191.59695865741</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>304</v>
@@ -7385,13 +7385,13 @@
         <v>306</v>
       </c>
       <c r="B93" s="8">
-        <v>46077.54519984954</v>
+        <v>46077.37853318287</v>
       </c>
       <c r="C93" s="8">
-        <v>46191.77043608796</v>
+        <v>46191.6037694213</v>
       </c>
       <c r="D93" s="8">
-        <v>46193.954018240736</v>
+        <v>46193.78735157408</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>307</v>
@@ -7450,13 +7450,13 @@
         <v>308</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.7814462963</v>
+        <v>46125.61477962963</v>
       </c>
       <c r="C94" s="5">
-        <v>46193.953992442126</v>
+        <v>46193.78732577546</v>
       </c>
       <c r="D94" s="5">
-        <v>46193.953995034724</v>
+        <v>46193.78732836805</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -7505,13 +7505,13 @@
         <v>311</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.78158427084</v>
+        <v>46125.614917604165</v>
       </c>
       <c r="C95" s="8">
-        <v>46193.95400423611</v>
+        <v>46193.78733756945</v>
       </c>
       <c r="D95" s="8">
-        <v>46193.9540056713</v>
+        <v>46193.78733900463</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>304</v>
@@ -7560,11 +7560,11 @@
         <v>314</v>
       </c>
       <c r="B96" s="5">
-        <v>46077.54520011574</v>
+        <v>46077.378533449075</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.87202574074</v>
+        <v>46198.70535907407</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>264</v>
@@ -7607,13 +7607,13 @@
         <v>316</v>
       </c>
       <c r="B97" s="8">
-        <v>46077.545198078704</v>
+        <v>46077.37853141203</v>
       </c>
       <c r="C97" s="8">
-        <v>46191.78640506945</v>
+        <v>46191.61973840278</v>
       </c>
       <c r="D97" s="8">
-        <v>46191.78642105324</v>
+        <v>46191.61975438657</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>317</v>
@@ -7672,13 +7672,13 @@
         <v>319</v>
       </c>
       <c r="B98" s="5">
-        <v>46077.54519778935</v>
+        <v>46077.37853112268</v>
       </c>
       <c r="C98" s="5">
-        <v>46191.78658587963</v>
+        <v>46191.619919212964</v>
       </c>
       <c r="D98" s="5">
-        <v>46191.78660222222</v>
+        <v>46191.61993555556</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>320</v>
@@ -7737,11 +7737,11 @@
         <v>322</v>
       </c>
       <c r="B99" s="8">
-        <v>46077.54520075231</v>
+        <v>46077.37853408565</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46199.847719363424</v>
+        <v>46199.68105269676</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>323</v>
@@ -7800,13 +7800,13 @@
         <v>324</v>
       </c>
       <c r="B100" s="5">
-        <v>46077.54519734954</v>
+        <v>46077.378530682865</v>
       </c>
       <c r="C100" s="5">
-        <v>46198.872020173614</v>
+        <v>46198.70535350694</v>
       </c>
       <c r="D100" s="5">
-        <v>46198.87203554398</v>
+        <v>46198.705368877316</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>60</v>
@@ -7865,11 +7865,11 @@
         <v>326</v>
       </c>
       <c r="B101" s="8">
-        <v>46077.55796549769</v>
+        <v>46077.39129883102</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46198.87327074074</v>
+        <v>46198.706604074076</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>327</v>
@@ -7928,13 +7928,13 @@
         <v>328</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.79029034722</v>
+        <v>46125.623623680556</v>
       </c>
       <c r="C102" s="5">
-        <v>46204.68543188657</v>
+        <v>46204.51876521991</v>
       </c>
       <c r="D102" s="5">
-        <v>46204.68545116898</v>
+        <v>46204.51878450232</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>329</v>
@@ -7991,11 +7991,11 @@
         <v>330</v>
       </c>
       <c r="B103" s="8">
-        <v>46077.54519841435</v>
+        <v>46077.37853174769</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.86928554398</v>
+        <v>46195.702618877316</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>331</v>
@@ -8038,13 +8038,13 @@
         <v>333</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.545198761574</v>
+        <v>46077.37853209491</v>
       </c>
       <c r="C104" s="5">
-        <v>46195.86927984953</v>
+        <v>46195.702613182875</v>
       </c>
       <c r="D104" s="5">
-        <v>46195.86929523148</v>
+        <v>46205.32310429398</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>334</v>
@@ -8088,8 +8088,8 @@
       <c r="R104" s="5">
         <v>46142</v>
       </c>
-      <c r="S104" s="10" t="s">
-        <v>31</v>
+      <c r="S104" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8103,11 +8103,13 @@
         <v>335</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.785526736116</v>
-      </c>
-      <c r="C105" s="9"/>
+        <v>46125.618860069444</v>
+      </c>
+      <c r="C105" s="8">
+        <v>46205.3172833912</v>
+      </c>
       <c r="D105" s="8">
-        <v>46204.68543935185</v>
+        <v>46205.31728560185</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>237</v>
@@ -8156,11 +8158,13 @@
         <v>338</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.7863228125</v>
-      </c>
-      <c r="C106" s="6"/>
+        <v>46125.619656145835</v>
+      </c>
+      <c r="C106" s="5">
+        <v>46205.323087129625</v>
+      </c>
       <c r="D106" s="5">
-        <v>46204.685440601854</v>
+        <v>46205.32308905093</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>241</v>
@@ -8209,11 +8213,11 @@
         <v>341</v>
       </c>
       <c r="B107" s="8">
-        <v>46077.558327129635</v>
+        <v>46077.39166046296</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46154.167828125</v>
+        <v>46154.001161458335</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>342</v>
@@ -8272,11 +8276,11 @@
         <v>343</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.793145185184</v>
+        <v>46125.62647851852</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46154.16895842593</v>
+        <v>46205.31729196759</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>237</v>
@@ -8325,11 +8329,11 @@
         <v>346</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.79326523148</v>
+        <v>46125.62659856481</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46154.168959930554</v>
+        <v>46205.32309762732</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>241</v>
@@ -8378,11 +8382,11 @@
         <v>349</v>
       </c>
       <c r="B110" s="5">
-        <v>46077.5451994676</v>
+        <v>46077.378532800925</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46197.504649062495</v>
+        <v>46197.33798239584</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>350</v>
@@ -8441,13 +8445,13 @@
         <v>351</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.793417939814</v>
+        <v>46125.62675127314</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.50464319444</v>
+        <v>46197.33797652778</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.504645196765</v>
+        <v>46197.33797853009</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>237</v>
@@ -8496,11 +8500,11 @@
         <v>354</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.793529525465</v>
+        <v>46125.6268628588</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46191.78659372685</v>
+        <v>46191.61992706019</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>241</v>
@@ -8549,11 +8553,11 @@
         <v>357</v>
       </c>
       <c r="B113" s="8">
-        <v>46077.54519980324</v>
+        <v>46077.37853313657</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.60860170139</v>
+        <v>46197.44193503472</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>358</v>
@@ -8612,11 +8616,11 @@
         <v>359</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.79363706018</v>
+        <v>46125.62697039352</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.60859815972</v>
+        <v>46197.44193149306</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>237</v>
@@ -8665,11 +8669,11 @@
         <v>362</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.79376541667</v>
+        <v>46125.62709875</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46192.79081532407</v>
+        <v>46192.62414865741</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>241</v>
@@ -8718,11 +8722,11 @@
         <v>365</v>
       </c>
       <c r="B116" s="5">
-        <v>46077.54519909722</v>
+        <v>46077.37853243056</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46198.61729309028</v>
+        <v>46198.45062642361</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>366</v>
@@ -8781,13 +8785,13 @@
         <v>367</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.79408877315</v>
+        <v>46125.62742210648</v>
       </c>
       <c r="C117" s="8">
-        <v>46197.599578124995</v>
+        <v>46197.43291145834</v>
       </c>
       <c r="D117" s="8">
-        <v>46197.6086021875</v>
+        <v>46197.44193552084</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>237</v>
@@ -8836,11 +8840,11 @@
         <v>370</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.79422275463</v>
+        <v>46125.62755608796</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46191.786412430556</v>
+        <v>46191.61974576389</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>241</v>
@@ -8889,11 +8893,11 @@
         <v>373</v>
       </c>
       <c r="B119" s="8">
-        <v>46077.545200127315</v>
+        <v>46077.37853346065</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46165.197340150466</v>
+        <v>46165.030673483794</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>374</v>
@@ -8952,11 +8956,11 @@
         <v>375</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.79434175926</v>
+        <v>46125.62767509259</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46197.59958675926</v>
+        <v>46197.43292009259</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>237</v>
@@ -9003,11 +9007,11 @@
         <v>377</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.79446019676</v>
+        <v>46125.62779353009</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46164.16915030092</v>
+        <v>46164.00248363426</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>241</v>
@@ -9054,11 +9058,11 @@
         <v>379</v>
       </c>
       <c r="B122" s="5">
-        <v>46077.54520043981</v>
+        <v>46077.37853377315</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46169.19579744213</v>
+        <v>46169.02913077547</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>380</v>
@@ -9117,11 +9121,11 @@
         <v>381</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.794598078704</v>
+        <v>46125.62793141203</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.16876332176</v>
+        <v>46168.002096655095</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>237</v>
@@ -9168,11 +9172,11 @@
         <v>383</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.794723252315</v>
+        <v>46125.62805658564</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46168.168764710645</v>
+        <v>46168.00209804398</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>241</v>
@@ -9219,11 +9223,11 @@
         <v>385</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.54519771991</v>
+        <v>46077.37853105324</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46125.907215011575</v>
+        <v>46125.74054834491</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>386</v>
@@ -9266,11 +9270,11 @@
         <v>388</v>
       </c>
       <c r="B126" s="5">
-        <v>46077.5451981713</v>
+        <v>46077.378531504626</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46170.199522905095</v>
+        <v>46170.032856238424</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>389</v>
@@ -9329,11 +9333,11 @@
         <v>393</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.81236390046</v>
+        <v>46125.64569723379</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46169.16854510417</v>
+        <v>46169.0018784375</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>237</v>
@@ -9380,11 +9384,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.81252253472</v>
+        <v>46125.64585586806</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46169.168546712965</v>
+        <v>46169.0018800463</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>241</v>
@@ -9431,11 +9435,11 @@
         <v>397</v>
       </c>
       <c r="B129" s="8">
-        <v>46125.812747199074</v>
+        <v>46125.6460805324</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.16854806713</v>
+        <v>46169.00188140046</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>398</v>
@@ -9482,11 +9486,11 @@
         <v>400</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.81326880787</v>
+        <v>46125.646602141205</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.16854940972</v>
+        <v>46169.001882743054</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>63</v>
@@ -9533,11 +9537,11 @@
         <v>402</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.81384030092</v>
+        <v>46125.647173634265</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46169.168550682865</v>
+        <v>46169.00188401621</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>66</v>
@@ -9584,11 +9588,11 @@
         <v>404</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.81410221064</v>
+        <v>46125.647435543986</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46169.16855229167</v>
+        <v>46169.001885624995</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>69</v>
@@ -9635,11 +9639,11 @@
         <v>406</v>
       </c>
       <c r="B133" s="8">
-        <v>46077.5451984838</v>
+        <v>46077.37853181713</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46175.20232467593</v>
+        <v>46175.03565800926</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>407</v>
@@ -9698,11 +9702,11 @@
         <v>409</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.81482075232</v>
+        <v>46125.64815408565</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46174.16943333333</v>
+        <v>46174.00276666667</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>237</v>
@@ -9751,11 +9755,11 @@
         <v>411</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.81494678241</v>
+        <v>46125.64828011574</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46174.16943504629</v>
+        <v>46174.00276837963</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>241</v>
@@ -9804,11 +9808,11 @@
         <v>413</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.81516034722</v>
+        <v>46125.64849368056</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46174.169436400465</v>
+        <v>46174.002769733794</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>398</v>
@@ -9857,11 +9861,11 @@
         <v>415</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.81531077546</v>
+        <v>46125.64864410879</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46174.169437847224</v>
+        <v>46174.00277118056</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>63</v>
@@ -9910,11 +9914,11 @@
         <v>417</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.81545193287</v>
+        <v>46125.6487852662</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46174.16943927083</v>
+        <v>46174.002772604166</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>66</v>
@@ -9963,11 +9967,11 @@
         <v>419</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.81557276621</v>
+        <v>46125.64890609954</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46174.16944046297</v>
+        <v>46174.002773796296</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>420</v>
@@ -10016,11 +10020,11 @@
         <v>422</v>
       </c>
       <c r="B140" s="5">
-        <v>46077.54519895834</v>
+        <v>46077.37853229167</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46176.19592085648</v>
+        <v>46176.029254189816</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>423</v>
@@ -10079,11 +10083,11 @@
         <v>426</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.815781006946</v>
+        <v>46125.64911434028</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46175.16831246528</v>
+        <v>46175.001645798606</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>237</v>
@@ -10130,11 +10134,11 @@
         <v>428</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.81592018518</v>
+        <v>46125.64925351852</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46175.168314062495</v>
+        <v>46175.00164739584</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>241</v>
@@ -10181,11 +10185,11 @@
         <v>430</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.81606405093</v>
+        <v>46125.64939738426</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46175.16831547454</v>
+        <v>46175.00164880787</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>59</v>
@@ -10232,11 +10236,11 @@
         <v>432</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.81619271991</v>
+        <v>46125.64952605324</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46175.16831677083</v>
+        <v>46175.00165010417</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>63</v>
@@ -10283,11 +10287,11 @@
         <v>434</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.81632106482</v>
+        <v>46125.64965439815</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46175.16831813657</v>
+        <v>46175.00165146991</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>66</v>
@@ -10334,11 +10338,11 @@
         <v>436</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.816468668985</v>
+        <v>46125.649802002314</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46175.16831954861</v>
+        <v>46175.00165288194</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>420</v>
@@ -10385,11 +10389,11 @@
         <v>438</v>
       </c>
       <c r="B147" s="8">
-        <v>46077.54519927083</v>
+        <v>46077.37853260417</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46177.189300150465</v>
+        <v>46177.02263348379</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>439</v>
@@ -10448,11 +10452,11 @@
         <v>442</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.81660767361</v>
+        <v>46125.649941006945</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46176.1683697338</v>
+        <v>46176.00170306713</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>237</v>
@@ -10499,11 +10503,11 @@
         <v>443</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.81673583333</v>
+        <v>46125.650069166666</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46176.16837118055</v>
+        <v>46176.00170451389</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>241</v>
@@ -10550,11 +10554,11 @@
         <v>444</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.81686799768</v>
+        <v>46125.650201331024</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46176.16837233797</v>
+        <v>46176.0017056713</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>398</v>
@@ -10601,11 +10605,11 @@
         <v>445</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.81698454861</v>
+        <v>46125.65031788194</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46176.16837344907</v>
+        <v>46176.00170678241</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>63</v>
@@ -10652,11 +10656,11 @@
         <v>446</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.81713481482</v>
+        <v>46125.650468148146</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46176.1683746412</v>
+        <v>46176.00170797454</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>66</v>
@@ -10703,11 +10707,11 @@
         <v>447</v>
       </c>
       <c r="B153" s="8">
-        <v>46125.8172621875</v>
+        <v>46125.650595520834</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46176.16837584491</v>
+        <v>46176.001709178236</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>420</v>
@@ -10754,11 +10758,11 @@
         <v>448</v>
       </c>
       <c r="B154" s="5">
-        <v>46077.54519966435</v>
+        <v>46077.37853299768</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46125.90721503472</v>
+        <v>46125.740548368056</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>449</v>
@@ -10801,11 +10805,11 @@
         <v>451</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.54519996527</v>
+        <v>46077.378533298615</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46186.20134465278</v>
+        <v>46186.034677986114</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>452</v>
@@ -10864,11 +10868,11 @@
         <v>455</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.545200277775</v>
+        <v>46077.37853361111</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46186.201344699075</v>
+        <v>46186.0346780324</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>456</v>
@@ -10927,11 +10931,11 @@
         <v>458</v>
       </c>
       <c r="B157" s="8">
-        <v>46090.70994861111</v>
+        <v>46090.54328194444</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46125.907787916665</v>
+        <v>46125.74112125</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>459</v>
@@ -10980,11 +10984,11 @@
         <v>461</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.71005349537</v>
+        <v>46090.54338682871</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46185.197705416664</v>
+        <v>46185.03103875</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>462</v>
@@ -11043,11 +11047,11 @@
         <v>464</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.70960611111</v>
+        <v>46090.54293944444</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46196.17368006945</v>
+        <v>46196.00701340278</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>465</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5932,7 +5932,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46197.85981012732</v>
+        <v>46205.9047290625</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5932,7 +5932,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46205.9047290625</v>
+        <v>46209.714337812504</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -2036,13 +2036,13 @@
         <v>23</v>
       </c>
       <c r="B4" s="5">
-        <v>46077.37853135417</v>
+        <v>46077.54519802083</v>
       </c>
       <c r="C4" s="5">
-        <v>46092.55453159723</v>
+        <v>46092.721198263884</v>
       </c>
       <c r="D4" s="5">
-        <v>46112.44251555555</v>
+        <v>46112.60918222222</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>24</v>
@@ -2085,13 +2085,13 @@
         <v>27</v>
       </c>
       <c r="B5" s="8">
-        <v>46077.378532048606</v>
+        <v>46077.54519871528</v>
       </c>
       <c r="C5" s="8">
-        <v>46092.55450226852</v>
+        <v>46092.72116893518</v>
       </c>
       <c r="D5" s="8">
-        <v>46092.55453317129</v>
+        <v>46092.721199837964</v>
       </c>
       <c r="E5" s="9" t="s">
         <v>28</v>
@@ -2150,13 +2150,13 @@
         <v>33</v>
       </c>
       <c r="B6" s="5">
-        <v>46077.37853246528</v>
+        <v>46077.54519913194</v>
       </c>
       <c r="C6" s="5">
-        <v>46092.55450283564</v>
+        <v>46092.721169502314</v>
       </c>
       <c r="D6" s="5">
-        <v>46134.48084798611</v>
+        <v>46134.64751465278</v>
       </c>
       <c r="E6" s="6" t="s">
         <v>34</v>
@@ -2215,13 +2215,13 @@
         <v>37</v>
       </c>
       <c r="B7" s="8">
-        <v>46077.37853282408</v>
+        <v>46077.54519949074</v>
       </c>
       <c r="C7" s="8">
-        <v>46092.554503287036</v>
+        <v>46092.7211699537</v>
       </c>
       <c r="D7" s="8">
-        <v>46134.48088872685</v>
+        <v>46134.647555393516</v>
       </c>
       <c r="E7" s="9" t="s">
         <v>38</v>
@@ -2280,13 +2280,13 @@
         <v>39</v>
       </c>
       <c r="B8" s="5">
-        <v>46077.378533194445</v>
+        <v>46077.54519986111</v>
       </c>
       <c r="C8" s="5">
-        <v>46092.55450377315</v>
+        <v>46092.721170439814</v>
       </c>
       <c r="D8" s="5">
-        <v>46134.48092777778</v>
+        <v>46134.64759444444</v>
       </c>
       <c r="E8" s="6" t="s">
         <v>40</v>
@@ -2345,13 +2345,13 @@
         <v>42</v>
       </c>
       <c r="B9" s="8">
-        <v>46077.37853353009</v>
+        <v>46077.545200196764</v>
       </c>
       <c r="C9" s="8">
-        <v>46092.55450440972</v>
+        <v>46092.72117107639</v>
       </c>
       <c r="D9" s="8">
-        <v>46134.48096153935</v>
+        <v>46134.64762820602</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>43</v>
@@ -2410,11 +2410,11 @@
         <v>44</v>
       </c>
       <c r="B10" s="5">
-        <v>46077.37853386574</v>
+        <v>46077.545200532404</v>
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.33967887731</v>
+        <v>46114.50634554398</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2457,13 +2457,13 @@
         <v>47</v>
       </c>
       <c r="B11" s="8">
-        <v>46077.37853422454</v>
+        <v>46077.5452008912</v>
       </c>
       <c r="C11" s="8">
-        <v>46114.33966869213</v>
+        <v>46114.5063353588</v>
       </c>
       <c r="D11" s="8">
-        <v>46114.33969057871</v>
+        <v>46114.506357245366</v>
       </c>
       <c r="E11" s="9" t="s">
         <v>48</v>
@@ -2522,11 +2522,11 @@
         <v>52</v>
       </c>
       <c r="B12" s="5">
-        <v>46077.37853454861</v>
+        <v>46077.54520121528</v>
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46204.70657071759</v>
+        <v>46204.87323738426</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2585,11 +2585,11 @@
         <v>58</v>
       </c>
       <c r="B13" s="8">
-        <v>46125.653105613426</v>
+        <v>46125.8197722801</v>
       </c>
       <c r="C13" s="9"/>
       <c r="D13" s="8">
-        <v>46204.70667425926</v>
+        <v>46204.87334092593</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2638,11 +2638,11 @@
         <v>62</v>
       </c>
       <c r="B14" s="5">
-        <v>46125.653381446755</v>
+        <v>46125.820048113426</v>
       </c>
       <c r="C14" s="6"/>
       <c r="D14" s="5">
-        <v>46204.70667364584</v>
+        <v>46204.8733403125</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>63</v>
@@ -2691,11 +2691,11 @@
         <v>65</v>
       </c>
       <c r="B15" s="8">
-        <v>46125.653666238424</v>
+        <v>46125.82033290509</v>
       </c>
       <c r="C15" s="9"/>
       <c r="D15" s="8">
-        <v>46204.70667302083</v>
+        <v>46204.8733396875</v>
       </c>
       <c r="E15" s="9" t="s">
         <v>66</v>
@@ -2744,11 +2744,11 @@
         <v>68</v>
       </c>
       <c r="B16" s="5">
-        <v>46125.65397035879</v>
+        <v>46125.82063702546</v>
       </c>
       <c r="C16" s="6"/>
       <c r="D16" s="5">
-        <v>46204.706672280096</v>
+        <v>46204.87333894676</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -2797,13 +2797,13 @@
         <v>71</v>
       </c>
       <c r="B17" s="8">
-        <v>46077.37853484954</v>
+        <v>46077.5452015162</v>
       </c>
       <c r="C17" s="8">
-        <v>46114.33866949074</v>
+        <v>46114.50533615741</v>
       </c>
       <c r="D17" s="8">
-        <v>46114.33868350694</v>
+        <v>46114.50535017361</v>
       </c>
       <c r="E17" s="9" t="s">
         <v>72</v>
@@ -2850,13 +2850,13 @@
         <v>74</v>
       </c>
       <c r="B18" s="5">
-        <v>46077.37853097222</v>
+        <v>46077.54519763889</v>
       </c>
       <c r="C18" s="5">
-        <v>46097.385715833334</v>
+        <v>46097.5523825</v>
       </c>
       <c r="D18" s="5">
-        <v>46097.385732916664</v>
+        <v>46097.552399583336</v>
       </c>
       <c r="E18" s="6" t="s">
         <v>75</v>
@@ -2915,13 +2915,13 @@
         <v>77</v>
       </c>
       <c r="B19" s="8">
-        <v>46077.3785321412</v>
+        <v>46077.54519880787</v>
       </c>
       <c r="C19" s="8">
-        <v>46114.33833371528</v>
+        <v>46114.50500038195</v>
       </c>
       <c r="D19" s="8">
-        <v>46114.33835142361</v>
+        <v>46114.505018090276</v>
       </c>
       <c r="E19" s="9" t="s">
         <v>78</v>
@@ -2980,13 +2980,13 @@
         <v>80</v>
       </c>
       <c r="B20" s="5">
-        <v>46077.37853248842</v>
+        <v>46077.545199155094</v>
       </c>
       <c r="C20" s="5">
-        <v>46097.385891805556</v>
+        <v>46097.55255847222</v>
       </c>
       <c r="D20" s="5">
-        <v>46125.596121608796</v>
+        <v>46125.76278827546</v>
       </c>
       <c r="E20" s="6" t="s">
         <v>81</v>
@@ -3045,13 +3045,13 @@
         <v>83</v>
       </c>
       <c r="B21" s="8">
-        <v>46077.37853289352</v>
+        <v>46077.54519956018</v>
       </c>
       <c r="C21" s="8">
-        <v>46114.33864616898</v>
+        <v>46114.50531283565</v>
       </c>
       <c r="D21" s="8">
-        <v>46114.338670625</v>
+        <v>46114.50533729167</v>
       </c>
       <c r="E21" s="9" t="s">
         <v>84</v>
@@ -3110,13 +3110,13 @@
         <v>87</v>
       </c>
       <c r="B22" s="5">
-        <v>46077.37853325231</v>
+        <v>46077.54519991898</v>
       </c>
       <c r="C22" s="5">
-        <v>46122.46080277778</v>
+        <v>46122.627469444444</v>
       </c>
       <c r="D22" s="5">
-        <v>46191.59758568287</v>
+        <v>46191.76425234954</v>
       </c>
       <c r="E22" s="6" t="s">
         <v>88</v>
@@ -3159,13 +3159,13 @@
         <v>90</v>
       </c>
       <c r="B23" s="8">
-        <v>46077.378533958334</v>
+        <v>46077.545200625</v>
       </c>
       <c r="C23" s="8">
-        <v>46097.38576923611</v>
+        <v>46097.55243590278</v>
       </c>
       <c r="D23" s="8">
-        <v>46097.38578491898</v>
+        <v>46097.55245158565</v>
       </c>
       <c r="E23" s="9" t="s">
         <v>91</v>
@@ -3224,13 +3224,13 @@
         <v>93</v>
       </c>
       <c r="B24" s="5">
-        <v>46077.37853364584</v>
+        <v>46077.545200312496</v>
       </c>
       <c r="C24" s="5">
-        <v>46097.38560695601</v>
+        <v>46097.552273622685</v>
       </c>
       <c r="D24" s="5">
-        <v>46135.597870694444</v>
+        <v>46135.764537361116</v>
       </c>
       <c r="E24" s="6" t="s">
         <v>94</v>
@@ -3289,13 +3289,13 @@
         <v>96</v>
       </c>
       <c r="B25" s="8">
-        <v>46077.37853428241</v>
+        <v>46077.54520094907</v>
       </c>
       <c r="C25" s="8">
-        <v>46114.340227002314</v>
+        <v>46114.50689366898</v>
       </c>
       <c r="D25" s="8">
-        <v>46114.34024363426</v>
+        <v>46114.50691030093</v>
       </c>
       <c r="E25" s="9" t="s">
         <v>97</v>
@@ -3354,13 +3354,13 @@
         <v>99</v>
       </c>
       <c r="B26" s="5">
-        <v>46077.37853461805</v>
+        <v>46077.54520128472</v>
       </c>
       <c r="C26" s="5">
-        <v>46122.46078450231</v>
+        <v>46122.627451168984</v>
       </c>
       <c r="D26" s="5">
-        <v>46122.46080328704</v>
+        <v>46122.6274699537</v>
       </c>
       <c r="E26" s="6" t="s">
         <v>100</v>
@@ -3419,13 +3419,13 @@
         <v>103</v>
       </c>
       <c r="B27" s="8">
-        <v>46077.38662109953</v>
+        <v>46077.553287766204</v>
       </c>
       <c r="C27" s="8">
-        <v>46114.33919636574</v>
+        <v>46114.505863032406</v>
       </c>
       <c r="D27" s="8">
-        <v>46114.33942283565</v>
+        <v>46114.50608950232</v>
       </c>
       <c r="E27" s="9" t="s">
         <v>104</v>
@@ -3484,13 +3484,13 @@
         <v>106</v>
       </c>
       <c r="B28" s="5">
-        <v>46077.378529884256</v>
+        <v>46077.54519655093</v>
       </c>
       <c r="C28" s="5">
-        <v>46191.59738630787</v>
+        <v>46191.76405297454</v>
       </c>
       <c r="D28" s="5">
-        <v>46191.5974027662</v>
+        <v>46191.76406943287</v>
       </c>
       <c r="E28" s="6" t="s">
         <v>107</v>
@@ -3549,13 +3549,13 @@
         <v>112</v>
       </c>
       <c r="B29" s="8">
-        <v>46125.52567444445</v>
+        <v>46125.69234111111</v>
       </c>
       <c r="C29" s="8">
-        <v>46191.59741462963</v>
+        <v>46191.76408129629</v>
       </c>
       <c r="D29" s="8">
-        <v>46191.59742997686</v>
+        <v>46191.764096643514</v>
       </c>
       <c r="E29" s="9" t="s">
         <v>113</v>
@@ -3614,13 +3614,13 @@
         <v>115</v>
       </c>
       <c r="B30" s="5">
-        <v>46125.525740717596</v>
+        <v>46125.69240738426</v>
       </c>
       <c r="C30" s="5">
-        <v>46191.59743829861</v>
+        <v>46191.764104965274</v>
       </c>
       <c r="D30" s="5">
-        <v>46191.5974546412</v>
+        <v>46191.764121307875</v>
       </c>
       <c r="E30" s="6" t="s">
         <v>116</v>
@@ -3679,13 +3679,13 @@
         <v>118</v>
       </c>
       <c r="B31" s="8">
-        <v>46125.52892121528</v>
+        <v>46125.69558788194</v>
       </c>
       <c r="C31" s="8">
-        <v>46191.59747957176</v>
+        <v>46191.76414623843</v>
       </c>
       <c r="D31" s="8">
-        <v>46191.597500856486</v>
+        <v>46191.76416752315</v>
       </c>
       <c r="E31" s="9" t="s">
         <v>119</v>
@@ -3744,11 +3744,11 @@
         <v>121</v>
       </c>
       <c r="B32" s="5">
-        <v>46077.37853021991</v>
+        <v>46077.545196886575</v>
       </c>
       <c r="C32" s="6"/>
       <c r="D32" s="5">
-        <v>46182.5259155324</v>
+        <v>46182.69258219907</v>
       </c>
       <c r="E32" s="6" t="s">
         <v>122</v>
@@ -3793,13 +3793,13 @@
         <v>125</v>
       </c>
       <c r="B33" s="8">
-        <v>46077.37853045139</v>
+        <v>46077.54519711806</v>
       </c>
       <c r="C33" s="8">
-        <v>46155.707855706016</v>
+        <v>46155.87452237269</v>
       </c>
       <c r="D33" s="8">
-        <v>46155.7078571412</v>
+        <v>46155.87452380787</v>
       </c>
       <c r="E33" s="9" t="s">
         <v>126</v>
@@ -3858,13 +3858,13 @@
         <v>131</v>
       </c>
       <c r="B34" s="5">
-        <v>46077.37853072917</v>
+        <v>46077.54519739583</v>
       </c>
       <c r="C34" s="5">
-        <v>46114.338860081014</v>
+        <v>46114.505526747686</v>
       </c>
       <c r="D34" s="5">
-        <v>46114.33886135417</v>
+        <v>46114.50552802083</v>
       </c>
       <c r="E34" s="6" t="s">
         <v>132</v>
@@ -3923,13 +3923,13 @@
         <v>134</v>
       </c>
       <c r="B35" s="8">
-        <v>46077.37853099537</v>
+        <v>46077.54519766204</v>
       </c>
       <c r="C35" s="8">
-        <v>46155.69955048611</v>
+        <v>46155.86621715278</v>
       </c>
       <c r="D35" s="8">
-        <v>46155.6995518287</v>
+        <v>46155.86621849537</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>135</v>
@@ -3988,13 +3988,13 @@
         <v>137</v>
       </c>
       <c r="B36" s="5">
-        <v>46077.37853125</v>
+        <v>46077.54519791667</v>
       </c>
       <c r="C36" s="5">
-        <v>46114.338964814815</v>
+        <v>46114.50563148149</v>
       </c>
       <c r="D36" s="5">
-        <v>46125.74698085648</v>
+        <v>46125.91364752315</v>
       </c>
       <c r="E36" s="6" t="s">
         <v>138</v>
@@ -4053,13 +4053,13 @@
         <v>140</v>
       </c>
       <c r="B37" s="8">
-        <v>46077.378530462964</v>
+        <v>46077.54519712963</v>
       </c>
       <c r="C37" s="8">
-        <v>46158.591688009255</v>
+        <v>46158.75835467593</v>
       </c>
       <c r="D37" s="8">
-        <v>46158.5916903125</v>
+        <v>46158.75835697917</v>
       </c>
       <c r="E37" s="9" t="s">
         <v>141</v>
@@ -4118,13 +4118,13 @@
         <v>143</v>
       </c>
       <c r="B38" s="5">
-        <v>46077.378530682865</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C38" s="5">
-        <v>46097.385650324075</v>
+        <v>46097.55231699074</v>
       </c>
       <c r="D38" s="5">
-        <v>46097.38565210648</v>
+        <v>46097.552318773145</v>
       </c>
       <c r="E38" s="6" t="s">
         <v>144</v>
@@ -4183,13 +4183,13 @@
         <v>146</v>
       </c>
       <c r="B39" s="8">
-        <v>46077.37853090277</v>
+        <v>46077.545197569445</v>
       </c>
       <c r="C39" s="8">
-        <v>46155.72882087963</v>
+        <v>46155.895487546295</v>
       </c>
       <c r="D39" s="8">
-        <v>46155.728822199075</v>
+        <v>46155.89548886574</v>
       </c>
       <c r="E39" s="9" t="s">
         <v>147</v>
@@ -4248,13 +4248,13 @@
         <v>149</v>
       </c>
       <c r="B40" s="5">
-        <v>46077.37853112268</v>
+        <v>46077.54519778935</v>
       </c>
       <c r="C40" s="5">
-        <v>46182.52589453704</v>
+        <v>46182.6925612037</v>
       </c>
       <c r="D40" s="5">
-        <v>46182.52590822917</v>
+        <v>46182.69257489583</v>
       </c>
       <c r="E40" s="6" t="s">
         <v>150</v>
@@ -4313,13 +4313,13 @@
         <v>152</v>
       </c>
       <c r="B41" s="8">
-        <v>46077.37853138889</v>
+        <v>46077.54519805555</v>
       </c>
       <c r="C41" s="8">
-        <v>46182.5148516551</v>
+        <v>46182.681518321755</v>
       </c>
       <c r="D41" s="8">
-        <v>46182.51485332176</v>
+        <v>46182.68151998843</v>
       </c>
       <c r="E41" s="9" t="s">
         <v>153</v>
@@ -4378,13 +4378,13 @@
         <v>155</v>
       </c>
       <c r="B42" s="5">
-        <v>46077.378531608796</v>
+        <v>46077.54519827546</v>
       </c>
       <c r="C42" s="5">
-        <v>46182.52588083333</v>
+        <v>46182.6925475</v>
       </c>
       <c r="D42" s="5">
-        <v>46182.5258822801</v>
+        <v>46182.692548946754</v>
       </c>
       <c r="E42" s="6" t="s">
         <v>156</v>
@@ -4443,13 +4443,13 @@
         <v>158</v>
       </c>
       <c r="B43" s="8">
-        <v>46077.378531828705</v>
+        <v>46077.54519849537</v>
       </c>
       <c r="C43" s="8">
-        <v>46126.663939363425</v>
+        <v>46126.8306060301</v>
       </c>
       <c r="D43" s="8">
-        <v>46126.66395278936</v>
+        <v>46126.830619456014</v>
       </c>
       <c r="E43" s="9" t="s">
         <v>159</v>
@@ -4508,13 +4508,13 @@
         <v>161</v>
       </c>
       <c r="B44" s="5">
-        <v>46077.37853207176</v>
+        <v>46077.54519873843</v>
       </c>
       <c r="C44" s="5">
-        <v>46126.66246944445</v>
+        <v>46126.82913611111</v>
       </c>
       <c r="D44" s="5">
-        <v>46126.66247059028</v>
+        <v>46126.829137256944</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>162</v>
@@ -4573,13 +4573,13 @@
         <v>164</v>
       </c>
       <c r="B45" s="8">
-        <v>46077.378530138885</v>
+        <v>46077.54519680556</v>
       </c>
       <c r="C45" s="8">
-        <v>46126.66392466435</v>
+        <v>46126.83059133102</v>
       </c>
       <c r="D45" s="8">
-        <v>46126.663925960645</v>
+        <v>46126.83059262732</v>
       </c>
       <c r="E45" s="9" t="s">
         <v>165</v>
@@ -4638,13 +4638,13 @@
         <v>167</v>
       </c>
       <c r="B46" s="5">
-        <v>46077.422494513885</v>
+        <v>46077.58916118056</v>
       </c>
       <c r="C46" s="5">
-        <v>46126.66291380787</v>
+        <v>46126.829580474536</v>
       </c>
       <c r="D46" s="5">
-        <v>46126.66292728009</v>
+        <v>46126.829593946764</v>
       </c>
       <c r="E46" s="6" t="s">
         <v>168</v>
@@ -4703,13 +4703,13 @@
         <v>172</v>
       </c>
       <c r="B47" s="8">
-        <v>46077.42261591435</v>
+        <v>46077.589282581015</v>
       </c>
       <c r="C47" s="8">
-        <v>46126.66237184028</v>
+        <v>46126.82903850694</v>
       </c>
       <c r="D47" s="8">
-        <v>46126.66237319444</v>
+        <v>46126.82903986111</v>
       </c>
       <c r="E47" s="9" t="s">
         <v>173</v>
@@ -4768,13 +4768,13 @@
         <v>175</v>
       </c>
       <c r="B48" s="5">
-        <v>46077.42283101851</v>
+        <v>46077.589497685185</v>
       </c>
       <c r="C48" s="5">
-        <v>46126.662899421295</v>
+        <v>46126.82956608797</v>
       </c>
       <c r="D48" s="5">
-        <v>46126.66290059028</v>
+        <v>46126.829567256944</v>
       </c>
       <c r="E48" s="6" t="s">
         <v>176</v>
@@ -4833,13 +4833,13 @@
         <v>178</v>
       </c>
       <c r="B49" s="8">
-        <v>46077.3785315162</v>
+        <v>46077.54519818287</v>
       </c>
       <c r="C49" s="8">
-        <v>46147.721473784724</v>
+        <v>46147.88814045139</v>
       </c>
       <c r="D49" s="8">
-        <v>46147.72147583333</v>
+        <v>46147.8881425</v>
       </c>
       <c r="E49" s="9" t="s">
         <v>179</v>
@@ -4898,13 +4898,13 @@
         <v>181</v>
       </c>
       <c r="B50" s="5">
-        <v>46077.37853177083</v>
+        <v>46077.545198437496</v>
       </c>
       <c r="C50" s="5">
-        <v>46097.386023935185</v>
+        <v>46097.55269060185</v>
       </c>
       <c r="D50" s="5">
-        <v>46191.597395081015</v>
+        <v>46191.764061747686</v>
       </c>
       <c r="E50" s="6" t="s">
         <v>182</v>
@@ -4963,13 +4963,13 @@
         <v>184</v>
       </c>
       <c r="B51" s="8">
-        <v>46077.37853203704</v>
+        <v>46077.54519870371</v>
       </c>
       <c r="C51" s="8">
-        <v>46147.68399586805</v>
+        <v>46147.85066253472</v>
       </c>
       <c r="D51" s="8">
-        <v>46150.616598078705</v>
+        <v>46150.78326474537</v>
       </c>
       <c r="E51" s="9" t="s">
         <v>185</v>
@@ -5028,13 +5028,13 @@
         <v>187</v>
       </c>
       <c r="B52" s="5">
-        <v>46125.52922377315</v>
+        <v>46125.69589043982</v>
       </c>
       <c r="C52" s="5">
-        <v>46191.60215334491</v>
+        <v>46191.76882001157</v>
       </c>
       <c r="D52" s="5">
-        <v>46191.603222199075</v>
+        <v>46191.76988886574</v>
       </c>
       <c r="E52" s="6" t="s">
         <v>188</v>
@@ -5093,13 +5093,13 @@
         <v>190</v>
       </c>
       <c r="B53" s="8">
-        <v>46125.53804006944</v>
+        <v>46125.70470673611</v>
       </c>
       <c r="C53" s="8">
-        <v>46191.60315177083</v>
+        <v>46191.769818437504</v>
       </c>
       <c r="D53" s="8">
-        <v>46191.60315309028</v>
+        <v>46191.76981975694</v>
       </c>
       <c r="E53" s="9" t="s">
         <v>120</v>
@@ -5148,13 +5148,13 @@
         <v>192</v>
       </c>
       <c r="B54" s="5">
-        <v>46125.53822739584</v>
+        <v>46125.704894062495</v>
       </c>
       <c r="C54" s="5">
-        <v>46191.60320644676</v>
+        <v>46191.76987311343</v>
       </c>
       <c r="D54" s="5">
-        <v>46191.603208182874</v>
+        <v>46191.76987484954</v>
       </c>
       <c r="E54" s="6" t="s">
         <v>193</v>
@@ -5203,13 +5203,13 @@
         <v>195</v>
       </c>
       <c r="B55" s="8">
-        <v>46125.516661539354</v>
+        <v>46125.68332820602</v>
       </c>
       <c r="C55" s="8">
-        <v>46204.492941585646</v>
+        <v>46204.65960825232</v>
       </c>
       <c r="D55" s="8">
-        <v>46204.492954236106</v>
+        <v>46204.65962090278</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>196</v>
@@ -5268,13 +5268,13 @@
         <v>200</v>
       </c>
       <c r="B56" s="5">
-        <v>46125.5385794676</v>
+        <v>46125.70524613426</v>
       </c>
       <c r="C56" s="5">
-        <v>46195.52308005787</v>
+        <v>46195.689746724536</v>
       </c>
       <c r="D56" s="5">
-        <v>46195.52308157407</v>
+        <v>46195.68974824074</v>
       </c>
       <c r="E56" s="6" t="s">
         <v>114</v>
@@ -5323,13 +5323,13 @@
         <v>202</v>
       </c>
       <c r="B57" s="8">
-        <v>46125.53871626157</v>
+        <v>46125.70538292824</v>
       </c>
       <c r="C57" s="8">
-        <v>46204.49292578704</v>
+        <v>46204.6595924537</v>
       </c>
       <c r="D57" s="8">
-        <v>46204.49292802083</v>
+        <v>46204.6595946875</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>203</v>
@@ -5378,13 +5378,13 @@
         <v>206</v>
       </c>
       <c r="B58" s="5">
-        <v>46125.55176141203</v>
+        <v>46125.718428078704</v>
       </c>
       <c r="C58" s="5">
-        <v>46195.52803144676</v>
+        <v>46195.694698113424</v>
       </c>
       <c r="D58" s="5">
-        <v>46195.52803275463</v>
+        <v>46195.69469942129</v>
       </c>
       <c r="E58" s="6" t="s">
         <v>207</v>
@@ -5433,13 +5433,13 @@
         <v>208</v>
       </c>
       <c r="B59" s="8">
-        <v>46125.551973877315</v>
+        <v>46125.718640543986</v>
       </c>
       <c r="C59" s="8">
-        <v>46195.5280415625</v>
+        <v>46195.694708229166</v>
       </c>
       <c r="D59" s="8">
-        <v>46195.52804291667</v>
+        <v>46195.69470958333</v>
       </c>
       <c r="E59" s="9" t="s">
         <v>209</v>
@@ -5488,13 +5488,13 @@
         <v>210</v>
       </c>
       <c r="B60" s="5">
-        <v>46125.55231115741</v>
+        <v>46125.71897782407</v>
       </c>
       <c r="C60" s="5">
-        <v>46195.52978842593</v>
+        <v>46195.69645509259</v>
       </c>
       <c r="D60" s="5">
-        <v>46195.529789733795</v>
+        <v>46195.69645640046</v>
       </c>
       <c r="E60" s="6" t="s">
         <v>211</v>
@@ -5543,13 +5543,13 @@
         <v>212</v>
       </c>
       <c r="B61" s="8">
-        <v>46125.55246883102</v>
+        <v>46125.71913549768</v>
       </c>
       <c r="C61" s="8">
-        <v>46195.528747222226</v>
+        <v>46195.69541388889</v>
       </c>
       <c r="D61" s="8">
-        <v>46195.528748599536</v>
+        <v>46195.69541526621</v>
       </c>
       <c r="E61" s="9" t="s">
         <v>213</v>
@@ -5598,13 +5598,13 @@
         <v>214</v>
       </c>
       <c r="B62" s="5">
-        <v>46126.64923972222</v>
+        <v>46126.81590638889</v>
       </c>
       <c r="C62" s="5">
-        <v>46195.52894888889</v>
+        <v>46195.69561555555</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.528950231484</v>
+        <v>46195.69561689815</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>215</v>
@@ -5653,11 +5653,11 @@
         <v>217</v>
       </c>
       <c r="B63" s="8">
-        <v>46191.60140883102</v>
+        <v>46191.76807549769</v>
       </c>
       <c r="C63" s="9"/>
       <c r="D63" s="8">
-        <v>46195.52895532407</v>
+        <v>46195.695621990744</v>
       </c>
       <c r="E63" s="9" t="s">
         <v>216</v>
@@ -5704,13 +5704,13 @@
         <v>220</v>
       </c>
       <c r="B64" s="5">
-        <v>46125.5267843287</v>
+        <v>46125.69345099537</v>
       </c>
       <c r="C64" s="5">
-        <v>46195.49327835648</v>
+        <v>46195.659945023144</v>
       </c>
       <c r="D64" s="5">
-        <v>46198.664843715276</v>
+        <v>46198.83151038195</v>
       </c>
       <c r="E64" s="6" t="s">
         <v>221</v>
@@ -5769,13 +5769,13 @@
         <v>223</v>
       </c>
       <c r="B65" s="8">
-        <v>46125.53893203704</v>
+        <v>46125.7055987037</v>
       </c>
       <c r="C65" s="8">
-        <v>46195.49317609954</v>
+        <v>46195.6598427662</v>
       </c>
       <c r="D65" s="8">
-        <v>46195.49317836805</v>
+        <v>46195.65984503472</v>
       </c>
       <c r="E65" s="9" t="s">
         <v>117</v>
@@ -5824,13 +5824,13 @@
         <v>225</v>
       </c>
       <c r="B66" s="5">
-        <v>46125.539031168984</v>
+        <v>46125.70569783565</v>
       </c>
       <c r="C66" s="5">
-        <v>46195.4932575</v>
+        <v>46195.65992416667</v>
       </c>
       <c r="D66" s="5">
-        <v>46195.49326045139</v>
+        <v>46195.65992711806</v>
       </c>
       <c r="E66" s="6" t="s">
         <v>226</v>
@@ -5879,11 +5879,11 @@
         <v>228</v>
       </c>
       <c r="B67" s="8">
-        <v>46077.37853229167</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C67" s="9"/>
       <c r="D67" s="8">
-        <v>46127.531820081014</v>
+        <v>46127.698486747686</v>
       </c>
       <c r="E67" s="9" t="s">
         <v>229</v>
@@ -5926,13 +5926,13 @@
         <v>231</v>
       </c>
       <c r="B68" s="5">
-        <v>46077.378532546296</v>
+        <v>46077.54519921297</v>
       </c>
       <c r="C68" s="5">
-        <v>46127.53098657407</v>
+        <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46209.54767114583</v>
+        <v>46209.714337812504</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>
@@ -5991,13 +5991,13 @@
         <v>236</v>
       </c>
       <c r="B69" s="8">
-        <v>46125.529720879626</v>
+        <v>46125.6963875463</v>
       </c>
       <c r="C69" s="8">
-        <v>46127.53096575232</v>
+        <v>46127.69763241898</v>
       </c>
       <c r="D69" s="8">
-        <v>46127.53096708334</v>
+        <v>46127.697633749995</v>
       </c>
       <c r="E69" s="9" t="s">
         <v>237</v>
@@ -6046,13 +6046,13 @@
         <v>240</v>
       </c>
       <c r="B70" s="5">
-        <v>46125.52990164352</v>
+        <v>46125.69656831019</v>
       </c>
       <c r="C70" s="5">
-        <v>46127.53097228009</v>
+        <v>46127.69763894676</v>
       </c>
       <c r="D70" s="5">
-        <v>46127.53097391204</v>
+        <v>46127.6976405787</v>
       </c>
       <c r="E70" s="6" t="s">
         <v>241</v>
@@ -6101,13 +6101,13 @@
         <v>242</v>
       </c>
       <c r="B71" s="8">
-        <v>46077.37853006944</v>
+        <v>46077.545196736115</v>
       </c>
       <c r="C71" s="8">
-        <v>46127.53123206018</v>
+        <v>46127.69789872685</v>
       </c>
       <c r="D71" s="8">
-        <v>46197.541633483794</v>
+        <v>46197.708300150465</v>
       </c>
       <c r="E71" s="9" t="s">
         <v>243</v>
@@ -6166,13 +6166,13 @@
         <v>245</v>
       </c>
       <c r="B72" s="5">
-        <v>46125.531222245365</v>
+        <v>46125.69788891204</v>
       </c>
       <c r="C72" s="5">
-        <v>46127.53121677083</v>
+        <v>46127.697883437504</v>
       </c>
       <c r="D72" s="5">
-        <v>46127.531218344906</v>
+        <v>46127.69788501157</v>
       </c>
       <c r="E72" s="6" t="s">
         <v>237</v>
@@ -6221,13 +6221,13 @@
         <v>248</v>
       </c>
       <c r="B73" s="8">
-        <v>46125.53134434028</v>
+        <v>46125.69801100694</v>
       </c>
       <c r="C73" s="8">
-        <v>46127.53120533565</v>
+        <v>46127.69787200232</v>
       </c>
       <c r="D73" s="8">
-        <v>46127.53120662037</v>
+        <v>46127.697873287034</v>
       </c>
       <c r="E73" s="9" t="s">
         <v>241</v>
@@ -6276,13 +6276,13 @@
         <v>251</v>
       </c>
       <c r="B74" s="5">
-        <v>46090.538085196764</v>
+        <v>46090.70475186342</v>
       </c>
       <c r="C74" s="5">
-        <v>46127.531810162036</v>
+        <v>46127.69847682871</v>
       </c>
       <c r="D74" s="5">
-        <v>46127.53182487268</v>
+        <v>46127.698491539355</v>
       </c>
       <c r="E74" s="6" t="s">
         <v>110</v>
@@ -6341,13 +6341,13 @@
         <v>253</v>
       </c>
       <c r="B75" s="8">
-        <v>46125.531473703704</v>
+        <v>46125.69814037037</v>
       </c>
       <c r="C75" s="8">
-        <v>46127.531782986116</v>
+        <v>46127.69844965277</v>
       </c>
       <c r="D75" s="8">
-        <v>46127.53178466435</v>
+        <v>46127.698451331016</v>
       </c>
       <c r="E75" s="9" t="s">
         <v>237</v>
@@ -6396,13 +6396,13 @@
         <v>254</v>
       </c>
       <c r="B76" s="5">
-        <v>46125.53165609954</v>
+        <v>46125.6983227662</v>
       </c>
       <c r="C76" s="5">
-        <v>46127.53179329861</v>
+        <v>46127.69845996528</v>
       </c>
       <c r="D76" s="5">
-        <v>46127.53179476852</v>
+        <v>46127.69846143518</v>
       </c>
       <c r="E76" s="6" t="s">
         <v>241</v>
@@ -6451,11 +6451,11 @@
         <v>255</v>
       </c>
       <c r="B77" s="8">
-        <v>46090.53813152778</v>
+        <v>46090.70479819445</v>
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.631803020835</v>
+        <v>46198.7984696875</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>256</v>
@@ -6514,11 +6514,11 @@
         <v>259</v>
       </c>
       <c r="B78" s="5">
-        <v>46125.532529178236</v>
+        <v>46125.69919584491</v>
       </c>
       <c r="C78" s="6"/>
       <c r="D78" s="5">
-        <v>46167.001553009264</v>
+        <v>46167.16821967592</v>
       </c>
       <c r="E78" s="6" t="s">
         <v>237</v>
@@ -6565,11 +6565,11 @@
         <v>261</v>
       </c>
       <c r="B79" s="8">
-        <v>46125.53265070602</v>
+        <v>46125.69931737268</v>
       </c>
       <c r="C79" s="9"/>
       <c r="D79" s="8">
-        <v>46167.00155489583</v>
+        <v>46167.168221562504</v>
       </c>
       <c r="E79" s="9" t="s">
         <v>241</v>
@@ -6616,13 +6616,13 @@
         <v>263</v>
       </c>
       <c r="B80" s="5">
-        <v>46077.37853043982</v>
+        <v>46077.54519710648</v>
       </c>
       <c r="C80" s="5">
-        <v>46198.66462106482</v>
+        <v>46198.83128773148</v>
       </c>
       <c r="D80" s="5">
-        <v>46198.664635532405</v>
+        <v>46198.831302199076</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>264</v>
@@ -6669,13 +6669,13 @@
         <v>266</v>
       </c>
       <c r="B81" s="8">
-        <v>46077.378531180555</v>
+        <v>46077.54519784723</v>
       </c>
       <c r="C81" s="8">
-        <v>46191.60288923611</v>
+        <v>46191.76955590278</v>
       </c>
       <c r="D81" s="8">
-        <v>46191.60290703704</v>
+        <v>46191.7695737037</v>
       </c>
       <c r="E81" s="9" t="s">
         <v>267</v>
@@ -6734,13 +6734,13 @@
         <v>271</v>
       </c>
       <c r="B82" s="5">
-        <v>46125.52948887731</v>
+        <v>46125.69615554398</v>
       </c>
       <c r="C82" s="5">
-        <v>46191.603465057866</v>
+        <v>46191.77013172454</v>
       </c>
       <c r="D82" s="5">
-        <v>46191.60348049768</v>
+        <v>46191.77014716435</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>272</v>
@@ -6799,13 +6799,13 @@
         <v>274</v>
       </c>
       <c r="B83" s="8">
-        <v>46125.53309398148</v>
+        <v>46125.699760648145</v>
       </c>
       <c r="C83" s="8">
-        <v>46198.66460232639</v>
+        <v>46198.83126899306</v>
       </c>
       <c r="D83" s="8">
-        <v>46198.66462225694</v>
+        <v>46198.83128892361</v>
       </c>
       <c r="E83" s="9" t="s">
         <v>275</v>
@@ -6864,13 +6864,13 @@
         <v>277</v>
       </c>
       <c r="B84" s="5">
-        <v>46077.37853180556</v>
+        <v>46077.545198472224</v>
       </c>
       <c r="C84" s="5">
-        <v>46191.602776608794</v>
+        <v>46191.769443275465</v>
       </c>
       <c r="D84" s="5">
-        <v>46191.60387020833</v>
+        <v>46191.770536875</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>278</v>
@@ -6929,13 +6929,13 @@
         <v>280</v>
       </c>
       <c r="B85" s="8">
-        <v>46125.60878079861</v>
+        <v>46125.775447465276</v>
       </c>
       <c r="C85" s="8">
-        <v>46191.60306925926</v>
+        <v>46191.769735925925</v>
       </c>
       <c r="D85" s="8">
-        <v>46191.603070578705</v>
+        <v>46191.76973724537</v>
       </c>
       <c r="E85" s="9" t="s">
         <v>281</v>
@@ -6984,13 +6984,13 @@
         <v>283</v>
       </c>
       <c r="B86" s="5">
-        <v>46125.60892753472</v>
+        <v>46125.77559420139</v>
       </c>
       <c r="C86" s="5">
-        <v>46191.60386525463</v>
+        <v>46191.7705319213</v>
       </c>
       <c r="D86" s="5">
-        <v>46191.60386658565</v>
+        <v>46191.77053325232</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>284</v>
@@ -7039,11 +7039,11 @@
         <v>285</v>
       </c>
       <c r="B87" s="8">
-        <v>46125.609070046296</v>
+        <v>46125.77573671297</v>
       </c>
       <c r="C87" s="9"/>
       <c r="D87" s="8">
-        <v>46198.664609988424</v>
+        <v>46198.831276655095</v>
       </c>
       <c r="E87" s="9" t="s">
         <v>276</v>
@@ -7092,13 +7092,13 @@
         <v>286</v>
       </c>
       <c r="B88" s="5">
-        <v>46077.37853238426</v>
+        <v>46077.545199050925</v>
       </c>
       <c r="C88" s="5">
-        <v>46191.603782754624</v>
+        <v>46191.770449421296</v>
       </c>
       <c r="D88" s="5">
-        <v>46191.60379815972</v>
+        <v>46191.77046482639</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>287</v>
@@ -7145,13 +7145,13 @@
         <v>289</v>
       </c>
       <c r="B89" s="8">
-        <v>46077.37853266204</v>
+        <v>46077.5451993287</v>
       </c>
       <c r="C89" s="8">
-        <v>46191.594611134264</v>
+        <v>46191.76127780092</v>
       </c>
       <c r="D89" s="8">
-        <v>46191.60347216435</v>
+        <v>46191.77013883102</v>
       </c>
       <c r="E89" s="9" t="s">
         <v>290</v>
@@ -7210,13 +7210,13 @@
         <v>295</v>
       </c>
       <c r="B90" s="5">
-        <v>46077.37853291667</v>
+        <v>46077.54519958333</v>
       </c>
       <c r="C90" s="5">
-        <v>46191.59697295139</v>
+        <v>46191.76363961806</v>
       </c>
       <c r="D90" s="5">
-        <v>46191.599957812505</v>
+        <v>46191.76662447916</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>296</v>
@@ -7275,13 +7275,13 @@
         <v>299</v>
       </c>
       <c r="B91" s="8">
-        <v>46125.61333424768</v>
+        <v>46125.780000914354</v>
       </c>
       <c r="C91" s="8">
-        <v>46191.59694178241</v>
+        <v>46191.76360844907</v>
       </c>
       <c r="D91" s="8">
-        <v>46191.596943599536</v>
+        <v>46191.76361026621</v>
       </c>
       <c r="E91" s="9" t="s">
         <v>300</v>
@@ -7330,13 +7330,13 @@
         <v>303</v>
       </c>
       <c r="B92" s="5">
-        <v>46125.61305056713</v>
+        <v>46125.779717233796</v>
       </c>
       <c r="C92" s="5">
-        <v>46191.59695709491</v>
+        <v>46191.76362376157</v>
       </c>
       <c r="D92" s="5">
-        <v>46191.59695865741</v>
+        <v>46191.76362532408</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>304</v>
@@ -7385,13 +7385,13 @@
         <v>306</v>
       </c>
       <c r="B93" s="8">
-        <v>46077.37853318287</v>
+        <v>46077.54519984954</v>
       </c>
       <c r="C93" s="8">
-        <v>46191.6037694213</v>
+        <v>46191.77043608796</v>
       </c>
       <c r="D93" s="8">
-        <v>46193.78735157408</v>
+        <v>46193.954018240736</v>
       </c>
       <c r="E93" s="9" t="s">
         <v>307</v>
@@ -7450,13 +7450,13 @@
         <v>308</v>
       </c>
       <c r="B94" s="5">
-        <v>46125.61477962963</v>
+        <v>46125.7814462963</v>
       </c>
       <c r="C94" s="5">
-        <v>46193.78732577546</v>
+        <v>46193.953992442126</v>
       </c>
       <c r="D94" s="5">
-        <v>46193.78732836805</v>
+        <v>46193.953995034724</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>300</v>
@@ -7505,13 +7505,13 @@
         <v>311</v>
       </c>
       <c r="B95" s="8">
-        <v>46125.614917604165</v>
+        <v>46125.78158427084</v>
       </c>
       <c r="C95" s="8">
-        <v>46193.78733756945</v>
+        <v>46193.95400423611</v>
       </c>
       <c r="D95" s="8">
-        <v>46193.78733900463</v>
+        <v>46193.9540056713</v>
       </c>
       <c r="E95" s="9" t="s">
         <v>304</v>
@@ -7560,11 +7560,11 @@
         <v>314</v>
       </c>
       <c r="B96" s="5">
-        <v>46077.378533449075</v>
+        <v>46077.54520011574</v>
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46198.70535907407</v>
+        <v>46198.87202574074</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>264</v>
@@ -7607,13 +7607,13 @@
         <v>316</v>
       </c>
       <c r="B97" s="8">
-        <v>46077.37853141203</v>
+        <v>46077.545198078704</v>
       </c>
       <c r="C97" s="8">
-        <v>46191.61973840278</v>
+        <v>46191.78640506945</v>
       </c>
       <c r="D97" s="8">
-        <v>46191.61975438657</v>
+        <v>46191.78642105324</v>
       </c>
       <c r="E97" s="9" t="s">
         <v>317</v>
@@ -7672,13 +7672,13 @@
         <v>319</v>
       </c>
       <c r="B98" s="5">
-        <v>46077.37853112268</v>
+        <v>46077.54519778935</v>
       </c>
       <c r="C98" s="5">
-        <v>46191.619919212964</v>
+        <v>46191.78658587963</v>
       </c>
       <c r="D98" s="5">
-        <v>46191.61993555556</v>
+        <v>46191.78660222222</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>320</v>
@@ -7737,11 +7737,11 @@
         <v>322</v>
       </c>
       <c r="B99" s="8">
-        <v>46077.37853408565</v>
+        <v>46077.54520075231</v>
       </c>
       <c r="C99" s="9"/>
       <c r="D99" s="8">
-        <v>46199.68105269676</v>
+        <v>46199.847719363424</v>
       </c>
       <c r="E99" s="9" t="s">
         <v>323</v>
@@ -7800,13 +7800,13 @@
         <v>324</v>
       </c>
       <c r="B100" s="5">
-        <v>46077.378530682865</v>
+        <v>46077.54519734954</v>
       </c>
       <c r="C100" s="5">
-        <v>46198.70535350694</v>
+        <v>46198.872020173614</v>
       </c>
       <c r="D100" s="5">
-        <v>46198.705368877316</v>
+        <v>46198.87203554398</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>60</v>
@@ -7865,11 +7865,11 @@
         <v>326</v>
       </c>
       <c r="B101" s="8">
-        <v>46077.39129883102</v>
+        <v>46077.55796549769</v>
       </c>
       <c r="C101" s="9"/>
       <c r="D101" s="8">
-        <v>46198.706604074076</v>
+        <v>46198.87327074074</v>
       </c>
       <c r="E101" s="9" t="s">
         <v>327</v>
@@ -7928,13 +7928,13 @@
         <v>328</v>
       </c>
       <c r="B102" s="5">
-        <v>46125.623623680556</v>
+        <v>46125.79029034722</v>
       </c>
       <c r="C102" s="5">
-        <v>46204.51876521991</v>
+        <v>46204.68543188657</v>
       </c>
       <c r="D102" s="5">
-        <v>46204.51878450232</v>
+        <v>46204.68545116898</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>329</v>
@@ -7991,11 +7991,11 @@
         <v>330</v>
       </c>
       <c r="B103" s="8">
-        <v>46077.37853174769</v>
+        <v>46077.54519841435</v>
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.702618877316</v>
+        <v>46195.86928554398</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>331</v>
@@ -8038,13 +8038,13 @@
         <v>333</v>
       </c>
       <c r="B104" s="5">
-        <v>46077.37853209491</v>
+        <v>46077.545198761574</v>
       </c>
       <c r="C104" s="5">
-        <v>46195.702613182875</v>
+        <v>46195.86927984953</v>
       </c>
       <c r="D104" s="5">
-        <v>46205.32310429398</v>
+        <v>46205.489770960645</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>334</v>
@@ -8103,13 +8103,13 @@
         <v>335</v>
       </c>
       <c r="B105" s="8">
-        <v>46125.618860069444</v>
+        <v>46125.785526736116</v>
       </c>
       <c r="C105" s="8">
-        <v>46205.3172833912</v>
+        <v>46205.48395005787</v>
       </c>
       <c r="D105" s="8">
-        <v>46205.31728560185</v>
+        <v>46205.48395226852</v>
       </c>
       <c r="E105" s="9" t="s">
         <v>237</v>
@@ -8158,13 +8158,13 @@
         <v>338</v>
       </c>
       <c r="B106" s="5">
-        <v>46125.619656145835</v>
+        <v>46125.7863228125</v>
       </c>
       <c r="C106" s="5">
-        <v>46205.323087129625</v>
+        <v>46205.4897537963</v>
       </c>
       <c r="D106" s="5">
-        <v>46205.32308905093</v>
+        <v>46205.489755717594</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>241</v>
@@ -8213,11 +8213,11 @@
         <v>341</v>
       </c>
       <c r="B107" s="8">
-        <v>46077.39166046296</v>
+        <v>46077.558327129635</v>
       </c>
       <c r="C107" s="9"/>
       <c r="D107" s="8">
-        <v>46154.001161458335</v>
+        <v>46154.167828125</v>
       </c>
       <c r="E107" s="9" t="s">
         <v>342</v>
@@ -8276,11 +8276,11 @@
         <v>343</v>
       </c>
       <c r="B108" s="5">
-        <v>46125.62647851852</v>
+        <v>46125.793145185184</v>
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46205.31729196759</v>
+        <v>46205.48395863426</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>237</v>
@@ -8329,11 +8329,11 @@
         <v>346</v>
       </c>
       <c r="B109" s="8">
-        <v>46125.62659856481</v>
+        <v>46125.79326523148</v>
       </c>
       <c r="C109" s="9"/>
       <c r="D109" s="8">
-        <v>46205.32309762732</v>
+        <v>46205.48976429398</v>
       </c>
       <c r="E109" s="9" t="s">
         <v>241</v>
@@ -8382,11 +8382,11 @@
         <v>349</v>
       </c>
       <c r="B110" s="5">
-        <v>46077.378532800925</v>
+        <v>46077.5451994676</v>
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46197.33798239584</v>
+        <v>46197.504649062495</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>350</v>
@@ -8445,13 +8445,13 @@
         <v>351</v>
       </c>
       <c r="B111" s="8">
-        <v>46125.62675127314</v>
+        <v>46125.793417939814</v>
       </c>
       <c r="C111" s="8">
-        <v>46197.33797652778</v>
+        <v>46197.50464319444</v>
       </c>
       <c r="D111" s="8">
-        <v>46197.33797853009</v>
+        <v>46197.504645196765</v>
       </c>
       <c r="E111" s="9" t="s">
         <v>237</v>
@@ -8500,11 +8500,11 @@
         <v>354</v>
       </c>
       <c r="B112" s="5">
-        <v>46125.6268628588</v>
+        <v>46125.793529525465</v>
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46191.61992706019</v>
+        <v>46191.78659372685</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>241</v>
@@ -8553,11 +8553,11 @@
         <v>357</v>
       </c>
       <c r="B113" s="8">
-        <v>46077.37853313657</v>
+        <v>46077.54519980324</v>
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46197.44193503472</v>
+        <v>46197.60860170139</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>358</v>
@@ -8616,11 +8616,11 @@
         <v>359</v>
       </c>
       <c r="B114" s="5">
-        <v>46125.62697039352</v>
+        <v>46125.79363706018</v>
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46197.44193149306</v>
+        <v>46197.60859815972</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>237</v>
@@ -8669,11 +8669,11 @@
         <v>362</v>
       </c>
       <c r="B115" s="8">
-        <v>46125.62709875</v>
+        <v>46125.79376541667</v>
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46192.62414865741</v>
+        <v>46192.79081532407</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>241</v>
@@ -8722,11 +8722,11 @@
         <v>365</v>
       </c>
       <c r="B116" s="5">
-        <v>46077.37853243056</v>
+        <v>46077.54519909722</v>
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46198.45062642361</v>
+        <v>46198.61729309028</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>366</v>
@@ -8785,13 +8785,13 @@
         <v>367</v>
       </c>
       <c r="B117" s="8">
-        <v>46125.62742210648</v>
+        <v>46125.79408877315</v>
       </c>
       <c r="C117" s="8">
-        <v>46197.43291145834</v>
+        <v>46197.599578124995</v>
       </c>
       <c r="D117" s="8">
-        <v>46197.44193552084</v>
+        <v>46197.6086021875</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>237</v>
@@ -8840,11 +8840,11 @@
         <v>370</v>
       </c>
       <c r="B118" s="5">
-        <v>46125.62755608796</v>
+        <v>46125.79422275463</v>
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46191.61974576389</v>
+        <v>46191.786412430556</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>241</v>
@@ -8893,11 +8893,11 @@
         <v>373</v>
       </c>
       <c r="B119" s="8">
-        <v>46077.37853346065</v>
+        <v>46077.545200127315</v>
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46165.030673483794</v>
+        <v>46165.197340150466</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>374</v>
@@ -8956,11 +8956,11 @@
         <v>375</v>
       </c>
       <c r="B120" s="5">
-        <v>46125.62767509259</v>
+        <v>46125.79434175926</v>
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46197.43292009259</v>
+        <v>46197.59958675926</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>237</v>
@@ -9007,11 +9007,11 @@
         <v>377</v>
       </c>
       <c r="B121" s="8">
-        <v>46125.62779353009</v>
+        <v>46125.79446019676</v>
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46164.00248363426</v>
+        <v>46164.16915030092</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>241</v>
@@ -9058,11 +9058,11 @@
         <v>379</v>
       </c>
       <c r="B122" s="5">
-        <v>46077.37853377315</v>
+        <v>46077.54520043981</v>
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46169.02913077547</v>
+        <v>46169.19579744213</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>380</v>
@@ -9121,11 +9121,11 @@
         <v>381</v>
       </c>
       <c r="B123" s="8">
-        <v>46125.62793141203</v>
+        <v>46125.794598078704</v>
       </c>
       <c r="C123" s="9"/>
       <c r="D123" s="8">
-        <v>46168.002096655095</v>
+        <v>46168.16876332176</v>
       </c>
       <c r="E123" s="9" t="s">
         <v>237</v>
@@ -9172,11 +9172,11 @@
         <v>383</v>
       </c>
       <c r="B124" s="5">
-        <v>46125.62805658564</v>
+        <v>46125.794723252315</v>
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46168.00209804398</v>
+        <v>46168.168764710645</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>241</v>
@@ -9223,11 +9223,11 @@
         <v>385</v>
       </c>
       <c r="B125" s="8">
-        <v>46077.37853105324</v>
+        <v>46077.54519771991</v>
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46125.74054834491</v>
+        <v>46125.907215011575</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>386</v>
@@ -9270,11 +9270,11 @@
         <v>388</v>
       </c>
       <c r="B126" s="5">
-        <v>46077.378531504626</v>
+        <v>46077.5451981713</v>
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46170.032856238424</v>
+        <v>46170.199522905095</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>389</v>
@@ -9333,11 +9333,11 @@
         <v>393</v>
       </c>
       <c r="B127" s="8">
-        <v>46125.64569723379</v>
+        <v>46125.81236390046</v>
       </c>
       <c r="C127" s="9"/>
       <c r="D127" s="8">
-        <v>46169.0018784375</v>
+        <v>46169.16854510417</v>
       </c>
       <c r="E127" s="9" t="s">
         <v>237</v>
@@ -9384,11 +9384,11 @@
         <v>395</v>
       </c>
       <c r="B128" s="5">
-        <v>46125.64585586806</v>
+        <v>46125.81252253472</v>
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46169.0018800463</v>
+        <v>46169.168546712965</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>241</v>
@@ -9435,11 +9435,11 @@
         <v>397</v>
       </c>
       <c r="B129" s="8">
-        <v>46125.6460805324</v>
+        <v>46125.812747199074</v>
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.00188140046</v>
+        <v>46169.16854806713</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>398</v>
@@ -9486,11 +9486,11 @@
         <v>400</v>
       </c>
       <c r="B130" s="5">
-        <v>46125.646602141205</v>
+        <v>46125.81326880787</v>
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.001882743054</v>
+        <v>46169.16854940972</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>63</v>
@@ -9537,11 +9537,11 @@
         <v>402</v>
       </c>
       <c r="B131" s="8">
-        <v>46125.647173634265</v>
+        <v>46125.81384030092</v>
       </c>
       <c r="C131" s="9"/>
       <c r="D131" s="8">
-        <v>46169.00188401621</v>
+        <v>46169.168550682865</v>
       </c>
       <c r="E131" s="9" t="s">
         <v>66</v>
@@ -9588,11 +9588,11 @@
         <v>404</v>
       </c>
       <c r="B132" s="5">
-        <v>46125.647435543986</v>
+        <v>46125.81410221064</v>
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46169.001885624995</v>
+        <v>46169.16855229167</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>69</v>
@@ -9639,11 +9639,11 @@
         <v>406</v>
       </c>
       <c r="B133" s="8">
-        <v>46077.37853181713</v>
+        <v>46077.5451984838</v>
       </c>
       <c r="C133" s="9"/>
       <c r="D133" s="8">
-        <v>46175.03565800926</v>
+        <v>46175.20232467593</v>
       </c>
       <c r="E133" s="9" t="s">
         <v>407</v>
@@ -9702,11 +9702,11 @@
         <v>409</v>
       </c>
       <c r="B134" s="5">
-        <v>46125.64815408565</v>
+        <v>46125.81482075232</v>
       </c>
       <c r="C134" s="6"/>
       <c r="D134" s="5">
-        <v>46174.00276666667</v>
+        <v>46174.16943333333</v>
       </c>
       <c r="E134" s="6" t="s">
         <v>237</v>
@@ -9755,11 +9755,11 @@
         <v>411</v>
       </c>
       <c r="B135" s="8">
-        <v>46125.64828011574</v>
+        <v>46125.81494678241</v>
       </c>
       <c r="C135" s="9"/>
       <c r="D135" s="8">
-        <v>46174.00276837963</v>
+        <v>46174.16943504629</v>
       </c>
       <c r="E135" s="9" t="s">
         <v>241</v>
@@ -9808,11 +9808,11 @@
         <v>413</v>
       </c>
       <c r="B136" s="5">
-        <v>46125.64849368056</v>
+        <v>46125.81516034722</v>
       </c>
       <c r="C136" s="6"/>
       <c r="D136" s="5">
-        <v>46174.002769733794</v>
+        <v>46174.169436400465</v>
       </c>
       <c r="E136" s="6" t="s">
         <v>398</v>
@@ -9861,11 +9861,11 @@
         <v>415</v>
       </c>
       <c r="B137" s="8">
-        <v>46125.64864410879</v>
+        <v>46125.81531077546</v>
       </c>
       <c r="C137" s="9"/>
       <c r="D137" s="8">
-        <v>46174.00277118056</v>
+        <v>46174.169437847224</v>
       </c>
       <c r="E137" s="9" t="s">
         <v>63</v>
@@ -9914,11 +9914,11 @@
         <v>417</v>
       </c>
       <c r="B138" s="5">
-        <v>46125.6487852662</v>
+        <v>46125.81545193287</v>
       </c>
       <c r="C138" s="6"/>
       <c r="D138" s="5">
-        <v>46174.002772604166</v>
+        <v>46174.16943927083</v>
       </c>
       <c r="E138" s="6" t="s">
         <v>66</v>
@@ -9967,11 +9967,11 @@
         <v>419</v>
       </c>
       <c r="B139" s="8">
-        <v>46125.64890609954</v>
+        <v>46125.81557276621</v>
       </c>
       <c r="C139" s="9"/>
       <c r="D139" s="8">
-        <v>46174.002773796296</v>
+        <v>46174.16944046297</v>
       </c>
       <c r="E139" s="9" t="s">
         <v>420</v>
@@ -10020,11 +10020,11 @@
         <v>422</v>
       </c>
       <c r="B140" s="5">
-        <v>46077.37853229167</v>
+        <v>46077.54519895834</v>
       </c>
       <c r="C140" s="6"/>
       <c r="D140" s="5">
-        <v>46176.029254189816</v>
+        <v>46176.19592085648</v>
       </c>
       <c r="E140" s="6" t="s">
         <v>423</v>
@@ -10083,11 +10083,11 @@
         <v>426</v>
       </c>
       <c r="B141" s="8">
-        <v>46125.64911434028</v>
+        <v>46125.815781006946</v>
       </c>
       <c r="C141" s="9"/>
       <c r="D141" s="8">
-        <v>46175.001645798606</v>
+        <v>46175.16831246528</v>
       </c>
       <c r="E141" s="9" t="s">
         <v>237</v>
@@ -10134,11 +10134,11 @@
         <v>428</v>
       </c>
       <c r="B142" s="5">
-        <v>46125.64925351852</v>
+        <v>46125.81592018518</v>
       </c>
       <c r="C142" s="6"/>
       <c r="D142" s="5">
-        <v>46175.00164739584</v>
+        <v>46175.168314062495</v>
       </c>
       <c r="E142" s="6" t="s">
         <v>241</v>
@@ -10185,11 +10185,11 @@
         <v>430</v>
       </c>
       <c r="B143" s="8">
-        <v>46125.64939738426</v>
+        <v>46125.81606405093</v>
       </c>
       <c r="C143" s="9"/>
       <c r="D143" s="8">
-        <v>46175.00164880787</v>
+        <v>46175.16831547454</v>
       </c>
       <c r="E143" s="9" t="s">
         <v>59</v>
@@ -10236,11 +10236,11 @@
         <v>432</v>
       </c>
       <c r="B144" s="5">
-        <v>46125.64952605324</v>
+        <v>46125.81619271991</v>
       </c>
       <c r="C144" s="6"/>
       <c r="D144" s="5">
-        <v>46175.00165010417</v>
+        <v>46175.16831677083</v>
       </c>
       <c r="E144" s="6" t="s">
         <v>63</v>
@@ -10287,11 +10287,11 @@
         <v>434</v>
       </c>
       <c r="B145" s="8">
-        <v>46125.64965439815</v>
+        <v>46125.81632106482</v>
       </c>
       <c r="C145" s="9"/>
       <c r="D145" s="8">
-        <v>46175.00165146991</v>
+        <v>46175.16831813657</v>
       </c>
       <c r="E145" s="9" t="s">
         <v>66</v>
@@ -10338,11 +10338,11 @@
         <v>436</v>
       </c>
       <c r="B146" s="5">
-        <v>46125.649802002314</v>
+        <v>46125.816468668985</v>
       </c>
       <c r="C146" s="6"/>
       <c r="D146" s="5">
-        <v>46175.00165288194</v>
+        <v>46175.16831954861</v>
       </c>
       <c r="E146" s="6" t="s">
         <v>420</v>
@@ -10389,11 +10389,11 @@
         <v>438</v>
       </c>
       <c r="B147" s="8">
-        <v>46077.37853260417</v>
+        <v>46077.54519927083</v>
       </c>
       <c r="C147" s="9"/>
       <c r="D147" s="8">
-        <v>46177.02263348379</v>
+        <v>46177.189300150465</v>
       </c>
       <c r="E147" s="9" t="s">
         <v>439</v>
@@ -10452,11 +10452,11 @@
         <v>442</v>
       </c>
       <c r="B148" s="5">
-        <v>46125.649941006945</v>
+        <v>46125.81660767361</v>
       </c>
       <c r="C148" s="6"/>
       <c r="D148" s="5">
-        <v>46176.00170306713</v>
+        <v>46176.1683697338</v>
       </c>
       <c r="E148" s="6" t="s">
         <v>237</v>
@@ -10503,11 +10503,11 @@
         <v>443</v>
       </c>
       <c r="B149" s="8">
-        <v>46125.650069166666</v>
+        <v>46125.81673583333</v>
       </c>
       <c r="C149" s="9"/>
       <c r="D149" s="8">
-        <v>46176.00170451389</v>
+        <v>46176.16837118055</v>
       </c>
       <c r="E149" s="9" t="s">
         <v>241</v>
@@ -10554,11 +10554,11 @@
         <v>444</v>
       </c>
       <c r="B150" s="5">
-        <v>46125.650201331024</v>
+        <v>46125.81686799768</v>
       </c>
       <c r="C150" s="6"/>
       <c r="D150" s="5">
-        <v>46176.0017056713</v>
+        <v>46176.16837233797</v>
       </c>
       <c r="E150" s="6" t="s">
         <v>398</v>
@@ -10605,11 +10605,11 @@
         <v>445</v>
       </c>
       <c r="B151" s="8">
-        <v>46125.65031788194</v>
+        <v>46125.81698454861</v>
       </c>
       <c r="C151" s="9"/>
       <c r="D151" s="8">
-        <v>46176.00170678241</v>
+        <v>46176.16837344907</v>
       </c>
       <c r="E151" s="9" t="s">
         <v>63</v>
@@ -10656,11 +10656,11 @@
         <v>446</v>
       </c>
       <c r="B152" s="5">
-        <v>46125.650468148146</v>
+        <v>46125.81713481482</v>
       </c>
       <c r="C152" s="6"/>
       <c r="D152" s="5">
-        <v>46176.00170797454</v>
+        <v>46176.1683746412</v>
       </c>
       <c r="E152" s="6" t="s">
         <v>66</v>
@@ -10707,11 +10707,11 @@
         <v>447</v>
       </c>
       <c r="B153" s="8">
-        <v>46125.650595520834</v>
+        <v>46125.8172621875</v>
       </c>
       <c r="C153" s="9"/>
       <c r="D153" s="8">
-        <v>46176.001709178236</v>
+        <v>46176.16837584491</v>
       </c>
       <c r="E153" s="9" t="s">
         <v>420</v>
@@ -10758,11 +10758,11 @@
         <v>448</v>
       </c>
       <c r="B154" s="5">
-        <v>46077.37853299768</v>
+        <v>46077.54519966435</v>
       </c>
       <c r="C154" s="6"/>
       <c r="D154" s="5">
-        <v>46125.740548368056</v>
+        <v>46125.90721503472</v>
       </c>
       <c r="E154" s="6" t="s">
         <v>449</v>
@@ -10805,11 +10805,11 @@
         <v>451</v>
       </c>
       <c r="B155" s="8">
-        <v>46077.378533298615</v>
+        <v>46077.54519996527</v>
       </c>
       <c r="C155" s="9"/>
       <c r="D155" s="8">
-        <v>46186.034677986114</v>
+        <v>46186.20134465278</v>
       </c>
       <c r="E155" s="9" t="s">
         <v>452</v>
@@ -10868,11 +10868,11 @@
         <v>455</v>
       </c>
       <c r="B156" s="5">
-        <v>46077.37853361111</v>
+        <v>46077.545200277775</v>
       </c>
       <c r="C156" s="6"/>
       <c r="D156" s="5">
-        <v>46186.0346780324</v>
+        <v>46186.201344699075</v>
       </c>
       <c r="E156" s="6" t="s">
         <v>456</v>
@@ -10931,11 +10931,11 @@
         <v>458</v>
       </c>
       <c r="B157" s="8">
-        <v>46090.54328194444</v>
+        <v>46090.70994861111</v>
       </c>
       <c r="C157" s="9"/>
       <c r="D157" s="8">
-        <v>46125.74112125</v>
+        <v>46125.907787916665</v>
       </c>
       <c r="E157" s="9" t="s">
         <v>459</v>
@@ -10984,11 +10984,11 @@
         <v>461</v>
       </c>
       <c r="B158" s="5">
-        <v>46090.54338682871</v>
+        <v>46090.71005349537</v>
       </c>
       <c r="C158" s="6"/>
       <c r="D158" s="5">
-        <v>46185.03103875</v>
+        <v>46185.197705416664</v>
       </c>
       <c r="E158" s="6" t="s">
         <v>462</v>
@@ -11047,11 +11047,11 @@
         <v>464</v>
       </c>
       <c r="B159" s="8">
-        <v>46090.54293944444</v>
+        <v>46090.70960611111</v>
       </c>
       <c r="C159" s="9"/>
       <c r="D159" s="8">
-        <v>46196.00701340278</v>
+        <v>46196.17368006945</v>
       </c>
       <c r="E159" s="9" t="s">
         <v>465</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -720,7 +720,7 @@
     <t>gonzalo.davila@zitron.com</t>
   </si>
   <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214046914974309</t>
@@ -5932,7 +5932,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46209.714337812504</v>
+        <v>46211.815882106486</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>232</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -720,7 +720,7 @@
     <t>gonzalo.davila@zitron.com</t>
   </si>
   <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ZVN 1-9-75/2,ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ot 4309- ZVN 1-9-75/2,ot 4309- ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214046914974309</t>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -7995,7 +7995,7 @@
       </c>
       <c r="C103" s="9"/>
       <c r="D103" s="8">
-        <v>46195.86928554398</v>
+        <v>46213.50901844907</v>
       </c>
       <c r="E103" s="9" t="s">
         <v>331</v>
@@ -8384,9 +8384,11 @@
       <c r="B110" s="5">
         <v>46077.5451994676</v>
       </c>
-      <c r="C110" s="6"/>
+      <c r="C110" s="5">
+        <v>46213.50886607639</v>
+      </c>
       <c r="D110" s="5">
-        <v>46197.504649062495</v>
+        <v>46213.50887829861</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>350</v>
@@ -8430,11 +8432,11 @@
       <c r="R110" s="5">
         <v>46155</v>
       </c>
-      <c r="S110" s="11" t="s">
-        <v>57</v>
+      <c r="S110" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T110" s="6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U110" s="11" t="s">
         <v>32</v>
@@ -8502,9 +8504,11 @@
       <c r="B112" s="5">
         <v>46125.793529525465</v>
       </c>
-      <c r="C112" s="6"/>
+      <c r="C112" s="5">
+        <v>46213.508852071755</v>
+      </c>
       <c r="D112" s="5">
-        <v>46191.78659372685</v>
+        <v>46213.5088541088</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>241</v>
@@ -8555,9 +8559,11 @@
       <c r="B113" s="8">
         <v>46077.54519980324</v>
       </c>
-      <c r="C113" s="9"/>
+      <c r="C113" s="8">
+        <v>46213.509007835644</v>
+      </c>
       <c r="D113" s="8">
-        <v>46197.60860170139</v>
+        <v>46213.50902185185</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>358</v>
@@ -8601,11 +8607,11 @@
       <c r="R113" s="8">
         <v>46157</v>
       </c>
-      <c r="S113" s="11" t="s">
-        <v>57</v>
+      <c r="S113" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T113" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U113" s="11" t="s">
         <v>32</v>
@@ -8618,9 +8624,11 @@
       <c r="B114" s="5">
         <v>46125.79363706018</v>
       </c>
-      <c r="C114" s="6"/>
+      <c r="C114" s="5">
+        <v>46213.50894438657</v>
+      </c>
       <c r="D114" s="5">
-        <v>46197.60859815972</v>
+        <v>46213.50894587963</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>237</v>
@@ -8671,9 +8679,11 @@
       <c r="B115" s="8">
         <v>46125.79376541667</v>
       </c>
-      <c r="C115" s="9"/>
+      <c r="C115" s="8">
+        <v>46213.508995833334</v>
+      </c>
       <c r="D115" s="8">
-        <v>46192.79081532407</v>
+        <v>46213.508997372686</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>241</v>
@@ -8791,7 +8801,7 @@
         <v>46197.599578124995</v>
       </c>
       <c r="D117" s="8">
-        <v>46197.6086021875</v>
+        <v>46213.50895231482</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>237</v>
@@ -8844,7 +8854,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46191.786412430556</v>
+        <v>46213.5090055787</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>241</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -184,217 +184,217 @@
     <t xml:space="preserve">OT 4217 TABLERO VDF 400 KW,OT 4218 TABLERO PLC,OT 4226 TABLERO VDF 575 KW,OT 4227 TABLERO PLC - MT </t>
   </si>
   <si>
+    <t>Tarea en curso</t>
+  </si>
+  <si>
+    <t>1214046914974588</t>
+  </si>
+  <si>
+    <t>OT 4217 TABLERO VDF 400 KW</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT  4217 TABLERO VDF 400 KW</t>
+  </si>
+  <si>
+    <t>1214046914974589</t>
+  </si>
+  <si>
+    <t>OT 4218 TABLERO PLC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recepcion Tableros y componentes electricos </t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4218 TABLERO PLC</t>
+  </si>
+  <si>
+    <t>1214046914974590</t>
+  </si>
+  <si>
+    <t>OT 4226 TABLERO VDF 575 KW</t>
+  </si>
+  <si>
+    <t>Revisión tableros pruebas,OT 4226 TABLERO VDF 575 KW</t>
+  </si>
+  <si>
+    <t>1214046914974591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OT 4227 TABLERO PLC - MT </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revisión tableros pruebas,OT 4227 TABLERO PLC - MT </t>
+  </si>
+  <si>
+    <t>1213390413187351</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>1213390413187352</t>
+  </si>
+  <si>
+    <t>Ingenieria Basica Motor</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
+  </si>
+  <si>
+    <t>1213390413187354</t>
+  </si>
+  <si>
+    <t>Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
+  </si>
+  <si>
+    <t>1213390413187355</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle</t>
+  </si>
+  <si>
+    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuestar Sensores ,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6</t>
+  </si>
+  <si>
+    <t>1213390413187356</t>
+  </si>
+  <si>
+    <t>Analisis de costeo</t>
+  </si>
+  <si>
+    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
+  </si>
+  <si>
+    <t>Ingenieria Jefe de proyecto:,Costos</t>
+  </si>
+  <si>
+    <t>1213390413187357</t>
+  </si>
+  <si>
+    <t>Propuesta compras:</t>
+  </si>
+  <si>
+    <t>propuesta motor,propuesta alabes,propuesta tableros,propuesta nucleo rodete,Propuestar Sensores ,Propuesta corte laser OT 4202 -4203</t>
+  </si>
+  <si>
+    <t>1213390413187359</t>
+  </si>
+  <si>
+    <t>propuesta motor</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC motor</t>
+  </si>
+  <si>
+    <t>1213390413187358</t>
+  </si>
+  <si>
+    <t>propuesta alabes</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Alabe</t>
+  </si>
+  <si>
+    <t>1213390413187360</t>
+  </si>
+  <si>
+    <t>propuesta tableros</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Tableros OT 4217 - 4218 - 4226 -4227</t>
+  </si>
+  <si>
+    <t>1213390413187361</t>
+  </si>
+  <si>
+    <t>propuesta nucleo rodete</t>
+  </si>
+  <si>
+    <t>nespinoza@zitron.com</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC Rodete</t>
+  </si>
+  <si>
+    <t>1213390201585047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propuestar Sensores </t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generaciónt OC sensores</t>
+  </si>
+  <si>
+    <t>1213390413187362</t>
+  </si>
+  <si>
+    <t>Propuesta corte laser OT 4202 -4203</t>
+  </si>
+  <si>
+    <t>Check Planos</t>
+  </si>
+  <si>
+    <t>Propuesta compras:,Generación OC corte laser</t>
+  </si>
+  <si>
+    <t>1214046914974302</t>
+  </si>
+  <si>
+    <t>Propuesta Fabricación externa  OT 4202 -4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generacion oc fabricación externa  OT 4202 -4203 </t>
+  </si>
+  <si>
+    <t>1214046914974303</t>
+  </si>
+  <si>
+    <t>Propuesta mecanizado OT 4202 -4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación oc mecanizado OT 4202 -4203 </t>
+  </si>
+  <si>
+    <t>1214046914974306</t>
+  </si>
+  <si>
+    <t>Propuesta Corte Plasma  OT 4202 -4203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación oc corte plasma OT 4202 -4203  </t>
+  </si>
+  <si>
+    <t>1213390413187363</t>
+  </si>
+  <si>
+    <t>Compras:</t>
+  </si>
+  <si>
+    <t>Motor,Alabe,Tablero OT 4217 - 4218 - 4226 -4227,rodete,Sensores,Corte Laser</t>
+  </si>
+  <si>
+    <t>1213390413187373</t>
+  </si>
+  <si>
+    <t>Motor</t>
+  </si>
+  <si>
+    <t>Eliana</t>
+  </si>
+  <si>
+    <t>ecarico@zitron.com</t>
+  </si>
+  <si>
+    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
+  </si>
+  <si>
     <t>Tarea sin iniciar</t>
-  </si>
-  <si>
-    <t>1214046914974588</t>
-  </si>
-  <si>
-    <t>OT 4217 TABLERO VDF 400 KW</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT  4217 TABLERO VDF 400 KW</t>
-  </si>
-  <si>
-    <t>1214046914974589</t>
-  </si>
-  <si>
-    <t>OT 4218 TABLERO PLC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recepcion Tableros y componentes electricos </t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4218 TABLERO PLC</t>
-  </si>
-  <si>
-    <t>1214046914974590</t>
-  </si>
-  <si>
-    <t>OT 4226 TABLERO VDF 575 KW</t>
-  </si>
-  <si>
-    <t>Revisión tableros pruebas,OT 4226 TABLERO VDF 575 KW</t>
-  </si>
-  <si>
-    <t>1214046914974591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OT 4227 TABLERO PLC - MT </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revisión tableros pruebas,OT 4227 TABLERO PLC - MT </t>
-  </si>
-  <si>
-    <t>1213390413187351</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>1213390413187352</t>
-  </si>
-  <si>
-    <t>Ingenieria Basica Motor</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta motor</t>
-  </si>
-  <si>
-    <t>1213390413187354</t>
-  </si>
-  <si>
-    <t>Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,propuesta nucleo rodete,propuesta alabes</t>
-  </si>
-  <si>
-    <t>1213390413187355</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle</t>
-  </si>
-  <si>
-    <t>Analisis de costeo,Ingenieria Jefe de proyecto:,Propuestar Sensores ,OT 4202 ZVN 1-22-400/6,OT 4203 ZVN 1-22-575/6</t>
-  </si>
-  <si>
-    <t>1213390413187356</t>
-  </si>
-  <si>
-    <t>Analisis de costeo</t>
-  </si>
-  <si>
-    <t>Ingenieria Detalle,Ingenieria Basica Motor,Ingenieria basica Rodete</t>
-  </si>
-  <si>
-    <t>Ingenieria Jefe de proyecto:,Costos</t>
-  </si>
-  <si>
-    <t>1213390413187357</t>
-  </si>
-  <si>
-    <t>Propuesta compras:</t>
-  </si>
-  <si>
-    <t>propuesta motor,propuesta alabes,propuesta tableros,propuesta nucleo rodete,Propuestar Sensores ,Propuesta corte laser OT 4202 -4203</t>
-  </si>
-  <si>
-    <t>1213390413187359</t>
-  </si>
-  <si>
-    <t>propuesta motor</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC motor</t>
-  </si>
-  <si>
-    <t>1213390413187358</t>
-  </si>
-  <si>
-    <t>propuesta alabes</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Alabe</t>
-  </si>
-  <si>
-    <t>1213390413187360</t>
-  </si>
-  <si>
-    <t>propuesta tableros</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Tableros OT 4217 - 4218 - 4226 -4227</t>
-  </si>
-  <si>
-    <t>1213390413187361</t>
-  </si>
-  <si>
-    <t>propuesta nucleo rodete</t>
-  </si>
-  <si>
-    <t>nespinoza@zitron.com</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC Rodete</t>
-  </si>
-  <si>
-    <t>1213390201585047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Propuestar Sensores </t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generaciónt OC sensores</t>
-  </si>
-  <si>
-    <t>1213390413187362</t>
-  </si>
-  <si>
-    <t>Propuesta corte laser OT 4202 -4203</t>
-  </si>
-  <si>
-    <t>Check Planos</t>
-  </si>
-  <si>
-    <t>Propuesta compras:,Generación OC corte laser</t>
-  </si>
-  <si>
-    <t>1214046914974302</t>
-  </si>
-  <si>
-    <t>Propuesta Fabricación externa  OT 4202 -4203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generacion oc fabricación externa  OT 4202 -4203 </t>
-  </si>
-  <si>
-    <t>1214046914974303</t>
-  </si>
-  <si>
-    <t>Propuesta mecanizado OT 4202 -4203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación oc mecanizado OT 4202 -4203 </t>
-  </si>
-  <si>
-    <t>1214046914974306</t>
-  </si>
-  <si>
-    <t>Propuesta Corte Plasma  OT 4202 -4203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generación oc corte plasma OT 4202 -4203  </t>
-  </si>
-  <si>
-    <t>1213390413187363</t>
-  </si>
-  <si>
-    <t>Compras:</t>
-  </si>
-  <si>
-    <t>Motor,Alabe,Tablero OT 4217 - 4218 - 4226 -4227,rodete,Sensores,Corte Laser</t>
-  </si>
-  <si>
-    <t>Tarea en curso</t>
-  </si>
-  <si>
-    <t>1213390413187373</t>
-  </si>
-  <si>
-    <t>Motor</t>
-  </si>
-  <si>
-    <t>Eliana</t>
-  </si>
-  <si>
-    <t>ecarico@zitron.com</t>
-  </si>
-  <si>
-    <t>Generación OC motor,Fabricación motor,Planos motor proveedor</t>
   </si>
   <si>
     <t>Baja</t>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C10" s="6"/>
       <c r="D10" s="5">
-        <v>46114.50634554398</v>
+        <v>46224.77537990741</v>
       </c>
       <c r="E10" s="6" t="s">
         <v>45</v>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="C12" s="6"/>
       <c r="D12" s="5">
-        <v>46204.87323738426</v>
+        <v>46224.79388761574</v>
       </c>
       <c r="E12" s="6" t="s">
         <v>53</v>
@@ -2564,11 +2564,11 @@
       <c r="R12" s="5">
         <v>46127</v>
       </c>
-      <c r="S12" s="11" t="s">
+      <c r="S12" s="12" t="s">
         <v>57</v>
       </c>
       <c r="T12" s="6">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="U12" s="11" t="s">
         <v>32</v>
@@ -2581,9 +2581,11 @@
       <c r="B13" s="8">
         <v>46125.8197722801</v>
       </c>
-      <c r="C13" s="9"/>
+      <c r="C13" s="8">
+        <v>46224.79371402778</v>
+      </c>
       <c r="D13" s="8">
-        <v>46218.652969375005</v>
+        <v>46224.79371621528</v>
       </c>
       <c r="E13" s="9" t="s">
         <v>59</v>
@@ -2634,9 +2636,11 @@
       <c r="B14" s="5">
         <v>46125.820048113426</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C14" s="5">
+        <v>46224.793809571755</v>
+      </c>
       <c r="D14" s="5">
-        <v>46204.8733403125</v>
+        <v>46224.793811400465</v>
       </c>
       <c r="E14" s="6" t="s">
         <v>62</v>
@@ -2740,9 +2744,11 @@
       <c r="B16" s="5">
         <v>46125.82063702546</v>
       </c>
-      <c r="C16" s="6"/>
+      <c r="C16" s="5">
+        <v>46224.79388222222</v>
+      </c>
       <c r="D16" s="5">
-        <v>46204.87333894676</v>
+        <v>46224.79388363426</v>
       </c>
       <c r="E16" s="6" t="s">
         <v>69</v>
@@ -3777,14 +3783,14 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
       <c r="S32" s="12" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="T32" s="6"/>
       <c r="U32" s="6"/>
     </row>
     <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B33" s="8">
         <v>46077.54519711806</v>
@@ -3796,16 +3802,16 @@
         <v>46155.87452380787</v>
       </c>
       <c r="E33" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G33" s="9" t="s">
         <v>124</v>
       </c>
-      <c r="F33" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G33" s="9" t="s">
+      <c r="H33" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H33" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I33" s="8">
         <v>46008</v>
@@ -3826,7 +3832,7 @@
         <v>120</v>
       </c>
       <c r="O33" s="9" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="P33" s="9" t="s">
         <v>120</v>
@@ -3838,7 +3844,7 @@
         <v>46008</v>
       </c>
       <c r="S33" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T33" s="9">
         <v>0</v>
@@ -3867,10 +3873,10 @@
         <v>26</v>
       </c>
       <c r="G34" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H34" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I34" s="5">
         <v>46008</v>
@@ -3888,7 +3894,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O34" s="6" t="s">
         <v>91</v>
@@ -3903,7 +3909,7 @@
         <v>46007</v>
       </c>
       <c r="S34" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T34" s="6">
         <v>0</v>
@@ -3932,10 +3938,10 @@
         <v>26</v>
       </c>
       <c r="G35" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H35" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H35" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I35" s="8">
         <v>46028</v>
@@ -3953,7 +3959,7 @@
         <v>26</v>
       </c>
       <c r="N35" s="9" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O35" s="9" t="s">
         <v>130</v>
@@ -3968,7 +3974,7 @@
         <v>46034</v>
       </c>
       <c r="S35" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T35" s="9">
         <v>0</v>
@@ -3997,10 +4003,10 @@
         <v>26</v>
       </c>
       <c r="G36" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H36" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H36" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I36" s="5">
         <v>46028</v>
@@ -4018,7 +4024,7 @@
         <v>26</v>
       </c>
       <c r="N36" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="O36" s="6" t="s">
         <v>130</v>
@@ -4033,7 +4039,7 @@
         <v>46031</v>
       </c>
       <c r="S36" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T36" s="6">
         <v>0</v>
@@ -4062,10 +4068,10 @@
         <v>26</v>
       </c>
       <c r="G37" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H37" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H37" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I37" s="8">
         <v>46015</v>
@@ -4098,7 +4104,7 @@
         <v>46015</v>
       </c>
       <c r="S37" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T37" s="9">
         <v>0</v>
@@ -4127,10 +4133,10 @@
         <v>26</v>
       </c>
       <c r="G38" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H38" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H38" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I38" s="5">
         <v>46015</v>
@@ -4163,7 +4169,7 @@
         <v>46014</v>
       </c>
       <c r="S38" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T38" s="6">
         <v>0</v>
@@ -4192,10 +4198,10 @@
         <v>26</v>
       </c>
       <c r="G39" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H39" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I39" s="8">
         <v>46020</v>
@@ -4228,7 +4234,7 @@
         <v>46017</v>
       </c>
       <c r="S39" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T39" s="9">
         <v>0</v>
@@ -4257,10 +4263,10 @@
         <v>26</v>
       </c>
       <c r="G40" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H40" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I40" s="5">
         <v>46009</v>
@@ -4322,10 +4328,10 @@
         <v>26</v>
       </c>
       <c r="G41" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H41" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H41" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I41" s="8">
         <v>46009</v>
@@ -4358,7 +4364,7 @@
         <v>46014</v>
       </c>
       <c r="S41" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T41" s="9">
         <v>0</v>
@@ -4387,10 +4393,10 @@
         <v>26</v>
       </c>
       <c r="G42" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H42" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H42" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I42" s="5">
         <v>46021</v>
@@ -4423,7 +4429,7 @@
         <v>46022</v>
       </c>
       <c r="S42" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T42" s="6">
         <v>0</v>
@@ -4452,10 +4458,10 @@
         <v>26</v>
       </c>
       <c r="G43" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H43" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H43" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I43" s="8">
         <v>46015</v>
@@ -4517,10 +4523,10 @@
         <v>26</v>
       </c>
       <c r="G44" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="H44" s="6" t="s">
         <v>125</v>
-      </c>
-      <c r="H44" s="6" t="s">
-        <v>126</v>
       </c>
       <c r="I44" s="5">
         <v>46015</v>
@@ -4553,7 +4559,7 @@
         <v>46014</v>
       </c>
       <c r="S44" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T44" s="6">
         <v>0</v>
@@ -4582,10 +4588,10 @@
         <v>26</v>
       </c>
       <c r="G45" s="9" t="s">
+        <v>124</v>
+      </c>
+      <c r="H45" s="9" t="s">
         <v>125</v>
-      </c>
-      <c r="H45" s="9" t="s">
-        <v>126</v>
       </c>
       <c r="I45" s="8">
         <v>46020</v>
@@ -4618,7 +4624,7 @@
         <v>46017</v>
       </c>
       <c r="S45" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T45" s="9">
         <v>0</v>
@@ -4748,7 +4754,7 @@
         <v>46014</v>
       </c>
       <c r="S47" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T47" s="9">
         <v>0</v>
@@ -4813,7 +4819,7 @@
         <v>46055</v>
       </c>
       <c r="S48" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T48" s="6">
         <v>0</v>
@@ -4943,7 +4949,7 @@
         <v>46014</v>
       </c>
       <c r="S50" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T50" s="6">
         <v>0</v>
@@ -5008,7 +5014,7 @@
         <v>46038</v>
       </c>
       <c r="S51" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T51" s="9">
         <v>0</v>
@@ -5073,7 +5079,7 @@
         <v>46078</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="T52" s="6">
         <v>1</v>
@@ -6494,7 +6500,7 @@
         <v>46167</v>
       </c>
       <c r="S77" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T77" s="9">
         <v>0</v>
@@ -7430,7 +7436,7 @@
         <v>46140</v>
       </c>
       <c r="S93" s="12" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="T93" s="9">
         <v>1</v>
@@ -7780,7 +7786,7 @@
         <v>46071</v>
       </c>
       <c r="S99" s="12" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="T99" s="9">
         <v>0</v>
@@ -7908,7 +7914,7 @@
         <v>46122</v>
       </c>
       <c r="S101" s="12" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="T101" s="9">
         <v>0</v>
@@ -8083,7 +8089,7 @@
         <v>46142</v>
       </c>
       <c r="S104" s="12" t="s">
-        <v>122</v>
+        <v>57</v>
       </c>
       <c r="T104" s="6">
         <v>1</v>
@@ -8256,7 +8262,7 @@
         <v>46153</v>
       </c>
       <c r="S107" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T107" s="9">
         <v>0</v>
@@ -8775,7 +8781,7 @@
         <v>46161</v>
       </c>
       <c r="S116" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T116" s="6">
         <v>0</v>
@@ -8946,7 +8952,7 @@
         <v>46164</v>
       </c>
       <c r="S119" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T119" s="9">
         <v>0</v>
@@ -9111,7 +9117,7 @@
         <v>46168</v>
       </c>
       <c r="S122" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T122" s="6">
         <v>0</v>
@@ -9323,7 +9329,7 @@
         <v>46169</v>
       </c>
       <c r="S126" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T126" s="6">
         <v>0</v>
@@ -9443,7 +9449,7 @@
       </c>
       <c r="C129" s="9"/>
       <c r="D129" s="8">
-        <v>46169.16854806713</v>
+        <v>46224.793723263894</v>
       </c>
       <c r="E129" s="9" t="s">
         <v>396</v>
@@ -9494,7 +9500,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46169.16854940972</v>
+        <v>46224.79381616898</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>62</v>
@@ -9596,7 +9602,7 @@
       </c>
       <c r="C132" s="6"/>
       <c r="D132" s="5">
-        <v>46169.16855229167</v>
+        <v>46224.79388892361</v>
       </c>
       <c r="E132" s="6" t="s">
         <v>69</v>
@@ -9692,7 +9698,7 @@
         <v>46170</v>
       </c>
       <c r="S133" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T133" s="9">
         <v>0</v>
@@ -10073,7 +10079,7 @@
         <v>46175</v>
       </c>
       <c r="S140" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T140" s="6">
         <v>0</v>
@@ -10442,7 +10448,7 @@
         <v>46176</v>
       </c>
       <c r="S147" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T147" s="9">
         <v>0</v>
@@ -10858,7 +10864,7 @@
         <v>46177</v>
       </c>
       <c r="S155" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T155" s="9">
         <v>0</v>
@@ -10921,7 +10927,7 @@
         <v>46177</v>
       </c>
       <c r="S156" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T156" s="6">
         <v>0</v>
@@ -10974,7 +10980,7 @@
       <c r="Q157" s="9"/>
       <c r="R157" s="9"/>
       <c r="S157" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T157" s="9">
         <v>0</v>
@@ -11037,7 +11043,7 @@
         <v>46176</v>
       </c>
       <c r="S158" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T158" s="6">
         <v>0</v>
@@ -11100,7 +11106,7 @@
         <v>46185</v>
       </c>
       <c r="S159" s="11" t="s">
-        <v>57</v>
+        <v>127</v>
       </c>
       <c r="T159" s="9">
         <v>0</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -714,7 +714,7 @@
     <t>gonzalo.davila@zitron.com</t>
   </si>
   <si>
-    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ot 4309- ZVN 1-9-75/2,ot 4309- ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
+    <t>OT 4302 -ZVN 1-10-26/2,OT 4302 -ZVN 1-10-26/2,ot 4309- ZVN 1-9-75/2,ot 4309- ZVN 1-9-75/2,OT 4315 ZVN 1-9-63/2,OT 4315 ZVN 1-9-63/2, OT4316  ZVN 1-9-25/4, OT4316  ZVN 1-9-25/4,OT 4317 ZVN 1-16-126/4 ,OT 4313 - ZVN 1-9-45/2,OT 4313 - ZVN 1-9-45/2,OT 4332 -  ZVN 1-16-126/4 ,OT 4324- ZVN 1-7-37/2 ,OT 4324- ZVN 1-7-37/2 ,OT 4327- ZVN 2-9-103/2,OT 4327- ZVN 2-9-103/2,OT 4326- ZVN 1-12-55/4,OT 4326- ZVN 1-12-55/4,OT 4328 - ZVN 1-9-86/2,OT 4328 - ZVN 1-9-86/2,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4335 - ZVN 1-7-37/2 + TOB + REJ,OT 4340 - JZR 6-18.5/2 + 2FAR 60/100 + BASTIDOR,OT 4342 - ZVN 1-16-160/4 + TOB + REJ + 2FAR 160/200 + TIPO A,OT 4347- ZVN 1-14-75/4 + TIPOC + 2FAR140/200 + TIPOB,OT4360 -  ZVN 1-9-90/2 + TOB + REJ,OT4360 -  ZVN 1-9-90/2 + TOB + REJ, ot 4363 ZVN 1-9-86/2, ot 4363 ZVN 1-9-86/2</t>
   </si>
   <si>
     <t>1214046914974309</t>
@@ -5932,7 +5932,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46211.815882106486</v>
+        <v>46225.017977881944</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>230</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1910" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1920" uniqueCount="458">
   <si>
     <t>50001499- EQ. CHAPARRAL</t>
   </si>
@@ -8547,7 +8547,7 @@
       </c>
       <c r="C113" s="9"/>
       <c r="D113" s="8">
-        <v>46225.81275493056</v>
+        <v>46230.71153075232</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>352</v>
@@ -8556,9 +8556,11 @@
         <v>26</v>
       </c>
       <c r="G113" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H113" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H113" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I113" s="9"/>
       <c r="J113" s="9"/>
       <c r="K113" s="9" t="s">
@@ -8600,7 +8602,7 @@
         <v>46225.813130532406</v>
       </c>
       <c r="D114" s="5">
-        <v>46225.81313171296</v>
+        <v>46230.711651805555</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>236</v>
@@ -8609,9 +8611,11 @@
         <v>26</v>
       </c>
       <c r="G114" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H114" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H114" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I114" s="6"/>
       <c r="J114" s="6"/>
       <c r="K114" s="6" t="s">
@@ -8647,7 +8651,7 @@
       </c>
       <c r="C115" s="9"/>
       <c r="D115" s="8">
-        <v>46225.81234634259</v>
+        <v>46230.711765625005</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>240</v>
@@ -8656,9 +8660,11 @@
         <v>26</v>
       </c>
       <c r="G115" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H115" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H115" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I115" s="9"/>
       <c r="J115" s="9"/>
       <c r="K115" s="9" t="s">
@@ -8694,7 +8700,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46225.81274479166</v>
+        <v>46230.71188780092</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>356</v>
@@ -8703,9 +8709,11 @@
         <v>26</v>
       </c>
       <c r="G116" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H116" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H116" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I116" s="6"/>
       <c r="J116" s="6"/>
       <c r="K116" s="6" t="s">
@@ -8747,7 +8755,7 @@
         <v>46225.813224363425</v>
       </c>
       <c r="D117" s="8">
-        <v>46225.81322589121</v>
+        <v>46230.71219160879</v>
       </c>
       <c r="E117" s="9" t="s">
         <v>236</v>
@@ -8756,9 +8764,11 @@
         <v>26</v>
       </c>
       <c r="G117" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H117" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H117" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I117" s="9"/>
       <c r="J117" s="9"/>
       <c r="K117" s="9" t="s">
@@ -8794,7 +8804,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46225.81252960648</v>
+        <v>46230.712052268515</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>240</v>
@@ -8803,9 +8813,11 @@
         <v>26</v>
       </c>
       <c r="G118" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H118" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H118" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I118" s="6"/>
       <c r="J118" s="6"/>
       <c r="K118" s="6" t="s">
@@ -8841,7 +8853,7 @@
       </c>
       <c r="C119" s="9"/>
       <c r="D119" s="8">
-        <v>46225.81401447917</v>
+        <v>46230.71299550926</v>
       </c>
       <c r="E119" s="9" t="s">
         <v>360</v>
@@ -8850,9 +8862,11 @@
         <v>26</v>
       </c>
       <c r="G119" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H119" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H119" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I119" s="9"/>
       <c r="J119" s="9"/>
       <c r="K119" s="9" t="s">
@@ -8890,7 +8904,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46226.82624630787</v>
+        <v>46230.71291037037</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>236</v>
@@ -8899,9 +8913,11 @@
         <v>26</v>
       </c>
       <c r="G120" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="H120" s="6"/>
+        <v>101</v>
+      </c>
+      <c r="H120" s="6" t="s">
+        <v>102</v>
+      </c>
       <c r="I120" s="6"/>
       <c r="J120" s="6"/>
       <c r="K120" s="6" t="s">
@@ -8937,7 +8953,7 @@
       </c>
       <c r="C121" s="9"/>
       <c r="D121" s="8">
-        <v>46225.81272188657</v>
+        <v>46230.71281320602</v>
       </c>
       <c r="E121" s="9" t="s">
         <v>240</v>
@@ -8946,9 +8962,11 @@
         <v>26</v>
       </c>
       <c r="G121" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H121" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H121" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I121" s="9"/>
       <c r="J121" s="9"/>
       <c r="K121" s="9" t="s">
@@ -9149,7 +9167,7 @@
       </c>
       <c r="C125" s="9"/>
       <c r="D125" s="8">
-        <v>46225.8141224537</v>
+        <v>46230.71270855324</v>
       </c>
       <c r="E125" s="9" t="s">
         <v>370</v>
@@ -9158,9 +9176,11 @@
         <v>26</v>
       </c>
       <c r="G125" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H125" s="9"/>
+        <v>101</v>
+      </c>
+      <c r="H125" s="9" t="s">
+        <v>102</v>
+      </c>
       <c r="I125" s="9"/>
       <c r="J125" s="9"/>
       <c r="K125" s="9" t="s">

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -6435,7 +6435,7 @@
       </c>
       <c r="C77" s="9"/>
       <c r="D77" s="8">
-        <v>46198.7984696875</v>
+        <v>46234.92808222222</v>
       </c>
       <c r="E77" s="9" t="s">
         <v>255</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1921" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1883" uniqueCount="450">
   <si>
     <t>50001499- EQ. CHAPARRAL</t>
   </si>
@@ -1363,30 +1363,6 @@
   </si>
   <si>
     <t>Despacho,Analisis de costeo</t>
-  </si>
-  <si>
-    <t>1213575386156403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puesta en marcha Servicios </t>
-  </si>
-  <si>
-    <t>Instalación de componentes,Pruebas de instalación de component</t>
-  </si>
-  <si>
-    <t>1213575386156405</t>
-  </si>
-  <si>
-    <t>Instalación de componentes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pruebas de instalación de component,Puesta en marcha Servicios </t>
-  </si>
-  <si>
-    <t>1213575386156401</t>
-  </si>
-  <si>
-    <t>Pruebas de instalación de component</t>
   </si>
 </sst>
 </file>
@@ -1910,7 +1886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U163"/>
+  <dimension ref="A1:U160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10.4" customWidth="1"/>
@@ -11088,185 +11064,6 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A161" s="7" t="s">
-        <v>450</v>
-      </c>
-      <c r="B161" s="8">
-        <v>46090.70994861111</v>
-      </c>
-      <c r="C161" s="9"/>
-      <c r="D161" s="8">
-        <v>46125.907787916665</v>
-      </c>
-      <c r="E161" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="F161" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="G161" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="H161" s="9"/>
-      <c r="I161" s="9"/>
-      <c r="J161" s="9"/>
-      <c r="K161" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L161" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M161" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="N161" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="O161" s="9" t="s">
-        <v>452</v>
-      </c>
-      <c r="P161" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="Q161" s="9"/>
-      <c r="R161" s="9"/>
-      <c r="S161" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="T161" s="9">
-        <v>0</v>
-      </c>
-      <c r="U161" s="10" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="162" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A162" s="4" t="s">
-        <v>453</v>
-      </c>
-      <c r="B162" s="5">
-        <v>46090.71005349537</v>
-      </c>
-      <c r="C162" s="6"/>
-      <c r="D162" s="5">
-        <v>46185.197705416664</v>
-      </c>
-      <c r="E162" s="6" t="s">
-        <v>454</v>
-      </c>
-      <c r="F162" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="G162" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="H162" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="I162" s="5">
-        <v>46176</v>
-      </c>
-      <c r="J162" s="5">
-        <v>46184</v>
-      </c>
-      <c r="K162" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="L162" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M162" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="N162" s="6" t="s">
-        <v>451</v>
-      </c>
-      <c r="O162" s="6" t="s">
-        <v>431</v>
-      </c>
-      <c r="P162" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="Q162" s="5">
-        <v>46184</v>
-      </c>
-      <c r="R162" s="5">
-        <v>46176</v>
-      </c>
-      <c r="S162" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="T162" s="6">
-        <v>0</v>
-      </c>
-      <c r="U162" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="163" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A163" s="7" t="s">
-        <v>456</v>
-      </c>
-      <c r="B163" s="8">
-        <v>46090.70960611111</v>
-      </c>
-      <c r="C163" s="9"/>
-      <c r="D163" s="8">
-        <v>46225.8069684838</v>
-      </c>
-      <c r="E163" s="9" t="s">
-        <v>457</v>
-      </c>
-      <c r="F163" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G163" s="9" t="s">
-        <v>50</v>
-      </c>
-      <c r="H163" s="9" t="s">
-        <v>51</v>
-      </c>
-      <c r="I163" s="8">
-        <v>46185</v>
-      </c>
-      <c r="J163" s="8">
-        <v>46195</v>
-      </c>
-      <c r="K163" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="L163" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M163" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="N163" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="O163" s="9" t="s">
-        <v>454</v>
-      </c>
-      <c r="P163" s="9" t="s">
-        <v>451</v>
-      </c>
-      <c r="Q163" s="8">
-        <v>46195</v>
-      </c>
-      <c r="R163" s="8">
-        <v>46185</v>
-      </c>
-      <c r="S163" s="11" t="s">
-        <v>132</v>
-      </c>
-      <c r="T163" s="9">
-        <v>0</v>
-      </c>
-      <c r="U163" s="11" t="s">
-        <v>32</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5171,7 +5171,7 @@
         <v>46204.65960825232</v>
       </c>
       <c r="D55" s="8">
-        <v>46204.65962090278</v>
+        <v>46250.22235877315</v>
       </c>
       <c r="E55" s="9" t="s">
         <v>195</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5894,7 +5894,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46227.576429872686</v>
+        <v>46260.596741747686</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>231</v>
@@ -8527,9 +8527,11 @@
       <c r="B113" s="8">
         <v>46225.80916310185</v>
       </c>
-      <c r="C113" s="9"/>
+      <c r="C113" s="8">
+        <v>46260.603206064814</v>
+      </c>
       <c r="D113" s="8">
-        <v>46237.513921307866</v>
+        <v>46260.603218599535</v>
       </c>
       <c r="E113" s="9" t="s">
         <v>352</v>
@@ -8565,8 +8567,8 @@
       </c>
       <c r="Q113" s="9"/>
       <c r="R113" s="9"/>
-      <c r="S113" s="12" t="s">
-        <v>47</v>
+      <c r="S113" s="10" t="s">
+        <v>31</v>
       </c>
       <c r="T113" s="9">
         <v>1</v>
@@ -8631,9 +8633,11 @@
       <c r="B115" s="8">
         <v>46225.81233881944</v>
       </c>
-      <c r="C115" s="9"/>
+      <c r="C115" s="8">
+        <v>46260.603187569446</v>
+      </c>
       <c r="D115" s="8">
-        <v>46230.711765625005</v>
+        <v>46260.603189456015</v>
       </c>
       <c r="E115" s="9" t="s">
         <v>240</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5894,7 +5894,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46260.596741747686</v>
+        <v>46260.64276190972</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>231</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5894,7 +5894,7 @@
         <v>46127.69765324074</v>
       </c>
       <c r="D68" s="5">
-        <v>46260.64276190972</v>
+        <v>46260.841631828705</v>
       </c>
       <c r="E68" s="6" t="s">
         <v>231</v>

--- a/data/50001499 - EQ CHAPARRAL.xlsx
+++ b/data/50001499 - EQ CHAPARRAL.xlsx
@@ -5291,7 +5291,7 @@
         <v>46204.6595924537</v>
       </c>
       <c r="D57" s="8">
-        <v>46228.45478835648</v>
+        <v>46263.3572133912</v>
       </c>
       <c r="E57" s="9" t="s">
         <v>202</v>
@@ -5566,7 +5566,7 @@
         <v>46195.69561555555</v>
       </c>
       <c r="D62" s="5">
-        <v>46195.69561689815</v>
+        <v>46263.35723202546</v>
       </c>
       <c r="E62" s="6" t="s">
         <v>214</v>
@@ -7060,7 +7060,7 @@
         <v>46191.770449421296</v>
       </c>
       <c r="D88" s="5">
-        <v>46191.77046482639</v>
+        <v>46263.34023461805</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>286</v>
